--- a/scripts/i18n.xlsx
+++ b/scripts/i18n.xlsx
@@ -113,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="722">
   <si>
     <t xml:space="preserve">페이지는 [피그마] PFPlay GUI 설계서 합본의 페이지 이름입니다. </t>
   </si>
@@ -1504,6 +1504,51 @@
     <t>Try again</t>
   </si>
   <si>
+    <t>common.btn.chat_mute</t>
+  </si>
+  <si>
+    <t>꿀</t>
+  </si>
+  <si>
+    <t>Chat Mute</t>
+  </si>
+  <si>
+    <t>common.btn.kick</t>
+  </si>
+  <si>
+    <t>킥</t>
+  </si>
+  <si>
+    <t>Kick</t>
+  </si>
+  <si>
+    <t>common.btn.ban</t>
+  </si>
+  <si>
+    <t>밴</t>
+  </si>
+  <si>
+    <t>Ban</t>
+  </si>
+  <si>
+    <t>Paragraph</t>
+  </si>
+  <si>
+    <t>common.para.reason</t>
+  </si>
+  <si>
+    <t>사유:</t>
+  </si>
+  <si>
+    <t>Reason:</t>
+  </si>
+  <si>
+    <t>common.para.to</t>
+  </si>
+  <si>
+    <t>To.</t>
+  </si>
+  <si>
     <t>Error Case</t>
   </si>
   <si>
@@ -1555,9 +1600,6 @@
     <t>권한 (Authorization)</t>
   </si>
   <si>
-    <t>Paragraph</t>
-  </si>
-  <si>
     <t>auth.para.need_wallet</t>
   </si>
   <si>
@@ -1600,12 +1642,105 @@
     <t>auth.para.auth_changed</t>
   </si>
   <si>
+    <t>관리자에 의해 권한이 변경되었습니다!</t>
+  </si>
+  <si>
     <t>auth.para.auth_quota_exceeded</t>
   </si>
   <si>
     <t>auth.para.no_change_authority</t>
   </si>
   <si>
+    <t>chat.para.delete_confirm</t>
+  </si>
+  <si>
+    <t>해당 메시지를 정말로 삭제하시겠어요? 삭제되면 복구할 수 없어요.</t>
+  </si>
+  <si>
+    <t>Are you sure you want to delete this message?/nOnce deleted, it can't be restored.</t>
+  </si>
+  <si>
+    <t>chat.para.cannot_delete_high_rank</t>
+  </si>
+  <si>
+    <t>상위 계급 유저의 메시지는 삭제할 수 없어요</t>
+  </si>
+  <si>
+    <t>You can't delete messages from higher-ranked users.</t>
+  </si>
+  <si>
+    <t>chat.para.chat_mute</t>
+  </si>
+  <si>
+    <t>30초간 채팅을 금지합니다.</t>
+  </si>
+  <si>
+    <t>Chat will be disabled for 30 seconds.</t>
+  </si>
+  <si>
+    <t>chat.para.kick_with_rejoin</t>
+  </si>
+  <si>
+    <t>즉시 퇴출되며 재입장이 가능합니다</t>
+  </si>
+  <si>
+    <t>You will be removed immediately, but re-entry is allowed.</t>
+  </si>
+  <si>
+    <t>chat.para.kick_no_rejoin</t>
+  </si>
+  <si>
+    <t>즉시 퇴출되며 재입장이 불가능합니다</t>
+  </si>
+  <si>
+    <t>You will be removed immediately, and re-entry is not allowed.</t>
+  </si>
+  <si>
+    <t>chat.para.reason_too_short</t>
+  </si>
+  <si>
+    <t>사유는 2자 이상 입력해주세요</t>
+  </si>
+  <si>
+    <t>Please enter a reason with at least 2 characters.</t>
+  </si>
+  <si>
+    <t>chat.para.reason_shared</t>
+  </si>
+  <si>
+    <t>작성된 사유는 사용자에게 전달됩니다</t>
+  </si>
+  <si>
+    <t>The reason you provided will be shared with the user.</t>
+  </si>
+  <si>
+    <t>chat.para.muted_by_admin</t>
+  </si>
+  <si>
+    <t>관리자에 의해 30초간 채팅이 금지됩니다.</t>
+  </si>
+  <si>
+    <t>Chat has been disabled for 30 seconds by an admin.</t>
+  </si>
+  <si>
+    <t>chat.para.removed_by_admin</t>
+  </si>
+  <si>
+    <t>관리자에 의해 퇴출되셨습니다.</t>
+  </si>
+  <si>
+    <t>You have been removed by an admin.</t>
+  </si>
+  <si>
+    <t>chat.para.permanent_ban</t>
+  </si>
+  <si>
+    <t>관리자에 의해 영구 퇴출되셨으며/n재입장은 불가합니다.</t>
+  </si>
+  <si>
+    <t>You have been permanently removed by an admin and can’t rejoin.</t>
+  </si>
+  <si>
     <t>auth.btn.connect_wallet</t>
   </si>
   <si>
@@ -1849,19 +1984,16 @@
     <t>party.para.close_party</t>
   </si>
   <si>
-    <t>현재 파티룸을 정말로 폐쇄하시겠어요?\n모든 데이터는 저장되지 않습니다.</t>
-  </si>
-  <si>
-    <t>Are you sure you want to close the current party room?\nAll data will not be saved.</t>
-  </si>
-  <si>
-    <t>party.para.enter_confirm</t>
-  </si>
-  <si>
-    <t>'확인했습니다' 입력</t>
-  </si>
-  <si>
-    <t>Enter 'Confirmed'</t>
+    <t>현재 파티룸을 정말로 폐쇄하시겠어요?\n모든 데이터는 저장되지 않습니다.\n폐쇄하려면 '$1'을 입력해주세요.</t>
+  </si>
+  <si>
+    <t>Are you sure you want to close the current party room?\nAll data will not be saved.\nPlease enter '$1' for close.</t>
+  </si>
+  <si>
+    <t>party.para.match_for_close_party</t>
+  </si>
+  <si>
+    <t>Confirmed</t>
   </si>
   <si>
     <t>party.para.no_longer_see_chat</t>
@@ -1882,9 +2014,6 @@
     <t>party.para.close</t>
   </si>
   <si>
-    <t>party.para.enter_confirm_phrase</t>
-  </si>
-  <si>
     <t>party.para.share_x_partyroom</t>
   </si>
   <si>
@@ -2027,6 +2156,15 @@
   </si>
   <si>
     <t>dj.para.played_sequentially</t>
+  </si>
+  <si>
+    <t>dj.para.display_count</t>
+  </si>
+  <si>
+    <t>노래가 끝나면 디제잉하는 동안 받은 좋아요, 그랩, 싫어요를 카운팅해 보여드려요.</t>
+  </si>
+  <si>
+    <t>Once the song ends, we'll display a count of the Like, Grab, and Boo received during your DJ set.</t>
   </si>
   <si>
     <t>dj.para.empty_dj</t>
@@ -2211,6 +2349,15 @@
   </si>
   <si>
     <t>chat.para.start_chat</t>
+  </si>
+  <si>
+    <t>chat.para.remove_chat</t>
+  </si>
+  <si>
+    <t>$1'가 '$2'의 채팅을 삭제했습니다.</t>
+  </si>
+  <si>
+    <t>$2''s chat was removed by '$1'.</t>
   </si>
 </sst>
 </file>
@@ -2310,7 +2457,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2381,6 +2528,9 @@
       <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -2398,15 +2548,15 @@
     <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf quotePrefix="1" borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6604,17 +6754,15 @@
       <c r="M35" s="18"/>
     </row>
     <row r="36">
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="17"/>
+      <c r="C36" s="20" t="s">
         <v>437</v>
       </c>
-      <c r="C36" s="22" t="s">
+      <c r="D36" s="8" t="s">
         <v>438</v>
       </c>
-      <c r="D36" s="8" t="s">
-        <v>36</v>
-      </c>
       <c r="E36" s="8" t="s">
-        <v>37</v>
+        <v>439</v>
       </c>
       <c r="F36" s="18"/>
       <c r="G36" s="19"/>
@@ -6626,14 +6774,15 @@
       <c r="M36" s="18"/>
     </row>
     <row r="37">
-      <c r="C37" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>42</v>
+      <c r="B37" s="17"/>
+      <c r="C37" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>442</v>
       </c>
       <c r="F37" s="18"/>
       <c r="G37" s="19"/>
@@ -6645,14 +6794,15 @@
       <c r="M37" s="18"/>
     </row>
     <row r="38">
-      <c r="C38" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>441</v>
+      <c r="B38" s="17"/>
+      <c r="C38" s="20" t="s">
+        <v>443</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="F38" s="18"/>
       <c r="G38" s="19"/>
@@ -6664,14 +6814,17 @@
       <c r="M38" s="18"/>
     </row>
     <row r="39">
-      <c r="C39" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>277</v>
+      <c r="B39" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>447</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>448</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="F39" s="18"/>
       <c r="G39" s="19"/>
@@ -6683,16 +6836,17 @@
       <c r="M39" s="18"/>
     </row>
     <row r="40">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="7" t="s">
-        <v>444</v>
+      <c r="B40" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>450</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="F40" s="18"/>
       <c r="G40" s="19"/>
@@ -6704,16 +6858,17 @@
       <c r="M40" s="18"/>
     </row>
     <row r="41">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="7" t="s">
-        <v>447</v>
+      <c r="B41" s="17" t="s">
+        <v>452</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>453</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>448</v>
+        <v>36</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>449</v>
+        <v>37</v>
       </c>
       <c r="F41" s="18"/>
       <c r="G41" s="19"/>
@@ -6725,16 +6880,14 @@
       <c r="M41" s="18"/>
     </row>
     <row r="42">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
       <c r="C42" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>452</v>
+        <v>454</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="F42" s="18"/>
       <c r="G42" s="19"/>
@@ -6746,19 +6899,13 @@
       <c r="M42" s="18"/>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="s">
-        <v>453</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>454</v>
-      </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="D43" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="E43" s="8" t="s">
+      <c r="D43" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>456</v>
       </c>
       <c r="F43" s="18"/>
@@ -6771,14 +6918,14 @@
       <c r="M43" s="18"/>
     </row>
     <row r="44">
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="D44" s="8" t="s">
-        <v>129</v>
+      <c r="D44" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>130</v>
+        <v>458</v>
       </c>
       <c r="F44" s="18"/>
       <c r="G44" s="19"/>
@@ -6790,14 +6937,16 @@
       <c r="M44" s="18"/>
     </row>
     <row r="45">
-      <c r="C45" s="17" t="s">
-        <v>458</v>
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="7" t="s">
+        <v>459</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>119</v>
+        <v>460</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>120</v>
+        <v>461</v>
       </c>
       <c r="F45" s="18"/>
       <c r="G45" s="19"/>
@@ -6809,14 +6958,16 @@
       <c r="M45" s="18"/>
     </row>
     <row r="46">
-      <c r="C46" s="20" t="s">
-        <v>459</v>
+      <c r="A46" s="17"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="7" t="s">
+        <v>462</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>125</v>
+        <v>463</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>126</v>
+        <v>464</v>
       </c>
       <c r="F46" s="18"/>
       <c r="G46" s="19"/>
@@ -6828,14 +6979,16 @@
       <c r="M46" s="18"/>
     </row>
     <row r="47">
-      <c r="C47" s="20" t="s">
-        <v>460</v>
+      <c r="A47" s="17"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="7" t="s">
+        <v>465</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>182</v>
+        <v>467</v>
       </c>
       <c r="F47" s="18"/>
       <c r="G47" s="19"/>
@@ -6847,14 +7000,20 @@
       <c r="M47" s="18"/>
     </row>
     <row r="48">
-      <c r="C48" s="20" t="s">
-        <v>462</v>
+      <c r="A48" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>469</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>463</v>
+        <v>128</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="F48" s="18"/>
       <c r="G48" s="19"/>
@@ -6866,14 +7025,14 @@
       <c r="M48" s="18"/>
     </row>
     <row r="49">
-      <c r="C49" s="20" t="s">
-        <v>465</v>
+      <c r="C49" s="17" t="s">
+        <v>471</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>466</v>
+        <v>129</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>467</v>
+        <v>130</v>
       </c>
       <c r="F49" s="18"/>
       <c r="G49" s="19"/>
@@ -6885,14 +7044,14 @@
       <c r="M49" s="18"/>
     </row>
     <row r="50">
-      <c r="C50" s="20" t="s">
-        <v>468</v>
+      <c r="C50" s="17" t="s">
+        <v>472</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>305</v>
+        <v>119</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>120</v>
       </c>
       <c r="F50" s="18"/>
       <c r="G50" s="19"/>
@@ -6905,13 +7064,13 @@
     </row>
     <row r="51">
       <c r="C51" s="20" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>307</v>
+        <v>125</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>308</v>
+        <v>126</v>
       </c>
       <c r="F51" s="18"/>
       <c r="G51" s="19"/>
@@ -6924,13 +7083,13 @@
     </row>
     <row r="52">
       <c r="C52" s="20" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>310</v>
+        <v>475</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>311</v>
+        <v>182</v>
       </c>
       <c r="F52" s="18"/>
       <c r="G52" s="19"/>
@@ -6942,17 +7101,14 @@
       <c r="M52" s="18"/>
     </row>
     <row r="53">
-      <c r="B53" s="20" t="s">
-        <v>396</v>
-      </c>
       <c r="C53" s="20" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>231</v>
+        <v>477</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>56</v>
+        <v>478</v>
       </c>
       <c r="F53" s="18"/>
       <c r="G53" s="19"/>
@@ -6965,13 +7121,13 @@
     </row>
     <row r="54">
       <c r="C54" s="20" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>27</v>
+        <v>480</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>28</v>
+        <v>481</v>
       </c>
       <c r="F54" s="18"/>
       <c r="G54" s="19"/>
@@ -6983,17 +7139,14 @@
       <c r="M54" s="18"/>
     </row>
     <row r="55">
-      <c r="B55" s="20" t="s">
-        <v>473</v>
-      </c>
       <c r="C55" s="20" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>475</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>476</v>
+        <v>483</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>305</v>
       </c>
       <c r="F55" s="18"/>
       <c r="G55" s="19"/>
@@ -7006,13 +7159,13 @@
     </row>
     <row r="56">
       <c r="C56" s="20" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="F56" s="18"/>
       <c r="G56" s="19"/>
@@ -7025,13 +7178,13 @@
     </row>
     <row r="57">
       <c r="C57" s="20" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="F57" s="18"/>
       <c r="G57" s="19"/>
@@ -7043,14 +7196,15 @@
       <c r="M57" s="18"/>
     </row>
     <row r="58">
-      <c r="C58" s="20" t="s">
-        <v>479</v>
+      <c r="B58" s="20"/>
+      <c r="C58" s="8" t="s">
+        <v>486</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>300</v>
+        <v>487</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>300</v>
+        <v>488</v>
       </c>
       <c r="F58" s="18"/>
       <c r="G58" s="19"/>
@@ -7062,14 +7216,15 @@
       <c r="M58" s="18"/>
     </row>
     <row r="59">
-      <c r="C59" s="20" t="s">
-        <v>480</v>
+      <c r="B59" s="20"/>
+      <c r="C59" s="8" t="s">
+        <v>489</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>301</v>
+        <v>490</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>301</v>
+        <v>491</v>
       </c>
       <c r="F59" s="18"/>
       <c r="G59" s="19"/>
@@ -7081,14 +7236,15 @@
       <c r="M59" s="18"/>
     </row>
     <row r="60">
-      <c r="C60" s="20" t="s">
-        <v>481</v>
+      <c r="B60" s="20"/>
+      <c r="C60" s="8" t="s">
+        <v>492</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>302</v>
+        <v>493</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>302</v>
+        <v>494</v>
       </c>
       <c r="F60" s="18"/>
       <c r="G60" s="19"/>
@@ -7100,14 +7256,15 @@
       <c r="M60" s="18"/>
     </row>
     <row r="61">
-      <c r="C61" s="20" t="s">
-        <v>482</v>
+      <c r="B61" s="20"/>
+      <c r="C61" s="8" t="s">
+        <v>495</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>178</v>
+        <v>496</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>179</v>
+        <v>497</v>
       </c>
       <c r="F61" s="18"/>
       <c r="G61" s="19"/>
@@ -7119,20 +7276,15 @@
       <c r="M61" s="18"/>
     </row>
     <row r="62">
-      <c r="A62" s="20" t="s">
-        <v>483</v>
-      </c>
-      <c r="B62" s="20" t="s">
-        <v>396</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>11</v>
+      <c r="B62" s="20"/>
+      <c r="C62" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>500</v>
       </c>
       <c r="F62" s="18"/>
       <c r="G62" s="19"/>
@@ -7144,14 +7296,15 @@
       <c r="M62" s="18"/>
     </row>
     <row r="63">
-      <c r="C63" s="20" t="s">
-        <v>485</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>14</v>
+      <c r="B63" s="20"/>
+      <c r="C63" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>503</v>
       </c>
       <c r="F63" s="18"/>
       <c r="G63" s="19"/>
@@ -7163,14 +7316,15 @@
       <c r="M63" s="18"/>
     </row>
     <row r="64">
-      <c r="C64" s="20" t="s">
-        <v>486</v>
+      <c r="B64" s="20"/>
+      <c r="C64" s="8" t="s">
+        <v>504</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>15</v>
+        <v>505</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>16</v>
+        <v>506</v>
       </c>
       <c r="F64" s="18"/>
       <c r="G64" s="19"/>
@@ -7182,14 +7336,15 @@
       <c r="M64" s="18"/>
     </row>
     <row r="65">
-      <c r="C65" s="20" t="s">
-        <v>487</v>
+      <c r="B65" s="20"/>
+      <c r="C65" s="8" t="s">
+        <v>507</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>18</v>
+        <v>508</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>19</v>
+        <v>509</v>
       </c>
       <c r="F65" s="18"/>
       <c r="G65" s="19"/>
@@ -7201,14 +7356,15 @@
       <c r="M65" s="18"/>
     </row>
     <row r="66">
-      <c r="C66" s="20" t="s">
-        <v>488</v>
+      <c r="B66" s="20"/>
+      <c r="C66" s="8" t="s">
+        <v>510</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>30</v>
+        <v>511</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>4</v>
+        <v>512</v>
       </c>
       <c r="F66" s="18"/>
       <c r="G66" s="19"/>
@@ -7220,14 +7376,15 @@
       <c r="M66" s="18"/>
     </row>
     <row r="67">
-      <c r="C67" s="20" t="s">
-        <v>489</v>
+      <c r="B67" s="20"/>
+      <c r="C67" s="8" t="s">
+        <v>513</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>490</v>
+        <v>514</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>26</v>
+        <v>515</v>
       </c>
       <c r="F67" s="18"/>
       <c r="G67" s="19"/>
@@ -7240,16 +7397,16 @@
     </row>
     <row r="68">
       <c r="B68" s="20" t="s">
-        <v>473</v>
+        <v>396</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>491</v>
+        <v>516</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>21</v>
+        <v>231</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F68" s="18"/>
       <c r="G68" s="19"/>
@@ -7261,17 +7418,14 @@
       <c r="M68" s="18"/>
     </row>
     <row r="69">
-      <c r="B69" s="20" t="s">
-        <v>454</v>
-      </c>
       <c r="C69" s="20" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>493</v>
+        <v>27</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>494</v>
+        <v>28</v>
       </c>
       <c r="F69" s="18"/>
       <c r="G69" s="19"/>
@@ -7283,20 +7437,17 @@
       <c r="M69" s="18"/>
     </row>
     <row r="70">
-      <c r="A70" s="20" t="s">
-        <v>495</v>
-      </c>
       <c r="B70" s="20" t="s">
-        <v>473</v>
+        <v>518</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>496</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>33</v>
+        <v>519</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>521</v>
       </c>
       <c r="F70" s="18"/>
       <c r="G70" s="19"/>
@@ -7309,13 +7460,13 @@
     </row>
     <row r="71">
       <c r="C71" s="20" t="s">
-        <v>497</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>35</v>
+        <v>522</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>298</v>
       </c>
       <c r="F71" s="18"/>
       <c r="G71" s="19"/>
@@ -7328,13 +7479,13 @@
     </row>
     <row r="72">
       <c r="C72" s="20" t="s">
-        <v>498</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>39</v>
+        <v>523</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>299</v>
       </c>
       <c r="F72" s="18"/>
       <c r="G72" s="19"/>
@@ -7347,13 +7498,13 @@
     </row>
     <row r="73">
       <c r="C73" s="20" t="s">
-        <v>499</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>47</v>
+        <v>524</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>300</v>
       </c>
       <c r="F73" s="18"/>
       <c r="G73" s="19"/>
@@ -7366,13 +7517,13 @@
     </row>
     <row r="74">
       <c r="C74" s="20" t="s">
-        <v>500</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>50</v>
+        <v>525</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>301</v>
       </c>
       <c r="F74" s="18"/>
       <c r="G74" s="19"/>
@@ -7385,13 +7536,13 @@
     </row>
     <row r="75">
       <c r="C75" s="20" t="s">
-        <v>501</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>51</v>
+        <v>526</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>302</v>
       </c>
       <c r="F75" s="18"/>
       <c r="G75" s="19"/>
@@ -7404,13 +7555,13 @@
     </row>
     <row r="76">
       <c r="C76" s="20" t="s">
-        <v>502</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>54</v>
+        <v>527</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>179</v>
       </c>
       <c r="F76" s="18"/>
       <c r="G76" s="19"/>
@@ -7422,17 +7573,20 @@
       <c r="M76" s="18"/>
     </row>
     <row r="77">
+      <c r="A77" s="20" t="s">
+        <v>528</v>
+      </c>
       <c r="B77" s="20" t="s">
-        <v>437</v>
+        <v>396</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>58</v>
+        <v>529</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F77" s="18"/>
       <c r="G77" s="19"/>
@@ -7444,17 +7598,14 @@
       <c r="M77" s="18"/>
     </row>
     <row r="78">
-      <c r="B78" s="20" t="s">
-        <v>396</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>61</v>
+      <c r="C78" s="20" t="s">
+        <v>530</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="F78" s="18"/>
       <c r="G78" s="19"/>
@@ -7466,17 +7617,14 @@
       <c r="M78" s="18"/>
     </row>
     <row r="79">
-      <c r="B79" s="20" t="s">
-        <v>454</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>505</v>
+      <c r="C79" s="20" t="s">
+        <v>531</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>506</v>
+        <v>16</v>
       </c>
       <c r="F79" s="18"/>
       <c r="G79" s="19"/>
@@ -7488,39 +7636,33 @@
       <c r="M79" s="18"/>
     </row>
     <row r="80">
-      <c r="C80" s="3" t="s">
-        <v>507</v>
+      <c r="C80" s="20" t="s">
+        <v>532</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="F80" s="23"/>
-      <c r="G80" s="23"/>
-      <c r="H80" s="23"/>
-      <c r="I80" s="23"/>
-      <c r="J80" s="23"/>
-      <c r="K80" s="23"/>
-      <c r="L80" s="23"/>
-      <c r="M80" s="23"/>
+        <v>19</v>
+      </c>
+      <c r="F80" s="18"/>
+      <c r="G80" s="19"/>
+      <c r="H80" s="18"/>
+      <c r="I80" s="18"/>
+      <c r="J80" s="18"/>
+      <c r="K80" s="18"/>
+      <c r="L80" s="18"/>
+      <c r="M80" s="18"/>
     </row>
     <row r="81">
-      <c r="A81" s="20" t="s">
-        <v>508</v>
-      </c>
-      <c r="B81" s="24" t="s">
-        <v>473</v>
-      </c>
       <c r="C81" s="20" t="s">
-        <v>509</v>
+        <v>533</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="F81" s="18"/>
       <c r="G81" s="19"/>
@@ -7533,13 +7675,13 @@
     </row>
     <row r="82">
       <c r="C82" s="20" t="s">
-        <v>510</v>
+        <v>534</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>94</v>
+        <v>535</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="F82" s="18"/>
       <c r="G82" s="19"/>
@@ -7551,14 +7693,17 @@
       <c r="M82" s="18"/>
     </row>
     <row r="83">
+      <c r="B83" s="20" t="s">
+        <v>518</v>
+      </c>
       <c r="C83" s="20" t="s">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="F83" s="18"/>
       <c r="G83" s="19"/>
@@ -7570,14 +7715,17 @@
       <c r="M83" s="18"/>
     </row>
     <row r="84">
+      <c r="B84" s="20" t="s">
+        <v>446</v>
+      </c>
       <c r="C84" s="20" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>98</v>
+        <v>538</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>100</v>
+        <v>539</v>
       </c>
       <c r="F84" s="18"/>
       <c r="G84" s="19"/>
@@ -7589,17 +7737,20 @@
       <c r="M84" s="18"/>
     </row>
     <row r="85">
+      <c r="A85" s="20" t="s">
+        <v>540</v>
+      </c>
       <c r="B85" s="20" t="s">
-        <v>454</v>
+        <v>518</v>
       </c>
       <c r="C85" s="20" t="s">
-        <v>513</v>
-      </c>
-      <c r="D85" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>76</v>
+        <v>541</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="F85" s="18"/>
       <c r="G85" s="19"/>
@@ -7611,20 +7762,14 @@
       <c r="M85" s="18"/>
     </row>
     <row r="86">
-      <c r="A86" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B86" s="20" t="s">
-        <v>454</v>
-      </c>
       <c r="C86" s="20" t="s">
-        <v>514</v>
-      </c>
-      <c r="D86" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="E86" s="8" t="s">
-        <v>382</v>
+        <v>542</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="F86" s="18"/>
       <c r="G86" s="19"/>
@@ -7636,20 +7781,14 @@
       <c r="M86" s="18"/>
     </row>
     <row r="87">
-      <c r="A87" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B87" s="20" t="s">
-        <v>454</v>
-      </c>
       <c r="C87" s="20" t="s">
-        <v>515</v>
-      </c>
-      <c r="D87" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="E87" s="8" t="s">
-        <v>384</v>
+        <v>543</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="F87" s="18"/>
       <c r="G87" s="19"/>
@@ -7661,1965 +7800,2293 @@
       <c r="M87" s="18"/>
     </row>
     <row r="88">
-      <c r="A88" s="20" t="s">
-        <v>516</v>
-      </c>
-      <c r="B88" s="20" t="s">
-        <v>454</v>
-      </c>
       <c r="C88" s="20" t="s">
-        <v>517</v>
+        <v>544</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>519</v>
-      </c>
-      <c r="F88" s="23"/>
-      <c r="G88" s="23"/>
-      <c r="H88" s="23"/>
-      <c r="I88" s="23"/>
-      <c r="J88" s="23"/>
-      <c r="K88" s="23"/>
-      <c r="L88" s="23"/>
-      <c r="M88" s="23"/>
+        <v>46</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F88" s="18"/>
+      <c r="G88" s="19"/>
+      <c r="H88" s="18"/>
+      <c r="I88" s="18"/>
+      <c r="J88" s="18"/>
+      <c r="K88" s="18"/>
+      <c r="L88" s="18"/>
+      <c r="M88" s="18"/>
     </row>
     <row r="89">
-      <c r="A89" s="20" t="s">
-        <v>516</v>
-      </c>
-      <c r="B89" s="20" t="s">
-        <v>454</v>
-      </c>
       <c r="C89" s="20" t="s">
-        <v>520</v>
+        <v>545</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>521</v>
+        <v>49</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="F89" s="23"/>
-      <c r="G89" s="23"/>
-      <c r="H89" s="23"/>
-      <c r="I89" s="23"/>
-      <c r="J89" s="23"/>
-      <c r="K89" s="23"/>
-      <c r="L89" s="23"/>
-      <c r="M89" s="23"/>
+        <v>50</v>
+      </c>
+      <c r="F89" s="18"/>
+      <c r="G89" s="19"/>
+      <c r="H89" s="18"/>
+      <c r="I89" s="18"/>
+      <c r="J89" s="18"/>
+      <c r="K89" s="18"/>
+      <c r="L89" s="18"/>
+      <c r="M89" s="18"/>
     </row>
     <row r="90">
-      <c r="A90" s="20" t="s">
-        <v>516</v>
-      </c>
-      <c r="B90" s="20" t="s">
-        <v>454</v>
-      </c>
       <c r="C90" s="20" t="s">
-        <v>522</v>
+        <v>546</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="E90" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="F90" s="23"/>
-      <c r="G90" s="23"/>
-      <c r="H90" s="23"/>
-      <c r="I90" s="23"/>
-      <c r="J90" s="23"/>
-      <c r="K90" s="23"/>
-      <c r="L90" s="23"/>
-      <c r="M90" s="23"/>
+        <v>51</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F90" s="18"/>
+      <c r="G90" s="19"/>
+      <c r="H90" s="18"/>
+      <c r="I90" s="18"/>
+      <c r="J90" s="18"/>
+      <c r="K90" s="18"/>
+      <c r="L90" s="18"/>
+      <c r="M90" s="18"/>
     </row>
     <row r="91">
-      <c r="A91" s="20" t="s">
-        <v>516</v>
-      </c>
-      <c r="B91" s="20" t="s">
-        <v>454</v>
-      </c>
       <c r="C91" s="20" t="s">
-        <v>523</v>
-      </c>
-      <c r="D91" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="F91" s="23"/>
-      <c r="G91" s="23"/>
-      <c r="H91" s="23"/>
-      <c r="I91" s="23"/>
-      <c r="J91" s="23"/>
-      <c r="K91" s="23"/>
-      <c r="L91" s="23"/>
-      <c r="M91" s="23"/>
+        <v>547</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F91" s="18"/>
+      <c r="G91" s="19"/>
+      <c r="H91" s="18"/>
+      <c r="I91" s="18"/>
+      <c r="J91" s="18"/>
+      <c r="K91" s="18"/>
+      <c r="L91" s="18"/>
+      <c r="M91" s="18"/>
     </row>
     <row r="92">
-      <c r="A92" s="20" t="s">
-        <v>516</v>
-      </c>
       <c r="B92" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F92" s="18"/>
+      <c r="G92" s="19"/>
+      <c r="H92" s="18"/>
+      <c r="I92" s="18"/>
+      <c r="J92" s="18"/>
+      <c r="K92" s="18"/>
+      <c r="L92" s="18"/>
+      <c r="M92" s="18"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="20" t="s">
         <v>396</v>
       </c>
-      <c r="C92" s="20" t="s">
-        <v>524</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="F92" s="23"/>
-      <c r="G92" s="23"/>
-      <c r="H92" s="23"/>
-      <c r="I92" s="23"/>
-      <c r="J92" s="23"/>
-      <c r="K92" s="23"/>
-      <c r="L92" s="23"/>
-      <c r="M92" s="23"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="20" t="s">
-        <v>516</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="C93" s="20" t="s">
-        <v>525</v>
+      <c r="C93" s="3" t="s">
+        <v>549</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>385</v>
+        <v>60</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="F93" s="23"/>
-      <c r="G93" s="23"/>
-      <c r="H93" s="23"/>
-      <c r="I93" s="23"/>
-      <c r="J93" s="23"/>
-      <c r="K93" s="23"/>
-      <c r="L93" s="23"/>
-      <c r="M93" s="23"/>
+        <v>61</v>
+      </c>
+      <c r="F93" s="18"/>
+      <c r="G93" s="19"/>
+      <c r="H93" s="18"/>
+      <c r="I93" s="18"/>
+      <c r="J93" s="18"/>
+      <c r="K93" s="18"/>
+      <c r="L93" s="18"/>
+      <c r="M93" s="18"/>
     </row>
     <row r="94">
-      <c r="A94" s="20" t="s">
-        <v>516</v>
-      </c>
       <c r="B94" s="20" t="s">
-        <v>454</v>
-      </c>
-      <c r="C94" s="20" t="s">
-        <v>526</v>
+        <v>446</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>527</v>
+        <v>45</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>528</v>
-      </c>
-      <c r="F94" s="23"/>
-      <c r="G94" s="23"/>
-      <c r="H94" s="23"/>
-      <c r="I94" s="23"/>
-      <c r="J94" s="23"/>
-      <c r="K94" s="23"/>
-      <c r="L94" s="23"/>
-      <c r="M94" s="23"/>
+        <v>551</v>
+      </c>
+      <c r="F94" s="18"/>
+      <c r="G94" s="19"/>
+      <c r="H94" s="18"/>
+      <c r="I94" s="18"/>
+      <c r="J94" s="18"/>
+      <c r="K94" s="18"/>
+      <c r="L94" s="18"/>
+      <c r="M94" s="18"/>
     </row>
     <row r="95">
-      <c r="A95" s="20" t="s">
-        <v>516</v>
-      </c>
-      <c r="B95" s="20" t="s">
-        <v>454</v>
-      </c>
-      <c r="C95" s="20" t="s">
-        <v>529</v>
+      <c r="C95" s="3" t="s">
+        <v>552</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>388</v>
+        <v>62</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="F95" s="23"/>
-      <c r="G95" s="23"/>
-      <c r="H95" s="23"/>
-      <c r="I95" s="23"/>
-      <c r="J95" s="23"/>
-      <c r="K95" s="23"/>
-      <c r="L95" s="23"/>
-      <c r="M95" s="23"/>
+        <v>63</v>
+      </c>
+      <c r="F95" s="24"/>
+      <c r="G95" s="24"/>
+      <c r="H95" s="24"/>
+      <c r="I95" s="24"/>
+      <c r="J95" s="24"/>
+      <c r="K95" s="24"/>
+      <c r="L95" s="24"/>
+      <c r="M95" s="24"/>
     </row>
     <row r="96">
       <c r="A96" s="20" t="s">
-        <v>516</v>
-      </c>
-      <c r="B96" s="20" t="s">
-        <v>454</v>
+        <v>553</v>
+      </c>
+      <c r="B96" s="25" t="s">
+        <v>518</v>
       </c>
       <c r="C96" s="20" t="s">
-        <v>530</v>
+        <v>554</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>390</v>
+        <v>74</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="F96" s="23"/>
-      <c r="G96" s="23"/>
-      <c r="H96" s="23"/>
-      <c r="I96" s="23"/>
-      <c r="J96" s="23"/>
-      <c r="K96" s="23"/>
-      <c r="L96" s="23"/>
-      <c r="M96" s="23"/>
+        <v>74</v>
+      </c>
+      <c r="F96" s="18"/>
+      <c r="G96" s="19"/>
+      <c r="H96" s="18"/>
+      <c r="I96" s="18"/>
+      <c r="J96" s="18"/>
+      <c r="K96" s="18"/>
+      <c r="L96" s="18"/>
+      <c r="M96" s="18"/>
     </row>
     <row r="97">
-      <c r="A97" s="20" t="s">
-        <v>531</v>
-      </c>
-      <c r="B97" s="20" t="s">
-        <v>473</v>
-      </c>
       <c r="C97" s="20" t="s">
-        <v>532</v>
+        <v>555</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="F97" s="23"/>
-      <c r="G97" s="23"/>
-      <c r="H97" s="23"/>
-      <c r="I97" s="23"/>
-      <c r="J97" s="23"/>
-      <c r="K97" s="23"/>
-      <c r="L97" s="23"/>
-      <c r="M97" s="23"/>
+        <v>95</v>
+      </c>
+      <c r="F97" s="18"/>
+      <c r="G97" s="19"/>
+      <c r="H97" s="18"/>
+      <c r="I97" s="18"/>
+      <c r="J97" s="18"/>
+      <c r="K97" s="18"/>
+      <c r="L97" s="18"/>
+      <c r="M97" s="18"/>
     </row>
     <row r="98">
       <c r="C98" s="20" t="s">
-        <v>533</v>
+        <v>556</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>534</v>
-      </c>
-      <c r="F98" s="23"/>
-      <c r="G98" s="23"/>
-      <c r="H98" s="23"/>
-      <c r="I98" s="23"/>
-      <c r="J98" s="23"/>
-      <c r="K98" s="23"/>
-      <c r="L98" s="23"/>
-      <c r="M98" s="23"/>
+        <v>97</v>
+      </c>
+      <c r="F98" s="18"/>
+      <c r="G98" s="19"/>
+      <c r="H98" s="18"/>
+      <c r="I98" s="18"/>
+      <c r="J98" s="18"/>
+      <c r="K98" s="18"/>
+      <c r="L98" s="18"/>
+      <c r="M98" s="18"/>
     </row>
     <row r="99">
-      <c r="B99" s="7" t="s">
-        <v>473</v>
-      </c>
       <c r="C99" s="20" t="s">
-        <v>535</v>
+        <v>557</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>536</v>
-      </c>
-      <c r="F99" s="23"/>
-      <c r="G99" s="23"/>
-      <c r="H99" s="23"/>
-      <c r="I99" s="23"/>
-      <c r="J99" s="23"/>
-      <c r="K99" s="23"/>
-      <c r="L99" s="23"/>
-      <c r="M99" s="23"/>
+        <v>100</v>
+      </c>
+      <c r="F99" s="18"/>
+      <c r="G99" s="19"/>
+      <c r="H99" s="18"/>
+      <c r="I99" s="18"/>
+      <c r="J99" s="18"/>
+      <c r="K99" s="18"/>
+      <c r="L99" s="18"/>
+      <c r="M99" s="18"/>
     </row>
     <row r="100">
-      <c r="B100" s="7" t="s">
-        <v>473</v>
+      <c r="B100" s="20" t="s">
+        <v>446</v>
       </c>
       <c r="C100" s="20" t="s">
-        <v>537</v>
+        <v>558</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="F100" s="23"/>
-      <c r="G100" s="23"/>
-      <c r="H100" s="23"/>
-      <c r="I100" s="23"/>
-      <c r="J100" s="23"/>
-      <c r="K100" s="23"/>
-      <c r="L100" s="23"/>
-      <c r="M100" s="23"/>
+        <v>76</v>
+      </c>
+      <c r="F100" s="18"/>
+      <c r="G100" s="19"/>
+      <c r="H100" s="18"/>
+      <c r="I100" s="18"/>
+      <c r="J100" s="18"/>
+      <c r="K100" s="18"/>
+      <c r="L100" s="18"/>
+      <c r="M100" s="18"/>
     </row>
     <row r="101">
+      <c r="A101" s="7" t="s">
+        <v>553</v>
+      </c>
       <c r="B101" s="20" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C101" s="20" t="s">
-        <v>539</v>
+        <v>559</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>103</v>
+        <v>382</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="F101" s="23"/>
-      <c r="G101" s="23"/>
-      <c r="H101" s="23"/>
-      <c r="I101" s="23"/>
-      <c r="J101" s="23"/>
-      <c r="K101" s="23"/>
-      <c r="L101" s="23"/>
-      <c r="M101" s="23"/>
+        <v>382</v>
+      </c>
+      <c r="F101" s="18"/>
+      <c r="G101" s="19"/>
+      <c r="H101" s="18"/>
+      <c r="I101" s="18"/>
+      <c r="J101" s="18"/>
+      <c r="K101" s="18"/>
+      <c r="L101" s="18"/>
+      <c r="M101" s="18"/>
     </row>
     <row r="102">
+      <c r="A102" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="B102" s="20" t="s">
+        <v>446</v>
+      </c>
       <c r="C102" s="20" t="s">
-        <v>540</v>
-      </c>
-      <c r="D102" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="E102" s="25" t="s">
-        <v>541</v>
-      </c>
-      <c r="F102" s="23"/>
-      <c r="G102" s="23"/>
-      <c r="H102" s="23"/>
-      <c r="I102" s="23"/>
-      <c r="J102" s="23"/>
-      <c r="K102" s="23"/>
-      <c r="L102" s="23"/>
-      <c r="M102" s="23"/>
+        <v>560</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="F102" s="18"/>
+      <c r="G102" s="19"/>
+      <c r="H102" s="18"/>
+      <c r="I102" s="18"/>
+      <c r="J102" s="18"/>
+      <c r="K102" s="18"/>
+      <c r="L102" s="18"/>
+      <c r="M102" s="18"/>
     </row>
     <row r="103">
+      <c r="A103" s="20" t="s">
+        <v>561</v>
+      </c>
+      <c r="B103" s="20" t="s">
+        <v>446</v>
+      </c>
       <c r="C103" s="20" t="s">
-        <v>542</v>
-      </c>
-      <c r="D103" s="25" t="s">
-        <v>521</v>
-      </c>
-      <c r="E103" s="25" t="s">
-        <v>543</v>
-      </c>
-      <c r="F103" s="23"/>
-      <c r="G103" s="23"/>
-      <c r="H103" s="23"/>
-      <c r="I103" s="23"/>
-      <c r="J103" s="23"/>
-      <c r="K103" s="23"/>
-      <c r="L103" s="23"/>
-      <c r="M103" s="23"/>
+        <v>562</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="F103" s="24"/>
+      <c r="G103" s="24"/>
+      <c r="H103" s="24"/>
+      <c r="I103" s="24"/>
+      <c r="J103" s="24"/>
+      <c r="K103" s="24"/>
+      <c r="L103" s="24"/>
+      <c r="M103" s="24"/>
     </row>
     <row r="104">
+      <c r="A104" s="20" t="s">
+        <v>561</v>
+      </c>
+      <c r="B104" s="20" t="s">
+        <v>446</v>
+      </c>
       <c r="C104" s="20" t="s">
-        <v>544</v>
-      </c>
-      <c r="D104" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="E104" s="25" t="s">
-        <v>545</v>
-      </c>
-      <c r="F104" s="23"/>
-      <c r="G104" s="23"/>
-      <c r="H104" s="23"/>
-      <c r="I104" s="23"/>
-      <c r="J104" s="23"/>
-      <c r="K104" s="23"/>
-      <c r="L104" s="23"/>
-      <c r="M104" s="23"/>
+        <v>565</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F104" s="24"/>
+      <c r="G104" s="24"/>
+      <c r="H104" s="24"/>
+      <c r="I104" s="24"/>
+      <c r="J104" s="24"/>
+      <c r="K104" s="24"/>
+      <c r="L104" s="24"/>
+      <c r="M104" s="24"/>
     </row>
     <row r="105">
+      <c r="A105" s="20" t="s">
+        <v>561</v>
+      </c>
+      <c r="B105" s="20" t="s">
+        <v>446</v>
+      </c>
       <c r="C105" s="20" t="s">
-        <v>546</v>
-      </c>
-      <c r="D105" s="5" t="s">
-        <v>547</v>
-      </c>
-      <c r="E105" s="5" t="s">
-        <v>548</v>
-      </c>
-      <c r="F105" s="23"/>
-      <c r="G105" s="26"/>
-      <c r="H105" s="25"/>
-      <c r="I105" s="25"/>
-      <c r="J105" s="27"/>
-      <c r="K105" s="27"/>
-      <c r="L105" s="27"/>
-      <c r="M105" s="23"/>
+        <v>567</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="F105" s="24"/>
+      <c r="G105" s="24"/>
+      <c r="H105" s="24"/>
+      <c r="I105" s="24"/>
+      <c r="J105" s="24"/>
+      <c r="K105" s="24"/>
+      <c r="L105" s="24"/>
+      <c r="M105" s="24"/>
     </row>
     <row r="106">
+      <c r="A106" s="20" t="s">
+        <v>561</v>
+      </c>
+      <c r="B106" s="20" t="s">
+        <v>446</v>
+      </c>
       <c r="C106" s="20" t="s">
-        <v>549</v>
-      </c>
-      <c r="D106" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="F106" s="23"/>
-      <c r="G106" s="28"/>
-      <c r="H106" s="26"/>
-      <c r="I106" s="25"/>
-      <c r="J106" s="25"/>
-      <c r="K106" s="27"/>
-      <c r="L106" s="27"/>
-      <c r="M106" s="27"/>
+        <v>568</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="F106" s="24"/>
+      <c r="G106" s="24"/>
+      <c r="H106" s="24"/>
+      <c r="I106" s="24"/>
+      <c r="J106" s="24"/>
+      <c r="K106" s="24"/>
+      <c r="L106" s="24"/>
+      <c r="M106" s="24"/>
     </row>
     <row r="107">
+      <c r="A107" s="20" t="s">
+        <v>561</v>
+      </c>
+      <c r="B107" s="20" t="s">
+        <v>396</v>
+      </c>
       <c r="C107" s="20" t="s">
-        <v>551</v>
-      </c>
-      <c r="D107" s="5" t="s">
-        <v>552</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="F107" s="23"/>
-      <c r="G107" s="28"/>
-      <c r="H107" s="26"/>
-      <c r="I107" s="25"/>
-      <c r="J107" s="25"/>
-      <c r="K107" s="27"/>
-      <c r="L107" s="27"/>
-      <c r="M107" s="27"/>
+        <v>569</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="F107" s="24"/>
+      <c r="G107" s="24"/>
+      <c r="H107" s="24"/>
+      <c r="I107" s="24"/>
+      <c r="J107" s="24"/>
+      <c r="K107" s="24"/>
+      <c r="L107" s="24"/>
+      <c r="M107" s="24"/>
     </row>
     <row r="108">
+      <c r="A108" s="20" t="s">
+        <v>561</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>518</v>
+      </c>
       <c r="C108" s="20" t="s">
-        <v>554</v>
-      </c>
-      <c r="D108" s="29" t="s">
-        <v>555</v>
-      </c>
-      <c r="E108" s="5" t="s">
-        <v>556</v>
-      </c>
-      <c r="F108" s="23"/>
-      <c r="G108" s="28"/>
-      <c r="H108" s="26"/>
-      <c r="I108" s="25"/>
-      <c r="J108" s="25"/>
-      <c r="K108" s="27"/>
-      <c r="L108" s="27"/>
-      <c r="M108" s="27"/>
+        <v>570</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="E108" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="F108" s="24"/>
+      <c r="G108" s="24"/>
+      <c r="H108" s="24"/>
+      <c r="I108" s="24"/>
+      <c r="J108" s="24"/>
+      <c r="K108" s="24"/>
+      <c r="L108" s="24"/>
+      <c r="M108" s="24"/>
     </row>
     <row r="109">
+      <c r="A109" s="20" t="s">
+        <v>561</v>
+      </c>
+      <c r="B109" s="20" t="s">
+        <v>446</v>
+      </c>
       <c r="C109" s="20" t="s">
-        <v>557</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="F109" s="23"/>
-      <c r="G109" s="28"/>
-      <c r="H109" s="26"/>
-      <c r="I109" s="25"/>
-      <c r="J109" s="25"/>
-      <c r="K109" s="27"/>
-      <c r="L109" s="27"/>
-      <c r="M109" s="27"/>
+        <v>571</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="E109" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="F109" s="24"/>
+      <c r="G109" s="24"/>
+      <c r="H109" s="24"/>
+      <c r="I109" s="24"/>
+      <c r="J109" s="24"/>
+      <c r="K109" s="24"/>
+      <c r="L109" s="24"/>
+      <c r="M109" s="24"/>
     </row>
     <row r="110">
+      <c r="A110" s="20" t="s">
+        <v>561</v>
+      </c>
+      <c r="B110" s="20" t="s">
+        <v>446</v>
+      </c>
       <c r="C110" s="20" t="s">
-        <v>558</v>
-      </c>
-      <c r="D110" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="E110" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="F110" s="23"/>
-      <c r="G110" s="28"/>
-      <c r="H110" s="26"/>
-      <c r="I110" s="25"/>
-      <c r="J110" s="25"/>
-      <c r="K110" s="27"/>
-      <c r="L110" s="27"/>
-      <c r="M110" s="27"/>
+        <v>574</v>
+      </c>
+      <c r="D110" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="F110" s="24"/>
+      <c r="G110" s="24"/>
+      <c r="H110" s="24"/>
+      <c r="I110" s="24"/>
+      <c r="J110" s="24"/>
+      <c r="K110" s="24"/>
+      <c r="L110" s="24"/>
+      <c r="M110" s="24"/>
     </row>
     <row r="111">
+      <c r="A111" s="20" t="s">
+        <v>561</v>
+      </c>
+      <c r="B111" s="20" t="s">
+        <v>446</v>
+      </c>
       <c r="C111" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="D111" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="E111" s="20" t="s">
-        <v>561</v>
-      </c>
-      <c r="F111" s="23"/>
-      <c r="G111" s="28"/>
-      <c r="H111" s="26"/>
-      <c r="I111" s="25"/>
-      <c r="J111" s="25"/>
-      <c r="K111" s="27"/>
-      <c r="L111" s="27"/>
-      <c r="M111" s="27"/>
+        <v>575</v>
+      </c>
+      <c r="D111" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="F111" s="24"/>
+      <c r="G111" s="24"/>
+      <c r="H111" s="24"/>
+      <c r="I111" s="24"/>
+      <c r="J111" s="24"/>
+      <c r="K111" s="24"/>
+      <c r="L111" s="24"/>
+      <c r="M111" s="24"/>
     </row>
     <row r="112">
+      <c r="A112" s="20" t="s">
+        <v>576</v>
+      </c>
+      <c r="B112" s="20" t="s">
+        <v>518</v>
+      </c>
       <c r="C112" s="20" t="s">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>197</v>
+        <v>112</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="F112" s="23"/>
-      <c r="G112" s="28"/>
-      <c r="H112" s="26"/>
-      <c r="I112" s="25"/>
-      <c r="J112" s="25"/>
-      <c r="K112" s="27"/>
-      <c r="L112" s="27"/>
-      <c r="M112" s="27"/>
+        <v>143</v>
+      </c>
+      <c r="F112" s="24"/>
+      <c r="G112" s="24"/>
+      <c r="H112" s="24"/>
+      <c r="I112" s="24"/>
+      <c r="J112" s="24"/>
+      <c r="K112" s="24"/>
+      <c r="L112" s="24"/>
+      <c r="M112" s="24"/>
     </row>
     <row r="113">
       <c r="C113" s="20" t="s">
-        <v>563</v>
+        <v>578</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>199</v>
+        <v>115</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="F113" s="23"/>
-      <c r="G113" s="28"/>
-      <c r="H113" s="26"/>
-      <c r="I113" s="25"/>
-      <c r="J113" s="25"/>
-      <c r="K113" s="27"/>
-      <c r="L113" s="27"/>
-      <c r="M113" s="27"/>
+        <v>579</v>
+      </c>
+      <c r="F113" s="24"/>
+      <c r="G113" s="24"/>
+      <c r="H113" s="24"/>
+      <c r="I113" s="24"/>
+      <c r="J113" s="24"/>
+      <c r="K113" s="24"/>
+      <c r="L113" s="24"/>
+      <c r="M113" s="24"/>
     </row>
     <row r="114">
-      <c r="B114" s="20"/>
+      <c r="B114" s="7" t="s">
+        <v>518</v>
+      </c>
       <c r="C114" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="D114" s="30" t="s">
-        <v>565</v>
-      </c>
-      <c r="E114" s="30" t="s">
-        <v>565</v>
-      </c>
-      <c r="F114" s="23"/>
-      <c r="G114" s="28"/>
-      <c r="H114" s="26"/>
-      <c r="I114" s="25"/>
-      <c r="J114" s="25"/>
-      <c r="K114" s="27"/>
-      <c r="L114" s="27"/>
-      <c r="M114" s="27"/>
+        <v>580</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="F114" s="24"/>
+      <c r="G114" s="24"/>
+      <c r="H114" s="24"/>
+      <c r="I114" s="24"/>
+      <c r="J114" s="24"/>
+      <c r="K114" s="24"/>
+      <c r="L114" s="24"/>
+      <c r="M114" s="24"/>
     </row>
     <row r="115">
-      <c r="B115" s="20" t="s">
-        <v>396</v>
+      <c r="B115" s="7" t="s">
+        <v>518</v>
       </c>
       <c r="C115" s="20" t="s">
+        <v>582</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="F115" s="24"/>
+      <c r="G115" s="24"/>
+      <c r="H115" s="24"/>
+      <c r="I115" s="24"/>
+      <c r="J115" s="24"/>
+      <c r="K115" s="24"/>
+      <c r="L115" s="24"/>
+      <c r="M115" s="24"/>
+    </row>
+    <row r="116">
+      <c r="B116" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="C116" s="20" t="s">
+        <v>584</v>
+      </c>
+      <c r="D116" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E116" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F116" s="24"/>
+      <c r="G116" s="24"/>
+      <c r="H116" s="24"/>
+      <c r="I116" s="24"/>
+      <c r="J116" s="24"/>
+      <c r="K116" s="24"/>
+      <c r="L116" s="24"/>
+      <c r="M116" s="24"/>
+    </row>
+    <row r="117">
+      <c r="C117" s="20" t="s">
+        <v>585</v>
+      </c>
+      <c r="D117" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E117" s="26" t="s">
+        <v>586</v>
+      </c>
+      <c r="F117" s="24"/>
+      <c r="G117" s="24"/>
+      <c r="H117" s="24"/>
+      <c r="I117" s="24"/>
+      <c r="J117" s="24"/>
+      <c r="K117" s="24"/>
+      <c r="L117" s="24"/>
+      <c r="M117" s="24"/>
+    </row>
+    <row r="118">
+      <c r="C118" s="20" t="s">
+        <v>587</v>
+      </c>
+      <c r="D118" s="26" t="s">
         <v>566</v>
       </c>
-      <c r="D115" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F115" s="23"/>
-      <c r="G115" s="28"/>
-      <c r="H115" s="26"/>
-      <c r="I115" s="25"/>
-      <c r="J115" s="25"/>
-      <c r="K115" s="27"/>
-      <c r="L115" s="27"/>
-      <c r="M115" s="27"/>
-    </row>
-    <row r="116">
-      <c r="C116" s="20" t="s">
-        <v>567</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="F116" s="23"/>
-      <c r="G116" s="28"/>
-      <c r="H116" s="26"/>
-      <c r="I116" s="25"/>
-      <c r="J116" s="25"/>
-      <c r="K116" s="27"/>
-      <c r="L116" s="27"/>
-      <c r="M116" s="27"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="17" t="s">
-        <v>569</v>
-      </c>
-      <c r="B117" s="17" t="s">
-        <v>473</v>
-      </c>
-      <c r="C117" s="17" t="s">
-        <v>570</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="F117" s="23"/>
-      <c r="G117" s="28"/>
-      <c r="H117" s="26"/>
-      <c r="I117" s="25"/>
-      <c r="J117" s="25"/>
-      <c r="K117" s="27"/>
-      <c r="L117" s="27"/>
-      <c r="M117" s="27"/>
-    </row>
-    <row r="118">
-      <c r="C118" s="17" t="s">
-        <v>571</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F118" s="23"/>
-      <c r="G118" s="28"/>
-      <c r="H118" s="26"/>
-      <c r="I118" s="25"/>
-      <c r="J118" s="25"/>
-      <c r="K118" s="23"/>
-      <c r="L118" s="23"/>
-      <c r="M118" s="23"/>
+      <c r="E118" s="26" t="s">
+        <v>588</v>
+      </c>
+      <c r="F118" s="24"/>
+      <c r="G118" s="24"/>
+      <c r="H118" s="24"/>
+      <c r="I118" s="24"/>
+      <c r="J118" s="24"/>
+      <c r="K118" s="24"/>
+      <c r="L118" s="24"/>
+      <c r="M118" s="24"/>
     </row>
     <row r="119">
-      <c r="C119" s="17" t="s">
-        <v>572</v>
-      </c>
-      <c r="D119" s="8" t="s">
-        <v>573</v>
-      </c>
-      <c r="E119" s="8" t="s">
-        <v>574</v>
-      </c>
-      <c r="F119" s="23"/>
-      <c r="G119" s="31"/>
-      <c r="H119" s="23"/>
-      <c r="I119" s="23"/>
-      <c r="J119" s="23"/>
-      <c r="K119" s="23"/>
-      <c r="L119" s="23"/>
-      <c r="M119" s="23"/>
+      <c r="C119" s="20" t="s">
+        <v>589</v>
+      </c>
+      <c r="D119" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="E119" s="26" t="s">
+        <v>590</v>
+      </c>
+      <c r="F119" s="24"/>
+      <c r="G119" s="24"/>
+      <c r="H119" s="24"/>
+      <c r="I119" s="24"/>
+      <c r="J119" s="24"/>
+      <c r="K119" s="24"/>
+      <c r="L119" s="24"/>
+      <c r="M119" s="24"/>
     </row>
     <row r="120">
       <c r="C120" s="20" t="s">
-        <v>575</v>
-      </c>
-      <c r="D120" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="E120" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="F120" s="23"/>
-      <c r="G120" s="23"/>
-      <c r="H120" s="23"/>
-      <c r="I120" s="23"/>
-      <c r="J120" s="23"/>
-      <c r="K120" s="23"/>
-      <c r="L120" s="23"/>
-      <c r="M120" s="23"/>
+        <v>591</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="F120" s="24"/>
+      <c r="G120" s="27"/>
+      <c r="H120" s="26"/>
+      <c r="I120" s="26"/>
+      <c r="J120" s="28"/>
+      <c r="K120" s="28"/>
+      <c r="L120" s="28"/>
+      <c r="M120" s="24"/>
     </row>
     <row r="121">
-      <c r="C121" s="17" t="s">
-        <v>576</v>
-      </c>
-      <c r="D121" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="F121" s="23"/>
-      <c r="G121" s="23"/>
-      <c r="H121" s="23"/>
-      <c r="I121" s="23"/>
-      <c r="J121" s="23"/>
-      <c r="K121" s="23"/>
-      <c r="L121" s="23"/>
-      <c r="M121" s="23"/>
+      <c r="C121" s="20" t="s">
+        <v>594</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="F121" s="24"/>
+      <c r="G121" s="29"/>
+      <c r="H121" s="27"/>
+      <c r="I121" s="26"/>
+      <c r="J121" s="26"/>
+      <c r="K121" s="28"/>
+      <c r="L121" s="28"/>
+      <c r="M121" s="28"/>
     </row>
     <row r="122">
-      <c r="C122" s="17" t="s">
-        <v>577</v>
-      </c>
-      <c r="D122" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="E122" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F122" s="23"/>
-      <c r="G122" s="23"/>
-      <c r="H122" s="23"/>
-      <c r="I122" s="23"/>
-      <c r="J122" s="23"/>
-      <c r="K122" s="23"/>
-      <c r="L122" s="23"/>
-      <c r="M122" s="23"/>
+      <c r="C122" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="F122" s="24"/>
+      <c r="G122" s="29"/>
+      <c r="H122" s="27"/>
+      <c r="I122" s="26"/>
+      <c r="J122" s="26"/>
+      <c r="K122" s="28"/>
+      <c r="L122" s="28"/>
+      <c r="M122" s="28"/>
     </row>
     <row r="123">
-      <c r="C123" s="17" t="s">
-        <v>578</v>
-      </c>
-      <c r="D123" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="E123" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F123" s="23"/>
-      <c r="G123" s="23"/>
-      <c r="H123" s="23"/>
-      <c r="I123" s="23"/>
-      <c r="J123" s="23"/>
-      <c r="K123" s="23"/>
-      <c r="L123" s="23"/>
-      <c r="M123" s="23"/>
+      <c r="C123" s="20" t="s">
+        <v>599</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="F123" s="24"/>
+      <c r="G123" s="29"/>
+      <c r="H123" s="27"/>
+      <c r="I123" s="26"/>
+      <c r="J123" s="26"/>
+      <c r="K123" s="28"/>
+      <c r="L123" s="28"/>
+      <c r="M123" s="28"/>
     </row>
     <row r="124">
-      <c r="C124" s="17" t="s">
-        <v>579</v>
-      </c>
-      <c r="D124" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="E124" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="F124" s="23"/>
-      <c r="G124" s="23"/>
-      <c r="H124" s="23"/>
-      <c r="I124" s="23"/>
-      <c r="J124" s="23"/>
-      <c r="K124" s="23"/>
-      <c r="L124" s="23"/>
-      <c r="M124" s="23"/>
+      <c r="C124" s="20" t="s">
+        <v>601</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F124" s="24"/>
+      <c r="G124" s="29"/>
+      <c r="H124" s="27"/>
+      <c r="I124" s="26"/>
+      <c r="J124" s="26"/>
+      <c r="K124" s="28"/>
+      <c r="L124" s="28"/>
+      <c r="M124" s="28"/>
     </row>
     <row r="125">
-      <c r="C125" s="17" t="s">
-        <v>580</v>
-      </c>
-      <c r="D125" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="E125" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F125" s="23"/>
-      <c r="G125" s="23"/>
-      <c r="H125" s="23"/>
-      <c r="I125" s="23"/>
-      <c r="J125" s="23"/>
-      <c r="K125" s="23"/>
-      <c r="L125" s="23"/>
-      <c r="M125" s="23"/>
+      <c r="C125" s="20" t="s">
+        <v>602</v>
+      </c>
+      <c r="D125" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="E125" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="F125" s="24"/>
+      <c r="G125" s="29"/>
+      <c r="H125" s="27"/>
+      <c r="I125" s="26"/>
+      <c r="J125" s="26"/>
+      <c r="K125" s="28"/>
+      <c r="L125" s="28"/>
+      <c r="M125" s="28"/>
     </row>
     <row r="126">
-      <c r="B126" s="17" t="s">
+      <c r="C126" s="20" t="s">
+        <v>603</v>
+      </c>
+      <c r="D126" s="20" t="s">
+        <v>604</v>
+      </c>
+      <c r="E126" s="20" t="s">
+        <v>605</v>
+      </c>
+      <c r="F126" s="24"/>
+      <c r="G126" s="29"/>
+      <c r="H126" s="27"/>
+      <c r="I126" s="26"/>
+      <c r="J126" s="26"/>
+      <c r="K126" s="28"/>
+      <c r="L126" s="28"/>
+      <c r="M126" s="28"/>
+    </row>
+    <row r="127">
+      <c r="C127" s="20" t="s">
+        <v>606</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F127" s="24"/>
+      <c r="G127" s="29"/>
+      <c r="H127" s="27"/>
+      <c r="I127" s="26"/>
+      <c r="J127" s="26"/>
+      <c r="K127" s="28"/>
+      <c r="L127" s="28"/>
+      <c r="M127" s="28"/>
+    </row>
+    <row r="128">
+      <c r="B128" s="20"/>
+      <c r="C128" s="20" t="s">
+        <v>607</v>
+      </c>
+      <c r="D128" s="30" t="s">
+        <v>608</v>
+      </c>
+      <c r="E128" s="30" t="s">
+        <v>608</v>
+      </c>
+      <c r="F128" s="24"/>
+      <c r="G128" s="29"/>
+      <c r="H128" s="27"/>
+      <c r="I128" s="26"/>
+      <c r="J128" s="26"/>
+      <c r="K128" s="28"/>
+      <c r="L128" s="28"/>
+      <c r="M128" s="28"/>
+    </row>
+    <row r="129">
+      <c r="B129" s="20" t="s">
         <v>396</v>
       </c>
-      <c r="C126" s="17" t="s">
-        <v>581</v>
-      </c>
-      <c r="D126" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="E126" s="8" t="s">
-        <v>582</v>
-      </c>
-      <c r="F126" s="23"/>
-      <c r="G126" s="23"/>
-      <c r="H126" s="23"/>
-      <c r="I126" s="23"/>
-      <c r="J126" s="23"/>
-      <c r="K126" s="23"/>
-      <c r="L126" s="23"/>
-      <c r="M126" s="23"/>
-    </row>
-    <row r="127">
-      <c r="C127" s="17" t="s">
-        <v>583</v>
-      </c>
-      <c r="D127" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="E127" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="F127" s="23"/>
-      <c r="G127" s="23"/>
-      <c r="H127" s="23"/>
-      <c r="I127" s="23"/>
-      <c r="J127" s="23"/>
-      <c r="K127" s="23"/>
-      <c r="L127" s="23"/>
-      <c r="M127" s="23"/>
-    </row>
-    <row r="128">
-      <c r="C128" s="32" t="s">
-        <v>584</v>
-      </c>
-      <c r="D128" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="E128" s="8" t="s">
-        <v>585</v>
-      </c>
-      <c r="F128" s="23"/>
-      <c r="G128" s="23"/>
-      <c r="H128" s="23"/>
-      <c r="I128" s="23"/>
-      <c r="J128" s="23"/>
-      <c r="K128" s="23"/>
-      <c r="L128" s="23"/>
-      <c r="M128" s="23"/>
-    </row>
-    <row r="129">
-      <c r="C129" s="17" t="s">
-        <v>586</v>
-      </c>
-      <c r="D129" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="E129" s="8" t="s">
-        <v>587</v>
-      </c>
-      <c r="F129" s="23"/>
-      <c r="G129" s="23"/>
-      <c r="H129" s="23"/>
-      <c r="I129" s="23"/>
-      <c r="J129" s="23"/>
-      <c r="K129" s="23"/>
-      <c r="L129" s="23"/>
-      <c r="M129" s="23"/>
+      <c r="C129" s="20" t="s">
+        <v>609</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F129" s="24"/>
+      <c r="G129" s="29"/>
+      <c r="H129" s="27"/>
+      <c r="I129" s="26"/>
+      <c r="J129" s="26"/>
+      <c r="K129" s="28"/>
+      <c r="L129" s="28"/>
+      <c r="M129" s="28"/>
     </row>
     <row r="130">
-      <c r="B130" s="17" t="s">
-        <v>454</v>
-      </c>
-      <c r="C130" s="17" t="s">
-        <v>588</v>
-      </c>
-      <c r="D130" s="8" t="s">
-        <v>589</v>
-      </c>
-      <c r="E130" s="8" t="s">
-        <v>590</v>
-      </c>
-      <c r="F130" s="23"/>
-      <c r="G130" s="23"/>
-      <c r="H130" s="23"/>
-      <c r="I130" s="23"/>
-      <c r="J130" s="23"/>
-      <c r="K130" s="23"/>
-      <c r="L130" s="23"/>
-      <c r="M130" s="23"/>
+      <c r="C130" s="20" t="s">
+        <v>610</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="F130" s="24"/>
+      <c r="G130" s="29"/>
+      <c r="H130" s="27"/>
+      <c r="I130" s="26"/>
+      <c r="J130" s="26"/>
+      <c r="K130" s="28"/>
+      <c r="L130" s="28"/>
+      <c r="M130" s="28"/>
     </row>
     <row r="131">
+      <c r="A131" s="17" t="s">
+        <v>612</v>
+      </c>
+      <c r="B131" s="17" t="s">
+        <v>518</v>
+      </c>
       <c r="C131" s="17" t="s">
-        <v>591</v>
-      </c>
-      <c r="D131" s="8" t="s">
-        <v>592</v>
+        <v>613</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>135</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="F131" s="23"/>
-      <c r="G131" s="23"/>
-      <c r="H131" s="23"/>
-      <c r="I131" s="23"/>
-      <c r="J131" s="23"/>
-      <c r="K131" s="23"/>
-      <c r="L131" s="23"/>
-      <c r="M131" s="23"/>
+        <v>314</v>
+      </c>
+      <c r="F131" s="24"/>
+      <c r="G131" s="29"/>
+      <c r="H131" s="27"/>
+      <c r="I131" s="26"/>
+      <c r="J131" s="26"/>
+      <c r="K131" s="28"/>
+      <c r="L131" s="28"/>
+      <c r="M131" s="28"/>
     </row>
     <row r="132">
       <c r="C132" s="17" t="s">
-        <v>594</v>
-      </c>
-      <c r="D132" s="7" t="s">
-        <v>367</v>
+        <v>614</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="F132" s="23"/>
-      <c r="G132" s="23"/>
-      <c r="H132" s="23"/>
-      <c r="I132" s="23"/>
-      <c r="J132" s="23"/>
-      <c r="K132" s="23"/>
-      <c r="L132" s="23"/>
-      <c r="M132" s="23"/>
+        <v>111</v>
+      </c>
+      <c r="F132" s="24"/>
+      <c r="G132" s="29"/>
+      <c r="H132" s="27"/>
+      <c r="I132" s="26"/>
+      <c r="J132" s="26"/>
+      <c r="K132" s="24"/>
+      <c r="L132" s="24"/>
+      <c r="M132" s="24"/>
     </row>
     <row r="133">
       <c r="C133" s="17" t="s">
-        <v>595</v>
+        <v>615</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="E133" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F133" s="23"/>
-      <c r="G133" s="23"/>
-      <c r="H133" s="23"/>
-      <c r="I133" s="23"/>
-      <c r="J133" s="23"/>
-      <c r="K133" s="23"/>
-      <c r="L133" s="23"/>
-      <c r="M133" s="23"/>
+        <v>616</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="F133" s="24"/>
+      <c r="G133" s="31"/>
+      <c r="H133" s="24"/>
+      <c r="I133" s="24"/>
+      <c r="J133" s="24"/>
+      <c r="K133" s="24"/>
+      <c r="L133" s="24"/>
+      <c r="M133" s="24"/>
     </row>
     <row r="134">
-      <c r="C134" s="17" t="s">
-        <v>596</v>
+      <c r="C134" s="20" t="s">
+        <v>618</v>
       </c>
       <c r="D134" s="8" t="s">
-        <v>597</v>
+        <v>354</v>
       </c>
       <c r="E134" s="8" t="s">
-        <v>598</v>
-      </c>
-      <c r="F134" s="23"/>
-      <c r="G134" s="23"/>
-      <c r="H134" s="23"/>
-      <c r="I134" s="23"/>
-      <c r="J134" s="23"/>
-      <c r="K134" s="23"/>
-      <c r="L134" s="23"/>
-      <c r="M134" s="23"/>
+        <v>355</v>
+      </c>
+      <c r="F134" s="24"/>
+      <c r="G134" s="24"/>
+      <c r="H134" s="24"/>
+      <c r="I134" s="24"/>
+      <c r="J134" s="24"/>
+      <c r="K134" s="24"/>
+      <c r="L134" s="24"/>
+      <c r="M134" s="24"/>
     </row>
     <row r="135">
       <c r="C135" s="17" t="s">
-        <v>599</v>
+        <v>619</v>
       </c>
       <c r="D135" s="8" t="s">
-        <v>333</v>
+        <v>137</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>600</v>
-      </c>
-      <c r="F135" s="23"/>
-      <c r="G135" s="23"/>
-      <c r="H135" s="23"/>
-      <c r="I135" s="23"/>
-      <c r="J135" s="23"/>
-      <c r="K135" s="23"/>
-      <c r="L135" s="23"/>
-      <c r="M135" s="23"/>
+        <v>138</v>
+      </c>
+      <c r="F135" s="24"/>
+      <c r="G135" s="24"/>
+      <c r="H135" s="24"/>
+      <c r="I135" s="24"/>
+      <c r="J135" s="24"/>
+      <c r="K135" s="24"/>
+      <c r="L135" s="24"/>
+      <c r="M135" s="24"/>
     </row>
     <row r="136">
       <c r="C136" s="17" t="s">
-        <v>601</v>
+        <v>620</v>
       </c>
       <c r="D136" s="8" t="s">
-        <v>336</v>
+        <v>150</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>602</v>
-      </c>
-      <c r="F136" s="23"/>
-      <c r="G136" s="23"/>
-      <c r="H136" s="23"/>
-      <c r="I136" s="23"/>
-      <c r="J136" s="23"/>
-      <c r="K136" s="23"/>
-      <c r="L136" s="23"/>
-      <c r="M136" s="23"/>
+        <v>151</v>
+      </c>
+      <c r="F136" s="24"/>
+      <c r="G136" s="24"/>
+      <c r="H136" s="24"/>
+      <c r="I136" s="24"/>
+      <c r="J136" s="24"/>
+      <c r="K136" s="24"/>
+      <c r="L136" s="24"/>
+      <c r="M136" s="24"/>
     </row>
     <row r="137">
       <c r="C137" s="17" t="s">
-        <v>603</v>
+        <v>621</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>338</v>
+        <v>152</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>604</v>
-      </c>
-      <c r="F137" s="23"/>
-      <c r="G137" s="23"/>
-      <c r="H137" s="23"/>
-      <c r="I137" s="23"/>
-      <c r="J137" s="23"/>
-      <c r="K137" s="23"/>
-      <c r="L137" s="23"/>
-      <c r="M137" s="23"/>
+        <v>153</v>
+      </c>
+      <c r="F137" s="24"/>
+      <c r="G137" s="24"/>
+      <c r="H137" s="24"/>
+      <c r="I137" s="24"/>
+      <c r="J137" s="24"/>
+      <c r="K137" s="24"/>
+      <c r="L137" s="24"/>
+      <c r="M137" s="24"/>
     </row>
     <row r="138">
       <c r="C138" s="17" t="s">
-        <v>605</v>
+        <v>622</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="E138" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="F138" s="23"/>
-      <c r="G138" s="23"/>
-      <c r="H138" s="23"/>
-      <c r="I138" s="23"/>
-      <c r="J138" s="23"/>
-      <c r="K138" s="23"/>
-      <c r="L138" s="23"/>
-      <c r="M138" s="23"/>
+        <v>154</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F138" s="24"/>
+      <c r="G138" s="24"/>
+      <c r="H138" s="24"/>
+      <c r="I138" s="24"/>
+      <c r="J138" s="24"/>
+      <c r="K138" s="24"/>
+      <c r="L138" s="24"/>
+      <c r="M138" s="24"/>
     </row>
     <row r="139">
       <c r="C139" s="17" t="s">
-        <v>606</v>
+        <v>623</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>344</v>
+        <v>117</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>607</v>
-      </c>
-      <c r="F139" s="23"/>
-      <c r="G139" s="23"/>
-      <c r="H139" s="23"/>
-      <c r="I139" s="23"/>
-      <c r="J139" s="23"/>
-      <c r="K139" s="23"/>
-      <c r="L139" s="23"/>
-      <c r="M139" s="23"/>
+        <v>118</v>
+      </c>
+      <c r="F139" s="24"/>
+      <c r="G139" s="24"/>
+      <c r="H139" s="24"/>
+      <c r="I139" s="24"/>
+      <c r="J139" s="24"/>
+      <c r="K139" s="24"/>
+      <c r="L139" s="24"/>
+      <c r="M139" s="24"/>
     </row>
     <row r="140">
+      <c r="B140" s="17" t="s">
+        <v>396</v>
+      </c>
       <c r="C140" s="17" t="s">
-        <v>608</v>
+        <v>624</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="E140" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="F140" s="23"/>
-      <c r="G140" s="23"/>
-      <c r="H140" s="23"/>
-      <c r="I140" s="23"/>
-      <c r="J140" s="23"/>
-      <c r="K140" s="23"/>
-      <c r="L140" s="23"/>
-      <c r="M140" s="23"/>
+        <v>317</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="F140" s="24"/>
+      <c r="G140" s="24"/>
+      <c r="H140" s="24"/>
+      <c r="I140" s="24"/>
+      <c r="J140" s="24"/>
+      <c r="K140" s="24"/>
+      <c r="L140" s="24"/>
+      <c r="M140" s="24"/>
     </row>
     <row r="141">
       <c r="C141" s="17" t="s">
-        <v>610</v>
+        <v>626</v>
       </c>
       <c r="D141" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="F141" s="24"/>
+      <c r="G141" s="24"/>
+      <c r="H141" s="24"/>
+      <c r="I141" s="24"/>
+      <c r="J141" s="24"/>
+      <c r="K141" s="24"/>
+      <c r="L141" s="24"/>
+      <c r="M141" s="24"/>
+    </row>
+    <row r="142">
+      <c r="C142" s="32" t="s">
+        <v>627</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="F142" s="24"/>
+      <c r="G142" s="24"/>
+      <c r="H142" s="24"/>
+      <c r="I142" s="24"/>
+      <c r="J142" s="24"/>
+      <c r="K142" s="24"/>
+      <c r="L142" s="24"/>
+      <c r="M142" s="24"/>
+    </row>
+    <row r="143">
+      <c r="C143" s="17" t="s">
+        <v>629</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="F143" s="24"/>
+      <c r="G143" s="24"/>
+      <c r="H143" s="24"/>
+      <c r="I143" s="24"/>
+      <c r="J143" s="24"/>
+      <c r="K143" s="24"/>
+      <c r="L143" s="24"/>
+      <c r="M143" s="24"/>
+    </row>
+    <row r="144">
+      <c r="B144" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="C144" s="17" t="s">
+        <v>631</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="E144" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="F144" s="24"/>
+      <c r="G144" s="24"/>
+      <c r="H144" s="24"/>
+      <c r="I144" s="24"/>
+      <c r="J144" s="24"/>
+      <c r="K144" s="24"/>
+      <c r="L144" s="24"/>
+      <c r="M144" s="24"/>
+    </row>
+    <row r="145">
+      <c r="C145" s="17" t="s">
+        <v>634</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="F145" s="24"/>
+      <c r="G145" s="24"/>
+      <c r="H145" s="24"/>
+      <c r="I145" s="24"/>
+      <c r="J145" s="24"/>
+      <c r="K145" s="24"/>
+      <c r="L145" s="24"/>
+      <c r="M145" s="24"/>
+    </row>
+    <row r="146">
+      <c r="C146" s="17" t="s">
+        <v>637</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="F146" s="24"/>
+      <c r="G146" s="24"/>
+      <c r="H146" s="24"/>
+      <c r="I146" s="24"/>
+      <c r="J146" s="24"/>
+      <c r="K146" s="24"/>
+      <c r="L146" s="24"/>
+      <c r="M146" s="24"/>
+    </row>
+    <row r="147">
+      <c r="C147" s="17" t="s">
+        <v>638</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="F147" s="24"/>
+      <c r="G147" s="24"/>
+      <c r="H147" s="24"/>
+      <c r="I147" s="24"/>
+      <c r="J147" s="24"/>
+      <c r="K147" s="24"/>
+      <c r="L147" s="24"/>
+      <c r="M147" s="24"/>
+    </row>
+    <row r="148">
+      <c r="C148" s="17" t="s">
+        <v>639</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="E148" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="F148" s="24"/>
+      <c r="G148" s="24"/>
+      <c r="H148" s="24"/>
+      <c r="I148" s="24"/>
+      <c r="J148" s="24"/>
+      <c r="K148" s="24"/>
+      <c r="L148" s="24"/>
+      <c r="M148" s="24"/>
+    </row>
+    <row r="149">
+      <c r="C149" s="17" t="s">
+        <v>642</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="F149" s="24"/>
+      <c r="G149" s="24"/>
+      <c r="H149" s="24"/>
+      <c r="I149" s="24"/>
+      <c r="J149" s="24"/>
+      <c r="K149" s="24"/>
+      <c r="L149" s="24"/>
+      <c r="M149" s="24"/>
+    </row>
+    <row r="150">
+      <c r="C150" s="17" t="s">
+        <v>644</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="F150" s="24"/>
+      <c r="G150" s="24"/>
+      <c r="H150" s="24"/>
+      <c r="I150" s="24"/>
+      <c r="J150" s="24"/>
+      <c r="K150" s="24"/>
+      <c r="L150" s="24"/>
+      <c r="M150" s="24"/>
+    </row>
+    <row r="151">
+      <c r="C151" s="17" t="s">
+        <v>646</v>
+      </c>
+      <c r="D151" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E151" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="F151" s="24"/>
+      <c r="G151" s="24"/>
+      <c r="H151" s="24"/>
+      <c r="I151" s="24"/>
+      <c r="J151" s="24"/>
+      <c r="K151" s="24"/>
+      <c r="L151" s="24"/>
+      <c r="M151" s="24"/>
+    </row>
+    <row r="152">
+      <c r="C152" s="17" t="s">
+        <v>648</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F152" s="24"/>
+      <c r="G152" s="24"/>
+      <c r="H152" s="24"/>
+      <c r="I152" s="24"/>
+      <c r="J152" s="24"/>
+      <c r="K152" s="24"/>
+      <c r="L152" s="24"/>
+      <c r="M152" s="24"/>
+    </row>
+    <row r="153">
+      <c r="C153" s="17" t="s">
+        <v>649</v>
+      </c>
+      <c r="D153" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="E153" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="F153" s="24"/>
+      <c r="G153" s="24"/>
+      <c r="H153" s="24"/>
+      <c r="I153" s="24"/>
+      <c r="J153" s="24"/>
+      <c r="K153" s="24"/>
+      <c r="L153" s="24"/>
+      <c r="M153" s="24"/>
+    </row>
+    <row r="154">
+      <c r="C154" s="17" t="s">
+        <v>651</v>
+      </c>
+      <c r="D154" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="F154" s="24"/>
+      <c r="G154" s="24"/>
+      <c r="H154" s="24"/>
+      <c r="I154" s="24"/>
+      <c r="J154" s="24"/>
+      <c r="K154" s="24"/>
+      <c r="L154" s="24"/>
+      <c r="M154" s="24"/>
+    </row>
+    <row r="155">
+      <c r="C155" s="17" t="s">
+        <v>653</v>
+      </c>
+      <c r="D155" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="E141" s="3" t="s">
+      <c r="E155" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="F141" s="23"/>
-      <c r="G141" s="23"/>
-      <c r="H141" s="23"/>
-      <c r="I141" s="23"/>
-      <c r="J141" s="23"/>
-      <c r="K141" s="23"/>
-      <c r="L141" s="23"/>
-      <c r="M141" s="23"/>
-    </row>
-    <row r="142">
-      <c r="C142" s="20" t="s">
-        <v>611</v>
-      </c>
-      <c r="D142" s="8" t="s">
+      <c r="F155" s="24"/>
+      <c r="G155" s="24"/>
+      <c r="H155" s="24"/>
+      <c r="I155" s="24"/>
+      <c r="J155" s="24"/>
+      <c r="K155" s="24"/>
+      <c r="L155" s="24"/>
+      <c r="M155" s="24"/>
+    </row>
+    <row r="156">
+      <c r="C156" s="20" t="s">
+        <v>654</v>
+      </c>
+      <c r="D156" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="E142" s="4" t="s">
+      <c r="E156" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="F142" s="23"/>
-      <c r="G142" s="23"/>
-      <c r="H142" s="23"/>
-      <c r="I142" s="23"/>
-      <c r="J142" s="23"/>
-      <c r="K142" s="23"/>
-      <c r="L142" s="23"/>
-      <c r="M142" s="23"/>
-    </row>
-    <row r="143">
-      <c r="C143" s="20" t="s">
-        <v>612</v>
-      </c>
-      <c r="D143" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="E143" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F143" s="23"/>
-      <c r="G143" s="23"/>
-      <c r="H143" s="23"/>
-      <c r="I143" s="23"/>
-      <c r="J143" s="23"/>
-      <c r="K143" s="23"/>
-      <c r="L143" s="23"/>
-      <c r="M143" s="23"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="20" t="s">
-        <v>613</v>
-      </c>
-      <c r="B144" s="20" t="s">
-        <v>396</v>
-      </c>
-      <c r="C144" s="20" t="s">
-        <v>614</v>
-      </c>
-      <c r="D144" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="E144" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="F144" s="23"/>
-      <c r="G144" s="23"/>
-      <c r="H144" s="23"/>
-      <c r="I144" s="23"/>
-      <c r="J144" s="23"/>
-      <c r="K144" s="23"/>
-      <c r="L144" s="23"/>
-      <c r="M144" s="23"/>
-    </row>
-    <row r="145">
-      <c r="B145" s="20" t="s">
-        <v>454</v>
-      </c>
-      <c r="C145" s="20" t="s">
-        <v>615</v>
-      </c>
-      <c r="D145" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="E145" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="F145" s="23"/>
-      <c r="G145" s="23"/>
-      <c r="H145" s="23"/>
-      <c r="I145" s="23"/>
-      <c r="J145" s="23"/>
-      <c r="K145" s="23"/>
-      <c r="L145" s="23"/>
-      <c r="M145" s="23"/>
-    </row>
-    <row r="146">
-      <c r="C146" s="20" t="s">
-        <v>616</v>
-      </c>
-      <c r="D146" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="E146" s="8" t="s">
-        <v>617</v>
-      </c>
-      <c r="F146" s="23"/>
-      <c r="G146" s="23"/>
-      <c r="H146" s="23"/>
-      <c r="I146" s="23"/>
-      <c r="J146" s="23"/>
-      <c r="K146" s="23"/>
-      <c r="L146" s="23"/>
-      <c r="M146" s="23"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="20" t="s">
-        <v>618</v>
-      </c>
-      <c r="B147" s="20" t="s">
-        <v>473</v>
-      </c>
-      <c r="C147" s="20" t="s">
-        <v>619</v>
-      </c>
-      <c r="D147" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E147" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="F147" s="23"/>
-      <c r="G147" s="23"/>
-      <c r="H147" s="23"/>
-      <c r="I147" s="23"/>
-      <c r="J147" s="23"/>
-      <c r="K147" s="23"/>
-      <c r="L147" s="23"/>
-      <c r="M147" s="23"/>
-    </row>
-    <row r="148">
-      <c r="C148" s="20" t="s">
-        <v>620</v>
-      </c>
-      <c r="D148" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E148" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F148" s="23"/>
-      <c r="G148" s="23"/>
-      <c r="H148" s="23"/>
-      <c r="I148" s="23"/>
-      <c r="J148" s="23"/>
-      <c r="K148" s="23"/>
-      <c r="L148" s="23"/>
-      <c r="M148" s="23"/>
-    </row>
-    <row r="149">
-      <c r="C149" s="20" t="s">
-        <v>621</v>
-      </c>
-      <c r="D149" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E149" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="F149" s="23"/>
-      <c r="G149" s="23"/>
-      <c r="H149" s="23"/>
-      <c r="I149" s="23"/>
-      <c r="J149" s="23"/>
-      <c r="K149" s="23"/>
-      <c r="L149" s="23"/>
-      <c r="M149" s="23"/>
-    </row>
-    <row r="150">
-      <c r="C150" s="7" t="s">
-        <v>623</v>
-      </c>
-      <c r="D150" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="E150" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="F150" s="23"/>
-      <c r="G150" s="23"/>
-      <c r="H150" s="23"/>
-      <c r="I150" s="23"/>
-      <c r="J150" s="23"/>
-      <c r="K150" s="23"/>
-      <c r="L150" s="23"/>
-      <c r="M150" s="23"/>
-    </row>
-    <row r="151">
-      <c r="B151" s="20" t="s">
-        <v>396</v>
-      </c>
-      <c r="C151" s="7" t="s">
-        <v>626</v>
-      </c>
-      <c r="D151" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E151" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F151" s="23"/>
-      <c r="G151" s="23"/>
-      <c r="H151" s="23"/>
-      <c r="I151" s="23"/>
-      <c r="J151" s="23"/>
-      <c r="K151" s="23"/>
-      <c r="L151" s="23"/>
-      <c r="M151" s="23"/>
-    </row>
-    <row r="152">
-      <c r="C152" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="D152" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="E152" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="F152" s="23"/>
-      <c r="G152" s="23"/>
-      <c r="H152" s="23"/>
-      <c r="I152" s="23"/>
-      <c r="J152" s="23"/>
-      <c r="K152" s="23"/>
-      <c r="L152" s="23"/>
-      <c r="M152" s="23"/>
-    </row>
-    <row r="153">
-      <c r="C153" s="7" t="s">
-        <v>628</v>
-      </c>
-      <c r="D153" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E153" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F153" s="23"/>
-      <c r="G153" s="23"/>
-      <c r="H153" s="23"/>
-      <c r="I153" s="23"/>
-      <c r="J153" s="23"/>
-      <c r="K153" s="23"/>
-      <c r="L153" s="23"/>
-      <c r="M153" s="23"/>
-    </row>
-    <row r="154">
-      <c r="C154" s="7" t="s">
-        <v>629</v>
-      </c>
-      <c r="D154" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E154" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="F154" s="23"/>
-      <c r="G154" s="23"/>
-      <c r="H154" s="23"/>
-      <c r="I154" s="23"/>
-      <c r="J154" s="23"/>
-      <c r="K154" s="23"/>
-      <c r="L154" s="23"/>
-      <c r="M154" s="23"/>
-    </row>
-    <row r="155">
-      <c r="C155" s="7" t="s">
-        <v>630</v>
-      </c>
-      <c r="D155" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F155" s="23"/>
-      <c r="G155" s="23"/>
-      <c r="H155" s="23"/>
-      <c r="I155" s="23"/>
-      <c r="J155" s="23"/>
-      <c r="K155" s="23"/>
-      <c r="L155" s="23"/>
-      <c r="M155" s="23"/>
-    </row>
-    <row r="156">
-      <c r="C156" s="7" t="s">
-        <v>631</v>
-      </c>
-      <c r="D156" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E156" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="F156" s="23"/>
-      <c r="G156" s="23"/>
-      <c r="H156" s="23"/>
-      <c r="I156" s="23"/>
-      <c r="J156" s="23"/>
-      <c r="K156" s="23"/>
-      <c r="L156" s="23"/>
-      <c r="M156" s="23"/>
+      <c r="F156" s="24"/>
+      <c r="G156" s="24"/>
+      <c r="H156" s="24"/>
+      <c r="I156" s="24"/>
+      <c r="J156" s="24"/>
+      <c r="K156" s="24"/>
+      <c r="L156" s="24"/>
+      <c r="M156" s="24"/>
     </row>
     <row r="157">
-      <c r="B157" s="20" t="s">
-        <v>454</v>
-      </c>
-      <c r="C157" s="20" t="s">
-        <v>632</v>
-      </c>
-      <c r="D157" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E157" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="F157" s="23"/>
-      <c r="G157" s="23"/>
-      <c r="H157" s="23"/>
-      <c r="I157" s="23"/>
-      <c r="J157" s="23"/>
-      <c r="K157" s="23"/>
-      <c r="L157" s="23"/>
-      <c r="M157" s="23"/>
+      <c r="C157" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="D157" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="E157" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="F157" s="24"/>
+      <c r="G157" s="24"/>
+      <c r="H157" s="24"/>
+      <c r="I157" s="24"/>
+      <c r="J157" s="24"/>
+      <c r="K157" s="24"/>
+      <c r="L157" s="24"/>
+      <c r="M157" s="24"/>
     </row>
     <row r="158">
       <c r="C158" s="20" t="s">
-        <v>633</v>
-      </c>
-      <c r="D158" s="3" t="s">
-        <v>253</v>
+        <v>658</v>
+      </c>
+      <c r="D158" s="8" t="s">
+        <v>261</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="F158" s="23"/>
-      <c r="G158" s="23"/>
-      <c r="H158" s="23"/>
-      <c r="I158" s="23"/>
-      <c r="J158" s="23"/>
-      <c r="K158" s="23"/>
-      <c r="L158" s="23"/>
-      <c r="M158" s="23"/>
+        <v>262</v>
+      </c>
+      <c r="F158" s="24"/>
+      <c r="G158" s="24"/>
+      <c r="H158" s="24"/>
+      <c r="I158" s="24"/>
+      <c r="J158" s="24"/>
+      <c r="K158" s="24"/>
+      <c r="L158" s="24"/>
+      <c r="M158" s="24"/>
     </row>
     <row r="159">
+      <c r="A159" s="20" t="s">
+        <v>659</v>
+      </c>
+      <c r="B159" s="20" t="s">
+        <v>396</v>
+      </c>
       <c r="C159" s="20" t="s">
-        <v>635</v>
-      </c>
-      <c r="D159" s="11" t="s">
-        <v>636</v>
-      </c>
-      <c r="E159" s="11" t="s">
-        <v>637</v>
-      </c>
-      <c r="F159" s="23"/>
-      <c r="G159" s="23"/>
-      <c r="H159" s="23"/>
-      <c r="I159" s="23"/>
-      <c r="J159" s="23"/>
-      <c r="K159" s="23"/>
-      <c r="L159" s="23"/>
-      <c r="M159" s="23"/>
+        <v>660</v>
+      </c>
+      <c r="D159" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E159" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="F159" s="24"/>
+      <c r="G159" s="24"/>
+      <c r="H159" s="24"/>
+      <c r="I159" s="24"/>
+      <c r="J159" s="24"/>
+      <c r="K159" s="24"/>
+      <c r="L159" s="24"/>
+      <c r="M159" s="24"/>
     </row>
     <row r="160">
+      <c r="B160" s="20" t="s">
+        <v>446</v>
+      </c>
       <c r="C160" s="20" t="s">
-        <v>638</v>
-      </c>
-      <c r="D160" s="3" t="s">
-        <v>208</v>
+        <v>661</v>
+      </c>
+      <c r="D160" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="F160" s="23"/>
-      <c r="G160" s="23"/>
-      <c r="H160" s="23"/>
-      <c r="I160" s="23"/>
-      <c r="J160" s="23"/>
-      <c r="K160" s="23"/>
-      <c r="L160" s="23"/>
-      <c r="M160" s="23"/>
+        <v>272</v>
+      </c>
+      <c r="F160" s="24"/>
+      <c r="G160" s="24"/>
+      <c r="H160" s="24"/>
+      <c r="I160" s="24"/>
+      <c r="J160" s="24"/>
+      <c r="K160" s="24"/>
+      <c r="L160" s="24"/>
+      <c r="M160" s="24"/>
     </row>
     <row r="161">
       <c r="C161" s="20" t="s">
-        <v>640</v>
-      </c>
-      <c r="D161" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E161" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="F161" s="23"/>
-      <c r="G161" s="23"/>
-      <c r="H161" s="23"/>
-      <c r="I161" s="23"/>
-      <c r="J161" s="23"/>
-      <c r="K161" s="23"/>
-      <c r="L161" s="23"/>
-      <c r="M161" s="23"/>
+        <v>662</v>
+      </c>
+      <c r="D161" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="E161" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="F161" s="24"/>
+      <c r="G161" s="24"/>
+      <c r="H161" s="24"/>
+      <c r="I161" s="24"/>
+      <c r="J161" s="24"/>
+      <c r="K161" s="24"/>
+      <c r="L161" s="24"/>
+      <c r="M161" s="24"/>
     </row>
     <row r="162">
+      <c r="A162" s="20" t="s">
+        <v>664</v>
+      </c>
+      <c r="B162" s="20" t="s">
+        <v>518</v>
+      </c>
       <c r="C162" s="20" t="s">
-        <v>641</v>
-      </c>
-      <c r="D162" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="E162" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="F162" s="23"/>
-      <c r="G162" s="23"/>
-      <c r="H162" s="23"/>
-      <c r="I162" s="23"/>
-      <c r="J162" s="23"/>
-      <c r="K162" s="23"/>
-      <c r="L162" s="23"/>
-      <c r="M162" s="23"/>
+        <v>665</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E162" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="F162" s="24"/>
+      <c r="G162" s="24"/>
+      <c r="H162" s="24"/>
+      <c r="I162" s="24"/>
+      <c r="J162" s="24"/>
+      <c r="K162" s="24"/>
+      <c r="L162" s="24"/>
+      <c r="M162" s="24"/>
     </row>
     <row r="163">
-      <c r="B163" s="20" t="s">
-        <v>437</v>
-      </c>
-      <c r="C163" s="7" t="s">
-        <v>644</v>
-      </c>
-      <c r="D163" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="E163" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="F163" s="23"/>
-      <c r="G163" s="23"/>
-      <c r="H163" s="23"/>
-      <c r="I163" s="23"/>
-      <c r="J163" s="23"/>
-      <c r="K163" s="23"/>
-      <c r="L163" s="23"/>
-      <c r="M163" s="23"/>
+      <c r="C163" s="20" t="s">
+        <v>666</v>
+      </c>
+      <c r="D163" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E163" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F163" s="24"/>
+      <c r="G163" s="24"/>
+      <c r="H163" s="24"/>
+      <c r="I163" s="24"/>
+      <c r="J163" s="24"/>
+      <c r="K163" s="24"/>
+      <c r="L163" s="24"/>
+      <c r="M163" s="24"/>
     </row>
     <row r="164">
-      <c r="C164" s="7" t="s">
-        <v>647</v>
+      <c r="C164" s="20" t="s">
+        <v>667</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>648</v>
+        <v>88</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F164" s="23"/>
-      <c r="G164" s="23"/>
-      <c r="H164" s="23"/>
-      <c r="I164" s="23"/>
-      <c r="J164" s="23"/>
-      <c r="K164" s="23"/>
-      <c r="L164" s="23"/>
-      <c r="M164" s="23"/>
+        <v>668</v>
+      </c>
+      <c r="F164" s="24"/>
+      <c r="G164" s="24"/>
+      <c r="H164" s="24"/>
+      <c r="I164" s="24"/>
+      <c r="J164" s="24"/>
+      <c r="K164" s="24"/>
+      <c r="L164" s="24"/>
+      <c r="M164" s="24"/>
     </row>
     <row r="165">
       <c r="C165" s="7" t="s">
-        <v>650</v>
+        <v>669</v>
       </c>
       <c r="D165" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="F165" s="24"/>
+      <c r="G165" s="24"/>
+      <c r="H165" s="24"/>
+      <c r="I165" s="24"/>
+      <c r="J165" s="24"/>
+      <c r="K165" s="24"/>
+      <c r="L165" s="24"/>
+      <c r="M165" s="24"/>
+    </row>
+    <row r="166">
+      <c r="B166" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>672</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F166" s="24"/>
+      <c r="G166" s="24"/>
+      <c r="H166" s="24"/>
+      <c r="I166" s="24"/>
+      <c r="J166" s="24"/>
+      <c r="K166" s="24"/>
+      <c r="L166" s="24"/>
+      <c r="M166" s="24"/>
+    </row>
+    <row r="167">
+      <c r="C167" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="F167" s="24"/>
+      <c r="G167" s="24"/>
+      <c r="H167" s="24"/>
+      <c r="I167" s="24"/>
+      <c r="J167" s="24"/>
+      <c r="K167" s="24"/>
+      <c r="L167" s="24"/>
+      <c r="M167" s="24"/>
+    </row>
+    <row r="168">
+      <c r="C168" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F168" s="24"/>
+      <c r="G168" s="24"/>
+      <c r="H168" s="24"/>
+      <c r="I168" s="24"/>
+      <c r="J168" s="24"/>
+      <c r="K168" s="24"/>
+      <c r="L168" s="24"/>
+      <c r="M168" s="24"/>
+    </row>
+    <row r="169">
+      <c r="C169" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F169" s="24"/>
+      <c r="G169" s="24"/>
+      <c r="H169" s="24"/>
+      <c r="I169" s="24"/>
+      <c r="J169" s="24"/>
+      <c r="K169" s="24"/>
+      <c r="L169" s="24"/>
+      <c r="M169" s="24"/>
+    </row>
+    <row r="170">
+      <c r="C170" s="7" t="s">
+        <v>676</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F170" s="24"/>
+      <c r="G170" s="24"/>
+      <c r="H170" s="24"/>
+      <c r="I170" s="24"/>
+      <c r="J170" s="24"/>
+      <c r="K170" s="24"/>
+      <c r="L170" s="24"/>
+      <c r="M170" s="24"/>
+    </row>
+    <row r="171">
+      <c r="C171" s="7" t="s">
+        <v>677</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F171" s="24"/>
+      <c r="G171" s="24"/>
+      <c r="H171" s="24"/>
+      <c r="I171" s="24"/>
+      <c r="J171" s="24"/>
+      <c r="K171" s="24"/>
+      <c r="L171" s="24"/>
+      <c r="M171" s="24"/>
+    </row>
+    <row r="172">
+      <c r="B172" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="C172" s="20" t="s">
+        <v>678</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E172" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="F172" s="24"/>
+      <c r="G172" s="24"/>
+      <c r="H172" s="24"/>
+      <c r="I172" s="24"/>
+      <c r="J172" s="24"/>
+      <c r="K172" s="24"/>
+      <c r="L172" s="24"/>
+      <c r="M172" s="24"/>
+    </row>
+    <row r="173">
+      <c r="C173" s="20" t="s">
+        <v>679</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="F173" s="24"/>
+      <c r="G173" s="24"/>
+      <c r="H173" s="24"/>
+      <c r="I173" s="24"/>
+      <c r="J173" s="24"/>
+      <c r="K173" s="24"/>
+      <c r="L173" s="24"/>
+      <c r="M173" s="24"/>
+    </row>
+    <row r="174">
+      <c r="C174" s="20" t="s">
+        <v>681</v>
+      </c>
+      <c r="D174" s="11" t="s">
+        <v>682</v>
+      </c>
+      <c r="E174" s="11" t="s">
+        <v>683</v>
+      </c>
+      <c r="F174" s="24"/>
+      <c r="G174" s="24"/>
+      <c r="H174" s="24"/>
+      <c r="I174" s="24"/>
+      <c r="J174" s="24"/>
+      <c r="K174" s="24"/>
+      <c r="L174" s="24"/>
+      <c r="M174" s="24"/>
+    </row>
+    <row r="175">
+      <c r="C175" s="20" t="s">
+        <v>684</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="F175" s="24"/>
+      <c r="G175" s="24"/>
+      <c r="H175" s="24"/>
+      <c r="I175" s="24"/>
+      <c r="J175" s="24"/>
+      <c r="K175" s="24"/>
+      <c r="L175" s="24"/>
+      <c r="M175" s="24"/>
+    </row>
+    <row r="176">
+      <c r="C176" s="20" t="s">
+        <v>686</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="F176" s="24"/>
+      <c r="G176" s="24"/>
+      <c r="H176" s="24"/>
+      <c r="I176" s="24"/>
+      <c r="J176" s="24"/>
+      <c r="K176" s="24"/>
+      <c r="L176" s="24"/>
+      <c r="M176" s="24"/>
+    </row>
+    <row r="177">
+      <c r="C177" s="20" t="s">
+        <v>687</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="F177" s="24"/>
+      <c r="G177" s="24"/>
+      <c r="H177" s="24"/>
+      <c r="I177" s="24"/>
+      <c r="J177" s="24"/>
+      <c r="K177" s="24"/>
+      <c r="L177" s="24"/>
+      <c r="M177" s="24"/>
+    </row>
+    <row r="178">
+      <c r="B178" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F178" s="24"/>
+      <c r="G178" s="24"/>
+      <c r="H178" s="24"/>
+      <c r="I178" s="24"/>
+      <c r="J178" s="24"/>
+      <c r="K178" s="24"/>
+      <c r="L178" s="24"/>
+      <c r="M178" s="24"/>
+    </row>
+    <row r="179">
+      <c r="C179" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="F179" s="24"/>
+      <c r="G179" s="24"/>
+      <c r="H179" s="24"/>
+      <c r="I179" s="24"/>
+      <c r="J179" s="24"/>
+      <c r="K179" s="24"/>
+      <c r="L179" s="24"/>
+      <c r="M179" s="24"/>
+    </row>
+    <row r="180">
+      <c r="C180" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="D180" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="E165" s="7" t="s">
+      <c r="E180" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="F165" s="23"/>
-      <c r="G165" s="23"/>
-      <c r="H165" s="23"/>
-      <c r="I165" s="23"/>
-      <c r="J165" s="23"/>
-      <c r="K165" s="23"/>
-      <c r="L165" s="23"/>
-      <c r="M165" s="23"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="20" t="s">
-        <v>651</v>
-      </c>
-      <c r="B166" s="20" t="s">
-        <v>652</v>
-      </c>
-      <c r="C166" s="20" t="s">
-        <v>653</v>
-      </c>
-      <c r="D166" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="E166" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="F166" s="23"/>
-      <c r="G166" s="23"/>
-      <c r="H166" s="23"/>
-      <c r="I166" s="23"/>
-      <c r="J166" s="23"/>
-      <c r="K166" s="23"/>
-      <c r="L166" s="23"/>
-      <c r="M166" s="23"/>
-    </row>
-    <row r="167">
-      <c r="C167" s="20" t="s">
-        <v>656</v>
-      </c>
-      <c r="D167" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="E167" s="8" t="s">
-        <v>658</v>
-      </c>
-      <c r="F167" s="23"/>
-      <c r="G167" s="23"/>
-      <c r="H167" s="23"/>
-      <c r="I167" s="23"/>
-      <c r="J167" s="23"/>
-      <c r="K167" s="23"/>
-      <c r="L167" s="23"/>
-      <c r="M167" s="23"/>
-    </row>
-    <row r="168">
-      <c r="C168" s="20" t="s">
-        <v>659</v>
-      </c>
-      <c r="D168" s="3" t="s">
-        <v>660</v>
-      </c>
-      <c r="E168" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="F168" s="23"/>
-      <c r="G168" s="23"/>
-      <c r="H168" s="23"/>
-      <c r="I168" s="23"/>
-      <c r="J168" s="23"/>
-      <c r="K168" s="23"/>
-      <c r="L168" s="23"/>
-      <c r="M168" s="23"/>
-    </row>
-    <row r="169">
-      <c r="C169" s="20" t="s">
-        <v>662</v>
-      </c>
-      <c r="D169" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="E169" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="F169" s="23"/>
-      <c r="G169" s="23"/>
-      <c r="H169" s="23"/>
-      <c r="I169" s="23"/>
-      <c r="J169" s="23"/>
-      <c r="K169" s="23"/>
-      <c r="L169" s="23"/>
-      <c r="M169" s="23"/>
-    </row>
-    <row r="170">
-      <c r="B170" s="20" t="s">
-        <v>437</v>
-      </c>
-      <c r="C170" s="20" t="s">
-        <v>665</v>
-      </c>
-      <c r="D170" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="E170" s="8" t="s">
-        <v>667</v>
-      </c>
-      <c r="F170" s="23"/>
-      <c r="G170" s="23"/>
-      <c r="H170" s="23"/>
-      <c r="I170" s="23"/>
-      <c r="J170" s="23"/>
-      <c r="K170" s="23"/>
-      <c r="L170" s="23"/>
-      <c r="M170" s="23"/>
-    </row>
-    <row r="171">
-      <c r="C171" s="20" t="s">
-        <v>668</v>
-      </c>
-      <c r="D171" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="E171" s="8" t="s">
-        <v>670</v>
-      </c>
-      <c r="F171" s="23"/>
-      <c r="G171" s="23"/>
-      <c r="H171" s="23"/>
-      <c r="I171" s="23"/>
-      <c r="J171" s="23"/>
-      <c r="K171" s="23"/>
-      <c r="L171" s="23"/>
-      <c r="M171" s="23"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="20" t="s">
-        <v>671</v>
-      </c>
-      <c r="B172" s="20" t="s">
-        <v>454</v>
-      </c>
-      <c r="C172" s="20" t="s">
-        <v>672</v>
-      </c>
-      <c r="D172" s="3" t="s">
+      <c r="F180" s="24"/>
+      <c r="G180" s="24"/>
+      <c r="H180" s="24"/>
+      <c r="I180" s="24"/>
+      <c r="J180" s="24"/>
+      <c r="K180" s="24"/>
+      <c r="L180" s="24"/>
+      <c r="M180" s="24"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="20" t="s">
+        <v>697</v>
+      </c>
+      <c r="B181" s="20" t="s">
+        <v>698</v>
+      </c>
+      <c r="C181" s="20" t="s">
+        <v>699</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="F181" s="24"/>
+      <c r="G181" s="24"/>
+      <c r="H181" s="24"/>
+      <c r="I181" s="24"/>
+      <c r="J181" s="24"/>
+      <c r="K181" s="24"/>
+      <c r="L181" s="24"/>
+      <c r="M181" s="24"/>
+    </row>
+    <row r="182">
+      <c r="C182" s="20" t="s">
+        <v>702</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="E182" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="F182" s="24"/>
+      <c r="G182" s="24"/>
+      <c r="H182" s="24"/>
+      <c r="I182" s="24"/>
+      <c r="J182" s="24"/>
+      <c r="K182" s="24"/>
+      <c r="L182" s="24"/>
+      <c r="M182" s="24"/>
+    </row>
+    <row r="183">
+      <c r="C183" s="20" t="s">
+        <v>705</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="F183" s="24"/>
+      <c r="G183" s="24"/>
+      <c r="H183" s="24"/>
+      <c r="I183" s="24"/>
+      <c r="J183" s="24"/>
+      <c r="K183" s="24"/>
+      <c r="L183" s="24"/>
+      <c r="M183" s="24"/>
+    </row>
+    <row r="184">
+      <c r="C184" s="20" t="s">
+        <v>708</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="F184" s="24"/>
+      <c r="G184" s="24"/>
+      <c r="H184" s="24"/>
+      <c r="I184" s="24"/>
+      <c r="J184" s="24"/>
+      <c r="K184" s="24"/>
+      <c r="L184" s="24"/>
+      <c r="M184" s="24"/>
+    </row>
+    <row r="185">
+      <c r="B185" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="C185" s="20" t="s">
+        <v>711</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="F185" s="24"/>
+      <c r="G185" s="24"/>
+      <c r="H185" s="24"/>
+      <c r="I185" s="24"/>
+      <c r="J185" s="24"/>
+      <c r="K185" s="24"/>
+      <c r="L185" s="24"/>
+      <c r="M185" s="24"/>
+    </row>
+    <row r="186">
+      <c r="C186" s="20" t="s">
+        <v>714</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="E186" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="F186" s="24"/>
+      <c r="G186" s="24"/>
+      <c r="H186" s="24"/>
+      <c r="I186" s="24"/>
+      <c r="J186" s="24"/>
+      <c r="K186" s="24"/>
+      <c r="L186" s="24"/>
+      <c r="M186" s="24"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="20" t="s">
+        <v>717</v>
+      </c>
+      <c r="B187" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="C187" s="20" t="s">
+        <v>718</v>
+      </c>
+      <c r="D187" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="E172" s="8" t="s">
+      <c r="E187" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="F172" s="23"/>
-      <c r="G172" s="23"/>
-      <c r="H172" s="23"/>
-      <c r="I172" s="23"/>
-      <c r="J172" s="23"/>
-      <c r="K172" s="23"/>
-      <c r="L172" s="23"/>
-      <c r="M172" s="23"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="20"/>
-      <c r="B173" s="20"/>
-      <c r="F173" s="23"/>
-      <c r="G173" s="23"/>
-      <c r="H173" s="23"/>
-      <c r="I173" s="23"/>
-      <c r="J173" s="23"/>
-      <c r="K173" s="23"/>
-      <c r="L173" s="23"/>
-      <c r="M173" s="23"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="20"/>
-      <c r="B174" s="20"/>
-      <c r="C174" s="20"/>
-      <c r="D174" s="3"/>
-      <c r="E174" s="3"/>
-      <c r="F174" s="23"/>
-      <c r="G174" s="23"/>
-      <c r="H174" s="23"/>
-      <c r="I174" s="23"/>
-      <c r="J174" s="23"/>
-      <c r="K174" s="23"/>
-      <c r="L174" s="23"/>
-      <c r="M174" s="23"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="20"/>
-      <c r="B175" s="20"/>
-      <c r="C175" s="20"/>
-      <c r="D175" s="3"/>
-      <c r="F175" s="23"/>
-      <c r="G175" s="23"/>
-      <c r="H175" s="23"/>
-      <c r="I175" s="23"/>
-      <c r="J175" s="23"/>
-      <c r="K175" s="23"/>
-      <c r="L175" s="23"/>
-      <c r="M175" s="23"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="20"/>
-      <c r="B176" s="20"/>
-      <c r="C176" s="20"/>
-      <c r="F176" s="23"/>
-      <c r="G176" s="23"/>
-      <c r="H176" s="23"/>
-      <c r="I176" s="23"/>
-      <c r="J176" s="23"/>
-      <c r="K176" s="23"/>
-      <c r="L176" s="23"/>
-      <c r="M176" s="23"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="20"/>
-      <c r="B177" s="20"/>
-      <c r="C177" s="20"/>
-      <c r="D177" s="3"/>
-      <c r="F177" s="23"/>
-      <c r="G177" s="23"/>
-      <c r="H177" s="23"/>
-      <c r="I177" s="23"/>
-      <c r="J177" s="23"/>
-      <c r="K177" s="23"/>
-      <c r="L177" s="23"/>
-      <c r="M177" s="23"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="20"/>
-      <c r="B178" s="20"/>
-      <c r="C178" s="20"/>
-      <c r="F178" s="23"/>
-      <c r="G178" s="23"/>
-      <c r="H178" s="23"/>
-      <c r="I178" s="23"/>
-      <c r="J178" s="23"/>
-      <c r="K178" s="23"/>
-      <c r="L178" s="23"/>
-      <c r="M178" s="23"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="20"/>
-      <c r="B179" s="20"/>
-      <c r="C179" s="20"/>
-      <c r="F179" s="23"/>
-      <c r="G179" s="23"/>
-      <c r="H179" s="23"/>
-      <c r="I179" s="23"/>
-      <c r="J179" s="23"/>
-      <c r="K179" s="23"/>
-      <c r="L179" s="23"/>
-      <c r="M179" s="23"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="20"/>
-      <c r="B180" s="20"/>
-      <c r="C180" s="20"/>
-      <c r="F180" s="23"/>
-      <c r="G180" s="23"/>
-      <c r="H180" s="23"/>
-      <c r="I180" s="23"/>
-      <c r="J180" s="23"/>
-      <c r="K180" s="23"/>
-      <c r="L180" s="23"/>
-      <c r="M180" s="23"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="20"/>
-      <c r="B181" s="20"/>
-      <c r="C181" s="20"/>
-      <c r="F181" s="23"/>
-      <c r="G181" s="23"/>
-      <c r="H181" s="23"/>
-      <c r="I181" s="23"/>
-      <c r="J181" s="23"/>
-      <c r="K181" s="23"/>
-      <c r="L181" s="23"/>
-      <c r="M181" s="23"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="20"/>
-      <c r="B182" s="20"/>
-      <c r="C182" s="20"/>
-      <c r="F182" s="23"/>
-      <c r="G182" s="23"/>
-      <c r="H182" s="23"/>
-      <c r="I182" s="23"/>
-      <c r="J182" s="23"/>
-      <c r="K182" s="23"/>
-      <c r="L182" s="23"/>
-      <c r="M182" s="23"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="20"/>
-      <c r="B183" s="20"/>
-      <c r="C183" s="20"/>
-      <c r="F183" s="23"/>
-      <c r="G183" s="23"/>
-      <c r="H183" s="23"/>
-      <c r="I183" s="23"/>
-      <c r="J183" s="23"/>
-      <c r="K183" s="23"/>
-      <c r="L183" s="23"/>
-      <c r="M183" s="23"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="20"/>
-      <c r="B184" s="20"/>
-      <c r="C184" s="20"/>
-      <c r="F184" s="23"/>
-      <c r="G184" s="23"/>
-      <c r="H184" s="23"/>
-      <c r="I184" s="23"/>
-      <c r="J184" s="23"/>
-      <c r="K184" s="23"/>
-      <c r="L184" s="23"/>
-      <c r="M184" s="23"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="20"/>
-      <c r="B185" s="20"/>
-      <c r="C185" s="20"/>
-      <c r="F185" s="23"/>
-      <c r="G185" s="23"/>
-      <c r="H185" s="23"/>
-      <c r="I185" s="23"/>
-      <c r="J185" s="23"/>
-      <c r="K185" s="23"/>
-      <c r="L185" s="23"/>
-      <c r="M185" s="23"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="20"/>
-      <c r="B186" s="20"/>
-      <c r="C186" s="20"/>
-      <c r="F186" s="23"/>
-      <c r="G186" s="23"/>
-      <c r="H186" s="23"/>
-      <c r="I186" s="23"/>
-      <c r="J186" s="23"/>
-      <c r="K186" s="23"/>
-      <c r="L186" s="23"/>
-      <c r="M186" s="23"/>
+      <c r="F187" s="24"/>
+      <c r="G187" s="24"/>
+      <c r="H187" s="24"/>
+      <c r="I187" s="24"/>
+      <c r="J187" s="24"/>
+      <c r="K187" s="24"/>
+      <c r="L187" s="24"/>
+      <c r="M187" s="24"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="20" t="s">
+        <v>717</v>
+      </c>
+      <c r="B188" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="C188" s="20" t="s">
+        <v>719</v>
+      </c>
+      <c r="D188" s="33" t="s">
+        <v>720</v>
+      </c>
+      <c r="E188" s="33" t="s">
+        <v>721</v>
+      </c>
+      <c r="F188" s="24"/>
+      <c r="G188" s="24"/>
+      <c r="H188" s="24"/>
+      <c r="I188" s="24"/>
+      <c r="J188" s="24"/>
+      <c r="K188" s="24"/>
+      <c r="L188" s="24"/>
+      <c r="M188" s="24"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="20"/>
+      <c r="B189" s="20"/>
+      <c r="C189" s="20"/>
+      <c r="D189" s="3"/>
+      <c r="E189" s="3"/>
+      <c r="F189" s="24"/>
+      <c r="G189" s="24"/>
+      <c r="H189" s="24"/>
+      <c r="I189" s="24"/>
+      <c r="J189" s="24"/>
+      <c r="K189" s="24"/>
+      <c r="L189" s="24"/>
+      <c r="M189" s="24"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="20"/>
+      <c r="B190" s="20"/>
+      <c r="C190" s="20"/>
+      <c r="D190" s="3"/>
+      <c r="F190" s="24"/>
+      <c r="G190" s="24"/>
+      <c r="H190" s="24"/>
+      <c r="I190" s="24"/>
+      <c r="J190" s="24"/>
+      <c r="K190" s="24"/>
+      <c r="L190" s="24"/>
+      <c r="M190" s="24"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="20"/>
+      <c r="B191" s="20"/>
+      <c r="C191" s="20"/>
+      <c r="F191" s="24"/>
+      <c r="G191" s="24"/>
+      <c r="H191" s="24"/>
+      <c r="I191" s="24"/>
+      <c r="J191" s="24"/>
+      <c r="K191" s="24"/>
+      <c r="L191" s="24"/>
+      <c r="M191" s="24"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="20"/>
+      <c r="B192" s="20"/>
+      <c r="C192" s="20"/>
+      <c r="D192" s="3"/>
+      <c r="F192" s="24"/>
+      <c r="G192" s="24"/>
+      <c r="H192" s="24"/>
+      <c r="I192" s="24"/>
+      <c r="J192" s="24"/>
+      <c r="K192" s="24"/>
+      <c r="L192" s="24"/>
+      <c r="M192" s="24"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="20"/>
+      <c r="B193" s="20"/>
+      <c r="C193" s="20"/>
+      <c r="F193" s="24"/>
+      <c r="G193" s="24"/>
+      <c r="H193" s="24"/>
+      <c r="I193" s="24"/>
+      <c r="J193" s="24"/>
+      <c r="K193" s="24"/>
+      <c r="L193" s="24"/>
+      <c r="M193" s="24"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="20"/>
+      <c r="B194" s="20"/>
+      <c r="C194" s="20"/>
+      <c r="F194" s="24"/>
+      <c r="G194" s="24"/>
+      <c r="H194" s="24"/>
+      <c r="I194" s="24"/>
+      <c r="J194" s="24"/>
+      <c r="K194" s="24"/>
+      <c r="L194" s="24"/>
+      <c r="M194" s="24"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="20"/>
+      <c r="B195" s="20"/>
+      <c r="C195" s="20"/>
+      <c r="F195" s="24"/>
+      <c r="G195" s="24"/>
+      <c r="H195" s="24"/>
+      <c r="I195" s="24"/>
+      <c r="J195" s="24"/>
+      <c r="K195" s="24"/>
+      <c r="L195" s="24"/>
+      <c r="M195" s="24"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="20"/>
+      <c r="B196" s="20"/>
+      <c r="C196" s="20"/>
+      <c r="F196" s="24"/>
+      <c r="G196" s="24"/>
+      <c r="H196" s="24"/>
+      <c r="I196" s="24"/>
+      <c r="J196" s="24"/>
+      <c r="K196" s="24"/>
+      <c r="L196" s="24"/>
+      <c r="M196" s="24"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="20"/>
+      <c r="B197" s="20"/>
+      <c r="C197" s="20"/>
+      <c r="F197" s="24"/>
+      <c r="G197" s="24"/>
+      <c r="H197" s="24"/>
+      <c r="I197" s="24"/>
+      <c r="J197" s="24"/>
+      <c r="K197" s="24"/>
+      <c r="L197" s="24"/>
+      <c r="M197" s="24"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="20"/>
+      <c r="B198" s="20"/>
+      <c r="C198" s="20"/>
+      <c r="F198" s="24"/>
+      <c r="G198" s="24"/>
+      <c r="H198" s="24"/>
+      <c r="I198" s="24"/>
+      <c r="J198" s="24"/>
+      <c r="K198" s="24"/>
+      <c r="L198" s="24"/>
+      <c r="M198" s="24"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="20"/>
+      <c r="B199" s="20"/>
+      <c r="C199" s="20"/>
+      <c r="F199" s="24"/>
+      <c r="G199" s="24"/>
+      <c r="H199" s="24"/>
+      <c r="I199" s="24"/>
+      <c r="J199" s="24"/>
+      <c r="K199" s="24"/>
+      <c r="L199" s="24"/>
+      <c r="M199" s="24"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="20"/>
+      <c r="B200" s="20"/>
+      <c r="C200" s="20"/>
+      <c r="F200" s="24"/>
+      <c r="G200" s="24"/>
+      <c r="H200" s="24"/>
+      <c r="I200" s="24"/>
+      <c r="J200" s="24"/>
+      <c r="K200" s="24"/>
+      <c r="L200" s="24"/>
+      <c r="M200" s="24"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="20"/>
+      <c r="B201" s="20"/>
+      <c r="C201" s="20"/>
+      <c r="F201" s="24"/>
+      <c r="G201" s="24"/>
+      <c r="H201" s="24"/>
+      <c r="I201" s="24"/>
+      <c r="J201" s="24"/>
+      <c r="K201" s="24"/>
+      <c r="L201" s="24"/>
+      <c r="M201" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="34">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A4:A39"/>
+    <mergeCell ref="A4:A44"/>
     <mergeCell ref="B4:B35"/>
-    <mergeCell ref="B36:B39"/>
-    <mergeCell ref="A43:A61"/>
-    <mergeCell ref="B43:B52"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="B81:B84"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="B55:B61"/>
-    <mergeCell ref="A62:A69"/>
-    <mergeCell ref="B62:B67"/>
-    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="A48:A76"/>
+    <mergeCell ref="B48:B57"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="B96:B99"/>
+    <mergeCell ref="B68:B69"/>
     <mergeCell ref="B70:B76"/>
-    <mergeCell ref="A81:A85"/>
-    <mergeCell ref="A117:A143"/>
-    <mergeCell ref="A144:A146"/>
-    <mergeCell ref="A147:A165"/>
-    <mergeCell ref="A166:A171"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="B147:B150"/>
-    <mergeCell ref="B151:B156"/>
-    <mergeCell ref="B157:B162"/>
-    <mergeCell ref="B163:B165"/>
-    <mergeCell ref="B166:B169"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="B101:B113"/>
-    <mergeCell ref="B130:B143"/>
-    <mergeCell ref="A97:A116"/>
-    <mergeCell ref="B126:B129"/>
-    <mergeCell ref="B117:B125"/>
-    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="A77:A84"/>
+    <mergeCell ref="B77:B82"/>
+    <mergeCell ref="A85:A95"/>
+    <mergeCell ref="B85:B91"/>
+    <mergeCell ref="A96:A100"/>
+    <mergeCell ref="A131:A158"/>
+    <mergeCell ref="A159:A161"/>
+    <mergeCell ref="A162:A180"/>
+    <mergeCell ref="A181:A186"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="B162:B165"/>
+    <mergeCell ref="B166:B171"/>
+    <mergeCell ref="B172:B177"/>
+    <mergeCell ref="B178:B180"/>
+    <mergeCell ref="B181:B184"/>
+    <mergeCell ref="B185:B186"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="B129:B130"/>
+    <mergeCell ref="B131:B139"/>
+    <mergeCell ref="B140:B143"/>
+    <mergeCell ref="B144:B158"/>
+    <mergeCell ref="A112:A130"/>
+    <mergeCell ref="B116:B127"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/scripts/i18n.xlsx
+++ b/scripts/i18n.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juyeonkim/Documents/pfplay-web/scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFDD514-0C1F-E347-B903-4CC724928F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C62D74A-73B2-0947-B205-18772E751CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5680" yWindow="500" windowWidth="23160" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2300" yWindow="500" windowWidth="26500" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="i18n" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="603">
   <si>
     <t xml:space="preserve">페이지는 [피그마] PFPlay GUI 설계서 합본의 페이지 이름입니다. </t>
   </si>
@@ -1668,12 +1668,6 @@
     <t>chat.para.remove_chat</t>
   </si>
   <si>
-    <t>'{{subject}}'가 '{{target}}'의 채팅을 삭제했습니다.</t>
-  </si>
-  <si>
-    <t>'{{target}}'s chat was removed by '{{subject}}'.</t>
-  </si>
-  <si>
     <t>common.btn.twitter_login</t>
   </si>
   <si>
@@ -1732,6 +1726,111 @@
   </si>
   <si>
     <t>auth.btn.connect_social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">common.para.points_to_unlock	</t>
+  </si>
+  <si>
+    <t>common.btn.language</t>
+  </si>
+  <si>
+    <t>언어</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>크루(Crews)</t>
+  </si>
+  <si>
+    <t>crews.title.all_count</t>
+  </si>
+  <si>
+    <t>{{points}} 포인트가 필요해요</t>
+  </si>
+  <si>
+    <t>Get {{points}} points to unlock!</t>
+  </si>
+  <si>
+    <t>crews.title.restriction</t>
+  </si>
+  <si>
+    <t>Restriction</t>
+  </si>
+  <si>
+    <t>ed.para.empty_notice</t>
+  </si>
+  <si>
+    <t>공지를 등록해주세요.</t>
+  </si>
+  <si>
+    <t>The party room has been closed.</t>
+  </si>
+  <si>
+    <t>파티룸이 폐쇄되었습니다</t>
+  </si>
+  <si>
+    <t>party.para.closed</t>
+  </si>
+  <si>
+    <t>웹 페이지 주소는 pfplay.xyz/도메인으로 시작</t>
+  </si>
+  <si>
+    <t>Web address starts with pfplay.xyz/domain</t>
+  </si>
+  <si>
+    <t>onboard.para.domain_format</t>
+  </si>
+  <si>
+    <t>This nickname is already used.</t>
+  </si>
+  <si>
+    <t>이미 사용 중인 닉네임입니다.</t>
+  </si>
+  <si>
+    <t>settings.para.nickname_taken</t>
+  </si>
+  <si>
+    <t>party.title.party_edit</t>
+  </si>
+  <si>
+    <t>Edit Party</t>
+  </si>
+  <si>
+    <t>파티 수정</t>
+  </si>
+  <si>
+    <t>Ban (No re-entry allowed)</t>
+  </si>
+  <si>
+    <t>영구 패널티</t>
+  </si>
+  <si>
+    <t>A list I blocked</t>
+  </si>
+  <si>
+    <t>auth.para.penalty</t>
+  </si>
+  <si>
+    <t>auth.para.block</t>
+  </si>
+  <si>
+    <t>Please post the announcement.</t>
+  </si>
+  <si>
+    <t>전체 {count}</t>
+  </si>
+  <si>
+    <t>All {count}</t>
+  </si>
+  <si>
+    <t>'{subject}'가 '{target}'의 채팅을 삭제했습니다.</t>
+  </si>
+  <si>
+    <t>'{target}'s chat was removed by '{subject}'.</t>
+  </si>
+  <si>
+    <t>URL 혹은 음악을 검색할 수 있어요</t>
   </si>
 </sst>
 </file>
@@ -1877,18 +1976,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2108,7 +2207,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M205"/>
+  <dimension ref="A1:M213"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.1640625" customWidth="1"/>
@@ -2121,7 +2220,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="20" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="21"/>
@@ -2138,7 +2237,7 @@
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="20" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="21"/>
@@ -2402,13 +2501,13 @@
       <c r="A14" s="21"/>
       <c r="B14" s="21"/>
       <c r="C14" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>550</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>552</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="5"/>
@@ -2864,13 +2963,13 @@
       <c r="A36" s="21"/>
       <c r="B36" s="21"/>
       <c r="C36" s="6" t="s">
-        <v>100</v>
+        <v>569</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>101</v>
+        <v>570</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>102</v>
+        <v>571</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="5"/>
@@ -2883,15 +2982,15 @@
     </row>
     <row r="37" spans="1:13" ht="15.75" customHeight="1">
       <c r="A37" s="21"/>
-      <c r="B37" s="2"/>
+      <c r="B37" s="21"/>
       <c r="C37" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="5"/>
@@ -2906,13 +3005,13 @@
       <c r="A38" s="21"/>
       <c r="B38" s="2"/>
       <c r="C38" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="5"/>
@@ -2927,13 +3026,13 @@
       <c r="A39" s="21"/>
       <c r="B39" s="2"/>
       <c r="C39" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="5"/>
@@ -2946,17 +3045,15 @@
     </row>
     <row r="40" spans="1:13" ht="15.75" customHeight="1">
       <c r="A40" s="21"/>
-      <c r="B40" s="2" t="s">
-        <v>112</v>
-      </c>
+      <c r="B40" s="2"/>
       <c r="C40" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="5"/>
@@ -2973,13 +3070,13 @@
         <v>112</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="5"/>
@@ -2992,17 +3089,15 @@
     </row>
     <row r="42" spans="1:13" ht="15.75" customHeight="1">
       <c r="A42" s="21"/>
-      <c r="B42" s="22" t="s">
-        <v>118</v>
-      </c>
+      <c r="B42" s="2"/>
       <c r="C42" s="6" t="s">
-        <v>119</v>
+        <v>568</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>120</v>
+        <v>574</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>121</v>
+        <v>575</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="5"/>
@@ -3015,15 +3110,17 @@
     </row>
     <row r="43" spans="1:13" ht="15.75" customHeight="1">
       <c r="A43" s="21"/>
-      <c r="B43" s="21"/>
-      <c r="C43" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>124</v>
+      <c r="B43" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="5"/>
@@ -3036,15 +3133,17 @@
     </row>
     <row r="44" spans="1:13" ht="15.75" customHeight="1">
       <c r="A44" s="21"/>
-      <c r="B44" s="21"/>
-      <c r="C44" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>127</v>
+      <c r="B44" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="5"/>
@@ -3059,13 +3158,13 @@
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="8" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>124</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="5"/>
@@ -3077,16 +3176,16 @@
       <c r="M45" s="4"/>
     </row>
     <row r="46" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
       <c r="C46" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="5"/>
@@ -3098,16 +3197,16 @@
       <c r="M46" s="4"/>
     </row>
     <row r="47" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
+      <c r="A47" s="21"/>
+      <c r="B47" s="21"/>
       <c r="C47" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>129</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="5"/>
@@ -3122,13 +3221,13 @@
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="8" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="5"/>
@@ -3140,20 +3239,16 @@
       <c r="M48" s="4"/>
     </row>
     <row r="49" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A49" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="B49" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>141</v>
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="8" t="s">
+        <v>134</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="5"/>
@@ -3165,16 +3260,16 @@
       <c r="M49" s="4"/>
     </row>
     <row r="50" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A50" s="21"/>
-      <c r="B50" s="21"/>
-      <c r="C50" s="2" t="s">
-        <v>144</v>
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="8" t="s">
+        <v>137</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="5"/>
@@ -3186,16 +3281,20 @@
       <c r="M50" s="4"/>
     </row>
     <row r="51" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A51" s="21"/>
-      <c r="B51" s="21"/>
+      <c r="A51" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>112</v>
+      </c>
       <c r="C51" s="2" t="s">
-        <v>554</v>
+        <v>141</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>553</v>
+        <v>142</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>555</v>
+        <v>143</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="5"/>
@@ -3206,17 +3305,17 @@
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
     </row>
-    <row r="52" spans="1:13" ht="13">
+    <row r="52" spans="1:13" ht="15.75" customHeight="1">
       <c r="A52" s="21"/>
       <c r="B52" s="21"/>
-      <c r="C52" s="6" t="s">
-        <v>561</v>
+      <c r="C52" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>562</v>
+        <v>145</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>563</v>
+        <v>146</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="5"/>
@@ -3227,17 +3326,17 @@
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
     </row>
-    <row r="53" spans="1:13" ht="13">
+    <row r="53" spans="1:13" ht="15.75" customHeight="1">
       <c r="A53" s="21"/>
       <c r="B53" s="21"/>
-      <c r="C53" s="6" t="s">
-        <v>147</v>
+      <c r="C53" s="2" t="s">
+        <v>552</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>148</v>
+        <v>551</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>149</v>
+        <v>553</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="5"/>
@@ -3252,13 +3351,13 @@
       <c r="A54" s="21"/>
       <c r="B54" s="21"/>
       <c r="C54" s="6" t="s">
-        <v>150</v>
+        <v>559</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>151</v>
+        <v>560</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>152</v>
+        <v>561</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="5"/>
@@ -3273,13 +3372,13 @@
       <c r="A55" s="21"/>
       <c r="B55" s="21"/>
       <c r="C55" s="6" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="5"/>
@@ -3290,17 +3389,17 @@
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
     </row>
-    <row r="56" spans="1:13" ht="14">
+    <row r="56" spans="1:13" ht="13">
       <c r="A56" s="21"/>
       <c r="B56" s="21"/>
       <c r="C56" s="6" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>158</v>
+        <v>151</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>152</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="5"/>
@@ -3315,13 +3414,13 @@
       <c r="A57" s="21"/>
       <c r="B57" s="21"/>
       <c r="C57" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="5"/>
@@ -3332,17 +3431,17 @@
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
     </row>
-    <row r="58" spans="1:13" ht="13">
+    <row r="58" spans="1:13" ht="14">
       <c r="A58" s="21"/>
       <c r="B58" s="21"/>
       <c r="C58" s="6" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>158</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="5"/>
@@ -3355,15 +3454,15 @@
     </row>
     <row r="59" spans="1:13" ht="13">
       <c r="A59" s="21"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="3" t="s">
-        <v>165</v>
+      <c r="B59" s="21"/>
+      <c r="C59" s="6" t="s">
+        <v>159</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="5"/>
@@ -3376,15 +3475,15 @@
     </row>
     <row r="60" spans="1:13" ht="13">
       <c r="A60" s="21"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="3" t="s">
-        <v>168</v>
+      <c r="B60" s="21"/>
+      <c r="C60" s="6" t="s">
+        <v>162</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="5"/>
@@ -3399,13 +3498,13 @@
       <c r="A61" s="21"/>
       <c r="B61" s="6"/>
       <c r="C61" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="5"/>
@@ -3420,13 +3519,13 @@
       <c r="A62" s="21"/>
       <c r="B62" s="6"/>
       <c r="C62" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="5"/>
@@ -3441,13 +3540,13 @@
       <c r="A63" s="21"/>
       <c r="B63" s="6"/>
       <c r="C63" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F63" s="4"/>
       <c r="G63" s="5"/>
@@ -3462,13 +3561,13 @@
       <c r="A64" s="21"/>
       <c r="B64" s="6"/>
       <c r="C64" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F64" s="4"/>
       <c r="G64" s="5"/>
@@ -3483,13 +3582,13 @@
       <c r="A65" s="21"/>
       <c r="B65" s="6"/>
       <c r="C65" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F65" s="4"/>
       <c r="G65" s="5"/>
@@ -3504,13 +3603,13 @@
       <c r="A66" s="21"/>
       <c r="B66" s="6"/>
       <c r="C66" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F66" s="4"/>
       <c r="G66" s="5"/>
@@ -3525,13 +3624,13 @@
       <c r="A67" s="21"/>
       <c r="B67" s="6"/>
       <c r="C67" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="5"/>
@@ -3546,13 +3645,13 @@
       <c r="A68" s="21"/>
       <c r="B68" s="6"/>
       <c r="C68" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="5"/>
@@ -3565,17 +3664,15 @@
     </row>
     <row r="69" spans="1:13" ht="13">
       <c r="A69" s="21"/>
-      <c r="B69" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>195</v>
+      <c r="B69" s="6"/>
+      <c r="C69" s="3" t="s">
+        <v>189</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="5"/>
@@ -3588,15 +3685,15 @@
     </row>
     <row r="70" spans="1:13" ht="13">
       <c r="A70" s="21"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="6" t="s">
-        <v>569</v>
+      <c r="B70" s="6"/>
+      <c r="C70" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>564</v>
+        <v>193</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>565</v>
+        <v>194</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="5"/>
@@ -3609,15 +3706,17 @@
     </row>
     <row r="71" spans="1:13" ht="13">
       <c r="A71" s="21"/>
-      <c r="B71" s="20"/>
+      <c r="B71" s="23" t="s">
+        <v>11</v>
+      </c>
       <c r="C71" s="6" t="s">
-        <v>568</v>
-      </c>
-      <c r="D71" s="19" t="s">
-        <v>567</v>
-      </c>
-      <c r="E71" s="19" t="s">
-        <v>566</v>
+        <v>195</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>197</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="5"/>
@@ -3630,15 +3729,15 @@
     </row>
     <row r="72" spans="1:13" ht="13">
       <c r="A72" s="21"/>
-      <c r="B72" s="20"/>
+      <c r="B72" s="23"/>
       <c r="C72" s="6" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="5"/>
@@ -3651,15 +3750,15 @@
     </row>
     <row r="73" spans="1:13" ht="13">
       <c r="A73" s="21"/>
-      <c r="B73" s="21"/>
+      <c r="B73" s="23"/>
       <c r="C73" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>200</v>
+        <v>566</v>
+      </c>
+      <c r="D73" s="19" t="s">
+        <v>565</v>
+      </c>
+      <c r="E73" s="19" t="s">
+        <v>564</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="5"/>
@@ -3672,17 +3771,15 @@
     </row>
     <row r="74" spans="1:13" ht="13">
       <c r="A74" s="21"/>
-      <c r="B74" s="20" t="s">
-        <v>201</v>
-      </c>
+      <c r="B74" s="23"/>
       <c r="C74" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="D74" s="10" t="s">
-        <v>203</v>
+        <v>554</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>555</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>204</v>
+        <v>556</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="5"/>
@@ -3695,15 +3792,15 @@
     </row>
     <row r="75" spans="1:13" ht="13">
       <c r="A75" s="21"/>
-      <c r="B75" s="21"/>
+      <c r="B75" s="23"/>
       <c r="C75" s="6" t="s">
-        <v>205</v>
+        <v>595</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>206</v>
+        <v>593</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>207</v>
+        <v>592</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="5"/>
@@ -3716,15 +3813,15 @@
     </row>
     <row r="76" spans="1:13" ht="13">
       <c r="A76" s="21"/>
-      <c r="B76" s="21"/>
+      <c r="B76" s="23"/>
       <c r="C76" s="6" t="s">
-        <v>208</v>
+        <v>596</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>209</v>
+        <v>36</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>209</v>
+        <v>594</v>
       </c>
       <c r="F76" s="4"/>
       <c r="G76" s="5"/>
@@ -3739,13 +3836,13 @@
       <c r="A77" s="21"/>
       <c r="B77" s="21"/>
       <c r="C77" s="6" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="5"/>
@@ -3758,15 +3855,17 @@
     </row>
     <row r="78" spans="1:13" ht="13">
       <c r="A78" s="21"/>
-      <c r="B78" s="21"/>
+      <c r="B78" s="23" t="s">
+        <v>201</v>
+      </c>
       <c r="C78" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>213</v>
+        <v>202</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="5"/>
@@ -3781,13 +3880,13 @@
       <c r="A79" s="21"/>
       <c r="B79" s="21"/>
       <c r="C79" s="6" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="F79" s="4"/>
       <c r="G79" s="5"/>
@@ -3802,13 +3901,13 @@
       <c r="A80" s="21"/>
       <c r="B80" s="21"/>
       <c r="C80" s="6" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>19</v>
+        <v>209</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="5"/>
@@ -3819,21 +3918,17 @@
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
     </row>
-    <row r="81" spans="1:13" ht="14">
-      <c r="A81" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="B81" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C81" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>220</v>
+    <row r="81" spans="1:13" ht="13">
+      <c r="A81" s="21"/>
+      <c r="B81" s="21"/>
+      <c r="C81" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>211</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="5"/>
@@ -3844,17 +3939,17 @@
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
     </row>
-    <row r="82" spans="1:13" ht="14">
+    <row r="82" spans="1:13" ht="13">
       <c r="A82" s="21"/>
       <c r="B82" s="21"/>
       <c r="C82" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="E82" s="11" t="s">
-        <v>222</v>
+        <v>212</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>213</v>
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="5"/>
@@ -3869,13 +3964,13 @@
       <c r="A83" s="21"/>
       <c r="B83" s="21"/>
       <c r="C83" s="6" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="5"/>
@@ -3890,13 +3985,13 @@
       <c r="A84" s="21"/>
       <c r="B84" s="21"/>
       <c r="C84" s="6" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="5"/>
@@ -3907,17 +4002,21 @@
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
     </row>
-    <row r="85" spans="1:13" ht="13">
-      <c r="A85" s="21"/>
-      <c r="B85" s="21"/>
-      <c r="C85" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>5</v>
+    <row r="85" spans="1:13" ht="14">
+      <c r="A85" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B85" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>220</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="5"/>
@@ -3928,17 +4027,17 @@
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
     </row>
-    <row r="86" spans="1:13" ht="13">
+    <row r="86" spans="1:13" ht="14">
       <c r="A86" s="21"/>
       <c r="B86" s="21"/>
       <c r="C86" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>232</v>
+        <v>221</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="E86" s="11" t="s">
+        <v>222</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="5"/>
@@ -3951,17 +4050,15 @@
     </row>
     <row r="87" spans="1:13" ht="13">
       <c r="A87" s="21"/>
-      <c r="B87" s="6" t="s">
-        <v>201</v>
-      </c>
+      <c r="B87" s="21"/>
       <c r="C87" s="6" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="5"/>
@@ -3974,17 +4071,15 @@
     </row>
     <row r="88" spans="1:13" ht="13">
       <c r="A88" s="21"/>
-      <c r="B88" s="6" t="s">
-        <v>112</v>
-      </c>
+      <c r="B88" s="21"/>
       <c r="C88" s="6" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>559</v>
+        <v>227</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>560</v>
+        <v>228</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="5"/>
@@ -3995,21 +4090,17 @@
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
     </row>
-    <row r="89" spans="1:13" ht="14">
-      <c r="A89" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="B89" s="20" t="s">
-        <v>201</v>
-      </c>
+    <row r="89" spans="1:13" ht="13">
+      <c r="A89" s="21"/>
+      <c r="B89" s="21"/>
       <c r="C89" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="E89" s="9" t="s">
-        <v>240</v>
+        <v>229</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F89" s="4"/>
       <c r="G89" s="5"/>
@@ -4020,17 +4111,17 @@
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
     </row>
-    <row r="90" spans="1:13" ht="14">
+    <row r="90" spans="1:13" ht="13">
       <c r="A90" s="21"/>
       <c r="B90" s="21"/>
       <c r="C90" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="E90" s="9" t="s">
-        <v>243</v>
+        <v>230</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>232</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="5"/>
@@ -4041,17 +4132,19 @@
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
     </row>
-    <row r="91" spans="1:13" ht="14">
+    <row r="91" spans="1:13" ht="13">
       <c r="A91" s="21"/>
-      <c r="B91" s="21"/>
+      <c r="B91" s="6" t="s">
+        <v>201</v>
+      </c>
       <c r="C91" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="E91" s="9" t="s">
-        <v>246</v>
+        <v>233</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="F91" s="4"/>
       <c r="G91" s="5"/>
@@ -4062,17 +4155,17 @@
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
     </row>
-    <row r="92" spans="1:13" ht="14">
+    <row r="92" spans="1:13" ht="13">
       <c r="A92" s="21"/>
-      <c r="B92" s="21"/>
+      <c r="B92" s="6"/>
       <c r="C92" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="D92" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="E92" s="9" t="s">
-        <v>249</v>
+        <v>585</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>584</v>
       </c>
       <c r="F92" s="4"/>
       <c r="G92" s="5"/>
@@ -4083,17 +4176,19 @@
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
     </row>
-    <row r="93" spans="1:13" ht="14">
+    <row r="93" spans="1:13" ht="13">
       <c r="A93" s="21"/>
-      <c r="B93" s="21"/>
+      <c r="B93" s="6" t="s">
+        <v>112</v>
+      </c>
       <c r="C93" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="E93" s="9" t="s">
-        <v>252</v>
+        <v>236</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>558</v>
       </c>
       <c r="F93" s="4"/>
       <c r="G93" s="5"/>
@@ -4105,16 +4200,20 @@
       <c r="M93" s="4"/>
     </row>
     <row r="94" spans="1:13" ht="14">
-      <c r="A94" s="21"/>
-      <c r="B94" s="21"/>
+      <c r="A94" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="B94" s="23" t="s">
+        <v>201</v>
+      </c>
       <c r="C94" s="6" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="F94" s="4"/>
       <c r="G94" s="5"/>
@@ -4129,13 +4228,13 @@
       <c r="A95" s="21"/>
       <c r="B95" s="21"/>
       <c r="C95" s="6" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="F95" s="4"/>
       <c r="G95" s="5"/>
@@ -4148,17 +4247,15 @@
     </row>
     <row r="96" spans="1:13" ht="14">
       <c r="A96" s="21"/>
-      <c r="B96" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C96" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>260</v>
+      <c r="B96" s="21"/>
+      <c r="C96" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>246</v>
       </c>
       <c r="F96" s="4"/>
       <c r="G96" s="5"/>
@@ -4171,17 +4268,15 @@
     </row>
     <row r="97" spans="1:13" ht="14">
       <c r="A97" s="21"/>
-      <c r="B97" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C97" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>263</v>
+      <c r="B97" s="21"/>
+      <c r="C97" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>249</v>
       </c>
       <c r="F97" s="4"/>
       <c r="G97" s="5"/>
@@ -4194,17 +4289,15 @@
     </row>
     <row r="98" spans="1:13" ht="14">
       <c r="A98" s="21"/>
-      <c r="B98" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C98" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>266</v>
+      <c r="B98" s="21"/>
+      <c r="C98" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E98" s="9" t="s">
+        <v>252</v>
       </c>
       <c r="F98" s="4"/>
       <c r="G98" s="5"/>
@@ -4218,39 +4311,35 @@
     <row r="99" spans="1:13" ht="14">
       <c r="A99" s="21"/>
       <c r="B99" s="21"/>
-      <c r="C99" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="F99" s="6"/>
-      <c r="G99" s="6"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="6"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="6"/>
-      <c r="L99" s="6"/>
-      <c r="M99" s="6"/>
-    </row>
-    <row r="100" spans="1:13" ht="13">
-      <c r="A100" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="B100" s="23" t="s">
-        <v>201</v>
-      </c>
+      <c r="C99" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="F99" s="4"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="4"/>
+      <c r="L99" s="4"/>
+      <c r="M99" s="4"/>
+    </row>
+    <row r="100" spans="1:13" ht="14">
+      <c r="A100" s="21"/>
+      <c r="B100" s="21"/>
       <c r="C100" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>272</v>
+        <v>255</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E100" s="9" t="s">
+        <v>257</v>
       </c>
       <c r="F100" s="4"/>
       <c r="G100" s="5"/>
@@ -4261,17 +4350,19 @@
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
     </row>
-    <row r="101" spans="1:13" ht="13">
+    <row r="101" spans="1:13" ht="14">
       <c r="A101" s="21"/>
-      <c r="B101" s="21"/>
-      <c r="C101" s="6" t="s">
-        <v>273</v>
+      <c r="B101" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>258</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="F101" s="4"/>
       <c r="G101" s="5"/>
@@ -4282,17 +4373,19 @@
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
     </row>
-    <row r="102" spans="1:13" ht="13">
+    <row r="102" spans="1:13" ht="14">
       <c r="A102" s="21"/>
-      <c r="B102" s="21"/>
-      <c r="C102" s="6" t="s">
-        <v>276</v>
+      <c r="B102" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>261</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="F102" s="4"/>
       <c r="G102" s="5"/>
@@ -4303,17 +4396,19 @@
       <c r="L102" s="4"/>
       <c r="M102" s="4"/>
     </row>
-    <row r="103" spans="1:13" ht="13">
+    <row r="103" spans="1:13" ht="14">
       <c r="A103" s="21"/>
-      <c r="B103" s="21"/>
-      <c r="C103" s="6" t="s">
-        <v>279</v>
+      <c r="B103" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>264</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="5"/>
@@ -4324,19 +4419,17 @@
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
     </row>
-    <row r="104" spans="1:13" ht="13">
+    <row r="104" spans="1:13" ht="14">
       <c r="A104" s="21"/>
-      <c r="B104" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>282</v>
+      <c r="B104" s="23"/>
+      <c r="C104" s="9" t="s">
+        <v>588</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>283</v>
+        <v>587</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>284</v>
+        <v>586</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="5"/>
@@ -4347,46 +4440,42 @@
       <c r="L104" s="4"/>
       <c r="M104" s="4"/>
     </row>
-    <row r="105" spans="1:13" ht="13">
-      <c r="A105" s="8" t="s">
+    <row r="105" spans="1:13" ht="14">
+      <c r="A105" s="21"/>
+      <c r="B105" s="21"/>
+      <c r="C105" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F105" s="6"/>
+      <c r="G105" s="6"/>
+      <c r="H105" s="6"/>
+      <c r="I105" s="6"/>
+      <c r="J105" s="6"/>
+      <c r="K105" s="6"/>
+      <c r="L105" s="6"/>
+      <c r="M105" s="6"/>
+    </row>
+    <row r="106" spans="1:13" ht="13">
+      <c r="A106" s="23" t="s">
         <v>270</v>
       </c>
-      <c r="B105" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="F105" s="4"/>
-      <c r="G105" s="5"/>
-      <c r="H105" s="4"/>
-      <c r="I105" s="4"/>
-      <c r="J105" s="4"/>
-      <c r="K105" s="4"/>
-      <c r="L105" s="4"/>
-      <c r="M105" s="4"/>
-    </row>
-    <row r="106" spans="1:13" ht="13">
-      <c r="A106" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>112</v>
+      <c r="B106" s="24" t="s">
+        <v>201</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="F106" s="4"/>
       <c r="G106" s="5"/>
@@ -4397,157 +4486,143 @@
       <c r="L106" s="4"/>
       <c r="M106" s="4"/>
     </row>
-    <row r="107" spans="1:13" ht="14">
-      <c r="A107" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>112</v>
-      </c>
+    <row r="107" spans="1:13" ht="13">
+      <c r="A107" s="21"/>
+      <c r="B107" s="21"/>
       <c r="C107" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>292</v>
+        <v>273</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="F107" s="6"/>
-      <c r="G107" s="6"/>
-      <c r="H107" s="6"/>
-      <c r="I107" s="6"/>
-      <c r="J107" s="6"/>
-      <c r="K107" s="6"/>
-      <c r="L107" s="6"/>
-      <c r="M107" s="6"/>
-    </row>
-    <row r="108" spans="1:13" ht="14">
-      <c r="A108" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>112</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="F107" s="4"/>
+      <c r="G107" s="5"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+    </row>
+    <row r="108" spans="1:13" ht="13">
+      <c r="A108" s="21"/>
+      <c r="B108" s="21"/>
       <c r="C108" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="D108" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="E108" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="F108" s="6"/>
-      <c r="G108" s="6"/>
-      <c r="H108" s="6"/>
-      <c r="I108" s="6"/>
-      <c r="J108" s="6"/>
-      <c r="K108" s="6"/>
-      <c r="L108" s="6"/>
-      <c r="M108" s="6"/>
-    </row>
-    <row r="109" spans="1:13" ht="14">
-      <c r="A109" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>112</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F108" s="4"/>
+      <c r="G108" s="5"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="4"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
+    </row>
+    <row r="109" spans="1:13" ht="13">
+      <c r="A109" s="21"/>
+      <c r="B109" s="21"/>
       <c r="C109" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="D109" s="9" t="s">
-        <v>298</v>
+        <v>279</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>280</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="F109" s="6"/>
-      <c r="G109" s="6"/>
-      <c r="H109" s="6"/>
-      <c r="I109" s="6"/>
-      <c r="J109" s="6"/>
-      <c r="K109" s="6"/>
-      <c r="L109" s="6"/>
-      <c r="M109" s="6"/>
+        <v>281</v>
+      </c>
+      <c r="F109" s="4"/>
+      <c r="G109" s="5"/>
+      <c r="H109" s="4"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
+      <c r="K109" s="4"/>
+      <c r="L109" s="4"/>
+      <c r="M109" s="4"/>
     </row>
     <row r="110" spans="1:13" ht="13">
-      <c r="A110" s="6" t="s">
-        <v>290</v>
-      </c>
+      <c r="A110" s="21"/>
       <c r="B110" s="6" t="s">
         <v>112</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="F110" s="6"/>
-      <c r="G110" s="6"/>
-      <c r="H110" s="6"/>
-      <c r="I110" s="6"/>
-      <c r="J110" s="6"/>
-      <c r="K110" s="6"/>
-      <c r="L110" s="6"/>
-      <c r="M110" s="6"/>
-    </row>
-    <row r="111" spans="1:13" ht="14">
-      <c r="A111" s="6" t="s">
-        <v>290</v>
+        <v>284</v>
+      </c>
+      <c r="F110" s="4"/>
+      <c r="G110" s="5"/>
+      <c r="H110" s="4"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4"/>
+      <c r="L110" s="4"/>
+      <c r="M110" s="4"/>
+    </row>
+    <row r="111" spans="1:13" ht="13">
+      <c r="A111" s="8" t="s">
+        <v>270</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>11</v>
+        <v>112</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="D111" s="9" t="s">
-        <v>304</v>
+        <v>285</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>286</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="F111" s="6"/>
-      <c r="G111" s="6"/>
-      <c r="H111" s="6"/>
-      <c r="I111" s="6"/>
-      <c r="J111" s="6"/>
-      <c r="K111" s="6"/>
-      <c r="L111" s="6"/>
-      <c r="M111" s="6"/>
+        <v>286</v>
+      </c>
+      <c r="F111" s="4"/>
+      <c r="G111" s="5"/>
+      <c r="H111" s="4"/>
+      <c r="I111" s="4"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="4"/>
+      <c r="L111" s="4"/>
+      <c r="M111" s="4"/>
     </row>
     <row r="112" spans="1:13" ht="13">
-      <c r="A112" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="B112" s="8" t="s">
-        <v>201</v>
+      <c r="A112" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="F112" s="6"/>
-      <c r="G112" s="6"/>
-      <c r="H112" s="6"/>
-      <c r="I112" s="6"/>
-      <c r="J112" s="6"/>
-      <c r="K112" s="6"/>
-      <c r="L112" s="6"/>
-      <c r="M112" s="6"/>
-    </row>
-    <row r="113" spans="1:13" ht="13">
+        <v>289</v>
+      </c>
+      <c r="F112" s="4"/>
+      <c r="G112" s="5"/>
+      <c r="H112" s="4"/>
+      <c r="I112" s="4"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="4"/>
+      <c r="L112" s="4"/>
+      <c r="M112" s="4"/>
+    </row>
+    <row r="113" spans="1:13" ht="14">
       <c r="A113" s="6" t="s">
         <v>290</v>
       </c>
@@ -4555,13 +4630,13 @@
         <v>112</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>309</v>
+        <v>291</v>
+      </c>
+      <c r="D113" s="9" t="s">
+        <v>292</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="F113" s="6"/>
       <c r="G113" s="6"/>
@@ -4572,7 +4647,7 @@
       <c r="L113" s="6"/>
       <c r="M113" s="6"/>
     </row>
-    <row r="114" spans="1:13" ht="13">
+    <row r="114" spans="1:13" ht="14">
       <c r="A114" s="6" t="s">
         <v>290</v>
       </c>
@@ -4580,13 +4655,13 @@
         <v>112</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>313</v>
+        <v>294</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="E114" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
@@ -4597,7 +4672,7 @@
       <c r="L114" s="6"/>
       <c r="M114" s="6"/>
     </row>
-    <row r="115" spans="1:13" ht="13">
+    <row r="115" spans="1:13" ht="14">
       <c r="A115" s="6" t="s">
         <v>290</v>
       </c>
@@ -4605,13 +4680,13 @@
         <v>112</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>315</v>
+        <v>297</v>
+      </c>
+      <c r="D115" s="9" t="s">
+        <v>298</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="F115" s="6"/>
       <c r="G115" s="6"/>
@@ -4623,20 +4698,20 @@
       <c r="M115" s="6"/>
     </row>
     <row r="116" spans="1:13" ht="13">
-      <c r="A116" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="B116" s="20" t="s">
-        <v>201</v>
+      <c r="A116" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="F116" s="6"/>
       <c r="G116" s="6"/>
@@ -4647,17 +4722,21 @@
       <c r="L116" s="6"/>
       <c r="M116" s="6"/>
     </row>
-    <row r="117" spans="1:13" ht="13">
-      <c r="A117" s="21"/>
-      <c r="B117" s="21"/>
+    <row r="117" spans="1:13" ht="14">
+      <c r="A117" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="C117" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>322</v>
+        <v>303</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>304</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
@@ -4669,18 +4748,20 @@
       <c r="M117" s="6"/>
     </row>
     <row r="118" spans="1:13" ht="13">
-      <c r="A118" s="21"/>
+      <c r="A118" s="6" t="s">
+        <v>290</v>
+      </c>
       <c r="B118" s="8" t="s">
         <v>201</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="F118" s="6"/>
       <c r="G118" s="6"/>
@@ -4692,18 +4773,20 @@
       <c r="M118" s="6"/>
     </row>
     <row r="119" spans="1:13" ht="13">
-      <c r="A119" s="21"/>
-      <c r="B119" s="8" t="s">
-        <v>201</v>
+      <c r="A119" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="F119" s="6"/>
       <c r="G119" s="6"/>
@@ -4715,18 +4798,20 @@
       <c r="M119" s="6"/>
     </row>
     <row r="120" spans="1:13" ht="13">
-      <c r="A120" s="21"/>
-      <c r="B120" s="20" t="s">
+      <c r="A120" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B120" s="6" t="s">
         <v>112</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="F120" s="6"/>
       <c r="G120" s="6"/>
@@ -4737,17 +4822,21 @@
       <c r="L120" s="6"/>
       <c r="M120" s="6"/>
     </row>
-    <row r="121" spans="1:13" ht="28">
-      <c r="A121" s="21"/>
-      <c r="B121" s="21"/>
+    <row r="121" spans="1:13" ht="13">
+      <c r="A121" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>112</v>
+      </c>
       <c r="C121" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="D121" s="12" t="s">
-        <v>334</v>
-      </c>
-      <c r="E121" s="12" t="s">
-        <v>335</v>
+        <v>314</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>316</v>
       </c>
       <c r="F121" s="6"/>
       <c r="G121" s="6"/>
@@ -4758,17 +4847,17 @@
       <c r="L121" s="6"/>
       <c r="M121" s="6"/>
     </row>
-    <row r="122" spans="1:13" ht="14">
-      <c r="A122" s="21"/>
-      <c r="B122" s="21"/>
+    <row r="122" spans="1:13" ht="13">
+      <c r="A122" s="6"/>
+      <c r="B122" s="6"/>
       <c r="C122" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="D122" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="E122" s="12" t="s">
-        <v>337</v>
+        <v>589</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>590</v>
       </c>
       <c r="F122" s="6"/>
       <c r="G122" s="6"/>
@@ -4779,17 +4868,21 @@
       <c r="L122" s="6"/>
       <c r="M122" s="6"/>
     </row>
-    <row r="123" spans="1:13" ht="14">
-      <c r="A123" s="21"/>
-      <c r="B123" s="21"/>
+    <row r="123" spans="1:13" ht="13">
+      <c r="A123" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="B123" s="23" t="s">
+        <v>201</v>
+      </c>
       <c r="C123" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="D123" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="E123" s="12" t="s">
-        <v>340</v>
+        <v>318</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>320</v>
       </c>
       <c r="F123" s="6"/>
       <c r="G123" s="6"/>
@@ -4800,185 +4893,191 @@
       <c r="L123" s="6"/>
       <c r="M123" s="6"/>
     </row>
-    <row r="124" spans="1:13" ht="28">
+    <row r="124" spans="1:13" ht="13">
       <c r="A124" s="21"/>
       <c r="B124" s="21"/>
       <c r="C124" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="D124" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="E124" s="11" t="s">
-        <v>343</v>
+        <v>321</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>323</v>
       </c>
       <c r="F124" s="6"/>
-      <c r="G124" s="8"/>
-      <c r="H124" s="12"/>
-      <c r="I124" s="12"/>
-      <c r="J124" s="8"/>
-      <c r="K124" s="8"/>
-      <c r="L124" s="8"/>
+      <c r="G124" s="6"/>
+      <c r="H124" s="6"/>
+      <c r="I124" s="6"/>
+      <c r="J124" s="6"/>
+      <c r="K124" s="6"/>
+      <c r="L124" s="6"/>
       <c r="M124" s="6"/>
     </row>
-    <row r="125" spans="1:13" ht="14">
+    <row r="125" spans="1:13" ht="13">
       <c r="A125" s="21"/>
-      <c r="B125" s="21"/>
+      <c r="B125" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="C125" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="D125" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="E125" s="11" t="s">
-        <v>346</v>
+        <v>324</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="F125" s="6"/>
-      <c r="G125" s="13"/>
-      <c r="H125" s="8"/>
-      <c r="I125" s="12"/>
-      <c r="J125" s="12"/>
-      <c r="K125" s="8"/>
-      <c r="L125" s="8"/>
-      <c r="M125" s="8"/>
-    </row>
-    <row r="126" spans="1:13" ht="42">
+      <c r="G125" s="6"/>
+      <c r="H125" s="6"/>
+      <c r="I125" s="6"/>
+      <c r="J125" s="6"/>
+      <c r="K125" s="6"/>
+      <c r="L125" s="6"/>
+      <c r="M125" s="6"/>
+    </row>
+    <row r="126" spans="1:13" ht="13">
       <c r="A126" s="21"/>
-      <c r="B126" s="21"/>
+      <c r="B126" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="C126" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="D126" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="E126" s="11" t="s">
-        <v>349</v>
+        <v>327</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>329</v>
       </c>
       <c r="F126" s="6"/>
-      <c r="G126" s="13"/>
-      <c r="H126" s="8"/>
-      <c r="I126" s="12"/>
-      <c r="J126" s="12"/>
-      <c r="K126" s="8"/>
-      <c r="L126" s="8"/>
-      <c r="M126" s="8"/>
-    </row>
-    <row r="127" spans="1:13" ht="14">
+      <c r="G126" s="6"/>
+      <c r="H126" s="6"/>
+      <c r="I126" s="6"/>
+      <c r="J126" s="6"/>
+      <c r="K126" s="6"/>
+      <c r="L126" s="6"/>
+      <c r="M126" s="6"/>
+    </row>
+    <row r="127" spans="1:13" ht="13">
       <c r="A127" s="21"/>
-      <c r="B127" s="21"/>
+      <c r="B127" s="23" t="s">
+        <v>112</v>
+      </c>
       <c r="C127" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="D127" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E127" s="11" t="s">
-        <v>351</v>
+        <v>330</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>332</v>
       </c>
       <c r="F127" s="6"/>
-      <c r="G127" s="13"/>
-      <c r="H127" s="8"/>
-      <c r="I127" s="12"/>
-      <c r="J127" s="12"/>
-      <c r="K127" s="8"/>
-      <c r="L127" s="8"/>
-      <c r="M127" s="8"/>
+      <c r="G127" s="6"/>
+      <c r="H127" s="6"/>
+      <c r="I127" s="6"/>
+      <c r="J127" s="6"/>
+      <c r="K127" s="6"/>
+      <c r="L127" s="6"/>
+      <c r="M127" s="6"/>
     </row>
     <row r="128" spans="1:13" ht="28">
       <c r="A128" s="21"/>
       <c r="B128" s="21"/>
       <c r="C128" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="D128" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="E128" s="11" t="s">
-        <v>354</v>
+        <v>333</v>
+      </c>
+      <c r="D128" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="E128" s="12" t="s">
+        <v>335</v>
       </c>
       <c r="F128" s="6"/>
-      <c r="G128" s="13"/>
-      <c r="H128" s="8"/>
-      <c r="I128" s="12"/>
-      <c r="J128" s="12"/>
-      <c r="K128" s="8"/>
-      <c r="L128" s="8"/>
-      <c r="M128" s="8"/>
-    </row>
-    <row r="129" spans="1:13" ht="13">
+      <c r="G128" s="6"/>
+      <c r="H128" s="6"/>
+      <c r="I128" s="6"/>
+      <c r="J128" s="6"/>
+      <c r="K128" s="6"/>
+      <c r="L128" s="6"/>
+      <c r="M128" s="6"/>
+    </row>
+    <row r="129" spans="1:13" ht="14">
       <c r="A129" s="21"/>
       <c r="B129" s="21"/>
       <c r="C129" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="D129" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="E129" s="6" t="s">
-        <v>356</v>
+        <v>336</v>
+      </c>
+      <c r="D129" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="E129" s="12" t="s">
+        <v>337</v>
       </c>
       <c r="F129" s="6"/>
-      <c r="G129" s="13"/>
-      <c r="H129" s="8"/>
-      <c r="I129" s="12"/>
-      <c r="J129" s="12"/>
-      <c r="K129" s="8"/>
-      <c r="L129" s="8"/>
-      <c r="M129" s="8"/>
-    </row>
-    <row r="130" spans="1:13" ht="13">
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="6"/>
+      <c r="K129" s="6"/>
+      <c r="L129" s="6"/>
+      <c r="M129" s="6"/>
+    </row>
+    <row r="130" spans="1:13" ht="14">
       <c r="A130" s="21"/>
       <c r="B130" s="21"/>
       <c r="C130" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="D130" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E130" s="6" t="s">
-        <v>359</v>
+        <v>338</v>
+      </c>
+      <c r="D130" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="E130" s="12" t="s">
+        <v>340</v>
       </c>
       <c r="F130" s="6"/>
-      <c r="G130" s="13"/>
-      <c r="H130" s="8"/>
-      <c r="I130" s="12"/>
-      <c r="J130" s="12"/>
-      <c r="K130" s="8"/>
-      <c r="L130" s="8"/>
-      <c r="M130" s="8"/>
-    </row>
-    <row r="131" spans="1:13" ht="13">
+      <c r="G130" s="6"/>
+      <c r="H130" s="6"/>
+      <c r="I130" s="6"/>
+      <c r="J130" s="6"/>
+      <c r="K130" s="6"/>
+      <c r="L130" s="6"/>
+      <c r="M130" s="6"/>
+    </row>
+    <row r="131" spans="1:13" ht="28">
       <c r="A131" s="21"/>
       <c r="B131" s="21"/>
       <c r="C131" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="E131" s="3" t="s">
-        <v>362</v>
+        <v>341</v>
+      </c>
+      <c r="D131" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="E131" s="11" t="s">
+        <v>343</v>
       </c>
       <c r="F131" s="6"/>
-      <c r="G131" s="13"/>
-      <c r="H131" s="8"/>
+      <c r="G131" s="8"/>
+      <c r="H131" s="12"/>
       <c r="I131" s="12"/>
-      <c r="J131" s="12"/>
+      <c r="J131" s="8"/>
       <c r="K131" s="8"/>
       <c r="L131" s="8"/>
-      <c r="M131" s="8"/>
+      <c r="M131" s="6"/>
     </row>
     <row r="132" spans="1:13" ht="14">
       <c r="A132" s="21"/>
-      <c r="B132" s="6"/>
+      <c r="B132" s="21"/>
       <c r="C132" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="D132" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="E132" s="14" t="s">
-        <v>364</v>
+        <v>344</v>
+      </c>
+      <c r="D132" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="E132" s="11" t="s">
+        <v>346</v>
       </c>
       <c r="F132" s="6"/>
       <c r="G132" s="13"/>
@@ -4989,19 +5088,17 @@
       <c r="L132" s="8"/>
       <c r="M132" s="8"/>
     </row>
-    <row r="133" spans="1:13" ht="14">
+    <row r="133" spans="1:13" ht="42">
       <c r="A133" s="21"/>
-      <c r="B133" s="20" t="s">
-        <v>11</v>
-      </c>
+      <c r="B133" s="21"/>
       <c r="C133" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="D133" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="E133" s="9" t="s">
-        <v>367</v>
+        <v>347</v>
+      </c>
+      <c r="D133" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="E133" s="11" t="s">
+        <v>349</v>
       </c>
       <c r="F133" s="6"/>
       <c r="G133" s="13"/>
@@ -5016,13 +5113,13 @@
       <c r="A134" s="21"/>
       <c r="B134" s="21"/>
       <c r="C134" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="D134" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="E134" s="9" t="s">
-        <v>370</v>
+        <v>350</v>
+      </c>
+      <c r="D134" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E134" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="F134" s="6"/>
       <c r="G134" s="13"/>
@@ -5033,21 +5130,17 @@
       <c r="L134" s="8"/>
       <c r="M134" s="8"/>
     </row>
-    <row r="135" spans="1:13" ht="14">
-      <c r="A135" s="22" t="s">
-        <v>371</v>
-      </c>
-      <c r="B135" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="D135" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="E135" s="9" t="s">
-        <v>374</v>
+    <row r="135" spans="1:13" ht="28">
+      <c r="A135" s="21"/>
+      <c r="B135" s="21"/>
+      <c r="C135" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="D135" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="E135" s="11" t="s">
+        <v>354</v>
       </c>
       <c r="F135" s="6"/>
       <c r="G135" s="13"/>
@@ -5058,193 +5151,197 @@
       <c r="L135" s="8"/>
       <c r="M135" s="8"/>
     </row>
-    <row r="136" spans="1:13" ht="14">
+    <row r="136" spans="1:13" ht="13">
       <c r="A136" s="21"/>
       <c r="B136" s="21"/>
-      <c r="C136" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="D136" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="E136" s="9" t="s">
-        <v>377</v>
+      <c r="C136" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>356</v>
       </c>
       <c r="F136" s="6"/>
       <c r="G136" s="13"/>
       <c r="H136" s="8"/>
       <c r="I136" s="12"/>
       <c r="J136" s="12"/>
-      <c r="K136" s="6"/>
-      <c r="L136" s="6"/>
-      <c r="M136" s="6"/>
-    </row>
-    <row r="137" spans="1:13" ht="14">
+      <c r="K136" s="8"/>
+      <c r="L136" s="8"/>
+      <c r="M136" s="8"/>
+    </row>
+    <row r="137" spans="1:13" ht="13">
       <c r="A137" s="21"/>
       <c r="B137" s="21"/>
-      <c r="C137" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="D137" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="E137" s="3" t="s">
-        <v>380</v>
+      <c r="C137" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>359</v>
       </c>
       <c r="F137" s="6"/>
-      <c r="G137" s="15"/>
-      <c r="H137" s="6"/>
-      <c r="I137" s="6"/>
-      <c r="J137" s="6"/>
-      <c r="K137" s="6"/>
-      <c r="L137" s="6"/>
-      <c r="M137" s="6"/>
+      <c r="G137" s="13"/>
+      <c r="H137" s="8"/>
+      <c r="I137" s="12"/>
+      <c r="J137" s="12"/>
+      <c r="K137" s="8"/>
+      <c r="L137" s="8"/>
+      <c r="M137" s="8"/>
     </row>
     <row r="138" spans="1:13" ht="13">
       <c r="A138" s="21"/>
       <c r="B138" s="21"/>
       <c r="C138" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="D138" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="E138" s="3" t="s">
-        <v>383</v>
+        <v>582</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>580</v>
       </c>
       <c r="F138" s="6"/>
-      <c r="G138" s="6"/>
-      <c r="H138" s="6"/>
-      <c r="I138" s="6"/>
-      <c r="J138" s="6"/>
-      <c r="K138" s="6"/>
-      <c r="L138" s="6"/>
-      <c r="M138" s="6"/>
-    </row>
-    <row r="139" spans="1:13" ht="14">
+      <c r="G138" s="13"/>
+      <c r="H138" s="8"/>
+      <c r="I138" s="12"/>
+      <c r="J138" s="12"/>
+      <c r="K138" s="8"/>
+      <c r="L138" s="8"/>
+      <c r="M138" s="8"/>
+    </row>
+    <row r="139" spans="1:13" ht="13">
       <c r="A139" s="21"/>
       <c r="B139" s="21"/>
-      <c r="C139" s="2" t="s">
-        <v>384</v>
+      <c r="C139" s="6" t="s">
+        <v>360</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="F139" s="6"/>
-      <c r="G139" s="6"/>
-      <c r="H139" s="6"/>
-      <c r="I139" s="6"/>
-      <c r="J139" s="6"/>
-      <c r="K139" s="6"/>
-      <c r="L139" s="6"/>
-      <c r="M139" s="6"/>
+      <c r="G139" s="13"/>
+      <c r="H139" s="8"/>
+      <c r="I139" s="12"/>
+      <c r="J139" s="12"/>
+      <c r="K139" s="8"/>
+      <c r="L139" s="8"/>
+      <c r="M139" s="8"/>
     </row>
     <row r="140" spans="1:13" ht="14">
       <c r="A140" s="21"/>
-      <c r="B140" s="21"/>
-      <c r="C140" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="D140" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E140" s="3" t="s">
-        <v>389</v>
+      <c r="B140" s="6"/>
+      <c r="C140" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="D140" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="E140" s="14" t="s">
+        <v>364</v>
       </c>
       <c r="F140" s="6"/>
-      <c r="G140" s="6"/>
-      <c r="H140" s="6"/>
-      <c r="I140" s="6"/>
-      <c r="J140" s="6"/>
-      <c r="K140" s="6"/>
-      <c r="L140" s="6"/>
-      <c r="M140" s="6"/>
+      <c r="G140" s="13"/>
+      <c r="H140" s="8"/>
+      <c r="I140" s="12"/>
+      <c r="J140" s="12"/>
+      <c r="K140" s="8"/>
+      <c r="L140" s="8"/>
+      <c r="M140" s="8"/>
     </row>
     <row r="141" spans="1:13" ht="14">
       <c r="A141" s="21"/>
-      <c r="B141" s="21"/>
-      <c r="C141" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="D141" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="E141" s="3" t="s">
-        <v>392</v>
+      <c r="B141" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="D141" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="E141" s="9" t="s">
+        <v>367</v>
       </c>
       <c r="F141" s="6"/>
-      <c r="G141" s="6"/>
-      <c r="H141" s="6"/>
-      <c r="I141" s="6"/>
-      <c r="J141" s="6"/>
-      <c r="K141" s="6"/>
-      <c r="L141" s="6"/>
-      <c r="M141" s="6"/>
+      <c r="G141" s="13"/>
+      <c r="H141" s="8"/>
+      <c r="I141" s="12"/>
+      <c r="J141" s="12"/>
+      <c r="K141" s="8"/>
+      <c r="L141" s="8"/>
+      <c r="M141" s="8"/>
     </row>
     <row r="142" spans="1:13" ht="14">
       <c r="A142" s="21"/>
       <c r="B142" s="21"/>
-      <c r="C142" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="D142" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="E142" s="3" t="s">
-        <v>395</v>
+      <c r="C142" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D142" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="E142" s="9" t="s">
+        <v>370</v>
       </c>
       <c r="F142" s="6"/>
-      <c r="G142" s="6"/>
-      <c r="H142" s="6"/>
-      <c r="I142" s="6"/>
-      <c r="J142" s="6"/>
-      <c r="K142" s="6"/>
-      <c r="L142" s="6"/>
-      <c r="M142" s="6"/>
+      <c r="G142" s="13"/>
+      <c r="H142" s="8"/>
+      <c r="I142" s="12"/>
+      <c r="J142" s="12"/>
+      <c r="K142" s="8"/>
+      <c r="L142" s="8"/>
+      <c r="M142" s="8"/>
     </row>
     <row r="143" spans="1:13" ht="14">
-      <c r="A143" s="21"/>
-      <c r="B143" s="21"/>
+      <c r="A143" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="B143" s="22" t="s">
+        <v>201</v>
+      </c>
       <c r="C143" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="D143" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="E143" s="3" t="s">
-        <v>398</v>
+        <v>372</v>
+      </c>
+      <c r="D143" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="E143" s="9" t="s">
+        <v>374</v>
       </c>
       <c r="F143" s="6"/>
-      <c r="G143" s="6"/>
-      <c r="H143" s="6"/>
-      <c r="I143" s="6"/>
-      <c r="J143" s="6"/>
-      <c r="K143" s="6"/>
-      <c r="L143" s="6"/>
-      <c r="M143" s="6"/>
+      <c r="G143" s="13"/>
+      <c r="H143" s="8"/>
+      <c r="I143" s="12"/>
+      <c r="J143" s="12"/>
+      <c r="K143" s="8"/>
+      <c r="L143" s="8"/>
+      <c r="M143" s="8"/>
     </row>
     <row r="144" spans="1:13" ht="14">
       <c r="A144" s="21"/>
-      <c r="B144" s="22" t="s">
-        <v>11</v>
-      </c>
+      <c r="B144" s="21"/>
       <c r="C144" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="D144" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="E144" s="3" t="s">
-        <v>401</v>
+        <v>375</v>
+      </c>
+      <c r="D144" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="E144" s="9" t="s">
+        <v>377</v>
       </c>
       <c r="F144" s="6"/>
-      <c r="G144" s="6"/>
-      <c r="H144" s="6"/>
-      <c r="I144" s="6"/>
-      <c r="J144" s="6"/>
+      <c r="G144" s="13"/>
+      <c r="H144" s="8"/>
+      <c r="I144" s="12"/>
+      <c r="J144" s="12"/>
       <c r="K144" s="6"/>
       <c r="L144" s="6"/>
       <c r="M144" s="6"/>
@@ -5253,16 +5350,16 @@
       <c r="A145" s="21"/>
       <c r="B145" s="21"/>
       <c r="C145" s="2" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="F145" s="6"/>
-      <c r="G145" s="6"/>
+      <c r="G145" s="15"/>
       <c r="H145" s="6"/>
       <c r="I145" s="6"/>
       <c r="J145" s="6"/>
@@ -5270,17 +5367,17 @@
       <c r="L145" s="6"/>
       <c r="M145" s="6"/>
     </row>
-    <row r="146" spans="1:13" ht="14">
+    <row r="146" spans="1:13" ht="13">
       <c r="A146" s="21"/>
       <c r="B146" s="21"/>
-      <c r="C146" s="16" t="s">
-        <v>405</v>
+      <c r="C146" s="6" t="s">
+        <v>381</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>406</v>
+        <v>382</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="F146" s="6"/>
       <c r="G146" s="6"/>
@@ -5295,13 +5392,13 @@
       <c r="A147" s="21"/>
       <c r="B147" s="21"/>
       <c r="C147" s="2" t="s">
-        <v>408</v>
+        <v>384</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>409</v>
+        <v>385</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="F147" s="6"/>
       <c r="G147" s="6"/>
@@ -5314,17 +5411,15 @@
     </row>
     <row r="148" spans="1:13" ht="14">
       <c r="A148" s="21"/>
-      <c r="B148" s="22" t="s">
-        <v>112</v>
-      </c>
+      <c r="B148" s="21"/>
       <c r="C148" s="2" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="F148" s="6"/>
       <c r="G148" s="6"/>
@@ -5335,17 +5430,17 @@
       <c r="L148" s="6"/>
       <c r="M148" s="6"/>
     </row>
-    <row r="149" spans="1:13" ht="28">
+    <row r="149" spans="1:13" ht="14">
       <c r="A149" s="21"/>
       <c r="B149" s="21"/>
       <c r="C149" s="2" t="s">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="E149" s="9" t="s">
-        <v>416</v>
+        <v>391</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>392</v>
       </c>
       <c r="F149" s="6"/>
       <c r="G149" s="6"/>
@@ -5360,13 +5455,13 @@
       <c r="A150" s="21"/>
       <c r="B150" s="21"/>
       <c r="C150" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D150" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="E150" s="9" t="s">
-        <v>419</v>
+        <v>393</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>395</v>
       </c>
       <c r="F150" s="6"/>
       <c r="G150" s="6"/>
@@ -5381,13 +5476,13 @@
       <c r="A151" s="21"/>
       <c r="B151" s="21"/>
       <c r="C151" s="2" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="E151" s="9" t="s">
-        <v>422</v>
+        <v>397</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>398</v>
       </c>
       <c r="F151" s="6"/>
       <c r="G151" s="6"/>
@@ -5400,15 +5495,17 @@
     </row>
     <row r="152" spans="1:13" ht="14">
       <c r="A152" s="21"/>
-      <c r="B152" s="21"/>
+      <c r="B152" s="22" t="s">
+        <v>11</v>
+      </c>
       <c r="C152" s="2" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="F152" s="6"/>
       <c r="G152" s="6"/>
@@ -5423,13 +5520,13 @@
       <c r="A153" s="21"/>
       <c r="B153" s="21"/>
       <c r="C153" s="2" t="s">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>427</v>
+        <v>403</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="F153" s="6"/>
       <c r="G153" s="6"/>
@@ -5443,14 +5540,14 @@
     <row r="154" spans="1:13" ht="14">
       <c r="A154" s="21"/>
       <c r="B154" s="21"/>
-      <c r="C154" s="2" t="s">
-        <v>429</v>
+      <c r="C154" s="16" t="s">
+        <v>405</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="F154" s="6"/>
       <c r="G154" s="6"/>
@@ -5465,13 +5562,13 @@
       <c r="A155" s="21"/>
       <c r="B155" s="21"/>
       <c r="C155" s="2" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="F155" s="6"/>
       <c r="G155" s="6"/>
@@ -5482,17 +5579,19 @@
       <c r="L155" s="6"/>
       <c r="M155" s="6"/>
     </row>
-    <row r="156" spans="1:13" ht="28">
+    <row r="156" spans="1:13" ht="14">
       <c r="A156" s="21"/>
-      <c r="B156" s="21"/>
+      <c r="B156" s="22" t="s">
+        <v>112</v>
+      </c>
       <c r="C156" s="2" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="E156" s="9" t="s">
-        <v>437</v>
+        <v>412</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>413</v>
       </c>
       <c r="F156" s="6"/>
       <c r="G156" s="6"/>
@@ -5503,17 +5602,17 @@
       <c r="L156" s="6"/>
       <c r="M156" s="6"/>
     </row>
-    <row r="157" spans="1:13" ht="14">
+    <row r="157" spans="1:13" ht="28">
       <c r="A157" s="21"/>
       <c r="B157" s="21"/>
       <c r="C157" s="2" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="E157" s="3" t="s">
-        <v>440</v>
+        <v>415</v>
+      </c>
+      <c r="E157" s="9" t="s">
+        <v>416</v>
       </c>
       <c r="F157" s="6"/>
       <c r="G157" s="6"/>
@@ -5524,17 +5623,17 @@
       <c r="L157" s="6"/>
       <c r="M157" s="6"/>
     </row>
-    <row r="158" spans="1:13" ht="28">
+    <row r="158" spans="1:13" ht="14">
       <c r="A158" s="21"/>
       <c r="B158" s="21"/>
       <c r="C158" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="D158" s="3" t="s">
-        <v>442</v>
+        <v>417</v>
+      </c>
+      <c r="D158" s="8" t="s">
+        <v>418</v>
       </c>
       <c r="E158" s="9" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="F158" s="6"/>
       <c r="G158" s="6"/>
@@ -5545,17 +5644,17 @@
       <c r="L158" s="6"/>
       <c r="M158" s="6"/>
     </row>
-    <row r="159" spans="1:13" ht="28">
+    <row r="159" spans="1:13" ht="14">
       <c r="A159" s="21"/>
       <c r="B159" s="21"/>
       <c r="C159" s="2" t="s">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="F159" s="6"/>
       <c r="G159" s="6"/>
@@ -5566,17 +5665,17 @@
       <c r="L159" s="6"/>
       <c r="M159" s="6"/>
     </row>
-    <row r="160" spans="1:13" ht="13">
+    <row r="160" spans="1:13" ht="14">
       <c r="A160" s="21"/>
       <c r="B160" s="21"/>
-      <c r="C160" s="6" t="s">
-        <v>447</v>
+      <c r="C160" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="E160" s="17" t="s">
-        <v>449</v>
+        <v>424</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>425</v>
       </c>
       <c r="F160" s="6"/>
       <c r="G160" s="6"/>
@@ -5587,17 +5686,17 @@
       <c r="L160" s="6"/>
       <c r="M160" s="6"/>
     </row>
-    <row r="161" spans="1:13" ht="13">
+    <row r="161" spans="1:13" ht="14">
       <c r="A161" s="21"/>
       <c r="B161" s="21"/>
-      <c r="C161" s="8" t="s">
-        <v>450</v>
+      <c r="C161" s="2" t="s">
+        <v>426</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>451</v>
+        <v>427</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>452</v>
+        <v>428</v>
       </c>
       <c r="F161" s="6"/>
       <c r="G161" s="6"/>
@@ -5611,14 +5710,14 @@
     <row r="162" spans="1:13" ht="14">
       <c r="A162" s="21"/>
       <c r="B162" s="21"/>
-      <c r="C162" s="6" t="s">
-        <v>453</v>
+      <c r="C162" s="2" t="s">
+        <v>429</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="E162" s="9" t="s">
-        <v>455</v>
+        <v>430</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>431</v>
       </c>
       <c r="F162" s="6"/>
       <c r="G162" s="6"/>
@@ -5629,21 +5728,17 @@
       <c r="L162" s="6"/>
       <c r="M162" s="6"/>
     </row>
-    <row r="163" spans="1:13" ht="13">
-      <c r="A163" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="B163" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C163" s="6" t="s">
-        <v>457</v>
+    <row r="163" spans="1:13" ht="14">
+      <c r="A163" s="21"/>
+      <c r="B163" s="21"/>
+      <c r="C163" s="2" t="s">
+        <v>432</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>458</v>
+        <v>433</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>459</v>
+        <v>434</v>
       </c>
       <c r="F163" s="6"/>
       <c r="G163" s="6"/>
@@ -5656,17 +5751,15 @@
     </row>
     <row r="164" spans="1:13" ht="28">
       <c r="A164" s="21"/>
-      <c r="B164" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C164" s="6" t="s">
-        <v>460</v>
+      <c r="B164" s="21"/>
+      <c r="C164" s="2" t="s">
+        <v>435</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>461</v>
+        <v>436</v>
       </c>
       <c r="E164" s="9" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="F164" s="6"/>
       <c r="G164" s="6"/>
@@ -5677,17 +5770,17 @@
       <c r="L164" s="6"/>
       <c r="M164" s="6"/>
     </row>
-    <row r="165" spans="1:13" ht="13">
+    <row r="165" spans="1:13" ht="14">
       <c r="A165" s="21"/>
       <c r="B165" s="21"/>
-      <c r="C165" s="6" t="s">
-        <v>463</v>
+      <c r="C165" s="2" t="s">
+        <v>438</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>464</v>
+        <v>439</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>465</v>
+        <v>440</v>
       </c>
       <c r="F165" s="6"/>
       <c r="G165" s="6"/>
@@ -5698,21 +5791,17 @@
       <c r="L165" s="6"/>
       <c r="M165" s="6"/>
     </row>
-    <row r="166" spans="1:13" ht="13">
-      <c r="A166" s="20" t="s">
-        <v>466</v>
-      </c>
-      <c r="B166" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="C166" s="6" t="s">
-        <v>467</v>
+    <row r="166" spans="1:13" ht="28">
+      <c r="A166" s="21"/>
+      <c r="B166" s="21"/>
+      <c r="C166" s="2" t="s">
+        <v>441</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="E166" s="3" t="s">
-        <v>469</v>
+        <v>442</v>
+      </c>
+      <c r="E166" s="9" t="s">
+        <v>443</v>
       </c>
       <c r="F166" s="6"/>
       <c r="G166" s="6"/>
@@ -5723,17 +5812,17 @@
       <c r="L166" s="6"/>
       <c r="M166" s="6"/>
     </row>
-    <row r="167" spans="1:13" ht="13">
+    <row r="167" spans="1:13" ht="28">
       <c r="A167" s="21"/>
       <c r="B167" s="21"/>
-      <c r="C167" s="6" t="s">
-        <v>470</v>
+      <c r="C167" s="2" t="s">
+        <v>444</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="E167" s="3" t="s">
-        <v>472</v>
+        <v>445</v>
+      </c>
+      <c r="E167" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="F167" s="6"/>
       <c r="G167" s="6"/>
@@ -5744,17 +5833,17 @@
       <c r="L167" s="6"/>
       <c r="M167" s="6"/>
     </row>
-    <row r="168" spans="1:13" ht="14">
+    <row r="168" spans="1:13" ht="13">
       <c r="A168" s="21"/>
       <c r="B168" s="21"/>
       <c r="C168" s="6" t="s">
-        <v>473</v>
-      </c>
-      <c r="D168" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="E168" s="9" t="s">
-        <v>475</v>
+        <v>447</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="E168" s="17" t="s">
+        <v>449</v>
       </c>
       <c r="F168" s="6"/>
       <c r="G168" s="6"/>
@@ -5765,17 +5854,17 @@
       <c r="L168" s="6"/>
       <c r="M168" s="6"/>
     </row>
-    <row r="169" spans="1:13" ht="14">
+    <row r="169" spans="1:13" ht="13">
       <c r="A169" s="21"/>
       <c r="B169" s="21"/>
       <c r="C169" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="D169" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="E169" s="9" t="s">
-        <v>478</v>
+        <v>450</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>452</v>
       </c>
       <c r="F169" s="6"/>
       <c r="G169" s="6"/>
@@ -5788,17 +5877,15 @@
     </row>
     <row r="170" spans="1:13" ht="14">
       <c r="A170" s="21"/>
-      <c r="B170" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C170" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="D170" s="9" t="s">
-        <v>480</v>
+      <c r="B170" s="21"/>
+      <c r="C170" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>454</v>
       </c>
       <c r="E170" s="9" t="s">
-        <v>481</v>
+        <v>455</v>
       </c>
       <c r="F170" s="6"/>
       <c r="G170" s="6"/>
@@ -5809,17 +5896,21 @@
       <c r="L170" s="6"/>
       <c r="M170" s="6"/>
     </row>
-    <row r="171" spans="1:13" ht="14">
-      <c r="A171" s="21"/>
-      <c r="B171" s="21"/>
-      <c r="C171" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="D171" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="E171" s="9" t="s">
-        <v>484</v>
+    <row r="171" spans="1:13" ht="13">
+      <c r="A171" s="23" t="s">
+        <v>456</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>459</v>
       </c>
       <c r="F171" s="6"/>
       <c r="G171" s="6"/>
@@ -5830,17 +5921,19 @@
       <c r="L171" s="6"/>
       <c r="M171" s="6"/>
     </row>
-    <row r="172" spans="1:13" ht="14">
+    <row r="172" spans="1:13" ht="28">
       <c r="A172" s="21"/>
-      <c r="B172" s="21"/>
-      <c r="C172" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="D172" s="9" t="s">
-        <v>486</v>
+      <c r="B172" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>461</v>
       </c>
       <c r="E172" s="9" t="s">
-        <v>487</v>
+        <v>462</v>
       </c>
       <c r="F172" s="6"/>
       <c r="G172" s="6"/>
@@ -5853,15 +5946,15 @@
     </row>
     <row r="173" spans="1:13" ht="14">
       <c r="A173" s="21"/>
-      <c r="B173" s="21"/>
-      <c r="C173" s="8" t="s">
-        <v>488</v>
-      </c>
-      <c r="D173" s="9" t="s">
-        <v>489</v>
+      <c r="B173" s="23"/>
+      <c r="C173" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>579</v>
       </c>
       <c r="E173" s="9" t="s">
-        <v>490</v>
+        <v>597</v>
       </c>
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
@@ -5872,17 +5965,17 @@
       <c r="L173" s="6"/>
       <c r="M173" s="6"/>
     </row>
-    <row r="174" spans="1:13" ht="14">
+    <row r="174" spans="1:13" ht="13">
       <c r="A174" s="21"/>
       <c r="B174" s="21"/>
-      <c r="C174" s="8" t="s">
-        <v>491</v>
-      </c>
-      <c r="D174" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="E174" s="9" t="s">
-        <v>493</v>
+      <c r="C174" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>465</v>
       </c>
       <c r="F174" s="6"/>
       <c r="G174" s="6"/>
@@ -5893,17 +5986,21 @@
       <c r="L174" s="6"/>
       <c r="M174" s="6"/>
     </row>
-    <row r="175" spans="1:13" ht="14">
-      <c r="A175" s="21"/>
-      <c r="B175" s="21"/>
-      <c r="C175" s="8" t="s">
-        <v>494</v>
-      </c>
-      <c r="D175" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="E175" s="9" t="s">
-        <v>496</v>
+    <row r="175" spans="1:13" ht="13">
+      <c r="A175" s="23" t="s">
+        <v>466</v>
+      </c>
+      <c r="B175" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>469</v>
       </c>
       <c r="F175" s="6"/>
       <c r="G175" s="6"/>
@@ -5914,19 +6011,17 @@
       <c r="L175" s="6"/>
       <c r="M175" s="6"/>
     </row>
-    <row r="176" spans="1:13" ht="14">
+    <row r="176" spans="1:13" ht="13">
       <c r="A176" s="21"/>
-      <c r="B176" s="20" t="s">
-        <v>112</v>
-      </c>
+      <c r="B176" s="21"/>
       <c r="C176" s="6" t="s">
-        <v>497</v>
-      </c>
-      <c r="D176" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="E176" s="8" t="s">
-        <v>499</v>
+        <v>470</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>472</v>
       </c>
       <c r="F176" s="6"/>
       <c r="G176" s="6"/>
@@ -5937,17 +6032,17 @@
       <c r="L176" s="6"/>
       <c r="M176" s="6"/>
     </row>
-    <row r="177" spans="1:13" ht="28">
+    <row r="177" spans="1:13" ht="14">
       <c r="A177" s="21"/>
       <c r="B177" s="21"/>
       <c r="C177" s="6" t="s">
-        <v>500</v>
+        <v>473</v>
       </c>
       <c r="D177" s="9" t="s">
-        <v>501</v>
+        <v>474</v>
       </c>
       <c r="E177" s="9" t="s">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="F177" s="6"/>
       <c r="G177" s="6"/>
@@ -5958,17 +6053,17 @@
       <c r="L177" s="6"/>
       <c r="M177" s="6"/>
     </row>
-    <row r="178" spans="1:13" ht="28">
+    <row r="178" spans="1:13" ht="14">
       <c r="A178" s="21"/>
       <c r="B178" s="21"/>
-      <c r="C178" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="D178" s="18" t="s">
-        <v>504</v>
+      <c r="C178" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="D178" s="9" t="s">
+        <v>477</v>
       </c>
       <c r="E178" s="9" t="s">
-        <v>505</v>
+        <v>478</v>
       </c>
       <c r="F178" s="6"/>
       <c r="G178" s="6"/>
@@ -5979,17 +6074,19 @@
       <c r="L178" s="6"/>
       <c r="M178" s="6"/>
     </row>
-    <row r="179" spans="1:13" ht="28">
+    <row r="179" spans="1:13" ht="14">
       <c r="A179" s="21"/>
-      <c r="B179" s="21"/>
-      <c r="C179" s="6" t="s">
-        <v>506</v>
+      <c r="B179" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>479</v>
       </c>
       <c r="D179" s="9" t="s">
-        <v>507</v>
+        <v>480</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>508</v>
+        <v>481</v>
       </c>
       <c r="F179" s="6"/>
       <c r="G179" s="6"/>
@@ -6003,14 +6100,14 @@
     <row r="180" spans="1:13" ht="14">
       <c r="A180" s="21"/>
       <c r="B180" s="21"/>
-      <c r="C180" s="6" t="s">
-        <v>509</v>
+      <c r="C180" s="8" t="s">
+        <v>482</v>
       </c>
       <c r="D180" s="9" t="s">
-        <v>510</v>
+        <v>483</v>
       </c>
       <c r="E180" s="9" t="s">
-        <v>510</v>
+        <v>484</v>
       </c>
       <c r="F180" s="6"/>
       <c r="G180" s="6"/>
@@ -6024,14 +6121,14 @@
     <row r="181" spans="1:13" ht="14">
       <c r="A181" s="21"/>
       <c r="B181" s="21"/>
-      <c r="C181" s="6" t="s">
-        <v>511</v>
+      <c r="C181" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="D181" s="9" t="s">
-        <v>512</v>
+        <v>486</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="F181" s="6"/>
       <c r="G181" s="6"/>
@@ -6042,19 +6139,17 @@
       <c r="L181" s="6"/>
       <c r="M181" s="6"/>
     </row>
-    <row r="182" spans="1:13" ht="28">
+    <row r="182" spans="1:13" ht="14">
       <c r="A182" s="21"/>
-      <c r="B182" s="20" t="s">
-        <v>118</v>
-      </c>
+      <c r="B182" s="21"/>
       <c r="C182" s="8" t="s">
-        <v>514</v>
+        <v>488</v>
       </c>
       <c r="D182" s="9" t="s">
-        <v>515</v>
+        <v>489</v>
       </c>
       <c r="E182" s="9" t="s">
-        <v>516</v>
+        <v>490</v>
       </c>
       <c r="F182" s="6"/>
       <c r="G182" s="6"/>
@@ -6065,17 +6160,17 @@
       <c r="L182" s="6"/>
       <c r="M182" s="6"/>
     </row>
-    <row r="183" spans="1:13" ht="28">
+    <row r="183" spans="1:13" ht="14">
       <c r="A183" s="21"/>
       <c r="B183" s="21"/>
       <c r="C183" s="8" t="s">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="D183" s="9" t="s">
-        <v>518</v>
+        <v>492</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="F183" s="6"/>
       <c r="G183" s="6"/>
@@ -6090,13 +6185,13 @@
       <c r="A184" s="21"/>
       <c r="B184" s="21"/>
       <c r="C184" s="8" t="s">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="D184" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="E184" s="8" t="s">
-        <v>522</v>
+        <v>495</v>
+      </c>
+      <c r="E184" s="9" t="s">
+        <v>496</v>
       </c>
       <c r="F184" s="6"/>
       <c r="G184" s="6"/>
@@ -6108,20 +6203,18 @@
       <c r="M184" s="6"/>
     </row>
     <row r="185" spans="1:13" ht="14">
-      <c r="A185" s="20" t="s">
-        <v>523</v>
-      </c>
-      <c r="B185" s="20" t="s">
-        <v>524</v>
+      <c r="A185" s="21"/>
+      <c r="B185" s="23" t="s">
+        <v>112</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>525</v>
+        <v>497</v>
       </c>
       <c r="D185" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="E185" s="9" t="s">
-        <v>527</v>
+        <v>498</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>499</v>
       </c>
       <c r="F185" s="6"/>
       <c r="G185" s="6"/>
@@ -6132,17 +6225,17 @@
       <c r="L185" s="6"/>
       <c r="M185" s="6"/>
     </row>
-    <row r="186" spans="1:13" ht="14">
+    <row r="186" spans="1:13" ht="28">
       <c r="A186" s="21"/>
       <c r="B186" s="21"/>
       <c r="C186" s="6" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="D186" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="E186" s="3" t="s">
-        <v>530</v>
+        <v>501</v>
+      </c>
+      <c r="E186" s="9" t="s">
+        <v>502</v>
       </c>
       <c r="F186" s="6"/>
       <c r="G186" s="6"/>
@@ -6153,17 +6246,17 @@
       <c r="L186" s="6"/>
       <c r="M186" s="6"/>
     </row>
-    <row r="187" spans="1:13" ht="14">
+    <row r="187" spans="1:13" ht="28">
       <c r="A187" s="21"/>
       <c r="B187" s="21"/>
       <c r="C187" s="6" t="s">
-        <v>531</v>
-      </c>
-      <c r="D187" s="9" t="s">
-        <v>532</v>
+        <v>503</v>
+      </c>
+      <c r="D187" s="18" t="s">
+        <v>504</v>
       </c>
       <c r="E187" s="9" t="s">
-        <v>533</v>
+        <v>505</v>
       </c>
       <c r="F187" s="6"/>
       <c r="G187" s="6"/>
@@ -6174,17 +6267,17 @@
       <c r="L187" s="6"/>
       <c r="M187" s="6"/>
     </row>
-    <row r="188" spans="1:13" ht="14">
+    <row r="188" spans="1:13" ht="28">
       <c r="A188" s="21"/>
       <c r="B188" s="21"/>
       <c r="C188" s="6" t="s">
-        <v>534</v>
+        <v>506</v>
       </c>
       <c r="D188" s="9" t="s">
-        <v>535</v>
+        <v>507</v>
       </c>
       <c r="E188" s="9" t="s">
-        <v>536</v>
+        <v>508</v>
       </c>
       <c r="F188" s="6"/>
       <c r="G188" s="6"/>
@@ -6197,17 +6290,15 @@
     </row>
     <row r="189" spans="1:13" ht="14">
       <c r="A189" s="21"/>
-      <c r="B189" s="20" t="s">
-        <v>118</v>
-      </c>
+      <c r="B189" s="21"/>
       <c r="C189" s="6" t="s">
-        <v>537</v>
+        <v>509</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>538</v>
-      </c>
-      <c r="E189" s="3" t="s">
-        <v>539</v>
+        <v>602</v>
+      </c>
+      <c r="E189" s="9" t="s">
+        <v>510</v>
       </c>
       <c r="F189" s="6"/>
       <c r="G189" s="6"/>
@@ -6222,13 +6313,13 @@
       <c r="A190" s="21"/>
       <c r="B190" s="21"/>
       <c r="C190" s="6" t="s">
-        <v>540</v>
+        <v>511</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>541</v>
-      </c>
-      <c r="E190" s="3" t="s">
-        <v>542</v>
+        <v>512</v>
+      </c>
+      <c r="E190" s="9" t="s">
+        <v>513</v>
       </c>
       <c r="F190" s="6"/>
       <c r="G190" s="6"/>
@@ -6239,21 +6330,19 @@
       <c r="L190" s="6"/>
       <c r="M190" s="6"/>
     </row>
-    <row r="191" spans="1:13" ht="14">
-      <c r="A191" s="6" t="s">
-        <v>543</v>
-      </c>
-      <c r="B191" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C191" s="6" t="s">
-        <v>544</v>
+    <row r="191" spans="1:13" ht="28">
+      <c r="A191" s="21"/>
+      <c r="B191" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C191" s="8" t="s">
+        <v>514</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>545</v>
-      </c>
-      <c r="E191" s="3" t="s">
-        <v>546</v>
+        <v>515</v>
+      </c>
+      <c r="E191" s="9" t="s">
+        <v>516</v>
       </c>
       <c r="F191" s="6"/>
       <c r="G191" s="6"/>
@@ -6264,21 +6353,17 @@
       <c r="L191" s="6"/>
       <c r="M191" s="6"/>
     </row>
-    <row r="192" spans="1:13" ht="13">
-      <c r="A192" s="6" t="s">
-        <v>543</v>
-      </c>
-      <c r="B192" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C192" s="6" t="s">
-        <v>547</v>
-      </c>
-      <c r="D192" s="10" t="s">
-        <v>548</v>
-      </c>
-      <c r="E192" s="10" t="s">
-        <v>549</v>
+    <row r="192" spans="1:13" ht="28">
+      <c r="A192" s="21"/>
+      <c r="B192" s="21"/>
+      <c r="C192" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="D192" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="E192" s="9" t="s">
+        <v>519</v>
       </c>
       <c r="F192" s="6"/>
       <c r="G192" s="6"/>
@@ -6289,12 +6374,18 @@
       <c r="L192" s="6"/>
       <c r="M192" s="6"/>
     </row>
-    <row r="193" spans="1:13" ht="13">
-      <c r="A193" s="6"/>
-      <c r="B193" s="6"/>
-      <c r="C193" s="6"/>
-      <c r="D193" s="9"/>
-      <c r="E193" s="9"/>
+    <row r="193" spans="1:13" ht="14">
+      <c r="A193" s="21"/>
+      <c r="B193" s="21"/>
+      <c r="C193" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="D193" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="E193" s="8" t="s">
+        <v>522</v>
+      </c>
       <c r="F193" s="6"/>
       <c r="G193" s="6"/>
       <c r="H193" s="6"/>
@@ -6304,11 +6395,22 @@
       <c r="L193" s="6"/>
       <c r="M193" s="6"/>
     </row>
-    <row r="194" spans="1:13" ht="13">
-      <c r="A194" s="6"/>
-      <c r="B194" s="6"/>
-      <c r="C194" s="6"/>
-      <c r="D194" s="9"/>
+    <row r="194" spans="1:13" ht="14">
+      <c r="A194" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="B194" s="23" t="s">
+        <v>524</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="D194" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="E194" s="9" t="s">
+        <v>527</v>
+      </c>
       <c r="F194" s="6"/>
       <c r="G194" s="6"/>
       <c r="H194" s="6"/>
@@ -6318,10 +6420,18 @@
       <c r="L194" s="6"/>
       <c r="M194" s="6"/>
     </row>
-    <row r="195" spans="1:13" ht="13">
-      <c r="A195" s="6"/>
-      <c r="B195" s="6"/>
-      <c r="C195" s="6"/>
+    <row r="195" spans="1:13" ht="14">
+      <c r="A195" s="21"/>
+      <c r="B195" s="21"/>
+      <c r="C195" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="D195" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>530</v>
+      </c>
       <c r="F195" s="6"/>
       <c r="G195" s="6"/>
       <c r="H195" s="6"/>
@@ -6331,11 +6441,18 @@
       <c r="L195" s="6"/>
       <c r="M195" s="6"/>
     </row>
-    <row r="196" spans="1:13" ht="13">
-      <c r="A196" s="6"/>
-      <c r="B196" s="6"/>
-      <c r="C196" s="6"/>
-      <c r="D196" s="9"/>
+    <row r="196" spans="1:13" ht="14">
+      <c r="A196" s="21"/>
+      <c r="B196" s="21"/>
+      <c r="C196" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D196" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="E196" s="9" t="s">
+        <v>533</v>
+      </c>
       <c r="F196" s="6"/>
       <c r="G196" s="6"/>
       <c r="H196" s="6"/>
@@ -6345,10 +6462,18 @@
       <c r="L196" s="6"/>
       <c r="M196" s="6"/>
     </row>
-    <row r="197" spans="1:13" ht="13">
-      <c r="A197" s="6"/>
-      <c r="B197" s="6"/>
-      <c r="C197" s="6"/>
+    <row r="197" spans="1:13" ht="14">
+      <c r="A197" s="21"/>
+      <c r="B197" s="21"/>
+      <c r="C197" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="D197" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="E197" s="9" t="s">
+        <v>536</v>
+      </c>
       <c r="F197" s="6"/>
       <c r="G197" s="6"/>
       <c r="H197" s="6"/>
@@ -6358,10 +6483,20 @@
       <c r="L197" s="6"/>
       <c r="M197" s="6"/>
     </row>
-    <row r="198" spans="1:13" ht="13">
-      <c r="A198" s="6"/>
-      <c r="B198" s="6"/>
-      <c r="C198" s="6"/>
+    <row r="198" spans="1:13" ht="14">
+      <c r="A198" s="21"/>
+      <c r="B198" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="D198" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>539</v>
+      </c>
       <c r="F198" s="6"/>
       <c r="G198" s="6"/>
       <c r="H198" s="6"/>
@@ -6371,10 +6506,18 @@
       <c r="L198" s="6"/>
       <c r="M198" s="6"/>
     </row>
-    <row r="199" spans="1:13" ht="13">
-      <c r="A199" s="6"/>
-      <c r="B199" s="6"/>
-      <c r="C199" s="6"/>
+    <row r="199" spans="1:13" ht="14">
+      <c r="A199" s="21"/>
+      <c r="B199" s="21"/>
+      <c r="C199" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="D199" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>542</v>
+      </c>
       <c r="F199" s="6"/>
       <c r="G199" s="6"/>
       <c r="H199" s="6"/>
@@ -6384,10 +6527,22 @@
       <c r="L199" s="6"/>
       <c r="M199" s="6"/>
     </row>
-    <row r="200" spans="1:13" ht="13">
-      <c r="A200" s="6"/>
-      <c r="B200" s="6"/>
-      <c r="C200" s="6"/>
+    <row r="200" spans="1:13" ht="14">
+      <c r="A200" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="D200" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>546</v>
+      </c>
       <c r="F200" s="6"/>
       <c r="G200" s="6"/>
       <c r="H200" s="6"/>
@@ -6398,9 +6553,21 @@
       <c r="M200" s="6"/>
     </row>
     <row r="201" spans="1:13" ht="13">
-      <c r="A201" s="6"/>
-      <c r="B201" s="6"/>
-      <c r="C201" s="6"/>
+      <c r="A201" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C201" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="D201" s="10" t="s">
+        <v>600</v>
+      </c>
+      <c r="E201" s="10" t="s">
+        <v>601</v>
+      </c>
       <c r="F201" s="6"/>
       <c r="G201" s="6"/>
       <c r="H201" s="6"/>
@@ -6410,10 +6577,22 @@
       <c r="L201" s="6"/>
       <c r="M201" s="6"/>
     </row>
-    <row r="202" spans="1:13" ht="13">
-      <c r="A202" s="6"/>
-      <c r="B202" s="6"/>
-      <c r="C202" s="6"/>
+    <row r="202" spans="1:13" ht="14">
+      <c r="A202" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="D202" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="E202" s="9" t="s">
+        <v>599</v>
+      </c>
       <c r="F202" s="6"/>
       <c r="G202" s="6"/>
       <c r="H202" s="6"/>
@@ -6423,10 +6602,20 @@
       <c r="L202" s="6"/>
       <c r="M202" s="6"/>
     </row>
-    <row r="203" spans="1:13" ht="13">
+    <row r="203" spans="1:13" ht="14">
       <c r="A203" s="6"/>
-      <c r="B203" s="6"/>
-      <c r="C203" s="6"/>
+      <c r="B203" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="D203" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>577</v>
+      </c>
       <c r="F203" s="6"/>
       <c r="G203" s="6"/>
       <c r="H203" s="6"/>
@@ -6440,6 +6629,7 @@
       <c r="A204" s="6"/>
       <c r="B204" s="6"/>
       <c r="C204" s="6"/>
+      <c r="D204" s="9"/>
       <c r="F204" s="6"/>
       <c r="G204" s="6"/>
       <c r="H204" s="6"/>
@@ -6462,42 +6652,146 @@
       <c r="L205" s="6"/>
       <c r="M205" s="6"/>
     </row>
+    <row r="206" spans="1:13" ht="13">
+      <c r="A206" s="6"/>
+      <c r="B206" s="6"/>
+      <c r="C206" s="6"/>
+      <c r="F206" s="6"/>
+      <c r="G206" s="6"/>
+      <c r="H206" s="6"/>
+      <c r="I206" s="6"/>
+      <c r="J206" s="6"/>
+      <c r="K206" s="6"/>
+      <c r="L206" s="6"/>
+      <c r="M206" s="6"/>
+    </row>
+    <row r="207" spans="1:13" ht="13">
+      <c r="A207" s="6"/>
+      <c r="B207" s="6"/>
+      <c r="C207" s="6"/>
+      <c r="F207" s="6"/>
+      <c r="G207" s="6"/>
+      <c r="H207" s="6"/>
+      <c r="I207" s="6"/>
+      <c r="J207" s="6"/>
+      <c r="K207" s="6"/>
+      <c r="L207" s="6"/>
+      <c r="M207" s="6"/>
+    </row>
+    <row r="208" spans="1:13" ht="13">
+      <c r="A208" s="6"/>
+      <c r="B208" s="6"/>
+      <c r="C208" s="6"/>
+      <c r="F208" s="6"/>
+      <c r="G208" s="6"/>
+      <c r="H208" s="6"/>
+      <c r="I208" s="6"/>
+      <c r="J208" s="6"/>
+      <c r="K208" s="6"/>
+      <c r="L208" s="6"/>
+      <c r="M208" s="6"/>
+    </row>
+    <row r="209" spans="1:13" ht="13">
+      <c r="A209" s="6"/>
+      <c r="B209" s="6"/>
+      <c r="C209" s="6"/>
+      <c r="F209" s="6"/>
+      <c r="G209" s="6"/>
+      <c r="H209" s="6"/>
+      <c r="I209" s="6"/>
+      <c r="J209" s="6"/>
+      <c r="K209" s="6"/>
+      <c r="L209" s="6"/>
+      <c r="M209" s="6"/>
+    </row>
+    <row r="210" spans="1:13" ht="13">
+      <c r="A210" s="6"/>
+      <c r="B210" s="6"/>
+      <c r="C210" s="6"/>
+      <c r="F210" s="6"/>
+      <c r="G210" s="6"/>
+      <c r="H210" s="6"/>
+      <c r="I210" s="6"/>
+      <c r="J210" s="6"/>
+      <c r="K210" s="6"/>
+      <c r="L210" s="6"/>
+      <c r="M210" s="6"/>
+    </row>
+    <row r="211" spans="1:13" ht="13">
+      <c r="A211" s="6"/>
+      <c r="B211" s="6"/>
+      <c r="C211" s="6"/>
+      <c r="F211" s="6"/>
+      <c r="G211" s="6"/>
+      <c r="H211" s="6"/>
+      <c r="I211" s="6"/>
+      <c r="J211" s="6"/>
+      <c r="K211" s="6"/>
+      <c r="L211" s="6"/>
+      <c r="M211" s="6"/>
+    </row>
+    <row r="212" spans="1:13" ht="13">
+      <c r="A212" s="6"/>
+      <c r="B212" s="6"/>
+      <c r="C212" s="6"/>
+      <c r="F212" s="6"/>
+      <c r="G212" s="6"/>
+      <c r="H212" s="6"/>
+      <c r="I212" s="6"/>
+      <c r="J212" s="6"/>
+      <c r="K212" s="6"/>
+      <c r="L212" s="6"/>
+      <c r="M212" s="6"/>
+    </row>
+    <row r="213" spans="1:13" ht="13">
+      <c r="A213" s="6"/>
+      <c r="B213" s="6"/>
+      <c r="C213" s="6"/>
+      <c r="F213" s="6"/>
+      <c r="G213" s="6"/>
+      <c r="H213" s="6"/>
+      <c r="I213" s="6"/>
+      <c r="J213" s="6"/>
+      <c r="K213" s="6"/>
+      <c r="L213" s="6"/>
+      <c r="M213" s="6"/>
+    </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="A123:A142"/>
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="B127:B139"/>
+    <mergeCell ref="B141:B142"/>
+    <mergeCell ref="B143:B151"/>
+    <mergeCell ref="A143:A170"/>
+    <mergeCell ref="B152:B155"/>
+    <mergeCell ref="B156:B170"/>
+    <mergeCell ref="A171:A174"/>
+    <mergeCell ref="A175:A193"/>
+    <mergeCell ref="A194:A199"/>
+    <mergeCell ref="B172:B174"/>
+    <mergeCell ref="B175:B178"/>
+    <mergeCell ref="B179:B184"/>
+    <mergeCell ref="B185:B190"/>
+    <mergeCell ref="B191:B193"/>
+    <mergeCell ref="B194:B197"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="A51:A84"/>
+    <mergeCell ref="B51:B60"/>
+    <mergeCell ref="B103:B105"/>
+    <mergeCell ref="B106:B109"/>
+    <mergeCell ref="B71:B77"/>
+    <mergeCell ref="B78:B84"/>
+    <mergeCell ref="A85:A93"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="A94:A105"/>
+    <mergeCell ref="B94:B100"/>
+    <mergeCell ref="A106:A110"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A4:A45"/>
-    <mergeCell ref="B4:B36"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="A49:A80"/>
-    <mergeCell ref="B49:B58"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="B100:B103"/>
-    <mergeCell ref="B69:B73"/>
-    <mergeCell ref="B74:B80"/>
-    <mergeCell ref="A81:A88"/>
-    <mergeCell ref="B81:B86"/>
-    <mergeCell ref="A89:A99"/>
-    <mergeCell ref="B89:B95"/>
-    <mergeCell ref="A100:A104"/>
-    <mergeCell ref="A163:A165"/>
-    <mergeCell ref="A166:A184"/>
-    <mergeCell ref="A185:A190"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="B166:B169"/>
-    <mergeCell ref="B170:B175"/>
-    <mergeCell ref="B176:B181"/>
-    <mergeCell ref="B182:B184"/>
-    <mergeCell ref="B185:B188"/>
-    <mergeCell ref="B189:B190"/>
-    <mergeCell ref="A116:A134"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="B120:B131"/>
-    <mergeCell ref="B133:B134"/>
-    <mergeCell ref="B135:B143"/>
-    <mergeCell ref="A135:A162"/>
-    <mergeCell ref="B144:B147"/>
-    <mergeCell ref="B148:B162"/>
+    <mergeCell ref="A4:A47"/>
+    <mergeCell ref="B4:B37"/>
+    <mergeCell ref="B44:B47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/scripts/i18n.xlsx
+++ b/scripts/i18n.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juyeonkim/Documents/pfplay-web/scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C62D74A-73B2-0947-B205-18772E751CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522C75AD-717F-0A41-B134-7B7081528BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2300" yWindow="500" windowWidth="26500" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,9 +124,6 @@
     <t>제재</t>
   </si>
   <si>
-    <t>Sanction</t>
-  </si>
-  <si>
     <t>common.btn.block</t>
   </si>
   <si>
@@ -328,18 +325,12 @@
     <t>다시 입장하기</t>
   </si>
   <si>
-    <t>Try again</t>
-  </si>
-  <si>
     <t>common.btn.chat_mute</t>
   </si>
   <si>
     <t>꿀</t>
   </si>
   <si>
-    <t>Chat Mute</t>
-  </si>
-  <si>
     <t>common.btn.kick</t>
   </si>
   <si>
@@ -469,9 +460,6 @@
     <t>로그아웃 하시겠어요? 로그아웃 시 메인 홈으로 이동합니다</t>
   </si>
   <si>
-    <t>Do you want to log out? If yes, you will be redirected to home</t>
-  </si>
-  <si>
     <t>auth.para.withdraw_confirm</t>
   </si>
   <si>
@@ -697,9 +685,6 @@
     <t>당신의 PFP는 안녕한가요?</t>
   </si>
   <si>
-    <t>How is your PFPlay?</t>
-  </si>
-  <si>
     <t>onboard.btn.take_a_look</t>
   </si>
   <si>
@@ -760,9 +745,6 @@
     <t>소개</t>
   </si>
   <si>
-    <t>Info</t>
-  </si>
-  <si>
     <t>settings.title.body</t>
   </si>
   <si>
@@ -829,9 +811,6 @@
     <t>보유한 내역이 없어요</t>
   </si>
   <si>
-    <t>You don't have any items</t>
-  </si>
-  <si>
     <t>로비 (Lobby)</t>
   </si>
   <si>
@@ -1153,9 +1132,6 @@
     <t>DJ 대기열</t>
   </si>
   <si>
-    <t>DJ queue</t>
-  </si>
-  <si>
     <t>dj.title.time_limit</t>
   </si>
   <si>
@@ -1261,9 +1237,6 @@
     <t>현재 디제잉 인원이 없어요\n파티의 흥을 책임질 DJ가 되어보세요!</t>
   </si>
   <si>
-    <t>No one is djing now.\nWhy not become the DJ and make some noise!</t>
-  </si>
-  <si>
     <t>dj.para.create_playlist_song</t>
   </si>
   <si>
@@ -1385,9 +1358,6 @@
   </si>
   <si>
     <t>진행 중인 디제잉이 없어요 zZz...</t>
-  </si>
-  <si>
-    <t>zZz...No Djing in currently in progress...</t>
   </si>
   <si>
     <t>전광판 (Electronic Display)</t>
@@ -1806,9 +1776,6 @@
     <t>영구 패널티</t>
   </si>
   <si>
-    <t>A list I blocked</t>
-  </si>
-  <si>
     <t>auth.para.penalty</t>
   </si>
   <si>
@@ -1831,6 +1798,39 @@
   </si>
   <si>
     <t>URL 혹은 음악을 검색할 수 있어요</t>
+  </si>
+  <si>
+    <t>Delete Account</t>
+  </si>
+  <si>
+    <t>Re-enter</t>
+  </si>
+  <si>
+    <t>Buzz</t>
+  </si>
+  <si>
+    <t>Are you sure you want to log out? You'll be redirected to the home</t>
+  </si>
+  <si>
+    <t>Blocked list</t>
+  </si>
+  <si>
+    <t>How's your PFP doing?</t>
+  </si>
+  <si>
+    <t>About me</t>
+  </si>
+  <si>
+    <t>You have no items</t>
+  </si>
+  <si>
+    <t>DJ Queue</t>
+  </si>
+  <si>
+    <t>No one is DJing now.\nWhy not become the DJ and make some noise!</t>
+  </si>
+  <si>
+    <t>zZz...No DJ currently playing...</t>
   </si>
 </sst>
 </file>
@@ -1976,18 +1976,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2220,7 +2220,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="24" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="21"/>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="21"/>
@@ -2339,7 +2339,7 @@
         <v>18</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>19</v>
+        <v>592</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="5"/>
@@ -2444,7 +2444,7 @@
         <v>33</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>34</v>
+        <v>567</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="5"/>
@@ -2459,13 +2459,13 @@
       <c r="A12" s="21"/>
       <c r="B12" s="21"/>
       <c r="C12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="5"/>
@@ -2480,13 +2480,13 @@
       <c r="A13" s="21"/>
       <c r="B13" s="21"/>
       <c r="C13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="5"/>
@@ -2501,13 +2501,13 @@
       <c r="A14" s="21"/>
       <c r="B14" s="21"/>
       <c r="C14" s="2" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="5"/>
@@ -2522,13 +2522,13 @@
       <c r="A15" s="21"/>
       <c r="B15" s="21"/>
       <c r="C15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="5"/>
@@ -2543,13 +2543,13 @@
       <c r="A16" s="21"/>
       <c r="B16" s="21"/>
       <c r="C16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="5"/>
@@ -2564,13 +2564,13 @@
       <c r="A17" s="21"/>
       <c r="B17" s="21"/>
       <c r="C17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="5"/>
@@ -2585,13 +2585,13 @@
       <c r="A18" s="21"/>
       <c r="B18" s="21"/>
       <c r="C18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="5"/>
@@ -2606,13 +2606,13 @@
       <c r="A19" s="21"/>
       <c r="B19" s="21"/>
       <c r="C19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="5"/>
@@ -2627,13 +2627,13 @@
       <c r="A20" s="21"/>
       <c r="B20" s="21"/>
       <c r="C20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="5"/>
@@ -2648,13 +2648,13 @@
       <c r="A21" s="21"/>
       <c r="B21" s="21"/>
       <c r="C21" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="5"/>
@@ -2669,13 +2669,13 @@
       <c r="A22" s="21"/>
       <c r="B22" s="21"/>
       <c r="C22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="5"/>
@@ -2690,13 +2690,13 @@
       <c r="A23" s="21"/>
       <c r="B23" s="21"/>
       <c r="C23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="5"/>
@@ -2711,13 +2711,13 @@
       <c r="A24" s="21"/>
       <c r="B24" s="21"/>
       <c r="C24" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="5"/>
@@ -2732,13 +2732,13 @@
       <c r="A25" s="21"/>
       <c r="B25" s="21"/>
       <c r="C25" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="5"/>
@@ -2753,13 +2753,13 @@
       <c r="A26" s="21"/>
       <c r="B26" s="21"/>
       <c r="C26" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="5"/>
@@ -2774,13 +2774,13 @@
       <c r="A27" s="21"/>
       <c r="B27" s="21"/>
       <c r="C27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="5"/>
@@ -2795,13 +2795,13 @@
       <c r="A28" s="21"/>
       <c r="B28" s="21"/>
       <c r="C28" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="5"/>
@@ -2816,13 +2816,13 @@
       <c r="A29" s="21"/>
       <c r="B29" s="21"/>
       <c r="C29" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="5"/>
@@ -2837,13 +2837,13 @@
       <c r="A30" s="21"/>
       <c r="B30" s="21"/>
       <c r="C30" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="5"/>
@@ -2858,13 +2858,13 @@
       <c r="A31" s="21"/>
       <c r="B31" s="21"/>
       <c r="C31" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="5"/>
@@ -2879,13 +2879,13 @@
       <c r="A32" s="21"/>
       <c r="B32" s="21"/>
       <c r="C32" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="E32" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="5"/>
@@ -2900,13 +2900,13 @@
       <c r="A33" s="21"/>
       <c r="B33" s="21"/>
       <c r="C33" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="5"/>
@@ -2921,13 +2921,13 @@
       <c r="A34" s="21"/>
       <c r="B34" s="21"/>
       <c r="C34" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="E34" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="5"/>
@@ -2942,7 +2942,7 @@
       <c r="A35" s="21"/>
       <c r="B35" s="21"/>
       <c r="C35" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>6</v>
@@ -2963,13 +2963,13 @@
       <c r="A36" s="21"/>
       <c r="B36" s="21"/>
       <c r="C36" s="6" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="5"/>
@@ -2984,13 +2984,13 @@
       <c r="A37" s="21"/>
       <c r="B37" s="21"/>
       <c r="C37" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>102</v>
+      <c r="E37" s="19" t="s">
+        <v>593</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="5"/>
@@ -3005,13 +3005,13 @@
       <c r="A38" s="21"/>
       <c r="B38" s="2"/>
       <c r="C38" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>594</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="5"/>
@@ -3026,13 +3026,13 @@
       <c r="A39" s="21"/>
       <c r="B39" s="2"/>
       <c r="C39" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="5"/>
@@ -3047,13 +3047,13 @@
       <c r="A40" s="21"/>
       <c r="B40" s="2"/>
       <c r="C40" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="5"/>
@@ -3067,16 +3067,16 @@
     <row r="41" spans="1:13" ht="15.75" customHeight="1">
       <c r="A41" s="21"/>
       <c r="B41" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="5"/>
@@ -3091,13 +3091,13 @@
       <c r="A42" s="21"/>
       <c r="B42" s="2"/>
       <c r="C42" s="6" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="5"/>
@@ -3111,16 +3111,16 @@
     <row r="43" spans="1:13" ht="15.75" customHeight="1">
       <c r="A43" s="21"/>
       <c r="B43" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="5"/>
@@ -3134,16 +3134,16 @@
     <row r="44" spans="1:13" ht="15.75" customHeight="1">
       <c r="A44" s="21"/>
       <c r="B44" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="5"/>
@@ -3158,13 +3158,13 @@
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="8" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="5"/>
@@ -3179,13 +3179,13 @@
       <c r="A46" s="21"/>
       <c r="B46" s="21"/>
       <c r="C46" s="8" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="5"/>
@@ -3200,13 +3200,13 @@
       <c r="A47" s="21"/>
       <c r="B47" s="21"/>
       <c r="C47" s="8" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="5"/>
@@ -3221,13 +3221,13 @@
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="8" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="5"/>
@@ -3242,13 +3242,13 @@
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="8" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="5"/>
@@ -3263,13 +3263,13 @@
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="5"/>
@@ -3282,19 +3282,19 @@
     </row>
     <row r="51" spans="1:13" ht="15.75" customHeight="1">
       <c r="A51" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="B51" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="5"/>
@@ -3309,13 +3309,13 @@
       <c r="A52" s="21"/>
       <c r="B52" s="21"/>
       <c r="C52" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="5"/>
@@ -3330,13 +3330,13 @@
       <c r="A53" s="21"/>
       <c r="B53" s="21"/>
       <c r="C53" s="2" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="5"/>
@@ -3351,13 +3351,13 @@
       <c r="A54" s="21"/>
       <c r="B54" s="21"/>
       <c r="C54" s="6" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="5"/>
@@ -3372,13 +3372,13 @@
       <c r="A55" s="21"/>
       <c r="B55" s="21"/>
       <c r="C55" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>595</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="5"/>
@@ -3393,13 +3393,13 @@
       <c r="A56" s="21"/>
       <c r="B56" s="21"/>
       <c r="C56" s="6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="5"/>
@@ -3414,13 +3414,13 @@
       <c r="A57" s="21"/>
       <c r="B57" s="21"/>
       <c r="C57" s="6" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="5"/>
@@ -3435,13 +3435,13 @@
       <c r="A58" s="21"/>
       <c r="B58" s="21"/>
       <c r="C58" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="5"/>
@@ -3456,13 +3456,13 @@
       <c r="A59" s="21"/>
       <c r="B59" s="21"/>
       <c r="C59" s="6" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="5"/>
@@ -3477,13 +3477,13 @@
       <c r="A60" s="21"/>
       <c r="B60" s="21"/>
       <c r="C60" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="5"/>
@@ -3498,13 +3498,13 @@
       <c r="A61" s="21"/>
       <c r="B61" s="6"/>
       <c r="C61" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="5"/>
@@ -3519,13 +3519,13 @@
       <c r="A62" s="21"/>
       <c r="B62" s="6"/>
       <c r="C62" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="5"/>
@@ -3540,13 +3540,13 @@
       <c r="A63" s="21"/>
       <c r="B63" s="6"/>
       <c r="C63" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F63" s="4"/>
       <c r="G63" s="5"/>
@@ -3561,13 +3561,13 @@
       <c r="A64" s="21"/>
       <c r="B64" s="6"/>
       <c r="C64" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F64" s="4"/>
       <c r="G64" s="5"/>
@@ -3582,13 +3582,13 @@
       <c r="A65" s="21"/>
       <c r="B65" s="6"/>
       <c r="C65" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F65" s="4"/>
       <c r="G65" s="5"/>
@@ -3603,13 +3603,13 @@
       <c r="A66" s="21"/>
       <c r="B66" s="6"/>
       <c r="C66" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F66" s="4"/>
       <c r="G66" s="5"/>
@@ -3624,13 +3624,13 @@
       <c r="A67" s="21"/>
       <c r="B67" s="6"/>
       <c r="C67" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="5"/>
@@ -3645,13 +3645,13 @@
       <c r="A68" s="21"/>
       <c r="B68" s="6"/>
       <c r="C68" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="5"/>
@@ -3666,13 +3666,13 @@
       <c r="A69" s="21"/>
       <c r="B69" s="6"/>
       <c r="C69" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="5"/>
@@ -3687,13 +3687,13 @@
       <c r="A70" s="21"/>
       <c r="B70" s="6"/>
       <c r="C70" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="5"/>
@@ -3706,17 +3706,17 @@
     </row>
     <row r="71" spans="1:13" ht="13">
       <c r="A71" s="21"/>
-      <c r="B71" s="23" t="s">
+      <c r="B71" s="20" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="5"/>
@@ -3729,15 +3729,15 @@
     </row>
     <row r="72" spans="1:13" ht="13">
       <c r="A72" s="21"/>
-      <c r="B72" s="23"/>
+      <c r="B72" s="20"/>
       <c r="C72" s="6" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="5"/>
@@ -3750,15 +3750,15 @@
     </row>
     <row r="73" spans="1:13" ht="13">
       <c r="A73" s="21"/>
-      <c r="B73" s="23"/>
+      <c r="B73" s="20"/>
       <c r="C73" s="6" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="5"/>
@@ -3771,15 +3771,15 @@
     </row>
     <row r="74" spans="1:13" ht="13">
       <c r="A74" s="21"/>
-      <c r="B74" s="23"/>
+      <c r="B74" s="20"/>
       <c r="C74" s="6" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="5"/>
@@ -3792,15 +3792,15 @@
     </row>
     <row r="75" spans="1:13" ht="13">
       <c r="A75" s="21"/>
-      <c r="B75" s="23"/>
+      <c r="B75" s="20"/>
       <c r="C75" s="6" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="5"/>
@@ -3813,15 +3813,15 @@
     </row>
     <row r="76" spans="1:13" ht="13">
       <c r="A76" s="21"/>
-      <c r="B76" s="23"/>
+      <c r="B76" s="20"/>
       <c r="C76" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>596</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>594</v>
       </c>
       <c r="F76" s="4"/>
       <c r="G76" s="5"/>
@@ -3836,13 +3836,13 @@
       <c r="A77" s="21"/>
       <c r="B77" s="21"/>
       <c r="C77" s="6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="5"/>
@@ -3855,17 +3855,17 @@
     </row>
     <row r="78" spans="1:13" ht="13">
       <c r="A78" s="21"/>
-      <c r="B78" s="23" t="s">
-        <v>201</v>
+      <c r="B78" s="20" t="s">
+        <v>197</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="5"/>
@@ -3880,13 +3880,13 @@
       <c r="A79" s="21"/>
       <c r="B79" s="21"/>
       <c r="C79" s="6" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F79" s="4"/>
       <c r="G79" s="5"/>
@@ -3901,13 +3901,13 @@
       <c r="A80" s="21"/>
       <c r="B80" s="21"/>
       <c r="C80" s="6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="5"/>
@@ -3922,13 +3922,13 @@
       <c r="A81" s="21"/>
       <c r="B81" s="21"/>
       <c r="C81" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="5"/>
@@ -3943,13 +3943,13 @@
       <c r="A82" s="21"/>
       <c r="B82" s="21"/>
       <c r="C82" s="6" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="5"/>
@@ -3964,13 +3964,13 @@
       <c r="A83" s="21"/>
       <c r="B83" s="21"/>
       <c r="C83" s="6" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="5"/>
@@ -3985,10 +3985,10 @@
       <c r="A84" s="21"/>
       <c r="B84" s="21"/>
       <c r="C84" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>19</v>
@@ -4003,20 +4003,20 @@
       <c r="M84" s="4"/>
     </row>
     <row r="85" spans="1:13" ht="14">
-      <c r="A85" s="23" t="s">
-        <v>218</v>
-      </c>
-      <c r="B85" s="23" t="s">
+      <c r="A85" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B85" s="20" t="s">
         <v>11</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="5"/>
@@ -4031,13 +4031,13 @@
       <c r="A86" s="21"/>
       <c r="B86" s="21"/>
       <c r="C86" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="5"/>
@@ -4052,13 +4052,13 @@
       <c r="A87" s="21"/>
       <c r="B87" s="21"/>
       <c r="C87" s="6" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
+      </c>
+      <c r="E87" s="19" t="s">
+        <v>597</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="5"/>
@@ -4073,13 +4073,13 @@
       <c r="A88" s="21"/>
       <c r="B88" s="21"/>
       <c r="C88" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="5"/>
@@ -4094,10 +4094,10 @@
       <c r="A89" s="21"/>
       <c r="B89" s="21"/>
       <c r="C89" s="6" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>5</v>
@@ -4115,13 +4115,13 @@
       <c r="A90" s="21"/>
       <c r="B90" s="21"/>
       <c r="C90" s="6" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="5"/>
@@ -4135,16 +4135,16 @@
     <row r="91" spans="1:13" ht="13">
       <c r="A91" s="21"/>
       <c r="B91" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F91" s="4"/>
       <c r="G91" s="5"/>
@@ -4159,13 +4159,13 @@
       <c r="A92" s="21"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="F92" s="4"/>
       <c r="G92" s="5"/>
@@ -4179,16 +4179,16 @@
     <row r="93" spans="1:13" ht="13">
       <c r="A93" s="21"/>
       <c r="B93" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="F93" s="4"/>
       <c r="G93" s="5"/>
@@ -4200,20 +4200,20 @@
       <c r="M93" s="4"/>
     </row>
     <row r="94" spans="1:13" ht="14">
-      <c r="A94" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="B94" s="23" t="s">
-        <v>201</v>
+      <c r="A94" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="B94" s="20" t="s">
+        <v>197</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F94" s="4"/>
       <c r="G94" s="5"/>
@@ -4228,13 +4228,13 @@
       <c r="A95" s="21"/>
       <c r="B95" s="21"/>
       <c r="C95" s="6" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="F95" s="4"/>
       <c r="G95" s="5"/>
@@ -4249,13 +4249,13 @@
       <c r="A96" s="21"/>
       <c r="B96" s="21"/>
       <c r="C96" s="6" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="E96" s="9" t="s">
-        <v>246</v>
+        <v>240</v>
+      </c>
+      <c r="E96" s="19" t="s">
+        <v>598</v>
       </c>
       <c r="F96" s="4"/>
       <c r="G96" s="5"/>
@@ -4270,13 +4270,13 @@
       <c r="A97" s="21"/>
       <c r="B97" s="21"/>
       <c r="C97" s="6" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F97" s="4"/>
       <c r="G97" s="5"/>
@@ -4291,13 +4291,13 @@
       <c r="A98" s="21"/>
       <c r="B98" s="21"/>
       <c r="C98" s="6" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="F98" s="4"/>
       <c r="G98" s="5"/>
@@ -4312,13 +4312,13 @@
       <c r="A99" s="21"/>
       <c r="B99" s="21"/>
       <c r="C99" s="6" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="F99" s="4"/>
       <c r="G99" s="5"/>
@@ -4333,13 +4333,13 @@
       <c r="A100" s="21"/>
       <c r="B100" s="21"/>
       <c r="C100" s="6" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F100" s="4"/>
       <c r="G100" s="5"/>
@@ -4353,16 +4353,16 @@
     <row r="101" spans="1:13" ht="14">
       <c r="A101" s="21"/>
       <c r="B101" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="F101" s="4"/>
       <c r="G101" s="5"/>
@@ -4379,13 +4379,13 @@
         <v>11</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="F102" s="4"/>
       <c r="G102" s="5"/>
@@ -4398,17 +4398,17 @@
     </row>
     <row r="103" spans="1:13" ht="14">
       <c r="A103" s="21"/>
-      <c r="B103" s="23" t="s">
-        <v>112</v>
+      <c r="B103" s="20" t="s">
+        <v>109</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="5"/>
@@ -4421,15 +4421,15 @@
     </row>
     <row r="104" spans="1:13" ht="14">
       <c r="A104" s="21"/>
-      <c r="B104" s="23"/>
+      <c r="B104" s="20"/>
       <c r="C104" s="9" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="5"/>
@@ -4444,13 +4444,13 @@
       <c r="A105" s="21"/>
       <c r="B105" s="21"/>
       <c r="C105" s="9" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>269</v>
+        <v>262</v>
+      </c>
+      <c r="E105" s="19" t="s">
+        <v>599</v>
       </c>
       <c r="F105" s="6"/>
       <c r="G105" s="6"/>
@@ -4462,20 +4462,20 @@
       <c r="M105" s="6"/>
     </row>
     <row r="106" spans="1:13" ht="13">
-      <c r="A106" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="B106" s="24" t="s">
-        <v>201</v>
+      <c r="A106" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="B106" s="23" t="s">
+        <v>197</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="F106" s="4"/>
       <c r="G106" s="5"/>
@@ -4490,13 +4490,13 @@
       <c r="A107" s="21"/>
       <c r="B107" s="21"/>
       <c r="C107" s="6" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="5"/>
@@ -4511,13 +4511,13 @@
       <c r="A108" s="21"/>
       <c r="B108" s="21"/>
       <c r="C108" s="6" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="F108" s="4"/>
       <c r="G108" s="5"/>
@@ -4532,13 +4532,13 @@
       <c r="A109" s="21"/>
       <c r="B109" s="21"/>
       <c r="C109" s="6" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="F109" s="4"/>
       <c r="G109" s="5"/>
@@ -4552,16 +4552,16 @@
     <row r="110" spans="1:13" ht="13">
       <c r="A110" s="21"/>
       <c r="B110" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="F110" s="4"/>
       <c r="G110" s="5"/>
@@ -4574,19 +4574,19 @@
     </row>
     <row r="111" spans="1:13" ht="13">
       <c r="A111" s="8" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="5"/>
@@ -4599,19 +4599,19 @@
     </row>
     <row r="112" spans="1:13" ht="13">
       <c r="A112" s="8" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="5"/>
@@ -4624,19 +4624,19 @@
     </row>
     <row r="113" spans="1:13" ht="14">
       <c r="A113" s="6" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="F113" s="6"/>
       <c r="G113" s="6"/>
@@ -4649,19 +4649,19 @@
     </row>
     <row r="114" spans="1:13" ht="14">
       <c r="A114" s="6" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
@@ -4674,19 +4674,19 @@
     </row>
     <row r="115" spans="1:13" ht="14">
       <c r="A115" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C115" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="B115" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C115" s="6" t="s">
-        <v>297</v>
-      </c>
       <c r="D115" s="9" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="F115" s="6"/>
       <c r="G115" s="6"/>
@@ -4699,19 +4699,19 @@
     </row>
     <row r="116" spans="1:13" ht="13">
       <c r="A116" s="6" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="F116" s="6"/>
       <c r="G116" s="6"/>
@@ -4724,19 +4724,19 @@
     </row>
     <row r="117" spans="1:13" ht="14">
       <c r="A117" s="6" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
@@ -4749,19 +4749,19 @@
     </row>
     <row r="118" spans="1:13" ht="13">
       <c r="A118" s="6" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="F118" s="6"/>
       <c r="G118" s="6"/>
@@ -4774,19 +4774,19 @@
     </row>
     <row r="119" spans="1:13" ht="13">
       <c r="A119" s="6" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F119" s="6"/>
       <c r="G119" s="6"/>
@@ -4799,19 +4799,19 @@
     </row>
     <row r="120" spans="1:13" ht="13">
       <c r="A120" s="6" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="F120" s="6"/>
       <c r="G120" s="6"/>
@@ -4824,19 +4824,19 @@
     </row>
     <row r="121" spans="1:13" ht="13">
       <c r="A121" s="6" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="F121" s="6"/>
       <c r="G121" s="6"/>
@@ -4851,13 +4851,13 @@
       <c r="A122" s="6"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="F122" s="6"/>
       <c r="G122" s="6"/>
@@ -4869,20 +4869,20 @@
       <c r="M122" s="6"/>
     </row>
     <row r="123" spans="1:13" ht="13">
-      <c r="A123" s="23" t="s">
-        <v>317</v>
-      </c>
-      <c r="B123" s="23" t="s">
-        <v>201</v>
+      <c r="A123" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="B123" s="20" t="s">
+        <v>197</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F123" s="6"/>
       <c r="G123" s="6"/>
@@ -4897,13 +4897,13 @@
       <c r="A124" s="21"/>
       <c r="B124" s="21"/>
       <c r="C124" s="6" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="F124" s="6"/>
       <c r="G124" s="6"/>
@@ -4917,16 +4917,16 @@
     <row r="125" spans="1:13" ht="13">
       <c r="A125" s="21"/>
       <c r="B125" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="F125" s="6"/>
       <c r="G125" s="6"/>
@@ -4940,16 +4940,16 @@
     <row r="126" spans="1:13" ht="13">
       <c r="A126" s="21"/>
       <c r="B126" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="F126" s="6"/>
       <c r="G126" s="6"/>
@@ -4962,17 +4962,17 @@
     </row>
     <row r="127" spans="1:13" ht="13">
       <c r="A127" s="21"/>
-      <c r="B127" s="23" t="s">
-        <v>112</v>
+      <c r="B127" s="20" t="s">
+        <v>109</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="F127" s="6"/>
       <c r="G127" s="6"/>
@@ -4987,13 +4987,13 @@
       <c r="A128" s="21"/>
       <c r="B128" s="21"/>
       <c r="C128" s="6" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="D128" s="12" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="E128" s="12" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="F128" s="6"/>
       <c r="G128" s="6"/>
@@ -5008,13 +5008,13 @@
       <c r="A129" s="21"/>
       <c r="B129" s="21"/>
       <c r="C129" s="6" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="D129" s="12" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="E129" s="12" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="F129" s="6"/>
       <c r="G129" s="6"/>
@@ -5029,13 +5029,13 @@
       <c r="A130" s="21"/>
       <c r="B130" s="21"/>
       <c r="C130" s="6" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="E130" s="12" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="F130" s="6"/>
       <c r="G130" s="6"/>
@@ -5050,13 +5050,13 @@
       <c r="A131" s="21"/>
       <c r="B131" s="21"/>
       <c r="C131" s="6" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="D131" s="11" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="E131" s="11" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="F131" s="6"/>
       <c r="G131" s="8"/>
@@ -5071,13 +5071,13 @@
       <c r="A132" s="21"/>
       <c r="B132" s="21"/>
       <c r="C132" s="6" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="E132" s="11" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F132" s="6"/>
       <c r="G132" s="13"/>
@@ -5092,13 +5092,13 @@
       <c r="A133" s="21"/>
       <c r="B133" s="21"/>
       <c r="C133" s="6" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="D133" s="11" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="E133" s="11" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="F133" s="6"/>
       <c r="G133" s="13"/>
@@ -5113,13 +5113,13 @@
       <c r="A134" s="21"/>
       <c r="B134" s="21"/>
       <c r="C134" s="6" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="D134" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E134" s="11" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="F134" s="6"/>
       <c r="G134" s="13"/>
@@ -5134,13 +5134,13 @@
       <c r="A135" s="21"/>
       <c r="B135" s="21"/>
       <c r="C135" s="6" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E135" s="11" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="F135" s="6"/>
       <c r="G135" s="13"/>
@@ -5155,13 +5155,13 @@
       <c r="A136" s="21"/>
       <c r="B136" s="21"/>
       <c r="C136" s="6" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="F136" s="6"/>
       <c r="G136" s="13"/>
@@ -5176,13 +5176,13 @@
       <c r="A137" s="21"/>
       <c r="B137" s="21"/>
       <c r="C137" s="6" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="F137" s="6"/>
       <c r="G137" s="13"/>
@@ -5197,13 +5197,13 @@
       <c r="A138" s="21"/>
       <c r="B138" s="21"/>
       <c r="C138" s="6" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="F138" s="6"/>
       <c r="G138" s="13"/>
@@ -5218,13 +5218,13 @@
       <c r="A139" s="21"/>
       <c r="B139" s="21"/>
       <c r="C139" s="6" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="F139" s="6"/>
       <c r="G139" s="13"/>
@@ -5239,13 +5239,13 @@
       <c r="A140" s="21"/>
       <c r="B140" s="6"/>
       <c r="C140" s="6" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="D140" s="14" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="E140" s="14" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="F140" s="6"/>
       <c r="G140" s="13"/>
@@ -5258,17 +5258,17 @@
     </row>
     <row r="141" spans="1:13" ht="14">
       <c r="A141" s="21"/>
-      <c r="B141" s="23" t="s">
+      <c r="B141" s="20" t="s">
         <v>11</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="F141" s="6"/>
       <c r="G141" s="13"/>
@@ -5283,13 +5283,13 @@
       <c r="A142" s="21"/>
       <c r="B142" s="21"/>
       <c r="C142" s="6" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="E142" s="9" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="F142" s="6"/>
       <c r="G142" s="13"/>
@@ -5302,19 +5302,19 @@
     </row>
     <row r="143" spans="1:13" ht="14">
       <c r="A143" s="22" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="B143" s="22" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="F143" s="6"/>
       <c r="G143" s="13"/>
@@ -5329,13 +5329,13 @@
       <c r="A144" s="21"/>
       <c r="B144" s="21"/>
       <c r="C144" s="2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="E144" s="9" t="s">
-        <v>377</v>
+        <v>600</v>
       </c>
       <c r="F144" s="6"/>
       <c r="G144" s="13"/>
@@ -5350,13 +5350,13 @@
       <c r="A145" s="21"/>
       <c r="B145" s="21"/>
       <c r="C145" s="2" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F145" s="6"/>
       <c r="G145" s="15"/>
@@ -5371,13 +5371,13 @@
       <c r="A146" s="21"/>
       <c r="B146" s="21"/>
       <c r="C146" s="6" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="F146" s="6"/>
       <c r="G146" s="6"/>
@@ -5392,13 +5392,13 @@
       <c r="A147" s="21"/>
       <c r="B147" s="21"/>
       <c r="C147" s="2" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="F147" s="6"/>
       <c r="G147" s="6"/>
@@ -5413,13 +5413,13 @@
       <c r="A148" s="21"/>
       <c r="B148" s="21"/>
       <c r="C148" s="2" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="F148" s="6"/>
       <c r="G148" s="6"/>
@@ -5434,13 +5434,13 @@
       <c r="A149" s="21"/>
       <c r="B149" s="21"/>
       <c r="C149" s="2" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="F149" s="6"/>
       <c r="G149" s="6"/>
@@ -5455,13 +5455,13 @@
       <c r="A150" s="21"/>
       <c r="B150" s="21"/>
       <c r="C150" s="2" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="F150" s="6"/>
       <c r="G150" s="6"/>
@@ -5476,13 +5476,13 @@
       <c r="A151" s="21"/>
       <c r="B151" s="21"/>
       <c r="C151" s="2" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="F151" s="6"/>
       <c r="G151" s="6"/>
@@ -5499,13 +5499,13 @@
         <v>11</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="F152" s="6"/>
       <c r="G152" s="6"/>
@@ -5520,13 +5520,13 @@
       <c r="A153" s="21"/>
       <c r="B153" s="21"/>
       <c r="C153" s="2" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="F153" s="6"/>
       <c r="G153" s="6"/>
@@ -5541,13 +5541,13 @@
       <c r="A154" s="21"/>
       <c r="B154" s="21"/>
       <c r="C154" s="16" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="F154" s="6"/>
       <c r="G154" s="6"/>
@@ -5562,13 +5562,13 @@
       <c r="A155" s="21"/>
       <c r="B155" s="21"/>
       <c r="C155" s="2" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="F155" s="6"/>
       <c r="G155" s="6"/>
@@ -5582,16 +5582,16 @@
     <row r="156" spans="1:13" ht="14">
       <c r="A156" s="21"/>
       <c r="B156" s="22" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="E156" s="3" t="s">
-        <v>413</v>
+        <v>404</v>
+      </c>
+      <c r="E156" s="19" t="s">
+        <v>601</v>
       </c>
       <c r="F156" s="6"/>
       <c r="G156" s="6"/>
@@ -5606,13 +5606,13 @@
       <c r="A157" s="21"/>
       <c r="B157" s="21"/>
       <c r="C157" s="2" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="F157" s="6"/>
       <c r="G157" s="6"/>
@@ -5627,13 +5627,13 @@
       <c r="A158" s="21"/>
       <c r="B158" s="21"/>
       <c r="C158" s="2" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="E158" s="9" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F158" s="6"/>
       <c r="G158" s="6"/>
@@ -5648,13 +5648,13 @@
       <c r="A159" s="21"/>
       <c r="B159" s="21"/>
       <c r="C159" s="2" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="F159" s="6"/>
       <c r="G159" s="6"/>
@@ -5669,13 +5669,13 @@
       <c r="A160" s="21"/>
       <c r="B160" s="21"/>
       <c r="C160" s="2" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="F160" s="6"/>
       <c r="G160" s="6"/>
@@ -5690,13 +5690,13 @@
       <c r="A161" s="21"/>
       <c r="B161" s="21"/>
       <c r="C161" s="2" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="F161" s="6"/>
       <c r="G161" s="6"/>
@@ -5711,13 +5711,13 @@
       <c r="A162" s="21"/>
       <c r="B162" s="21"/>
       <c r="C162" s="2" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="F162" s="6"/>
       <c r="G162" s="6"/>
@@ -5732,13 +5732,13 @@
       <c r="A163" s="21"/>
       <c r="B163" s="21"/>
       <c r="C163" s="2" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="F163" s="6"/>
       <c r="G163" s="6"/>
@@ -5753,13 +5753,13 @@
       <c r="A164" s="21"/>
       <c r="B164" s="21"/>
       <c r="C164" s="2" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="E164" s="9" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="F164" s="6"/>
       <c r="G164" s="6"/>
@@ -5774,13 +5774,13 @@
       <c r="A165" s="21"/>
       <c r="B165" s="21"/>
       <c r="C165" s="2" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="F165" s="6"/>
       <c r="G165" s="6"/>
@@ -5795,13 +5795,13 @@
       <c r="A166" s="21"/>
       <c r="B166" s="21"/>
       <c r="C166" s="2" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="E166" s="9" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="F166" s="6"/>
       <c r="G166" s="6"/>
@@ -5816,13 +5816,13 @@
       <c r="A167" s="21"/>
       <c r="B167" s="21"/>
       <c r="C167" s="2" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="F167" s="6"/>
       <c r="G167" s="6"/>
@@ -5837,13 +5837,13 @@
       <c r="A168" s="21"/>
       <c r="B168" s="21"/>
       <c r="C168" s="6" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="E168" s="17" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="F168" s="6"/>
       <c r="G168" s="6"/>
@@ -5858,13 +5858,13 @@
       <c r="A169" s="21"/>
       <c r="B169" s="21"/>
       <c r="C169" s="8" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="F169" s="6"/>
       <c r="G169" s="6"/>
@@ -5875,17 +5875,17 @@
       <c r="L169" s="6"/>
       <c r="M169" s="6"/>
     </row>
-    <row r="170" spans="1:13" ht="14">
+    <row r="170" spans="1:13" ht="13">
       <c r="A170" s="21"/>
       <c r="B170" s="21"/>
       <c r="C170" s="6" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="E170" s="9" t="s">
-        <v>455</v>
+        <v>445</v>
+      </c>
+      <c r="E170" s="19" t="s">
+        <v>602</v>
       </c>
       <c r="F170" s="6"/>
       <c r="G170" s="6"/>
@@ -5897,20 +5897,20 @@
       <c r="M170" s="6"/>
     </row>
     <row r="171" spans="1:13" ht="13">
-      <c r="A171" s="23" t="s">
-        <v>456</v>
+      <c r="A171" s="20" t="s">
+        <v>446</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="F171" s="6"/>
       <c r="G171" s="6"/>
@@ -5923,17 +5923,17 @@
     </row>
     <row r="172" spans="1:13" ht="28">
       <c r="A172" s="21"/>
-      <c r="B172" s="23" t="s">
-        <v>112</v>
+      <c r="B172" s="20" t="s">
+        <v>109</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="E172" s="9" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="F172" s="6"/>
       <c r="G172" s="6"/>
@@ -5946,15 +5946,15 @@
     </row>
     <row r="173" spans="1:13" ht="14">
       <c r="A173" s="21"/>
-      <c r="B173" s="23"/>
+      <c r="B173" s="20"/>
       <c r="C173" s="6" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="E173" s="9" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
@@ -5969,13 +5969,13 @@
       <c r="A174" s="21"/>
       <c r="B174" s="21"/>
       <c r="C174" s="6" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="F174" s="6"/>
       <c r="G174" s="6"/>
@@ -5987,20 +5987,20 @@
       <c r="M174" s="6"/>
     </row>
     <row r="175" spans="1:13" ht="13">
-      <c r="A175" s="23" t="s">
-        <v>466</v>
-      </c>
-      <c r="B175" s="23" t="s">
-        <v>201</v>
+      <c r="A175" s="20" t="s">
+        <v>456</v>
+      </c>
+      <c r="B175" s="20" t="s">
+        <v>197</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="F175" s="6"/>
       <c r="G175" s="6"/>
@@ -6015,13 +6015,13 @@
       <c r="A176" s="21"/>
       <c r="B176" s="21"/>
       <c r="C176" s="6" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="F176" s="6"/>
       <c r="G176" s="6"/>
@@ -6036,13 +6036,13 @@
       <c r="A177" s="21"/>
       <c r="B177" s="21"/>
       <c r="C177" s="6" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="D177" s="9" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="E177" s="9" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="F177" s="6"/>
       <c r="G177" s="6"/>
@@ -6057,13 +6057,13 @@
       <c r="A178" s="21"/>
       <c r="B178" s="21"/>
       <c r="C178" s="8" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="D178" s="9" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="E178" s="9" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="F178" s="6"/>
       <c r="G178" s="6"/>
@@ -6076,17 +6076,17 @@
     </row>
     <row r="179" spans="1:13" ht="14">
       <c r="A179" s="21"/>
-      <c r="B179" s="23" t="s">
+      <c r="B179" s="20" t="s">
         <v>11</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="D179" s="9" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="F179" s="6"/>
       <c r="G179" s="6"/>
@@ -6101,13 +6101,13 @@
       <c r="A180" s="21"/>
       <c r="B180" s="21"/>
       <c r="C180" s="8" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="D180" s="9" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="E180" s="9" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="F180" s="6"/>
       <c r="G180" s="6"/>
@@ -6122,13 +6122,13 @@
       <c r="A181" s="21"/>
       <c r="B181" s="21"/>
       <c r="C181" s="8" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="D181" s="9" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="F181" s="6"/>
       <c r="G181" s="6"/>
@@ -6143,13 +6143,13 @@
       <c r="A182" s="21"/>
       <c r="B182" s="21"/>
       <c r="C182" s="8" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="D182" s="9" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="E182" s="9" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="F182" s="6"/>
       <c r="G182" s="6"/>
@@ -6164,13 +6164,13 @@
       <c r="A183" s="21"/>
       <c r="B183" s="21"/>
       <c r="C183" s="8" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="D183" s="9" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="F183" s="6"/>
       <c r="G183" s="6"/>
@@ -6185,13 +6185,13 @@
       <c r="A184" s="21"/>
       <c r="B184" s="21"/>
       <c r="C184" s="8" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="D184" s="9" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="E184" s="9" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="F184" s="6"/>
       <c r="G184" s="6"/>
@@ -6204,17 +6204,17 @@
     </row>
     <row r="185" spans="1:13" ht="14">
       <c r="A185" s="21"/>
-      <c r="B185" s="23" t="s">
-        <v>112</v>
+      <c r="B185" s="20" t="s">
+        <v>109</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="D185" s="9" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="E185" s="8" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="F185" s="6"/>
       <c r="G185" s="6"/>
@@ -6229,13 +6229,13 @@
       <c r="A186" s="21"/>
       <c r="B186" s="21"/>
       <c r="C186" s="6" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="D186" s="9" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="E186" s="9" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="F186" s="6"/>
       <c r="G186" s="6"/>
@@ -6250,13 +6250,13 @@
       <c r="A187" s="21"/>
       <c r="B187" s="21"/>
       <c r="C187" s="6" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="D187" s="18" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="E187" s="9" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="F187" s="6"/>
       <c r="G187" s="6"/>
@@ -6271,13 +6271,13 @@
       <c r="A188" s="21"/>
       <c r="B188" s="21"/>
       <c r="C188" s="6" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D188" s="9" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="E188" s="9" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="F188" s="6"/>
       <c r="G188" s="6"/>
@@ -6292,13 +6292,13 @@
       <c r="A189" s="21"/>
       <c r="B189" s="21"/>
       <c r="C189" s="6" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="F189" s="6"/>
       <c r="G189" s="6"/>
@@ -6313,13 +6313,13 @@
       <c r="A190" s="21"/>
       <c r="B190" s="21"/>
       <c r="C190" s="6" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="F190" s="6"/>
       <c r="G190" s="6"/>
@@ -6332,17 +6332,17 @@
     </row>
     <row r="191" spans="1:13" ht="28">
       <c r="A191" s="21"/>
-      <c r="B191" s="23" t="s">
-        <v>118</v>
+      <c r="B191" s="20" t="s">
+        <v>115</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="F191" s="6"/>
       <c r="G191" s="6"/>
@@ -6357,13 +6357,13 @@
       <c r="A192" s="21"/>
       <c r="B192" s="21"/>
       <c r="C192" s="8" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="F192" s="6"/>
       <c r="G192" s="6"/>
@@ -6378,13 +6378,13 @@
       <c r="A193" s="21"/>
       <c r="B193" s="21"/>
       <c r="C193" s="8" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="E193" s="8" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="F193" s="6"/>
       <c r="G193" s="6"/>
@@ -6396,20 +6396,20 @@
       <c r="M193" s="6"/>
     </row>
     <row r="194" spans="1:13" ht="14">
-      <c r="A194" s="23" t="s">
-        <v>523</v>
-      </c>
-      <c r="B194" s="23" t="s">
-        <v>524</v>
+      <c r="A194" s="20" t="s">
+        <v>513</v>
+      </c>
+      <c r="B194" s="20" t="s">
+        <v>514</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="F194" s="6"/>
       <c r="G194" s="6"/>
@@ -6424,13 +6424,13 @@
       <c r="A195" s="21"/>
       <c r="B195" s="21"/>
       <c r="C195" s="6" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="F195" s="6"/>
       <c r="G195" s="6"/>
@@ -6445,13 +6445,13 @@
       <c r="A196" s="21"/>
       <c r="B196" s="21"/>
       <c r="C196" s="6" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="F196" s="6"/>
       <c r="G196" s="6"/>
@@ -6466,13 +6466,13 @@
       <c r="A197" s="21"/>
       <c r="B197" s="21"/>
       <c r="C197" s="6" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="F197" s="6"/>
       <c r="G197" s="6"/>
@@ -6485,17 +6485,17 @@
     </row>
     <row r="198" spans="1:13" ht="14">
       <c r="A198" s="21"/>
-      <c r="B198" s="23" t="s">
-        <v>118</v>
+      <c r="B198" s="20" t="s">
+        <v>115</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="F198" s="6"/>
       <c r="G198" s="6"/>
@@ -6510,13 +6510,13 @@
       <c r="A199" s="21"/>
       <c r="B199" s="21"/>
       <c r="C199" s="6" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="F199" s="6"/>
       <c r="G199" s="6"/>
@@ -6529,19 +6529,19 @@
     </row>
     <row r="200" spans="1:13" ht="14">
       <c r="A200" s="6" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="F200" s="6"/>
       <c r="G200" s="6"/>
@@ -6554,19 +6554,19 @@
     </row>
     <row r="201" spans="1:13" ht="13">
       <c r="A201" s="6" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="D201" s="10" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="F201" s="6"/>
       <c r="G201" s="6"/>
@@ -6579,19 +6579,19 @@
     </row>
     <row r="202" spans="1:13" ht="14">
       <c r="A202" s="6" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="F202" s="6"/>
       <c r="G202" s="6"/>
@@ -6605,16 +6605,16 @@
     <row r="203" spans="1:13" ht="14">
       <c r="A203" s="6"/>
       <c r="B203" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="D203" s="9" t="s">
         <v>33</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="F203" s="6"/>
       <c r="G203" s="6"/>
@@ -6758,24 +6758,11 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="A123:A142"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="B127:B139"/>
-    <mergeCell ref="B141:B142"/>
-    <mergeCell ref="B143:B151"/>
-    <mergeCell ref="A143:A170"/>
-    <mergeCell ref="B152:B155"/>
-    <mergeCell ref="B156:B170"/>
-    <mergeCell ref="A171:A174"/>
-    <mergeCell ref="A175:A193"/>
-    <mergeCell ref="A194:A199"/>
-    <mergeCell ref="B172:B174"/>
-    <mergeCell ref="B175:B178"/>
-    <mergeCell ref="B179:B184"/>
-    <mergeCell ref="B185:B190"/>
-    <mergeCell ref="B191:B193"/>
-    <mergeCell ref="B194:B197"/>
-    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="A4:A47"/>
+    <mergeCell ref="B4:B37"/>
+    <mergeCell ref="B44:B47"/>
     <mergeCell ref="A51:A84"/>
     <mergeCell ref="B51:B60"/>
     <mergeCell ref="B103:B105"/>
@@ -6787,11 +6774,24 @@
     <mergeCell ref="A94:A105"/>
     <mergeCell ref="B94:B100"/>
     <mergeCell ref="A106:A110"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A4:A47"/>
-    <mergeCell ref="B4:B37"/>
-    <mergeCell ref="B44:B47"/>
+    <mergeCell ref="A171:A174"/>
+    <mergeCell ref="A175:A193"/>
+    <mergeCell ref="A194:A199"/>
+    <mergeCell ref="B172:B174"/>
+    <mergeCell ref="B175:B178"/>
+    <mergeCell ref="B179:B184"/>
+    <mergeCell ref="B185:B190"/>
+    <mergeCell ref="B191:B193"/>
+    <mergeCell ref="B194:B197"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="A123:A142"/>
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="B127:B139"/>
+    <mergeCell ref="B141:B142"/>
+    <mergeCell ref="B143:B151"/>
+    <mergeCell ref="A143:A170"/>
+    <mergeCell ref="B152:B155"/>
+    <mergeCell ref="B156:B170"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/scripts/i18n.xlsx
+++ b/scripts/i18n.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juyeonkim/Documents/pfplay-web/scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522C75AD-717F-0A41-B134-7B7081528BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A28D84E-AD2B-2947-AD2D-077E0C5896A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2300" yWindow="500" windowWidth="26500" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1240" yWindow="520" windowWidth="26500" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="i18n" sheetId="1" r:id="rId1"/>
@@ -1330,28 +1330,10 @@
     <t>dj.para.dj_in_order</t>
   </si>
   <si>
-    <t>대기 중인 DJ 한명씩 순서대로 음악을 디제잉 합니다</t>
-  </si>
-  <si>
-    <t>DJing one person at a time from the waiting list, in order</t>
-  </si>
-  <si>
     <t>dj.para.played_sequentially</t>
   </si>
   <si>
-    <t>플레이리스트의 가장 상단에 있는 곡부터 순차적으로 한명당 하나씩 플레이됩니다</t>
-  </si>
-  <si>
-    <t>Songs from the top of the playlist are played sequentially, one song per person</t>
-  </si>
-  <si>
     <t>dj.para.display_count</t>
-  </si>
-  <si>
-    <t>노래가 끝나면 디제잉하는 동안 받은 좋아요, 그랩, 싫어요를 카운팅해 보여드려요.</t>
-  </si>
-  <si>
-    <t>Once the song ends, we'll display a count of the Like, Grab, and Boo received during your DJ set.</t>
   </si>
   <si>
     <t>dj.para.empty_dj</t>
@@ -1831,13 +1813,151 @@
   </si>
   <si>
     <t>zZz...No DJ currently playing...</t>
+  </si>
+  <si>
+    <r>
+      <t>대기 중인 DJ **한명씩**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFEBCB8B"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFA3BE8C"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> **순서대로** 음악을 디제잉 합니다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">플레이리스트의 가장 상단에 있는 곡부터 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFEBCB8B"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFA3BE8C"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> **순차적으로 한명당 하나씩 플레이**됩니다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">노래가 끝나면 디제잉하는 동안 받은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFEBCB8B"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFA3BE8C"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> **좋아요, 그랩, 싫어요**를 카운팅해 보여드려요.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DJing **one person at a time** </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFEBCB8B"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFA3BE8C"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> from the waiting list, in order</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Songs from the top of the playlist are </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFEBCB8B"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFA3BE8C"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> **played sequentially, one song per person**</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Once the song ends, we'll display </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFEBCB8B"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFA3BE8C"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> a count of the **Like, Grab, and Boo** received during your DJ set.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1886,6 +2006,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFA3BE8C"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFEBCB8B"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1925,7 +2057,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1969,25 +2101,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2220,12 +2349,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -2237,12 +2366,12 @@
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -2284,10 +2413,10 @@
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -2309,8 +2438,8 @@
       <c r="M4" s="4"/>
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
       <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
@@ -2330,8 +2459,8 @@
       <c r="M5" s="4"/>
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
       <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
@@ -2339,7 +2468,7 @@
         <v>18</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="5"/>
@@ -2351,8 +2480,8 @@
       <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
       <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
@@ -2372,8 +2501,8 @@
       <c r="M7" s="4"/>
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
       <c r="C8" s="2" t="s">
         <v>23</v>
       </c>
@@ -2393,8 +2522,8 @@
       <c r="M8" s="4"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
       <c r="C9" s="2" t="s">
         <v>26</v>
       </c>
@@ -2414,8 +2543,8 @@
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
       <c r="C10" s="2" t="s">
         <v>29</v>
       </c>
@@ -2435,8 +2564,8 @@
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A11" s="21"/>
-      <c r="B11" s="21"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
       <c r="C11" s="2" t="s">
         <v>32</v>
       </c>
@@ -2444,7 +2573,7 @@
         <v>33</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="5"/>
@@ -2456,8 +2585,8 @@
       <c r="M11" s="4"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
       <c r="C12" s="2" t="s">
         <v>34</v>
       </c>
@@ -2477,8 +2606,8 @@
       <c r="M12" s="4"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A13" s="21"/>
-      <c r="B13" s="21"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
       <c r="C13" s="2" t="s">
         <v>37</v>
       </c>
@@ -2498,16 +2627,16 @@
       <c r="M13" s="4"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A14" s="21"/>
-      <c r="B14" s="21"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
       <c r="C14" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="5"/>
@@ -2519,8 +2648,8 @@
       <c r="M14" s="4"/>
     </row>
     <row r="15" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
       <c r="C15" s="2" t="s">
         <v>40</v>
       </c>
@@ -2540,8 +2669,8 @@
       <c r="M15" s="4"/>
     </row>
     <row r="16" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
       <c r="C16" s="2" t="s">
         <v>43</v>
       </c>
@@ -2561,8 +2690,8 @@
       <c r="M16" s="4"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
       <c r="C17" s="2" t="s">
         <v>46</v>
       </c>
@@ -2582,8 +2711,8 @@
       <c r="M17" s="4"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
       <c r="C18" s="2" t="s">
         <v>49</v>
       </c>
@@ -2603,8 +2732,8 @@
       <c r="M18" s="4"/>
     </row>
     <row r="19" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A19" s="21"/>
-      <c r="B19" s="21"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
       <c r="C19" s="2" t="s">
         <v>52</v>
       </c>
@@ -2624,8 +2753,8 @@
       <c r="M19" s="4"/>
     </row>
     <row r="20" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A20" s="21"/>
-      <c r="B20" s="21"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
       <c r="C20" s="2" t="s">
         <v>55</v>
       </c>
@@ -2645,8 +2774,8 @@
       <c r="M20" s="4"/>
     </row>
     <row r="21" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A21" s="21"/>
-      <c r="B21" s="21"/>
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
       <c r="C21" s="6" t="s">
         <v>58</v>
       </c>
@@ -2666,8 +2795,8 @@
       <c r="M21" s="4"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A22" s="21"/>
-      <c r="B22" s="21"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
       <c r="C22" s="2" t="s">
         <v>61</v>
       </c>
@@ -2687,8 +2816,8 @@
       <c r="M22" s="4"/>
     </row>
     <row r="23" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A23" s="21"/>
-      <c r="B23" s="21"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
       <c r="C23" s="2" t="s">
         <v>64</v>
       </c>
@@ -2708,8 +2837,8 @@
       <c r="M23" s="4"/>
     </row>
     <row r="24" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21"/>
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
       <c r="C24" s="7" t="s">
         <v>67</v>
       </c>
@@ -2729,8 +2858,8 @@
       <c r="M24" s="4"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A25" s="21"/>
-      <c r="B25" s="21"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
       <c r="C25" s="7" t="s">
         <v>70</v>
       </c>
@@ -2750,8 +2879,8 @@
       <c r="M25" s="4"/>
     </row>
     <row r="26" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A26" s="21"/>
-      <c r="B26" s="21"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
       <c r="C26" s="7" t="s">
         <v>73</v>
       </c>
@@ -2771,8 +2900,8 @@
       <c r="M26" s="4"/>
     </row>
     <row r="27" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A27" s="21"/>
-      <c r="B27" s="21"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
       <c r="C27" s="7" t="s">
         <v>76</v>
       </c>
@@ -2792,8 +2921,8 @@
       <c r="M27" s="4"/>
     </row>
     <row r="28" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A28" s="21"/>
-      <c r="B28" s="21"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
       <c r="C28" s="7" t="s">
         <v>79</v>
       </c>
@@ -2813,8 +2942,8 @@
       <c r="M28" s="4"/>
     </row>
     <row r="29" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A29" s="21"/>
-      <c r="B29" s="21"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
       <c r="C29" s="7" t="s">
         <v>82</v>
       </c>
@@ -2834,8 +2963,8 @@
       <c r="M29" s="4"/>
     </row>
     <row r="30" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A30" s="21"/>
-      <c r="B30" s="21"/>
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
       <c r="C30" s="2" t="s">
         <v>85</v>
       </c>
@@ -2855,8 +2984,8 @@
       <c r="M30" s="4"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A31" s="21"/>
-      <c r="B31" s="21"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
       <c r="C31" s="2" t="s">
         <v>88</v>
       </c>
@@ -2876,8 +3005,8 @@
       <c r="M31" s="4"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A32" s="21"/>
-      <c r="B32" s="21"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
       <c r="C32" s="6" t="s">
         <v>91</v>
       </c>
@@ -2897,8 +3026,8 @@
       <c r="M32" s="4"/>
     </row>
     <row r="33" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A33" s="21"/>
-      <c r="B33" s="21"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="20"/>
       <c r="C33" s="6" t="s">
         <v>93</v>
       </c>
@@ -2918,8 +3047,8 @@
       <c r="M33" s="4"/>
     </row>
     <row r="34" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A34" s="21"/>
-      <c r="B34" s="21"/>
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
       <c r="C34" s="6" t="s">
         <v>96</v>
       </c>
@@ -2939,8 +3068,8 @@
       <c r="M34" s="4"/>
     </row>
     <row r="35" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A35" s="21"/>
-      <c r="B35" s="21"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="20"/>
       <c r="C35" s="6" t="s">
         <v>98</v>
       </c>
@@ -2960,16 +3089,16 @@
       <c r="M35" s="4"/>
     </row>
     <row r="36" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A36" s="21"/>
-      <c r="B36" s="21"/>
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
       <c r="C36" s="6" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="5"/>
@@ -2981,16 +3110,16 @@
       <c r="M36" s="4"/>
     </row>
     <row r="37" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A37" s="21"/>
-      <c r="B37" s="21"/>
+      <c r="A37" s="20"/>
+      <c r="B37" s="20"/>
       <c r="C37" s="6" t="s">
         <v>99</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E37" s="19" t="s">
-        <v>593</v>
+      <c r="E37" s="18" t="s">
+        <v>587</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="5"/>
@@ -3002,7 +3131,7 @@
       <c r="M37" s="4"/>
     </row>
     <row r="38" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A38" s="21"/>
+      <c r="A38" s="20"/>
       <c r="B38" s="2"/>
       <c r="C38" s="6" t="s">
         <v>101</v>
@@ -3010,8 +3139,8 @@
       <c r="D38" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E38" s="19" t="s">
-        <v>594</v>
+      <c r="E38" s="18" t="s">
+        <v>588</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="5"/>
@@ -3023,7 +3152,7 @@
       <c r="M38" s="4"/>
     </row>
     <row r="39" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A39" s="21"/>
+      <c r="A39" s="20"/>
       <c r="B39" s="2"/>
       <c r="C39" s="6" t="s">
         <v>103</v>
@@ -3044,7 +3173,7 @@
       <c r="M39" s="4"/>
     </row>
     <row r="40" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A40" s="21"/>
+      <c r="A40" s="20"/>
       <c r="B40" s="2"/>
       <c r="C40" s="6" t="s">
         <v>106</v>
@@ -3065,7 +3194,7 @@
       <c r="M40" s="4"/>
     </row>
     <row r="41" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A41" s="21"/>
+      <c r="A41" s="20"/>
       <c r="B41" s="2" t="s">
         <v>109</v>
       </c>
@@ -3088,16 +3217,16 @@
       <c r="M41" s="4"/>
     </row>
     <row r="42" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A42" s="21"/>
+      <c r="A42" s="20"/>
       <c r="B42" s="2"/>
       <c r="C42" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>564</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="5"/>
@@ -3109,7 +3238,7 @@
       <c r="M42" s="4"/>
     </row>
     <row r="43" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A43" s="21"/>
+      <c r="A43" s="20"/>
       <c r="B43" s="2" t="s">
         <v>109</v>
       </c>
@@ -3132,8 +3261,8 @@
       <c r="M43" s="4"/>
     </row>
     <row r="44" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A44" s="21"/>
-      <c r="B44" s="22" t="s">
+      <c r="A44" s="20"/>
+      <c r="B44" s="21" t="s">
         <v>115</v>
       </c>
       <c r="C44" s="6" t="s">
@@ -3155,8 +3284,8 @@
       <c r="M44" s="4"/>
     </row>
     <row r="45" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A45" s="21"/>
-      <c r="B45" s="21"/>
+      <c r="A45" s="20"/>
+      <c r="B45" s="20"/>
       <c r="C45" s="8" t="s">
         <v>119</v>
       </c>
@@ -3176,8 +3305,8 @@
       <c r="M45" s="4"/>
     </row>
     <row r="46" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A46" s="21"/>
-      <c r="B46" s="21"/>
+      <c r="A46" s="20"/>
+      <c r="B46" s="20"/>
       <c r="C46" s="8" t="s">
         <v>122</v>
       </c>
@@ -3197,8 +3326,8 @@
       <c r="M46" s="4"/>
     </row>
     <row r="47" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A47" s="21"/>
-      <c r="B47" s="21"/>
+      <c r="A47" s="20"/>
+      <c r="B47" s="20"/>
       <c r="C47" s="8" t="s">
         <v>125</v>
       </c>
@@ -3281,10 +3410,10 @@
       <c r="M50" s="4"/>
     </row>
     <row r="51" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A51" s="22" t="s">
+      <c r="A51" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="B51" s="20" t="s">
+      <c r="B51" s="22" t="s">
         <v>109</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -3306,8 +3435,8 @@
       <c r="M51" s="4"/>
     </row>
     <row r="52" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A52" s="21"/>
-      <c r="B52" s="21"/>
+      <c r="A52" s="20"/>
+      <c r="B52" s="20"/>
       <c r="C52" s="2" t="s">
         <v>141</v>
       </c>
@@ -3327,16 +3456,16 @@
       <c r="M52" s="4"/>
     </row>
     <row r="53" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21"/>
+      <c r="A53" s="20"/>
+      <c r="B53" s="20"/>
       <c r="C53" s="2" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="5"/>
@@ -3348,16 +3477,16 @@
       <c r="M53" s="4"/>
     </row>
     <row r="54" spans="1:13" ht="13">
-      <c r="A54" s="21"/>
-      <c r="B54" s="21"/>
+      <c r="A54" s="20"/>
+      <c r="B54" s="20"/>
       <c r="C54" s="6" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="5"/>
@@ -3369,16 +3498,16 @@
       <c r="M54" s="4"/>
     </row>
     <row r="55" spans="1:13" ht="13">
-      <c r="A55" s="21"/>
-      <c r="B55" s="21"/>
+      <c r="A55" s="20"/>
+      <c r="B55" s="20"/>
       <c r="C55" s="6" t="s">
         <v>144</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E55" s="19" t="s">
-        <v>595</v>
+      <c r="E55" s="18" t="s">
+        <v>589</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="5"/>
@@ -3390,8 +3519,8 @@
       <c r="M55" s="4"/>
     </row>
     <row r="56" spans="1:13" ht="13">
-      <c r="A56" s="21"/>
-      <c r="B56" s="21"/>
+      <c r="A56" s="20"/>
+      <c r="B56" s="20"/>
       <c r="C56" s="6" t="s">
         <v>146</v>
       </c>
@@ -3411,8 +3540,8 @@
       <c r="M56" s="4"/>
     </row>
     <row r="57" spans="1:13" ht="13">
-      <c r="A57" s="21"/>
-      <c r="B57" s="21"/>
+      <c r="A57" s="20"/>
+      <c r="B57" s="20"/>
       <c r="C57" s="6" t="s">
         <v>149</v>
       </c>
@@ -3432,8 +3561,8 @@
       <c r="M57" s="4"/>
     </row>
     <row r="58" spans="1:13" ht="14">
-      <c r="A58" s="21"/>
-      <c r="B58" s="21"/>
+      <c r="A58" s="20"/>
+      <c r="B58" s="20"/>
       <c r="C58" s="6" t="s">
         <v>152</v>
       </c>
@@ -3453,8 +3582,8 @@
       <c r="M58" s="4"/>
     </row>
     <row r="59" spans="1:13" ht="13">
-      <c r="A59" s="21"/>
-      <c r="B59" s="21"/>
+      <c r="A59" s="20"/>
+      <c r="B59" s="20"/>
       <c r="C59" s="6" t="s">
         <v>155</v>
       </c>
@@ -3474,8 +3603,8 @@
       <c r="M59" s="4"/>
     </row>
     <row r="60" spans="1:13" ht="13">
-      <c r="A60" s="21"/>
-      <c r="B60" s="21"/>
+      <c r="A60" s="20"/>
+      <c r="B60" s="20"/>
       <c r="C60" s="6" t="s">
         <v>158</v>
       </c>
@@ -3495,7 +3624,7 @@
       <c r="M60" s="4"/>
     </row>
     <row r="61" spans="1:13" ht="13">
-      <c r="A61" s="21"/>
+      <c r="A61" s="20"/>
       <c r="B61" s="6"/>
       <c r="C61" s="3" t="s">
         <v>161</v>
@@ -3516,7 +3645,7 @@
       <c r="M61" s="4"/>
     </row>
     <row r="62" spans="1:13" ht="13">
-      <c r="A62" s="21"/>
+      <c r="A62" s="20"/>
       <c r="B62" s="6"/>
       <c r="C62" s="3" t="s">
         <v>164</v>
@@ -3537,7 +3666,7 @@
       <c r="M62" s="4"/>
     </row>
     <row r="63" spans="1:13" ht="13">
-      <c r="A63" s="21"/>
+      <c r="A63" s="20"/>
       <c r="B63" s="6"/>
       <c r="C63" s="3" t="s">
         <v>167</v>
@@ -3558,7 +3687,7 @@
       <c r="M63" s="4"/>
     </row>
     <row r="64" spans="1:13" ht="13">
-      <c r="A64" s="21"/>
+      <c r="A64" s="20"/>
       <c r="B64" s="6"/>
       <c r="C64" s="3" t="s">
         <v>170</v>
@@ -3579,7 +3708,7 @@
       <c r="M64" s="4"/>
     </row>
     <row r="65" spans="1:13" ht="13">
-      <c r="A65" s="21"/>
+      <c r="A65" s="20"/>
       <c r="B65" s="6"/>
       <c r="C65" s="3" t="s">
         <v>173</v>
@@ -3600,7 +3729,7 @@
       <c r="M65" s="4"/>
     </row>
     <row r="66" spans="1:13" ht="13">
-      <c r="A66" s="21"/>
+      <c r="A66" s="20"/>
       <c r="B66" s="6"/>
       <c r="C66" s="3" t="s">
         <v>176</v>
@@ -3621,7 +3750,7 @@
       <c r="M66" s="4"/>
     </row>
     <row r="67" spans="1:13" ht="13">
-      <c r="A67" s="21"/>
+      <c r="A67" s="20"/>
       <c r="B67" s="6"/>
       <c r="C67" s="3" t="s">
         <v>179</v>
@@ -3642,7 +3771,7 @@
       <c r="M67" s="4"/>
     </row>
     <row r="68" spans="1:13" ht="13">
-      <c r="A68" s="21"/>
+      <c r="A68" s="20"/>
       <c r="B68" s="6"/>
       <c r="C68" s="3" t="s">
         <v>182</v>
@@ -3663,7 +3792,7 @@
       <c r="M68" s="4"/>
     </row>
     <row r="69" spans="1:13" ht="13">
-      <c r="A69" s="21"/>
+      <c r="A69" s="20"/>
       <c r="B69" s="6"/>
       <c r="C69" s="3" t="s">
         <v>185</v>
@@ -3684,7 +3813,7 @@
       <c r="M69" s="4"/>
     </row>
     <row r="70" spans="1:13" ht="13">
-      <c r="A70" s="21"/>
+      <c r="A70" s="20"/>
       <c r="B70" s="6"/>
       <c r="C70" s="3" t="s">
         <v>188</v>
@@ -3705,8 +3834,8 @@
       <c r="M70" s="4"/>
     </row>
     <row r="71" spans="1:13" ht="13">
-      <c r="A71" s="21"/>
-      <c r="B71" s="20" t="s">
+      <c r="A71" s="20"/>
+      <c r="B71" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -3728,16 +3857,16 @@
       <c r="M71" s="4"/>
     </row>
     <row r="72" spans="1:13" ht="13">
-      <c r="A72" s="21"/>
-      <c r="B72" s="20"/>
+      <c r="A72" s="20"/>
+      <c r="B72" s="22"/>
       <c r="C72" s="6" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="5"/>
@@ -3749,16 +3878,16 @@
       <c r="M72" s="4"/>
     </row>
     <row r="73" spans="1:13" ht="13">
-      <c r="A73" s="21"/>
-      <c r="B73" s="20"/>
+      <c r="A73" s="20"/>
+      <c r="B73" s="22"/>
       <c r="C73" s="6" t="s">
-        <v>556</v>
-      </c>
-      <c r="D73" s="19" t="s">
-        <v>555</v>
-      </c>
-      <c r="E73" s="19" t="s">
-        <v>554</v>
+        <v>550</v>
+      </c>
+      <c r="D73" s="18" t="s">
+        <v>549</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>548</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="5"/>
@@ -3770,16 +3899,16 @@
       <c r="M73" s="4"/>
     </row>
     <row r="74" spans="1:13" ht="13">
-      <c r="A74" s="21"/>
-      <c r="B74" s="20"/>
+      <c r="A74" s="20"/>
+      <c r="B74" s="22"/>
       <c r="C74" s="6" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="5"/>
@@ -3791,16 +3920,16 @@
       <c r="M74" s="4"/>
     </row>
     <row r="75" spans="1:13" ht="13">
-      <c r="A75" s="21"/>
-      <c r="B75" s="20"/>
+      <c r="A75" s="20"/>
+      <c r="B75" s="22"/>
       <c r="C75" s="6" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="5"/>
@@ -3812,16 +3941,16 @@
       <c r="M75" s="4"/>
     </row>
     <row r="76" spans="1:13" ht="13">
-      <c r="A76" s="21"/>
-      <c r="B76" s="20"/>
+      <c r="A76" s="20"/>
+      <c r="B76" s="22"/>
       <c r="C76" s="6" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="F76" s="4"/>
       <c r="G76" s="5"/>
@@ -3833,8 +3962,8 @@
       <c r="M76" s="4"/>
     </row>
     <row r="77" spans="1:13" ht="13">
-      <c r="A77" s="21"/>
-      <c r="B77" s="21"/>
+      <c r="A77" s="20"/>
+      <c r="B77" s="20"/>
       <c r="C77" s="6" t="s">
         <v>194</v>
       </c>
@@ -3854,8 +3983,8 @@
       <c r="M77" s="4"/>
     </row>
     <row r="78" spans="1:13" ht="13">
-      <c r="A78" s="21"/>
-      <c r="B78" s="20" t="s">
+      <c r="A78" s="20"/>
+      <c r="B78" s="22" t="s">
         <v>197</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -3877,8 +4006,8 @@
       <c r="M78" s="4"/>
     </row>
     <row r="79" spans="1:13" ht="13">
-      <c r="A79" s="21"/>
-      <c r="B79" s="21"/>
+      <c r="A79" s="20"/>
+      <c r="B79" s="20"/>
       <c r="C79" s="6" t="s">
         <v>201</v>
       </c>
@@ -3898,8 +4027,8 @@
       <c r="M79" s="4"/>
     </row>
     <row r="80" spans="1:13" ht="13">
-      <c r="A80" s="21"/>
-      <c r="B80" s="21"/>
+      <c r="A80" s="20"/>
+      <c r="B80" s="20"/>
       <c r="C80" s="6" t="s">
         <v>204</v>
       </c>
@@ -3919,8 +4048,8 @@
       <c r="M80" s="4"/>
     </row>
     <row r="81" spans="1:13" ht="13">
-      <c r="A81" s="21"/>
-      <c r="B81" s="21"/>
+      <c r="A81" s="20"/>
+      <c r="B81" s="20"/>
       <c r="C81" s="6" t="s">
         <v>206</v>
       </c>
@@ -3940,8 +4069,8 @@
       <c r="M81" s="4"/>
     </row>
     <row r="82" spans="1:13" ht="13">
-      <c r="A82" s="21"/>
-      <c r="B82" s="21"/>
+      <c r="A82" s="20"/>
+      <c r="B82" s="20"/>
       <c r="C82" s="6" t="s">
         <v>208</v>
       </c>
@@ -3961,8 +4090,8 @@
       <c r="M82" s="4"/>
     </row>
     <row r="83" spans="1:13" ht="13">
-      <c r="A83" s="21"/>
-      <c r="B83" s="21"/>
+      <c r="A83" s="20"/>
+      <c r="B83" s="20"/>
       <c r="C83" s="6" t="s">
         <v>210</v>
       </c>
@@ -3982,8 +4111,8 @@
       <c r="M83" s="4"/>
     </row>
     <row r="84" spans="1:13" ht="13">
-      <c r="A84" s="21"/>
-      <c r="B84" s="21"/>
+      <c r="A84" s="20"/>
+      <c r="B84" s="20"/>
       <c r="C84" s="6" t="s">
         <v>212</v>
       </c>
@@ -4003,10 +4132,10 @@
       <c r="M84" s="4"/>
     </row>
     <row r="85" spans="1:13" ht="14">
-      <c r="A85" s="20" t="s">
+      <c r="A85" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="B85" s="20" t="s">
+      <c r="B85" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C85" s="9" t="s">
@@ -4028,8 +4157,8 @@
       <c r="M85" s="4"/>
     </row>
     <row r="86" spans="1:13" ht="14">
-      <c r="A86" s="21"/>
-      <c r="B86" s="21"/>
+      <c r="A86" s="20"/>
+      <c r="B86" s="20"/>
       <c r="C86" s="6" t="s">
         <v>217</v>
       </c>
@@ -4049,16 +4178,16 @@
       <c r="M86" s="4"/>
     </row>
     <row r="87" spans="1:13" ht="13">
-      <c r="A87" s="21"/>
-      <c r="B87" s="21"/>
+      <c r="A87" s="20"/>
+      <c r="B87" s="20"/>
       <c r="C87" s="6" t="s">
         <v>219</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E87" s="19" t="s">
-        <v>597</v>
+      <c r="E87" s="18" t="s">
+        <v>591</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="5"/>
@@ -4070,8 +4199,8 @@
       <c r="M87" s="4"/>
     </row>
     <row r="88" spans="1:13" ht="13">
-      <c r="A88" s="21"/>
-      <c r="B88" s="21"/>
+      <c r="A88" s="20"/>
+      <c r="B88" s="20"/>
       <c r="C88" s="6" t="s">
         <v>221</v>
       </c>
@@ -4091,8 +4220,8 @@
       <c r="M88" s="4"/>
     </row>
     <row r="89" spans="1:13" ht="13">
-      <c r="A89" s="21"/>
-      <c r="B89" s="21"/>
+      <c r="A89" s="20"/>
+      <c r="B89" s="20"/>
       <c r="C89" s="6" t="s">
         <v>224</v>
       </c>
@@ -4112,8 +4241,8 @@
       <c r="M89" s="4"/>
     </row>
     <row r="90" spans="1:13" ht="13">
-      <c r="A90" s="21"/>
-      <c r="B90" s="21"/>
+      <c r="A90" s="20"/>
+      <c r="B90" s="20"/>
       <c r="C90" s="6" t="s">
         <v>225</v>
       </c>
@@ -4133,7 +4262,7 @@
       <c r="M90" s="4"/>
     </row>
     <row r="91" spans="1:13" ht="13">
-      <c r="A91" s="21"/>
+      <c r="A91" s="20"/>
       <c r="B91" s="6" t="s">
         <v>197</v>
       </c>
@@ -4156,16 +4285,16 @@
       <c r="M91" s="4"/>
     </row>
     <row r="92" spans="1:13" ht="13">
-      <c r="A92" s="21"/>
+      <c r="A92" s="20"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="F92" s="4"/>
       <c r="G92" s="5"/>
@@ -4177,7 +4306,7 @@
       <c r="M92" s="4"/>
     </row>
     <row r="93" spans="1:13" ht="13">
-      <c r="A93" s="21"/>
+      <c r="A93" s="20"/>
       <c r="B93" s="6" t="s">
         <v>109</v>
       </c>
@@ -4185,10 +4314,10 @@
         <v>231</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="F93" s="4"/>
       <c r="G93" s="5"/>
@@ -4200,10 +4329,10 @@
       <c r="M93" s="4"/>
     </row>
     <row r="94" spans="1:13" ht="14">
-      <c r="A94" s="20" t="s">
+      <c r="A94" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="B94" s="20" t="s">
+      <c r="B94" s="22" t="s">
         <v>197</v>
       </c>
       <c r="C94" s="6" t="s">
@@ -4225,8 +4354,8 @@
       <c r="M94" s="4"/>
     </row>
     <row r="95" spans="1:13" ht="14">
-      <c r="A95" s="21"/>
-      <c r="B95" s="21"/>
+      <c r="A95" s="20"/>
+      <c r="B95" s="20"/>
       <c r="C95" s="6" t="s">
         <v>236</v>
       </c>
@@ -4246,16 +4375,16 @@
       <c r="M95" s="4"/>
     </row>
     <row r="96" spans="1:13" ht="14">
-      <c r="A96" s="21"/>
-      <c r="B96" s="21"/>
+      <c r="A96" s="20"/>
+      <c r="B96" s="20"/>
       <c r="C96" s="6" t="s">
         <v>239</v>
       </c>
       <c r="D96" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="E96" s="19" t="s">
-        <v>598</v>
+      <c r="E96" s="18" t="s">
+        <v>592</v>
       </c>
       <c r="F96" s="4"/>
       <c r="G96" s="5"/>
@@ -4267,8 +4396,8 @@
       <c r="M96" s="4"/>
     </row>
     <row r="97" spans="1:13" ht="14">
-      <c r="A97" s="21"/>
-      <c r="B97" s="21"/>
+      <c r="A97" s="20"/>
+      <c r="B97" s="20"/>
       <c r="C97" s="6" t="s">
         <v>241</v>
       </c>
@@ -4288,8 +4417,8 @@
       <c r="M97" s="4"/>
     </row>
     <row r="98" spans="1:13" ht="14">
-      <c r="A98" s="21"/>
-      <c r="B98" s="21"/>
+      <c r="A98" s="20"/>
+      <c r="B98" s="20"/>
       <c r="C98" s="6" t="s">
         <v>244</v>
       </c>
@@ -4309,8 +4438,8 @@
       <c r="M98" s="4"/>
     </row>
     <row r="99" spans="1:13" ht="14">
-      <c r="A99" s="21"/>
-      <c r="B99" s="21"/>
+      <c r="A99" s="20"/>
+      <c r="B99" s="20"/>
       <c r="C99" s="6" t="s">
         <v>247</v>
       </c>
@@ -4330,8 +4459,8 @@
       <c r="M99" s="4"/>
     </row>
     <row r="100" spans="1:13" ht="14">
-      <c r="A100" s="21"/>
-      <c r="B100" s="21"/>
+      <c r="A100" s="20"/>
+      <c r="B100" s="20"/>
       <c r="C100" s="6" t="s">
         <v>249</v>
       </c>
@@ -4351,7 +4480,7 @@
       <c r="M100" s="4"/>
     </row>
     <row r="101" spans="1:13" ht="14">
-      <c r="A101" s="21"/>
+      <c r="A101" s="20"/>
       <c r="B101" s="6" t="s">
         <v>115</v>
       </c>
@@ -4374,7 +4503,7 @@
       <c r="M101" s="4"/>
     </row>
     <row r="102" spans="1:13" ht="14">
-      <c r="A102" s="21"/>
+      <c r="A102" s="20"/>
       <c r="B102" s="6" t="s">
         <v>11</v>
       </c>
@@ -4397,8 +4526,8 @@
       <c r="M102" s="4"/>
     </row>
     <row r="103" spans="1:13" ht="14">
-      <c r="A103" s="21"/>
-      <c r="B103" s="20" t="s">
+      <c r="A103" s="20"/>
+      <c r="B103" s="22" t="s">
         <v>109</v>
       </c>
       <c r="C103" s="9" t="s">
@@ -4420,16 +4549,16 @@
       <c r="M103" s="4"/>
     </row>
     <row r="104" spans="1:13" ht="14">
-      <c r="A104" s="21"/>
-      <c r="B104" s="20"/>
+      <c r="A104" s="20"/>
+      <c r="B104" s="22"/>
       <c r="C104" s="9" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="5"/>
@@ -4441,16 +4570,16 @@
       <c r="M104" s="4"/>
     </row>
     <row r="105" spans="1:13" ht="14">
-      <c r="A105" s="21"/>
-      <c r="B105" s="21"/>
+      <c r="A105" s="20"/>
+      <c r="B105" s="20"/>
       <c r="C105" s="9" t="s">
         <v>261</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="E105" s="19" t="s">
-        <v>599</v>
+      <c r="E105" s="18" t="s">
+        <v>593</v>
       </c>
       <c r="F105" s="6"/>
       <c r="G105" s="6"/>
@@ -4462,7 +4591,7 @@
       <c r="M105" s="6"/>
     </row>
     <row r="106" spans="1:13" ht="13">
-      <c r="A106" s="20" t="s">
+      <c r="A106" s="22" t="s">
         <v>263</v>
       </c>
       <c r="B106" s="23" t="s">
@@ -4487,8 +4616,8 @@
       <c r="M106" s="4"/>
     </row>
     <row r="107" spans="1:13" ht="13">
-      <c r="A107" s="21"/>
-      <c r="B107" s="21"/>
+      <c r="A107" s="20"/>
+      <c r="B107" s="20"/>
       <c r="C107" s="6" t="s">
         <v>266</v>
       </c>
@@ -4508,8 +4637,8 @@
       <c r="M107" s="4"/>
     </row>
     <row r="108" spans="1:13" ht="13">
-      <c r="A108" s="21"/>
-      <c r="B108" s="21"/>
+      <c r="A108" s="20"/>
+      <c r="B108" s="20"/>
       <c r="C108" s="6" t="s">
         <v>269</v>
       </c>
@@ -4529,8 +4658,8 @@
       <c r="M108" s="4"/>
     </row>
     <row r="109" spans="1:13" ht="13">
-      <c r="A109" s="21"/>
-      <c r="B109" s="21"/>
+      <c r="A109" s="20"/>
+      <c r="B109" s="20"/>
       <c r="C109" s="6" t="s">
         <v>272</v>
       </c>
@@ -4550,7 +4679,7 @@
       <c r="M109" s="4"/>
     </row>
     <row r="110" spans="1:13" ht="13">
-      <c r="A110" s="21"/>
+      <c r="A110" s="20"/>
       <c r="B110" s="6" t="s">
         <v>109</v>
       </c>
@@ -4851,13 +4980,13 @@
       <c r="A122" s="6"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="F122" s="6"/>
       <c r="G122" s="6"/>
@@ -4869,10 +4998,10 @@
       <c r="M122" s="6"/>
     </row>
     <row r="123" spans="1:13" ht="13">
-      <c r="A123" s="20" t="s">
+      <c r="A123" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="B123" s="20" t="s">
+      <c r="B123" s="22" t="s">
         <v>197</v>
       </c>
       <c r="C123" s="6" t="s">
@@ -4894,8 +5023,8 @@
       <c r="M123" s="6"/>
     </row>
     <row r="124" spans="1:13" ht="13">
-      <c r="A124" s="21"/>
-      <c r="B124" s="21"/>
+      <c r="A124" s="20"/>
+      <c r="B124" s="20"/>
       <c r="C124" s="6" t="s">
         <v>314</v>
       </c>
@@ -4915,7 +5044,7 @@
       <c r="M124" s="6"/>
     </row>
     <row r="125" spans="1:13" ht="13">
-      <c r="A125" s="21"/>
+      <c r="A125" s="20"/>
       <c r="B125" s="8" t="s">
         <v>197</v>
       </c>
@@ -4938,7 +5067,7 @@
       <c r="M125" s="6"/>
     </row>
     <row r="126" spans="1:13" ht="13">
-      <c r="A126" s="21"/>
+      <c r="A126" s="20"/>
       <c r="B126" s="8" t="s">
         <v>197</v>
       </c>
@@ -4961,8 +5090,8 @@
       <c r="M126" s="6"/>
     </row>
     <row r="127" spans="1:13" ht="13">
-      <c r="A127" s="21"/>
-      <c r="B127" s="20" t="s">
+      <c r="A127" s="20"/>
+      <c r="B127" s="22" t="s">
         <v>109</v>
       </c>
       <c r="C127" s="6" t="s">
@@ -4984,8 +5113,8 @@
       <c r="M127" s="6"/>
     </row>
     <row r="128" spans="1:13" ht="28">
-      <c r="A128" s="21"/>
-      <c r="B128" s="21"/>
+      <c r="A128" s="20"/>
+      <c r="B128" s="20"/>
       <c r="C128" s="6" t="s">
         <v>326</v>
       </c>
@@ -5005,8 +5134,8 @@
       <c r="M128" s="6"/>
     </row>
     <row r="129" spans="1:13" ht="14">
-      <c r="A129" s="21"/>
-      <c r="B129" s="21"/>
+      <c r="A129" s="20"/>
+      <c r="B129" s="20"/>
       <c r="C129" s="6" t="s">
         <v>329</v>
       </c>
@@ -5026,8 +5155,8 @@
       <c r="M129" s="6"/>
     </row>
     <row r="130" spans="1:13" ht="14">
-      <c r="A130" s="21"/>
-      <c r="B130" s="21"/>
+      <c r="A130" s="20"/>
+      <c r="B130" s="20"/>
       <c r="C130" s="6" t="s">
         <v>331</v>
       </c>
@@ -5047,8 +5176,8 @@
       <c r="M130" s="6"/>
     </row>
     <row r="131" spans="1:13" ht="28">
-      <c r="A131" s="21"/>
-      <c r="B131" s="21"/>
+      <c r="A131" s="20"/>
+      <c r="B131" s="20"/>
       <c r="C131" s="6" t="s">
         <v>334</v>
       </c>
@@ -5068,8 +5197,8 @@
       <c r="M131" s="6"/>
     </row>
     <row r="132" spans="1:13" ht="14">
-      <c r="A132" s="21"/>
-      <c r="B132" s="21"/>
+      <c r="A132" s="20"/>
+      <c r="B132" s="20"/>
       <c r="C132" s="6" t="s">
         <v>337</v>
       </c>
@@ -5089,8 +5218,8 @@
       <c r="M132" s="8"/>
     </row>
     <row r="133" spans="1:13" ht="42">
-      <c r="A133" s="21"/>
-      <c r="B133" s="21"/>
+      <c r="A133" s="20"/>
+      <c r="B133" s="20"/>
       <c r="C133" s="6" t="s">
         <v>340</v>
       </c>
@@ -5110,8 +5239,8 @@
       <c r="M133" s="8"/>
     </row>
     <row r="134" spans="1:13" ht="14">
-      <c r="A134" s="21"/>
-      <c r="B134" s="21"/>
+      <c r="A134" s="20"/>
+      <c r="B134" s="20"/>
       <c r="C134" s="6" t="s">
         <v>343</v>
       </c>
@@ -5131,8 +5260,8 @@
       <c r="M134" s="8"/>
     </row>
     <row r="135" spans="1:13" ht="28">
-      <c r="A135" s="21"/>
-      <c r="B135" s="21"/>
+      <c r="A135" s="20"/>
+      <c r="B135" s="20"/>
       <c r="C135" s="6" t="s">
         <v>345</v>
       </c>
@@ -5152,8 +5281,8 @@
       <c r="M135" s="8"/>
     </row>
     <row r="136" spans="1:13" ht="13">
-      <c r="A136" s="21"/>
-      <c r="B136" s="21"/>
+      <c r="A136" s="20"/>
+      <c r="B136" s="20"/>
       <c r="C136" s="6" t="s">
         <v>348</v>
       </c>
@@ -5173,8 +5302,8 @@
       <c r="M136" s="8"/>
     </row>
     <row r="137" spans="1:13" ht="13">
-      <c r="A137" s="21"/>
-      <c r="B137" s="21"/>
+      <c r="A137" s="20"/>
+      <c r="B137" s="20"/>
       <c r="C137" s="6" t="s">
         <v>350</v>
       </c>
@@ -5194,16 +5323,16 @@
       <c r="M137" s="8"/>
     </row>
     <row r="138" spans="1:13" ht="13">
-      <c r="A138" s="21"/>
-      <c r="B138" s="21"/>
+      <c r="A138" s="20"/>
+      <c r="B138" s="20"/>
       <c r="C138" s="6" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="F138" s="6"/>
       <c r="G138" s="13"/>
@@ -5215,8 +5344,8 @@
       <c r="M138" s="8"/>
     </row>
     <row r="139" spans="1:13" ht="13">
-      <c r="A139" s="21"/>
-      <c r="B139" s="21"/>
+      <c r="A139" s="20"/>
+      <c r="B139" s="20"/>
       <c r="C139" s="6" t="s">
         <v>353</v>
       </c>
@@ -5236,7 +5365,7 @@
       <c r="M139" s="8"/>
     </row>
     <row r="140" spans="1:13" ht="14">
-      <c r="A140" s="21"/>
+      <c r="A140" s="20"/>
       <c r="B140" s="6"/>
       <c r="C140" s="6" t="s">
         <v>356</v>
@@ -5257,8 +5386,8 @@
       <c r="M140" s="8"/>
     </row>
     <row r="141" spans="1:13" ht="14">
-      <c r="A141" s="21"/>
-      <c r="B141" s="20" t="s">
+      <c r="A141" s="20"/>
+      <c r="B141" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C141" s="6" t="s">
@@ -5280,8 +5409,8 @@
       <c r="M141" s="8"/>
     </row>
     <row r="142" spans="1:13" ht="14">
-      <c r="A142" s="21"/>
-      <c r="B142" s="21"/>
+      <c r="A142" s="20"/>
+      <c r="B142" s="20"/>
       <c r="C142" s="6" t="s">
         <v>361</v>
       </c>
@@ -5301,10 +5430,10 @@
       <c r="M142" s="8"/>
     </row>
     <row r="143" spans="1:13" ht="14">
-      <c r="A143" s="22" t="s">
+      <c r="A143" s="21" t="s">
         <v>364</v>
       </c>
-      <c r="B143" s="22" t="s">
+      <c r="B143" s="21" t="s">
         <v>197</v>
       </c>
       <c r="C143" s="2" t="s">
@@ -5326,8 +5455,8 @@
       <c r="M143" s="8"/>
     </row>
     <row r="144" spans="1:13" ht="14">
-      <c r="A144" s="21"/>
-      <c r="B144" s="21"/>
+      <c r="A144" s="20"/>
+      <c r="B144" s="20"/>
       <c r="C144" s="2" t="s">
         <v>368</v>
       </c>
@@ -5335,7 +5464,7 @@
         <v>369</v>
       </c>
       <c r="E144" s="9" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="F144" s="6"/>
       <c r="G144" s="13"/>
@@ -5347,8 +5476,8 @@
       <c r="M144" s="6"/>
     </row>
     <row r="145" spans="1:13" ht="14">
-      <c r="A145" s="21"/>
-      <c r="B145" s="21"/>
+      <c r="A145" s="20"/>
+      <c r="B145" s="20"/>
       <c r="C145" s="2" t="s">
         <v>370</v>
       </c>
@@ -5368,8 +5497,8 @@
       <c r="M145" s="6"/>
     </row>
     <row r="146" spans="1:13" ht="13">
-      <c r="A146" s="21"/>
-      <c r="B146" s="21"/>
+      <c r="A146" s="20"/>
+      <c r="B146" s="20"/>
       <c r="C146" s="6" t="s">
         <v>373</v>
       </c>
@@ -5389,8 +5518,8 @@
       <c r="M146" s="6"/>
     </row>
     <row r="147" spans="1:13" ht="14">
-      <c r="A147" s="21"/>
-      <c r="B147" s="21"/>
+      <c r="A147" s="20"/>
+      <c r="B147" s="20"/>
       <c r="C147" s="2" t="s">
         <v>376</v>
       </c>
@@ -5410,8 +5539,8 @@
       <c r="M147" s="6"/>
     </row>
     <row r="148" spans="1:13" ht="14">
-      <c r="A148" s="21"/>
-      <c r="B148" s="21"/>
+      <c r="A148" s="20"/>
+      <c r="B148" s="20"/>
       <c r="C148" s="2" t="s">
         <v>379</v>
       </c>
@@ -5431,8 +5560,8 @@
       <c r="M148" s="6"/>
     </row>
     <row r="149" spans="1:13" ht="14">
-      <c r="A149" s="21"/>
-      <c r="B149" s="21"/>
+      <c r="A149" s="20"/>
+      <c r="B149" s="20"/>
       <c r="C149" s="2" t="s">
         <v>382</v>
       </c>
@@ -5452,8 +5581,8 @@
       <c r="M149" s="6"/>
     </row>
     <row r="150" spans="1:13" ht="14">
-      <c r="A150" s="21"/>
-      <c r="B150" s="21"/>
+      <c r="A150" s="20"/>
+      <c r="B150" s="20"/>
       <c r="C150" s="2" t="s">
         <v>385</v>
       </c>
@@ -5473,8 +5602,8 @@
       <c r="M150" s="6"/>
     </row>
     <row r="151" spans="1:13" ht="14">
-      <c r="A151" s="21"/>
-      <c r="B151" s="21"/>
+      <c r="A151" s="20"/>
+      <c r="B151" s="20"/>
       <c r="C151" s="2" t="s">
         <v>388</v>
       </c>
@@ -5494,8 +5623,8 @@
       <c r="M151" s="6"/>
     </row>
     <row r="152" spans="1:13" ht="14">
-      <c r="A152" s="21"/>
-      <c r="B152" s="22" t="s">
+      <c r="A152" s="20"/>
+      <c r="B152" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C152" s="2" t="s">
@@ -5517,8 +5646,8 @@
       <c r="M152" s="6"/>
     </row>
     <row r="153" spans="1:13" ht="14">
-      <c r="A153" s="21"/>
-      <c r="B153" s="21"/>
+      <c r="A153" s="20"/>
+      <c r="B153" s="20"/>
       <c r="C153" s="2" t="s">
         <v>394</v>
       </c>
@@ -5538,8 +5667,8 @@
       <c r="M153" s="6"/>
     </row>
     <row r="154" spans="1:13" ht="14">
-      <c r="A154" s="21"/>
-      <c r="B154" s="21"/>
+      <c r="A154" s="20"/>
+      <c r="B154" s="20"/>
       <c r="C154" s="16" t="s">
         <v>397</v>
       </c>
@@ -5559,8 +5688,8 @@
       <c r="M154" s="6"/>
     </row>
     <row r="155" spans="1:13" ht="14">
-      <c r="A155" s="21"/>
-      <c r="B155" s="21"/>
+      <c r="A155" s="20"/>
+      <c r="B155" s="20"/>
       <c r="C155" s="2" t="s">
         <v>400</v>
       </c>
@@ -5580,8 +5709,8 @@
       <c r="M155" s="6"/>
     </row>
     <row r="156" spans="1:13" ht="14">
-      <c r="A156" s="21"/>
-      <c r="B156" s="22" t="s">
+      <c r="A156" s="20"/>
+      <c r="B156" s="21" t="s">
         <v>109</v>
       </c>
       <c r="C156" s="2" t="s">
@@ -5590,8 +5719,8 @@
       <c r="D156" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="E156" s="19" t="s">
-        <v>601</v>
+      <c r="E156" s="18" t="s">
+        <v>595</v>
       </c>
       <c r="F156" s="6"/>
       <c r="G156" s="6"/>
@@ -5603,8 +5732,8 @@
       <c r="M156" s="6"/>
     </row>
     <row r="157" spans="1:13" ht="28">
-      <c r="A157" s="21"/>
-      <c r="B157" s="21"/>
+      <c r="A157" s="20"/>
+      <c r="B157" s="20"/>
       <c r="C157" s="2" t="s">
         <v>405</v>
       </c>
@@ -5624,8 +5753,8 @@
       <c r="M157" s="6"/>
     </row>
     <row r="158" spans="1:13" ht="14">
-      <c r="A158" s="21"/>
-      <c r="B158" s="21"/>
+      <c r="A158" s="20"/>
+      <c r="B158" s="20"/>
       <c r="C158" s="2" t="s">
         <v>408</v>
       </c>
@@ -5645,8 +5774,8 @@
       <c r="M158" s="6"/>
     </row>
     <row r="159" spans="1:13" ht="14">
-      <c r="A159" s="21"/>
-      <c r="B159" s="21"/>
+      <c r="A159" s="20"/>
+      <c r="B159" s="20"/>
       <c r="C159" s="2" t="s">
         <v>411</v>
       </c>
@@ -5666,8 +5795,8 @@
       <c r="M159" s="6"/>
     </row>
     <row r="160" spans="1:13" ht="14">
-      <c r="A160" s="21"/>
-      <c r="B160" s="21"/>
+      <c r="A160" s="20"/>
+      <c r="B160" s="20"/>
       <c r="C160" s="2" t="s">
         <v>414</v>
       </c>
@@ -5687,8 +5816,8 @@
       <c r="M160" s="6"/>
     </row>
     <row r="161" spans="1:13" ht="14">
-      <c r="A161" s="21"/>
-      <c r="B161" s="21"/>
+      <c r="A161" s="20"/>
+      <c r="B161" s="20"/>
       <c r="C161" s="2" t="s">
         <v>417</v>
       </c>
@@ -5708,8 +5837,8 @@
       <c r="M161" s="6"/>
     </row>
     <row r="162" spans="1:13" ht="14">
-      <c r="A162" s="21"/>
-      <c r="B162" s="21"/>
+      <c r="A162" s="20"/>
+      <c r="B162" s="20"/>
       <c r="C162" s="2" t="s">
         <v>420</v>
       </c>
@@ -5729,8 +5858,8 @@
       <c r="M162" s="6"/>
     </row>
     <row r="163" spans="1:13" ht="14">
-      <c r="A163" s="21"/>
-      <c r="B163" s="21"/>
+      <c r="A163" s="20"/>
+      <c r="B163" s="20"/>
       <c r="C163" s="2" t="s">
         <v>423</v>
       </c>
@@ -5750,8 +5879,8 @@
       <c r="M163" s="6"/>
     </row>
     <row r="164" spans="1:13" ht="28">
-      <c r="A164" s="21"/>
-      <c r="B164" s="21"/>
+      <c r="A164" s="20"/>
+      <c r="B164" s="20"/>
       <c r="C164" s="2" t="s">
         <v>426</v>
       </c>
@@ -5771,8 +5900,8 @@
       <c r="M164" s="6"/>
     </row>
     <row r="165" spans="1:13" ht="14">
-      <c r="A165" s="21"/>
-      <c r="B165" s="21"/>
+      <c r="A165" s="20"/>
+      <c r="B165" s="20"/>
       <c r="C165" s="2" t="s">
         <v>429</v>
       </c>
@@ -5791,16 +5920,16 @@
       <c r="L165" s="6"/>
       <c r="M165" s="6"/>
     </row>
-    <row r="166" spans="1:13" ht="28">
-      <c r="A166" s="21"/>
-      <c r="B166" s="21"/>
+    <row r="166" spans="1:13" ht="14">
+      <c r="A166" s="20"/>
+      <c r="B166" s="20"/>
       <c r="C166" s="2" t="s">
         <v>432</v>
       </c>
       <c r="D166" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="E166" s="9" t="s">
+      <c r="E166" s="3" t="s">
         <v>434</v>
       </c>
       <c r="F166" s="6"/>
@@ -5812,17 +5941,17 @@
       <c r="L166" s="6"/>
       <c r="M166" s="6"/>
     </row>
-    <row r="167" spans="1:13" ht="28">
-      <c r="A167" s="21"/>
-      <c r="B167" s="21"/>
+    <row r="167" spans="1:13" ht="16">
+      <c r="A167" s="20"/>
+      <c r="B167" s="20"/>
       <c r="C167" s="2" t="s">
         <v>435</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="E167" s="9" t="s">
-        <v>437</v>
+        <v>597</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>600</v>
       </c>
       <c r="F167" s="6"/>
       <c r="G167" s="6"/>
@@ -5833,17 +5962,17 @@
       <c r="L167" s="6"/>
       <c r="M167" s="6"/>
     </row>
-    <row r="168" spans="1:13" ht="13">
-      <c r="A168" s="21"/>
-      <c r="B168" s="21"/>
+    <row r="168" spans="1:13" ht="16">
+      <c r="A168" s="20"/>
+      <c r="B168" s="20"/>
       <c r="C168" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="E168" s="17" t="s">
-        <v>440</v>
+        <v>598</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>601</v>
       </c>
       <c r="F168" s="6"/>
       <c r="G168" s="6"/>
@@ -5854,17 +5983,17 @@
       <c r="L168" s="6"/>
       <c r="M168" s="6"/>
     </row>
-    <row r="169" spans="1:13" ht="13">
-      <c r="A169" s="21"/>
-      <c r="B169" s="21"/>
+    <row r="169" spans="1:13" ht="16">
+      <c r="A169" s="20"/>
+      <c r="B169" s="20"/>
       <c r="C169" s="8" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>442</v>
+        <v>599</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>443</v>
+        <v>602</v>
       </c>
       <c r="F169" s="6"/>
       <c r="G169" s="6"/>
@@ -5876,16 +6005,16 @@
       <c r="M169" s="6"/>
     </row>
     <row r="170" spans="1:13" ht="13">
-      <c r="A170" s="21"/>
-      <c r="B170" s="21"/>
+      <c r="A170" s="20"/>
+      <c r="B170" s="20"/>
       <c r="C170" s="6" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="E170" s="19" t="s">
-        <v>602</v>
+        <v>439</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>596</v>
       </c>
       <c r="F170" s="6"/>
       <c r="G170" s="6"/>
@@ -5897,20 +6026,20 @@
       <c r="M170" s="6"/>
     </row>
     <row r="171" spans="1:13" ht="13">
-      <c r="A171" s="20" t="s">
-        <v>446</v>
+      <c r="A171" s="22" t="s">
+        <v>440</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="F171" s="6"/>
       <c r="G171" s="6"/>
@@ -5922,18 +6051,18 @@
       <c r="M171" s="6"/>
     </row>
     <row r="172" spans="1:13" ht="28">
-      <c r="A172" s="21"/>
-      <c r="B172" s="20" t="s">
+      <c r="A172" s="20"/>
+      <c r="B172" s="22" t="s">
         <v>109</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="E172" s="9" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="F172" s="6"/>
       <c r="G172" s="6"/>
@@ -5945,16 +6074,16 @@
       <c r="M172" s="6"/>
     </row>
     <row r="173" spans="1:13" ht="14">
-      <c r="A173" s="21"/>
-      <c r="B173" s="20"/>
+      <c r="A173" s="20"/>
+      <c r="B173" s="22"/>
       <c r="C173" s="6" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="E173" s="9" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
@@ -5966,16 +6095,16 @@
       <c r="M173" s="6"/>
     </row>
     <row r="174" spans="1:13" ht="13">
-      <c r="A174" s="21"/>
-      <c r="B174" s="21"/>
+      <c r="A174" s="20"/>
+      <c r="B174" s="20"/>
       <c r="C174" s="6" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="F174" s="6"/>
       <c r="G174" s="6"/>
@@ -5987,20 +6116,20 @@
       <c r="M174" s="6"/>
     </row>
     <row r="175" spans="1:13" ht="13">
-      <c r="A175" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="B175" s="20" t="s">
+      <c r="A175" s="22" t="s">
+        <v>450</v>
+      </c>
+      <c r="B175" s="22" t="s">
         <v>197</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="F175" s="6"/>
       <c r="G175" s="6"/>
@@ -6012,16 +6141,16 @@
       <c r="M175" s="6"/>
     </row>
     <row r="176" spans="1:13" ht="13">
-      <c r="A176" s="21"/>
-      <c r="B176" s="21"/>
+      <c r="A176" s="20"/>
+      <c r="B176" s="20"/>
       <c r="C176" s="6" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="F176" s="6"/>
       <c r="G176" s="6"/>
@@ -6033,16 +6162,16 @@
       <c r="M176" s="6"/>
     </row>
     <row r="177" spans="1:13" ht="14">
-      <c r="A177" s="21"/>
-      <c r="B177" s="21"/>
+      <c r="A177" s="20"/>
+      <c r="B177" s="20"/>
       <c r="C177" s="6" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D177" s="9" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="E177" s="9" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="F177" s="6"/>
       <c r="G177" s="6"/>
@@ -6054,16 +6183,16 @@
       <c r="M177" s="6"/>
     </row>
     <row r="178" spans="1:13" ht="14">
-      <c r="A178" s="21"/>
-      <c r="B178" s="21"/>
+      <c r="A178" s="20"/>
+      <c r="B178" s="20"/>
       <c r="C178" s="8" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="D178" s="9" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="E178" s="9" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="F178" s="6"/>
       <c r="G178" s="6"/>
@@ -6075,18 +6204,18 @@
       <c r="M178" s="6"/>
     </row>
     <row r="179" spans="1:13" ht="14">
-      <c r="A179" s="21"/>
-      <c r="B179" s="20" t="s">
+      <c r="A179" s="20"/>
+      <c r="B179" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="D179" s="9" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="F179" s="6"/>
       <c r="G179" s="6"/>
@@ -6098,16 +6227,16 @@
       <c r="M179" s="6"/>
     </row>
     <row r="180" spans="1:13" ht="14">
-      <c r="A180" s="21"/>
-      <c r="B180" s="21"/>
+      <c r="A180" s="20"/>
+      <c r="B180" s="20"/>
       <c r="C180" s="8" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D180" s="9" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E180" s="9" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="F180" s="6"/>
       <c r="G180" s="6"/>
@@ -6119,16 +6248,16 @@
       <c r="M180" s="6"/>
     </row>
     <row r="181" spans="1:13" ht="14">
-      <c r="A181" s="21"/>
-      <c r="B181" s="21"/>
+      <c r="A181" s="20"/>
+      <c r="B181" s="20"/>
       <c r="C181" s="8" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="D181" s="9" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="F181" s="6"/>
       <c r="G181" s="6"/>
@@ -6140,16 +6269,16 @@
       <c r="M181" s="6"/>
     </row>
     <row r="182" spans="1:13" ht="14">
-      <c r="A182" s="21"/>
-      <c r="B182" s="21"/>
+      <c r="A182" s="20"/>
+      <c r="B182" s="20"/>
       <c r="C182" s="8" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="D182" s="9" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="E182" s="9" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="F182" s="6"/>
       <c r="G182" s="6"/>
@@ -6161,16 +6290,16 @@
       <c r="M182" s="6"/>
     </row>
     <row r="183" spans="1:13" ht="14">
-      <c r="A183" s="21"/>
-      <c r="B183" s="21"/>
+      <c r="A183" s="20"/>
+      <c r="B183" s="20"/>
       <c r="C183" s="8" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="D183" s="9" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="F183" s="6"/>
       <c r="G183" s="6"/>
@@ -6182,16 +6311,16 @@
       <c r="M183" s="6"/>
     </row>
     <row r="184" spans="1:13" ht="14">
-      <c r="A184" s="21"/>
-      <c r="B184" s="21"/>
+      <c r="A184" s="20"/>
+      <c r="B184" s="20"/>
       <c r="C184" s="8" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="D184" s="9" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="E184" s="9" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="F184" s="6"/>
       <c r="G184" s="6"/>
@@ -6203,18 +6332,18 @@
       <c r="M184" s="6"/>
     </row>
     <row r="185" spans="1:13" ht="14">
-      <c r="A185" s="21"/>
-      <c r="B185" s="20" t="s">
+      <c r="A185" s="20"/>
+      <c r="B185" s="22" t="s">
         <v>109</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="D185" s="9" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="E185" s="8" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="F185" s="6"/>
       <c r="G185" s="6"/>
@@ -6226,16 +6355,16 @@
       <c r="M185" s="6"/>
     </row>
     <row r="186" spans="1:13" ht="28">
-      <c r="A186" s="21"/>
-      <c r="B186" s="21"/>
+      <c r="A186" s="20"/>
+      <c r="B186" s="20"/>
       <c r="C186" s="6" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="D186" s="9" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="E186" s="9" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="F186" s="6"/>
       <c r="G186" s="6"/>
@@ -6247,16 +6376,16 @@
       <c r="M186" s="6"/>
     </row>
     <row r="187" spans="1:13" ht="28">
-      <c r="A187" s="21"/>
-      <c r="B187" s="21"/>
+      <c r="A187" s="20"/>
+      <c r="B187" s="20"/>
       <c r="C187" s="6" t="s">
-        <v>493</v>
-      </c>
-      <c r="D187" s="18" t="s">
-        <v>494</v>
+        <v>487</v>
+      </c>
+      <c r="D187" s="17" t="s">
+        <v>488</v>
       </c>
       <c r="E187" s="9" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="F187" s="6"/>
       <c r="G187" s="6"/>
@@ -6268,16 +6397,16 @@
       <c r="M187" s="6"/>
     </row>
     <row r="188" spans="1:13" ht="28">
-      <c r="A188" s="21"/>
-      <c r="B188" s="21"/>
+      <c r="A188" s="20"/>
+      <c r="B188" s="20"/>
       <c r="C188" s="6" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="D188" s="9" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="E188" s="9" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="F188" s="6"/>
       <c r="G188" s="6"/>
@@ -6289,16 +6418,16 @@
       <c r="M188" s="6"/>
     </row>
     <row r="189" spans="1:13" ht="14">
-      <c r="A189" s="21"/>
-      <c r="B189" s="21"/>
+      <c r="A189" s="20"/>
+      <c r="B189" s="20"/>
       <c r="C189" s="6" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="F189" s="6"/>
       <c r="G189" s="6"/>
@@ -6310,16 +6439,16 @@
       <c r="M189" s="6"/>
     </row>
     <row r="190" spans="1:13" ht="14">
-      <c r="A190" s="21"/>
-      <c r="B190" s="21"/>
+      <c r="A190" s="20"/>
+      <c r="B190" s="20"/>
       <c r="C190" s="6" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="F190" s="6"/>
       <c r="G190" s="6"/>
@@ -6331,18 +6460,18 @@
       <c r="M190" s="6"/>
     </row>
     <row r="191" spans="1:13" ht="28">
-      <c r="A191" s="21"/>
-      <c r="B191" s="20" t="s">
+      <c r="A191" s="20"/>
+      <c r="B191" s="22" t="s">
         <v>115</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="F191" s="6"/>
       <c r="G191" s="6"/>
@@ -6354,16 +6483,16 @@
       <c r="M191" s="6"/>
     </row>
     <row r="192" spans="1:13" ht="28">
-      <c r="A192" s="21"/>
-      <c r="B192" s="21"/>
+      <c r="A192" s="20"/>
+      <c r="B192" s="20"/>
       <c r="C192" s="8" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="F192" s="6"/>
       <c r="G192" s="6"/>
@@ -6375,16 +6504,16 @@
       <c r="M192" s="6"/>
     </row>
     <row r="193" spans="1:13" ht="14">
-      <c r="A193" s="21"/>
-      <c r="B193" s="21"/>
+      <c r="A193" s="20"/>
+      <c r="B193" s="20"/>
       <c r="C193" s="8" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="E193" s="8" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="F193" s="6"/>
       <c r="G193" s="6"/>
@@ -6396,20 +6525,20 @@
       <c r="M193" s="6"/>
     </row>
     <row r="194" spans="1:13" ht="14">
-      <c r="A194" s="20" t="s">
-        <v>513</v>
-      </c>
-      <c r="B194" s="20" t="s">
-        <v>514</v>
+      <c r="A194" s="22" t="s">
+        <v>507</v>
+      </c>
+      <c r="B194" s="22" t="s">
+        <v>508</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="F194" s="6"/>
       <c r="G194" s="6"/>
@@ -6421,16 +6550,16 @@
       <c r="M194" s="6"/>
     </row>
     <row r="195" spans="1:13" ht="14">
-      <c r="A195" s="21"/>
-      <c r="B195" s="21"/>
+      <c r="A195" s="20"/>
+      <c r="B195" s="20"/>
       <c r="C195" s="6" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="F195" s="6"/>
       <c r="G195" s="6"/>
@@ -6442,16 +6571,16 @@
       <c r="M195" s="6"/>
     </row>
     <row r="196" spans="1:13" ht="14">
-      <c r="A196" s="21"/>
-      <c r="B196" s="21"/>
+      <c r="A196" s="20"/>
+      <c r="B196" s="20"/>
       <c r="C196" s="6" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="F196" s="6"/>
       <c r="G196" s="6"/>
@@ -6463,16 +6592,16 @@
       <c r="M196" s="6"/>
     </row>
     <row r="197" spans="1:13" ht="14">
-      <c r="A197" s="21"/>
-      <c r="B197" s="21"/>
+      <c r="A197" s="20"/>
+      <c r="B197" s="20"/>
       <c r="C197" s="6" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F197" s="6"/>
       <c r="G197" s="6"/>
@@ -6484,18 +6613,18 @@
       <c r="M197" s="6"/>
     </row>
     <row r="198" spans="1:13" ht="14">
-      <c r="A198" s="21"/>
-      <c r="B198" s="20" t="s">
+      <c r="A198" s="20"/>
+      <c r="B198" s="22" t="s">
         <v>115</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="F198" s="6"/>
       <c r="G198" s="6"/>
@@ -6507,16 +6636,16 @@
       <c r="M198" s="6"/>
     </row>
     <row r="199" spans="1:13" ht="14">
-      <c r="A199" s="21"/>
-      <c r="B199" s="21"/>
+      <c r="A199" s="20"/>
+      <c r="B199" s="20"/>
       <c r="C199" s="6" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="F199" s="6"/>
       <c r="G199" s="6"/>
@@ -6529,19 +6658,19 @@
     </row>
     <row r="200" spans="1:13" ht="14">
       <c r="A200" s="6" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>109</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="F200" s="6"/>
       <c r="G200" s="6"/>
@@ -6554,19 +6683,19 @@
     </row>
     <row r="201" spans="1:13" ht="13">
       <c r="A201" s="6" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>109</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="D201" s="10" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="F201" s="6"/>
       <c r="G201" s="6"/>
@@ -6579,19 +6708,19 @@
     </row>
     <row r="202" spans="1:13" ht="14">
       <c r="A202" s="6" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>197</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="F202" s="6"/>
       <c r="G202" s="6"/>
@@ -6608,13 +6737,13 @@
         <v>197</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="D203" s="9" t="s">
         <v>33</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="F203" s="6"/>
       <c r="G203" s="6"/>
@@ -6758,11 +6887,24 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A4:A47"/>
-    <mergeCell ref="B4:B37"/>
-    <mergeCell ref="B44:B47"/>
+    <mergeCell ref="A123:A142"/>
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="B127:B139"/>
+    <mergeCell ref="B141:B142"/>
+    <mergeCell ref="B143:B151"/>
+    <mergeCell ref="A143:A170"/>
+    <mergeCell ref="B152:B155"/>
+    <mergeCell ref="B156:B170"/>
+    <mergeCell ref="A171:A174"/>
+    <mergeCell ref="A175:A193"/>
+    <mergeCell ref="A194:A199"/>
+    <mergeCell ref="B172:B174"/>
+    <mergeCell ref="B175:B178"/>
+    <mergeCell ref="B179:B184"/>
+    <mergeCell ref="B185:B190"/>
+    <mergeCell ref="B191:B193"/>
+    <mergeCell ref="B194:B197"/>
+    <mergeCell ref="B198:B199"/>
     <mergeCell ref="A51:A84"/>
     <mergeCell ref="B51:B60"/>
     <mergeCell ref="B103:B105"/>
@@ -6774,24 +6916,11 @@
     <mergeCell ref="A94:A105"/>
     <mergeCell ref="B94:B100"/>
     <mergeCell ref="A106:A110"/>
-    <mergeCell ref="A171:A174"/>
-    <mergeCell ref="A175:A193"/>
-    <mergeCell ref="A194:A199"/>
-    <mergeCell ref="B172:B174"/>
-    <mergeCell ref="B175:B178"/>
-    <mergeCell ref="B179:B184"/>
-    <mergeCell ref="B185:B190"/>
-    <mergeCell ref="B191:B193"/>
-    <mergeCell ref="B194:B197"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="A123:A142"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="B127:B139"/>
-    <mergeCell ref="B141:B142"/>
-    <mergeCell ref="B143:B151"/>
-    <mergeCell ref="A143:A170"/>
-    <mergeCell ref="B152:B155"/>
-    <mergeCell ref="B156:B170"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="A4:A47"/>
+    <mergeCell ref="B4:B37"/>
+    <mergeCell ref="B44:B47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/scripts/i18n.xlsx
+++ b/scripts/i18n.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="786">
   <si>
     <t xml:space="preserve">페이지는 [피그마] PFPlay GUI 설계서 합본의 페이지 이름입니다. </t>
   </si>
@@ -2121,6 +2121,284 @@
   </si>
   <si>
     <t>Up to 2000 characters allowed</t>
+  </si>
+  <si>
+    <t>chat.para.crew_entered</t>
+  </si>
+  <si>
+    <t>{{nickname}}님이 들어왔습니다</t>
+  </si>
+  <si>
+    <t>{{nickname}} joined</t>
+  </si>
+  <si>
+    <t>playlist.ec.exceeded_list_am</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이런! 준회원은 플레이리스트를 1개까지만 만들 수 있어요
+지갑을 연동하면 최대 10개까지 생성할 수 있어요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oh no! Associate members can create only 1 playlist.
+Connect your wallet to create up to 10.</t>
+  </si>
+  <si>
+    <t>partyroom.queue.guest_cta_title</t>
+  </si>
+  <si>
+    <t>🎧 음악을 직접 틀어보세요</t>
+  </si>
+  <si>
+    <t>🎧 Play music yourself</t>
+  </si>
+  <si>
+    <t>partyroom.queue.guest_cta_subtitle</t>
+  </si>
+  <si>
+    <t>3초만에 가입 →</t>
+  </si>
+  <si>
+    <t>Sign up in 3 seconds →</t>
+  </si>
+  <si>
+    <t>partyroom.queue.member_action_register</t>
+  </si>
+  <si>
+    <t>+ DJ 등록</t>
+  </si>
+  <si>
+    <t>+ Register as DJ</t>
+  </si>
+  <si>
+    <t>partyroom.queue.member_action_unregister</t>
+  </si>
+  <si>
+    <t>큐에서 나가기</t>
+  </si>
+  <si>
+    <t>Leave queue</t>
+  </si>
+  <si>
+    <t>partyroom.queue.member_action_change_playlist</t>
+  </si>
+  <si>
+    <t>변경</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>partyroom.queue.member_action_manage_playlists</t>
+  </si>
+  <si>
+    <t>내 플레이리스트 관리</t>
+  </si>
+  <si>
+    <t>Manage my playlists</t>
+  </si>
+  <si>
+    <t>partyroom.queue.current_dj_title</t>
+  </si>
+  <si>
+    <t>현재 DJ</t>
+  </si>
+  <si>
+    <t>Current DJ</t>
+  </si>
+  <si>
+    <t>partyroom.queue.empty</t>
+  </si>
+  <si>
+    <t>큐 비어있음</t>
+  </si>
+  <si>
+    <t>Queue empty</t>
+  </si>
+  <si>
+    <t>partyroom.queue.unregister_confirm</t>
+  </si>
+  <si>
+    <t>정말 큐에서 나가시겠어요?</t>
+  </si>
+  <si>
+    <t>Leave the queue?</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_select_playlist_title</t>
+  </si>
+  <si>
+    <t>플레이리스트 선택</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_add_tracks_title</t>
+  </si>
+  <si>
+    <t>곡 추가</t>
+  </si>
+  <si>
+    <t>Add tracks</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_playlists_management_title</t>
+  </si>
+  <si>
+    <t>My playlists</t>
+  </si>
+  <si>
+    <t>partyroom.queue.playlists_empty</t>
+  </si>
+  <si>
+    <t>아직 플레이리스트가 없어요</t>
+  </si>
+  <si>
+    <t>No playlists yet</t>
+  </si>
+  <si>
+    <t>partyroom.queue.playlist_tracks_empty</t>
+  </si>
+  <si>
+    <t>아직 곡이 없어요</t>
+  </si>
+  <si>
+    <t>No songs yet</t>
+  </si>
+  <si>
+    <t>partyroom.queue.create_playlist_cta</t>
+  </si>
+  <si>
+    <t>+ 새 플레이리스트</t>
+  </si>
+  <si>
+    <t>+ New playlist</t>
+  </si>
+  <si>
+    <t>partyroom.queue.create_playlist_placeholder</t>
+  </si>
+  <si>
+    <t>플레이리스트 이름</t>
+  </si>
+  <si>
+    <t>Playlist name</t>
+  </si>
+  <si>
+    <t>partyroom.queue.create_playlist_submit</t>
+  </si>
+  <si>
+    <t>추가</t>
+  </si>
+  <si>
+    <t>partyroom.queue.remove_track_label</t>
+  </si>
+  <si>
+    <t>Remove</t>
+  </si>
+  <si>
+    <t>partyroom.queue.add_tracks_cta</t>
+  </si>
+  <si>
+    <t>+ 곡 추가</t>
+  </si>
+  <si>
+    <t>+ Add songs</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_search_placeholder</t>
+  </si>
+  <si>
+    <t>곡명 또는 아티스트로 검색</t>
+  </si>
+  <si>
+    <t>Search by song or artist</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_empty_search</t>
+  </si>
+  <si>
+    <t>다른 키워드로 시도해보세요</t>
+  </si>
+  <si>
+    <t>Try another keyword</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_search_failed</t>
+  </si>
+  <si>
+    <t>검색에 실패했어요</t>
+  </si>
+  <si>
+    <t>Search failed</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_preview_unavailable</t>
+  </si>
+  <si>
+    <t>재생할 수 없어요</t>
+  </si>
+  <si>
+    <t>Cannot play</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_add_button</t>
+  </si>
+  <si>
+    <t>+ 추가</t>
+  </si>
+  <si>
+    <t>+ Add</t>
+  </si>
+  <si>
+    <t>partyroom.queue.add_success</t>
+  </si>
+  <si>
+    <t>플레이리스트에 추가했어요</t>
+  </si>
+  <si>
+    <t>Added to playlist</t>
+  </si>
+  <si>
+    <t>partyroom.queue.add_already_exists</t>
+  </si>
+  <si>
+    <t>이미 플레이리스트에 있어요</t>
+  </si>
+  <si>
+    <t>Already in playlist</t>
+  </si>
+  <si>
+    <t>partyroom.queue.add_limit_exceeded</t>
+  </si>
+  <si>
+    <t>플레이리스트가 가득 찼어요</t>
+  </si>
+  <si>
+    <t>Playlist is full</t>
+  </si>
+  <si>
+    <t>partyroom.queue.guest_action_blocked</t>
+  </si>
+  <si>
+    <t>로그인이 필요해요</t>
+  </si>
+  <si>
+    <t>Sign-in required</t>
+  </si>
+  <si>
+    <t>partyroom.queue.guide_start</t>
+  </si>
+  <si>
+    <t>시작</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>partyroom.queue.guide_title</t>
+  </si>
+  <si>
+    <t>DJ 규칙</t>
+  </si>
+  <si>
+    <t>DJ rules</t>
   </si>
 </sst>
 </file>
@@ -2488,7 +2766,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M235"/>
+  <dimension ref="A1:M267"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="12.6640625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.1640625" customWidth="1"/>
@@ -6969,7 +7247,7 @@
       <c r="L206" s="7"/>
       <c r="M206" s="7"/>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C207" t="s">
         <v>612</v>
       </c>
@@ -6980,7 +7258,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C208" t="s">
         <v>615</v>
       </c>
@@ -6991,7 +7269,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C209" t="s">
         <v>618</v>
       </c>
@@ -7002,7 +7280,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C210" t="s">
         <v>621</v>
       </c>
@@ -7013,7 +7291,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C211" t="s">
         <v>624</v>
       </c>
@@ -7024,7 +7302,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C212" t="s">
         <v>627</v>
       </c>
@@ -7035,7 +7313,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C213" t="s">
         <v>630</v>
       </c>
@@ -7046,7 +7324,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C214" t="s">
         <v>633</v>
       </c>
@@ -7057,7 +7335,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C215" t="s">
         <v>636</v>
       </c>
@@ -7068,7 +7346,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C216" t="s">
         <v>639</v>
       </c>
@@ -7079,7 +7357,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C217" t="s">
         <v>642</v>
       </c>
@@ -7090,7 +7368,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C218" t="s">
         <v>645</v>
       </c>
@@ -7101,7 +7379,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C219" t="s">
         <v>648</v>
       </c>
@@ -7112,7 +7390,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C220" t="s">
         <v>651</v>
       </c>
@@ -7123,7 +7401,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C221" t="s">
         <v>654</v>
       </c>
@@ -7134,7 +7412,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C222" t="s">
         <v>657</v>
       </c>
@@ -7145,7 +7423,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C223" t="s">
         <v>660</v>
       </c>
@@ -7156,7 +7434,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C224" t="s">
         <v>662</v>
       </c>
@@ -7167,7 +7445,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C225" t="s">
         <v>665</v>
       </c>
@@ -7178,7 +7456,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C226" t="s">
         <v>668</v>
       </c>
@@ -7189,7 +7467,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C227" t="s">
         <v>671</v>
       </c>
@@ -7200,7 +7478,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C228" t="s">
         <v>672</v>
       </c>
@@ -7211,7 +7489,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C229" t="s">
         <v>673</v>
       </c>
@@ -7222,7 +7500,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C230" t="s">
         <v>676</v>
       </c>
@@ -7233,7 +7511,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C231" t="s">
         <v>679</v>
       </c>
@@ -7244,7 +7522,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C232" t="s">
         <v>682</v>
       </c>
@@ -7255,7 +7533,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C233" t="s">
         <v>685</v>
       </c>
@@ -7266,7 +7544,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C234" t="s">
         <v>688</v>
       </c>
@@ -7277,7 +7555,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C235" t="s">
         <v>691</v>
       </c>
@@ -7286,6 +7564,358 @@
       </c>
       <c r="E235" t="s">
         <v>693</v>
+      </c>
+    </row>
+    <row r="236" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C236" t="s">
+        <v>694</v>
+      </c>
+      <c r="D236" t="s">
+        <v>695</v>
+      </c>
+      <c r="E236" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="237" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C237" t="s">
+        <v>697</v>
+      </c>
+      <c r="D237" t="s">
+        <v>698</v>
+      </c>
+      <c r="E237" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="238" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C238" t="s">
+        <v>700</v>
+      </c>
+      <c r="D238" t="s">
+        <v>701</v>
+      </c>
+      <c r="E238" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="239" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C239" t="s">
+        <v>703</v>
+      </c>
+      <c r="D239" t="s">
+        <v>704</v>
+      </c>
+      <c r="E239" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="240" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C240" t="s">
+        <v>706</v>
+      </c>
+      <c r="D240" t="s">
+        <v>707</v>
+      </c>
+      <c r="E240" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="241" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C241" t="s">
+        <v>709</v>
+      </c>
+      <c r="D241" t="s">
+        <v>710</v>
+      </c>
+      <c r="E241" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="242" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C242" t="s">
+        <v>712</v>
+      </c>
+      <c r="D242" t="s">
+        <v>713</v>
+      </c>
+      <c r="E242" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="243" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C243" t="s">
+        <v>715</v>
+      </c>
+      <c r="D243" t="s">
+        <v>716</v>
+      </c>
+      <c r="E243" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="244" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C244" t="s">
+        <v>718</v>
+      </c>
+      <c r="D244" t="s">
+        <v>719</v>
+      </c>
+      <c r="E244" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="245" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C245" t="s">
+        <v>721</v>
+      </c>
+      <c r="D245" t="s">
+        <v>722</v>
+      </c>
+      <c r="E245" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="246" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C246" t="s">
+        <v>724</v>
+      </c>
+      <c r="D246" t="s">
+        <v>725</v>
+      </c>
+      <c r="E246" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="247" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C247" t="s">
+        <v>727</v>
+      </c>
+      <c r="D247" t="s">
+        <v>728</v>
+      </c>
+      <c r="E247" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="248" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C248" t="s">
+        <v>729</v>
+      </c>
+      <c r="D248" t="s">
+        <v>730</v>
+      </c>
+      <c r="E248" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="249" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C249" t="s">
+        <v>732</v>
+      </c>
+      <c r="D249" t="s">
+        <v>515</v>
+      </c>
+      <c r="E249" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="250" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C250" t="s">
+        <v>734</v>
+      </c>
+      <c r="D250" t="s">
+        <v>735</v>
+      </c>
+      <c r="E250" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="251" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C251" t="s">
+        <v>737</v>
+      </c>
+      <c r="D251" t="s">
+        <v>738</v>
+      </c>
+      <c r="E251" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="252" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C252" t="s">
+        <v>740</v>
+      </c>
+      <c r="D252" t="s">
+        <v>741</v>
+      </c>
+      <c r="E252" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="253" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C253" t="s">
+        <v>743</v>
+      </c>
+      <c r="D253" t="s">
+        <v>744</v>
+      </c>
+      <c r="E253" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="254" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C254" t="s">
+        <v>746</v>
+      </c>
+      <c r="D254" t="s">
+        <v>747</v>
+      </c>
+      <c r="E254" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="255" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C255" t="s">
+        <v>748</v>
+      </c>
+      <c r="D255" t="s">
+        <v>57</v>
+      </c>
+      <c r="E255" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="256" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C256" t="s">
+        <v>750</v>
+      </c>
+      <c r="D256" t="s">
+        <v>751</v>
+      </c>
+      <c r="E256" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="257" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C257" t="s">
+        <v>753</v>
+      </c>
+      <c r="D257" t="s">
+        <v>754</v>
+      </c>
+      <c r="E257" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="258" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C258" t="s">
+        <v>756</v>
+      </c>
+      <c r="D258" t="s">
+        <v>757</v>
+      </c>
+      <c r="E258" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="259" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C259" t="s">
+        <v>759</v>
+      </c>
+      <c r="D259" t="s">
+        <v>760</v>
+      </c>
+      <c r="E259" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="260" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C260" t="s">
+        <v>762</v>
+      </c>
+      <c r="D260" t="s">
+        <v>763</v>
+      </c>
+      <c r="E260" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="261" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C261" t="s">
+        <v>765</v>
+      </c>
+      <c r="D261" t="s">
+        <v>766</v>
+      </c>
+      <c r="E261" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="262" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C262" t="s">
+        <v>768</v>
+      </c>
+      <c r="D262" t="s">
+        <v>769</v>
+      </c>
+      <c r="E262" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="263" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C263" t="s">
+        <v>771</v>
+      </c>
+      <c r="D263" t="s">
+        <v>772</v>
+      </c>
+      <c r="E263" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="264" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C264" t="s">
+        <v>774</v>
+      </c>
+      <c r="D264" t="s">
+        <v>775</v>
+      </c>
+      <c r="E264" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="265" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C265" t="s">
+        <v>777</v>
+      </c>
+      <c r="D265" t="s">
+        <v>778</v>
+      </c>
+      <c r="E265" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="266" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C266" t="s">
+        <v>780</v>
+      </c>
+      <c r="D266" t="s">
+        <v>781</v>
+      </c>
+      <c r="E266" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="267" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C267" t="s">
+        <v>783</v>
+      </c>
+      <c r="D267" t="s">
+        <v>784</v>
+      </c>
+      <c r="E267" t="s">
+        <v>785</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/i18n.xlsx
+++ b/scripts/i18n.xlsx
@@ -1549,10 +1549,12 @@
     <t>ed.para.edit_only_admin</t>
   </si>
   <si>
-    <t>Community Manager이상 관리자만 수정 가능해요</t>
-  </si>
-  <si>
-    <t>Only Community Manager and above can make edit action</t>
+    <t xml:space="preserve">Community Manager이상
+관리자만 수정 가능해요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only Community Manager and above
+can make edit action</t>
   </si>
   <si>
     <t>ed.para.empty_notice</t>
@@ -6969,7 +6971,7 @@
       <c r="L206" s="7"/>
       <c r="M206" s="7"/>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C207" t="s">
         <v>612</v>
       </c>
@@ -6980,7 +6982,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C208" t="s">
         <v>615</v>
       </c>
@@ -6991,7 +6993,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C209" t="s">
         <v>618</v>
       </c>
@@ -7002,7 +7004,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C210" t="s">
         <v>621</v>
       </c>
@@ -7013,7 +7015,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C211" t="s">
         <v>624</v>
       </c>
@@ -7024,7 +7026,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C212" t="s">
         <v>627</v>
       </c>
@@ -7035,7 +7037,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C213" t="s">
         <v>630</v>
       </c>
@@ -7046,7 +7048,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C214" t="s">
         <v>633</v>
       </c>
@@ -7057,7 +7059,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C215" t="s">
         <v>636</v>
       </c>
@@ -7068,7 +7070,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C216" t="s">
         <v>639</v>
       </c>
@@ -7079,7 +7081,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C217" t="s">
         <v>642</v>
       </c>
@@ -7090,7 +7092,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C218" t="s">
         <v>645</v>
       </c>
@@ -7101,7 +7103,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C219" t="s">
         <v>648</v>
       </c>
@@ -7112,7 +7114,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C220" t="s">
         <v>651</v>
       </c>
@@ -7123,7 +7125,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C221" t="s">
         <v>654</v>
       </c>
@@ -7134,7 +7136,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C222" t="s">
         <v>657</v>
       </c>
@@ -7145,7 +7147,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C223" t="s">
         <v>660</v>
       </c>
@@ -7156,7 +7158,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C224" t="s">
         <v>662</v>
       </c>
@@ -7167,7 +7169,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C225" t="s">
         <v>665</v>
       </c>
@@ -7178,7 +7180,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C226" t="s">
         <v>668</v>
       </c>
@@ -7189,7 +7191,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C227" t="s">
         <v>671</v>
       </c>
@@ -7200,7 +7202,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C228" t="s">
         <v>672</v>
       </c>
@@ -7211,7 +7213,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C229" t="s">
         <v>673</v>
       </c>
@@ -7222,7 +7224,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C230" t="s">
         <v>676</v>
       </c>
@@ -7233,7 +7235,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C231" t="s">
         <v>679</v>
       </c>
@@ -7244,7 +7246,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C232" t="s">
         <v>682</v>
       </c>
@@ -7255,7 +7257,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C233" t="s">
         <v>685</v>
       </c>
@@ -7266,7 +7268,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C234" t="s">
         <v>688</v>
       </c>
@@ -7277,7 +7279,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C235" t="s">
         <v>691</v>
       </c>

--- a/scripts/i18n.xlsx
+++ b/scripts/i18n.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="857">
   <si>
     <t xml:space="preserve">페이지는 [피그마] PFPlay GUI 설계서 합본의 페이지 이름입니다. </t>
   </si>
@@ -817,10 +817,10 @@
     <t>onboard.para.domain_format</t>
   </si>
   <si>
-    <t>웹 페이지 주소는 pfplay.xyz/도메인으로 시작</t>
-  </si>
-  <si>
-    <t>Web address starts with pfplay.xyz/domain</t>
+    <t>예: pfplay.xyz/link/my-room</t>
+  </si>
+  <si>
+    <t>e.g. pfplay.xyz/link/my-room</t>
   </si>
   <si>
     <t>onboard.para.guest_limit</t>
@@ -1277,9 +1277,6 @@
     <t>dj.title.current_dj</t>
   </si>
   <si>
-    <t>현재 디제잉</t>
-  </si>
-  <si>
     <t>Now DJing</t>
   </si>
   <si>
@@ -1394,12 +1391,12 @@
     <t>dj.para.no_dj_crew</t>
   </si>
   <si>
-    <t xml:space="preserve">현재 디제잉 인원이 없어요
-파티의 흥을 책임질 DJ가 되어보세요!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No one is DJing now.
-Why not become the DJ and make some noise!</t>
+    <t xml:space="preserve">현재 디제잉하는 사람이 없어요.
+첫 곡을 틀어보세요!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No one is DJing right now.
+Play the first song!</t>
   </si>
   <si>
     <t>dj.para.create_playlist_song</t>
@@ -2123,6 +2120,502 @@
   </si>
   <si>
     <t>Up to 2000 characters allowed</t>
+  </si>
+  <si>
+    <t>common.menu.title</t>
+  </si>
+  <si>
+    <t>메뉴</t>
+  </si>
+  <si>
+    <t>Menu</t>
+  </si>
+  <si>
+    <t>common.menu.notification_settings</t>
+  </si>
+  <si>
+    <t>알림 설정</t>
+  </si>
+  <si>
+    <t>Notification settings</t>
+  </si>
+  <si>
+    <t>common.ec.char_limit_12_short</t>
+  </si>
+  <si>
+    <t>최대 12자, 공백·특수문자 불가</t>
+  </si>
+  <si>
+    <t>Max 12 chars, no spaces</t>
+  </si>
+  <si>
+    <t>common.ec.char_limit_50_short</t>
+  </si>
+  <si>
+    <t>최대 50자</t>
+  </si>
+  <si>
+    <t>Max 50 characters</t>
+  </si>
+  <si>
+    <t>chat.para.playback_summary_skipped</t>
+  </si>
+  <si>
+    <t>스킵</t>
+  </si>
+  <si>
+    <t>skipped</t>
+  </si>
+  <si>
+    <t>chat.para.playback_summary_dj_fallback</t>
+  </si>
+  <si>
+    <t>DJ</t>
+  </si>
+  <si>
+    <t>chat.btn.choose_emoji</t>
+  </si>
+  <si>
+    <t>이모지 선택</t>
+  </si>
+  <si>
+    <t>Choose emoji</t>
+  </si>
+  <si>
+    <t>chat.title.recently_used</t>
+  </si>
+  <si>
+    <t>최근 사용</t>
+  </si>
+  <si>
+    <t>Recently used</t>
+  </si>
+  <si>
+    <t>settings.notifications.title</t>
+  </si>
+  <si>
+    <t>알림</t>
+  </si>
+  <si>
+    <t>Notifications</t>
+  </si>
+  <si>
+    <t>settings.notifications.toggle_label</t>
+  </si>
+  <si>
+    <t>공지 푸시 알림 받기</t>
+  </si>
+  <si>
+    <t>Receive announcement push notifications</t>
+  </si>
+  <si>
+    <t>settings.notifications.description</t>
+  </si>
+  <si>
+    <t>운영 공지와 이벤트 소식을 푸시 알림으로 받아볼 수 있어요.</t>
+  </si>
+  <si>
+    <t>Get operational announcements and event news as push notifications.</t>
+  </si>
+  <si>
+    <t>settings.notifications.needs_install_hint</t>
+  </si>
+  <si>
+    <t>홈 화면에 앱을 추가한 뒤 알림을 켤 수 있어요.</t>
+  </si>
+  <si>
+    <t>Add the app to your home screen first, then you can turn on notifications.</t>
+  </si>
+  <si>
+    <t>settings.notifications.denied_hint</t>
+  </si>
+  <si>
+    <t>브라우저 설정에서 알림 차단을 해제해 주세요.</t>
+  </si>
+  <si>
+    <t>Please unblock notifications in your browser settings.</t>
+  </si>
+  <si>
+    <t>dj.btn.search_and_register_dj</t>
+  </si>
+  <si>
+    <t>곡 검색하고 DJ 등록</t>
+  </si>
+  <si>
+    <t>Search a song and be a DJ</t>
+  </si>
+  <si>
+    <t>dj.btn.pick_from_my_playlist</t>
+  </si>
+  <si>
+    <t>내 플레이리스트에서 고르기</t>
+  </si>
+  <si>
+    <t>Choose from my playlist</t>
+  </si>
+  <si>
+    <t>dj.btn.register_with_this_song</t>
+  </si>
+  <si>
+    <t>이 곡으로 DJ 등록</t>
+  </si>
+  <si>
+    <t>Be a DJ</t>
+  </si>
+  <si>
+    <t>dj.para.search_song_to_dj</t>
+  </si>
+  <si>
+    <t>디제잉할 곡을 검색하세요.</t>
+  </si>
+  <si>
+    <t>Search for a song to DJ</t>
+  </si>
+  <si>
+    <t>dj.para.select_song_to_dj</t>
+  </si>
+  <si>
+    <t>디제잉할 곡을 선택해 주세요</t>
+  </si>
+  <si>
+    <t>Choose a song to DJ</t>
+  </si>
+  <si>
+    <t>dj.para.start_djing_with_this_song</t>
+  </si>
+  <si>
+    <t>이 곡으로 디제잉을 시작해요</t>
+  </si>
+  <si>
+    <t>Let's start DJing with this song</t>
+  </si>
+  <si>
+    <t>playlist.para.now_playing</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>playlist.para.next_up</t>
+  </si>
+  <si>
+    <t>NEXT</t>
+  </si>
+  <si>
+    <t>playlist.ec.exceeded_list_am</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이런! 준회원은 플레이리스트를 1개까지만 만들 수 있어요
+지갑을 연동하면 최대 10개까지 생성할 수 있어요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oh no! Associate members can create only 1 playlist.
+Connect your wallet to create up to 10.</t>
+  </si>
+  <si>
+    <t>partyroom.ec.concurrent_entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다른 기기나 탭에서 입장을 처리하고 있어요.
+잠시 후 다시 시도해 주세요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Another device or tab is entering a party room.
+Please try again in a moment.</t>
+  </si>
+  <si>
+    <t>partyroom.queue.guest_cta_title</t>
+  </si>
+  <si>
+    <t>🎧 음악을 직접 틀어보세요</t>
+  </si>
+  <si>
+    <t>🎧 Play music yourself</t>
+  </si>
+  <si>
+    <t>partyroom.queue.guest_cta_subtitle</t>
+  </si>
+  <si>
+    <t>3초만에 가입 →</t>
+  </si>
+  <si>
+    <t>Sign up in 3 seconds →</t>
+  </si>
+  <si>
+    <t>partyroom.queue.member_action_register</t>
+  </si>
+  <si>
+    <t>+ DJ 등록</t>
+  </si>
+  <si>
+    <t>+ Register as DJ</t>
+  </si>
+  <si>
+    <t>partyroom.queue.member_action_unregister</t>
+  </si>
+  <si>
+    <t>큐에서 나가기</t>
+  </si>
+  <si>
+    <t>Leave queue</t>
+  </si>
+  <si>
+    <t>partyroom.queue.member_action_change_playlist</t>
+  </si>
+  <si>
+    <t>변경</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>partyroom.queue.member_action_manage_playlists</t>
+  </si>
+  <si>
+    <t>내 플레이리스트 관리</t>
+  </si>
+  <si>
+    <t>Manage my playlists</t>
+  </si>
+  <si>
+    <t>partyroom.queue.current_dj_title</t>
+  </si>
+  <si>
+    <t>현재 DJ</t>
+  </si>
+  <si>
+    <t>Current DJ</t>
+  </si>
+  <si>
+    <t>partyroom.queue.empty</t>
+  </si>
+  <si>
+    <t>큐 비어있음</t>
+  </si>
+  <si>
+    <t>Queue empty</t>
+  </si>
+  <si>
+    <t>partyroom.queue.unregister_confirm</t>
+  </si>
+  <si>
+    <t>정말 큐에서 나가시겠어요?</t>
+  </si>
+  <si>
+    <t>Leave the queue?</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_select_playlist_title</t>
+  </si>
+  <si>
+    <t>플레이리스트 선택</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_add_tracks_title</t>
+  </si>
+  <si>
+    <t>곡 추가</t>
+  </si>
+  <si>
+    <t>Add tracks</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_playlists_management_title</t>
+  </si>
+  <si>
+    <t>My playlists</t>
+  </si>
+  <si>
+    <t>partyroom.queue.playlists_empty</t>
+  </si>
+  <si>
+    <t>아직 플레이리스트가 없어요</t>
+  </si>
+  <si>
+    <t>No playlists yet</t>
+  </si>
+  <si>
+    <t>partyroom.queue.playlist_tracks_empty</t>
+  </si>
+  <si>
+    <t>아직 곡이 없어요</t>
+  </si>
+  <si>
+    <t>No songs yet</t>
+  </si>
+  <si>
+    <t>partyroom.queue.create_playlist_cta</t>
+  </si>
+  <si>
+    <t>+ 새 플레이리스트</t>
+  </si>
+  <si>
+    <t>+ New playlist</t>
+  </si>
+  <si>
+    <t>partyroom.queue.create_playlist_placeholder</t>
+  </si>
+  <si>
+    <t>플레이리스트 이름</t>
+  </si>
+  <si>
+    <t>Playlist name</t>
+  </si>
+  <si>
+    <t>partyroom.queue.create_playlist_submit</t>
+  </si>
+  <si>
+    <t>추가</t>
+  </si>
+  <si>
+    <t>partyroom.queue.remove_track_label</t>
+  </si>
+  <si>
+    <t>Remove</t>
+  </si>
+  <si>
+    <t>partyroom.queue.add_tracks_cta</t>
+  </si>
+  <si>
+    <t>+ 곡 추가</t>
+  </si>
+  <si>
+    <t>+ Add songs</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_search_placeholder</t>
+  </si>
+  <si>
+    <t>곡명 또는 아티스트로 검색</t>
+  </si>
+  <si>
+    <t>Search by song or artist</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_empty_search</t>
+  </si>
+  <si>
+    <t>다른 키워드로 시도해보세요</t>
+  </si>
+  <si>
+    <t>Try another keyword</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_search_failed</t>
+  </si>
+  <si>
+    <t>검색에 실패했어요</t>
+  </si>
+  <si>
+    <t>Search failed</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_preview_unavailable</t>
+  </si>
+  <si>
+    <t>재생할 수 없어요</t>
+  </si>
+  <si>
+    <t>Cannot play</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_add_button</t>
+  </si>
+  <si>
+    <t>+ 추가</t>
+  </si>
+  <si>
+    <t>+ Add</t>
+  </si>
+  <si>
+    <t>partyroom.queue.add_success</t>
+  </si>
+  <si>
+    <t>플레이리스트에 추가했어요</t>
+  </si>
+  <si>
+    <t>Added to playlist</t>
+  </si>
+  <si>
+    <t>partyroom.queue.add_already_exists</t>
+  </si>
+  <si>
+    <t>이미 플레이리스트에 있어요</t>
+  </si>
+  <si>
+    <t>Already in playlist</t>
+  </si>
+  <si>
+    <t>partyroom.queue.add_limit_exceeded</t>
+  </si>
+  <si>
+    <t>플레이리스트가 가득 찼어요</t>
+  </si>
+  <si>
+    <t>Playlist is full</t>
+  </si>
+  <si>
+    <t>partyroom.queue.guest_action_blocked</t>
+  </si>
+  <si>
+    <t>로그인이 필요해요</t>
+  </si>
+  <si>
+    <t>Sign-in required</t>
+  </si>
+  <si>
+    <t>partyroom.queue.guide_start</t>
+  </si>
+  <si>
+    <t>시작</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>partyroom.queue.guide_title</t>
+  </si>
+  <si>
+    <t>DJ 규칙</t>
+  </si>
+  <si>
+    <t>DJ rules</t>
+  </si>
+  <si>
+    <t>partyroom.queue.song_count</t>
+  </si>
+  <si>
+    <t>{{count}}곡</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_select_confirm</t>
+  </si>
+  <si>
+    <t>선택 완료</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>partyroom.queue.no_track</t>
+  </si>
+  <si>
+    <t>지금 재생 중인 곡이 없어요</t>
+  </si>
+  <si>
+    <t>No song playing right now</t>
+  </si>
+  <si>
+    <t>partyroom.queue.tab_chat</t>
+  </si>
+  <si>
+    <t>partyroom.queue.my_position</t>
+  </si>
+  <si>
+    <t>내 순서 {{position}}번째 · 총 {{total}}명</t>
+  </si>
+  <si>
+    <t>You're #{{position}} of {{total}}</t>
   </si>
 </sst>
 </file>
@@ -2490,7 +2983,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M235"/>
+  <dimension ref="A1:M293"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="12.6640625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.1640625" customWidth="1"/>
@@ -5597,7 +6090,7 @@
         <v>417</v>
       </c>
       <c r="E143" s="11" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F143" s="7"/>
       <c r="G143" s="15"/>
@@ -5612,13 +6105,13 @@
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="D144" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="D144" s="11" t="s">
+      <c r="E144" s="11" t="s">
         <v>420</v>
-      </c>
-      <c r="E144" s="11" t="s">
-        <v>421</v>
       </c>
       <c r="F144" s="7"/>
       <c r="G144" s="15"/>
@@ -5633,13 +6126,13 @@
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D145" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="D145" s="4" t="s">
+      <c r="E145" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="E145" s="4" t="s">
-        <v>424</v>
       </c>
       <c r="F145" s="7"/>
       <c r="G145" s="17"/>
@@ -5654,13 +6147,13 @@
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D146" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="D146" s="4" t="s">
+      <c r="E146" s="4" t="s">
         <v>426</v>
-      </c>
-      <c r="E146" s="4" t="s">
-        <v>427</v>
       </c>
       <c r="F146" s="7"/>
       <c r="G146" s="7"/>
@@ -5675,13 +6168,13 @@
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="D147" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="D147" s="4" t="s">
+      <c r="E147" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="E147" s="4" t="s">
-        <v>430</v>
       </c>
       <c r="F147" s="7"/>
       <c r="G147" s="7"/>
@@ -5696,13 +6189,13 @@
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D148" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="D148" s="4" t="s">
+      <c r="E148" s="4" t="s">
         <v>432</v>
-      </c>
-      <c r="E148" s="4" t="s">
-        <v>433</v>
       </c>
       <c r="F148" s="7"/>
       <c r="G148" s="7"/>
@@ -5717,13 +6210,13 @@
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D149" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="D149" s="4" t="s">
+      <c r="E149" s="4" t="s">
         <v>435</v>
-      </c>
-      <c r="E149" s="4" t="s">
-        <v>436</v>
       </c>
       <c r="F149" s="7"/>
       <c r="G149" s="7"/>
@@ -5738,13 +6231,13 @@
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D150" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="D150" s="4" t="s">
+      <c r="E150" s="4" t="s">
         <v>438</v>
-      </c>
-      <c r="E150" s="4" t="s">
-        <v>439</v>
       </c>
       <c r="F150" s="7"/>
       <c r="G150" s="7"/>
@@ -5759,13 +6252,13 @@
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="D151" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="D151" s="4" t="s">
+      <c r="E151" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="E151" s="4" t="s">
-        <v>442</v>
       </c>
       <c r="F151" s="7"/>
       <c r="G151" s="7"/>
@@ -5782,13 +6275,13 @@
         <v>11</v>
       </c>
       <c r="C152" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D152" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="D152" s="4" t="s">
+      <c r="E152" s="4" t="s">
         <v>444</v>
-      </c>
-      <c r="E152" s="4" t="s">
-        <v>445</v>
       </c>
       <c r="F152" s="7"/>
       <c r="G152" s="7"/>
@@ -5803,13 +6296,13 @@
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D153" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="D153" s="4" t="s">
+      <c r="E153" s="4" t="s">
         <v>447</v>
-      </c>
-      <c r="E153" s="4" t="s">
-        <v>448</v>
       </c>
       <c r="F153" s="7"/>
       <c r="G153" s="7"/>
@@ -5824,13 +6317,13 @@
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="18" t="s">
+        <v>448</v>
+      </c>
+      <c r="D154" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="D154" s="4" t="s">
+      <c r="E154" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="E154" s="4" t="s">
-        <v>451</v>
       </c>
       <c r="F154" s="7"/>
       <c r="G154" s="7"/>
@@ -5845,13 +6338,13 @@
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="D155" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="D155" s="4" t="s">
+      <c r="E155" s="4" t="s">
         <v>453</v>
-      </c>
-      <c r="E155" s="4" t="s">
-        <v>454</v>
       </c>
       <c r="F155" s="7"/>
       <c r="G155" s="7"/>
@@ -5868,13 +6361,13 @@
         <v>118</v>
       </c>
       <c r="C156" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="D156" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="D156" s="4" t="s">
+      <c r="E156" s="9" t="s">
         <v>456</v>
-      </c>
-      <c r="E156" s="9" t="s">
-        <v>457</v>
       </c>
       <c r="F156" s="7"/>
       <c r="G156" s="7"/>
@@ -5889,13 +6382,13 @@
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="D157" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="D157" s="4" t="s">
+      <c r="E157" s="11" t="s">
         <v>459</v>
-      </c>
-      <c r="E157" s="11" t="s">
-        <v>460</v>
       </c>
       <c r="F157" s="7"/>
       <c r="G157" s="7"/>
@@ -5910,13 +6403,13 @@
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="D158" s="10" t="s">
         <v>461</v>
       </c>
-      <c r="D158" s="10" t="s">
+      <c r="E158" s="11" t="s">
         <v>462</v>
-      </c>
-      <c r="E158" s="11" t="s">
-        <v>463</v>
       </c>
       <c r="F158" s="7"/>
       <c r="G158" s="7"/>
@@ -5931,13 +6424,13 @@
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D159" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="D159" s="4" t="s">
+      <c r="E159" s="11" t="s">
         <v>465</v>
-      </c>
-      <c r="E159" s="11" t="s">
-        <v>466</v>
       </c>
       <c r="F159" s="7"/>
       <c r="G159" s="7"/>
@@ -5952,13 +6445,13 @@
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="D160" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="D160" s="4" t="s">
+      <c r="E160" s="4" t="s">
         <v>468</v>
-      </c>
-      <c r="E160" s="4" t="s">
-        <v>469</v>
       </c>
       <c r="F160" s="7"/>
       <c r="G160" s="7"/>
@@ -5973,13 +6466,13 @@
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D161" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="D161" s="4" t="s">
+      <c r="E161" s="4" t="s">
         <v>471</v>
-      </c>
-      <c r="E161" s="4" t="s">
-        <v>472</v>
       </c>
       <c r="F161" s="7"/>
       <c r="G161" s="7"/>
@@ -5994,13 +6487,13 @@
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="D162" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="D162" s="4" t="s">
+      <c r="E162" s="4" t="s">
         <v>474</v>
-      </c>
-      <c r="E162" s="4" t="s">
-        <v>475</v>
       </c>
       <c r="F162" s="7"/>
       <c r="G162" s="7"/>
@@ -6015,13 +6508,13 @@
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="D163" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="D163" s="4" t="s">
+      <c r="E163" s="4" t="s">
         <v>477</v>
-      </c>
-      <c r="E163" s="4" t="s">
-        <v>478</v>
       </c>
       <c r="F163" s="7"/>
       <c r="G163" s="7"/>
@@ -6036,13 +6529,13 @@
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D164" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="D164" s="4" t="s">
+      <c r="E164" s="11" t="s">
         <v>480</v>
-      </c>
-      <c r="E164" s="11" t="s">
-        <v>481</v>
       </c>
       <c r="F164" s="7"/>
       <c r="G164" s="7"/>
@@ -6057,13 +6550,13 @@
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="D165" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="D165" s="4" t="s">
+      <c r="E165" s="4" t="s">
         <v>483</v>
-      </c>
-      <c r="E165" s="4" t="s">
-        <v>484</v>
       </c>
       <c r="F165" s="7"/>
       <c r="G165" s="7"/>
@@ -6078,13 +6571,13 @@
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="D166" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="D166" s="4" t="s">
+      <c r="E166" s="4" t="s">
         <v>486</v>
-      </c>
-      <c r="E166" s="4" t="s">
-        <v>487</v>
       </c>
       <c r="F166" s="7"/>
       <c r="G166" s="7"/>
@@ -6099,13 +6592,13 @@
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D167" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="D167" s="4" t="s">
+      <c r="E167" s="4" t="s">
         <v>489</v>
-      </c>
-      <c r="E167" s="4" t="s">
-        <v>490</v>
       </c>
       <c r="F167" s="7"/>
       <c r="G167" s="7"/>
@@ -6120,13 +6613,13 @@
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="D168" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="D168" s="4" t="s">
+      <c r="E168" s="4" t="s">
         <v>492</v>
-      </c>
-      <c r="E168" s="4" t="s">
-        <v>493</v>
       </c>
       <c r="F168" s="7"/>
       <c r="G168" s="7"/>
@@ -6141,13 +6634,13 @@
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="D169" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="D169" s="4" t="s">
+      <c r="E169" s="4" t="s">
         <v>495</v>
-      </c>
-      <c r="E169" s="4" t="s">
-        <v>496</v>
       </c>
       <c r="F169" s="7"/>
       <c r="G169" s="7"/>
@@ -6162,13 +6655,13 @@
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="D170" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="D170" s="4" t="s">
+      <c r="E170" s="4" t="s">
         <v>498</v>
-      </c>
-      <c r="E170" s="4" t="s">
-        <v>499</v>
       </c>
       <c r="F170" s="7"/>
       <c r="G170" s="7"/>
@@ -6181,19 +6674,19 @@
     </row>
     <row r="171" ht="13" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B171" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C171" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="D171" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="D171" s="4" t="s">
+      <c r="E171" s="4" t="s">
         <v>502</v>
-      </c>
-      <c r="E171" s="4" t="s">
-        <v>503</v>
       </c>
       <c r="F171" s="7"/>
       <c r="G171" s="7"/>
@@ -6210,13 +6703,13 @@
         <v>118</v>
       </c>
       <c r="C172" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="D172" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="D172" s="4" t="s">
+      <c r="E172" s="11" t="s">
         <v>505</v>
-      </c>
-      <c r="E172" s="11" t="s">
-        <v>506</v>
       </c>
       <c r="F172" s="7"/>
       <c r="G172" s="7"/>
@@ -6231,13 +6724,13 @@
       <c r="A173" s="2"/>
       <c r="B173" s="7"/>
       <c r="C173" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="D173" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="D173" s="4" t="s">
+      <c r="E173" s="11" t="s">
         <v>508</v>
-      </c>
-      <c r="E173" s="11" t="s">
-        <v>509</v>
       </c>
       <c r="F173" s="7"/>
       <c r="G173" s="7"/>
@@ -6252,13 +6745,13 @@
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="D174" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="D174" s="4" t="s">
+      <c r="E174" s="4" t="s">
         <v>511</v>
-      </c>
-      <c r="E174" s="4" t="s">
-        <v>512</v>
       </c>
       <c r="F174" s="7"/>
       <c r="G174" s="7"/>
@@ -6271,19 +6764,19 @@
     </row>
     <row r="175" ht="13" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B175" s="7" t="s">
         <v>230</v>
       </c>
       <c r="C175" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="D175" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="D175" s="4" t="s">
+      <c r="E175" s="4" t="s">
         <v>515</v>
-      </c>
-      <c r="E175" s="4" t="s">
-        <v>516</v>
       </c>
       <c r="F175" s="7"/>
       <c r="G175" s="7"/>
@@ -6298,13 +6791,13 @@
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="D176" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="D176" s="4" t="s">
+      <c r="E176" s="4" t="s">
         <v>518</v>
-      </c>
-      <c r="E176" s="4" t="s">
-        <v>519</v>
       </c>
       <c r="F176" s="7"/>
       <c r="G176" s="7"/>
@@ -6319,13 +6812,13 @@
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="D177" s="11" t="s">
         <v>520</v>
       </c>
-      <c r="D177" s="11" t="s">
+      <c r="E177" s="11" t="s">
         <v>521</v>
-      </c>
-      <c r="E177" s="11" t="s">
-        <v>522</v>
       </c>
       <c r="F177" s="7"/>
       <c r="G177" s="7"/>
@@ -6340,13 +6833,13 @@
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="D178" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="D178" s="11" t="s">
+      <c r="E178" s="11" t="s">
         <v>524</v>
-      </c>
-      <c r="E178" s="11" t="s">
-        <v>525</v>
       </c>
       <c r="F178" s="7"/>
       <c r="G178" s="7"/>
@@ -6363,13 +6856,13 @@
         <v>11</v>
       </c>
       <c r="C179" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="D179" s="11" t="s">
         <v>526</v>
       </c>
-      <c r="D179" s="11" t="s">
+      <c r="E179" s="11" t="s">
         <v>527</v>
-      </c>
-      <c r="E179" s="11" t="s">
-        <v>528</v>
       </c>
       <c r="F179" s="7"/>
       <c r="G179" s="7"/>
@@ -6384,13 +6877,13 @@
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="D180" s="11" t="s">
         <v>529</v>
       </c>
-      <c r="D180" s="11" t="s">
+      <c r="E180" s="11" t="s">
         <v>530</v>
-      </c>
-      <c r="E180" s="11" t="s">
-        <v>531</v>
       </c>
       <c r="F180" s="7"/>
       <c r="G180" s="7"/>
@@ -6405,13 +6898,13 @@
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="10" t="s">
+        <v>531</v>
+      </c>
+      <c r="D181" s="11" t="s">
         <v>532</v>
       </c>
-      <c r="D181" s="11" t="s">
+      <c r="E181" s="11" t="s">
         <v>533</v>
-      </c>
-      <c r="E181" s="11" t="s">
-        <v>534</v>
       </c>
       <c r="F181" s="7"/>
       <c r="G181" s="7"/>
@@ -6426,13 +6919,13 @@
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="10" t="s">
+        <v>534</v>
+      </c>
+      <c r="D182" s="11" t="s">
         <v>535</v>
       </c>
-      <c r="D182" s="11" t="s">
+      <c r="E182" s="11" t="s">
         <v>536</v>
-      </c>
-      <c r="E182" s="11" t="s">
-        <v>537</v>
       </c>
       <c r="F182" s="7"/>
       <c r="G182" s="7"/>
@@ -6447,13 +6940,13 @@
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="D183" s="11" t="s">
         <v>538</v>
       </c>
-      <c r="D183" s="11" t="s">
+      <c r="E183" s="11" t="s">
         <v>539</v>
-      </c>
-      <c r="E183" s="11" t="s">
-        <v>540</v>
       </c>
       <c r="F183" s="7"/>
       <c r="G183" s="7"/>
@@ -6468,13 +6961,13 @@
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="D184" s="11" t="s">
         <v>541</v>
       </c>
-      <c r="D184" s="11" t="s">
+      <c r="E184" s="11" t="s">
         <v>542</v>
-      </c>
-      <c r="E184" s="11" t="s">
-        <v>543</v>
       </c>
       <c r="F184" s="7"/>
       <c r="G184" s="7"/>
@@ -6491,13 +6984,13 @@
         <v>118</v>
       </c>
       <c r="C185" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="D185" s="11" t="s">
         <v>544</v>
       </c>
-      <c r="D185" s="11" t="s">
+      <c r="E185" s="10" t="s">
         <v>545</v>
-      </c>
-      <c r="E185" s="10" t="s">
-        <v>546</v>
       </c>
       <c r="F185" s="7"/>
       <c r="G185" s="7"/>
@@ -6512,13 +7005,13 @@
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="D186" s="11" t="s">
         <v>547</v>
       </c>
-      <c r="D186" s="11" t="s">
+      <c r="E186" s="11" t="s">
         <v>548</v>
-      </c>
-      <c r="E186" s="11" t="s">
-        <v>549</v>
       </c>
       <c r="F186" s="7"/>
       <c r="G186" s="7"/>
@@ -6533,13 +7026,13 @@
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="D187" s="11" t="s">
         <v>550</v>
       </c>
-      <c r="D187" s="11" t="s">
+      <c r="E187" s="11" t="s">
         <v>551</v>
-      </c>
-      <c r="E187" s="11" t="s">
-        <v>552</v>
       </c>
       <c r="F187" s="7"/>
       <c r="G187" s="7"/>
@@ -6554,13 +7047,13 @@
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="D188" s="11" t="s">
         <v>553</v>
       </c>
-      <c r="D188" s="11" t="s">
+      <c r="E188" s="11" t="s">
         <v>554</v>
-      </c>
-      <c r="E188" s="11" t="s">
-        <v>555</v>
       </c>
       <c r="F188" s="7"/>
       <c r="G188" s="7"/>
@@ -6575,13 +7068,13 @@
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="D189" s="11" t="s">
         <v>556</v>
       </c>
-      <c r="D189" s="11" t="s">
+      <c r="E189" s="11" t="s">
         <v>557</v>
-      </c>
-      <c r="E189" s="11" t="s">
-        <v>558</v>
       </c>
       <c r="F189" s="7"/>
       <c r="G189" s="7"/>
@@ -6596,13 +7089,13 @@
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="D190" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="D190" s="11" t="s">
+      <c r="E190" s="11" t="s">
         <v>560</v>
-      </c>
-      <c r="E190" s="11" t="s">
-        <v>561</v>
       </c>
       <c r="F190" s="7"/>
       <c r="G190" s="7"/>
@@ -6619,13 +7112,13 @@
         <v>127</v>
       </c>
       <c r="C191" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="D191" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="D191" s="11" t="s">
+      <c r="E191" s="11" t="s">
         <v>563</v>
-      </c>
-      <c r="E191" s="11" t="s">
-        <v>564</v>
       </c>
       <c r="F191" s="7"/>
       <c r="G191" s="7"/>
@@ -6640,13 +7133,13 @@
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="D192" s="11" t="s">
         <v>565</v>
       </c>
-      <c r="D192" s="11" t="s">
+      <c r="E192" s="11" t="s">
         <v>566</v>
-      </c>
-      <c r="E192" s="11" t="s">
-        <v>567</v>
       </c>
       <c r="F192" s="7"/>
       <c r="G192" s="7"/>
@@ -6661,13 +7154,13 @@
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="D193" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="D193" s="11" t="s">
+      <c r="E193" s="10" t="s">
         <v>569</v>
-      </c>
-      <c r="E193" s="10" t="s">
-        <v>570</v>
       </c>
       <c r="F193" s="7"/>
       <c r="G193" s="7"/>
@@ -6680,19 +7173,19 @@
     </row>
     <row r="194" ht="14" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="B194" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="B194" s="7" t="s">
+      <c r="C194" s="7" t="s">
         <v>572</v>
       </c>
-      <c r="C194" s="7" t="s">
+      <c r="D194" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="D194" s="11" t="s">
+      <c r="E194" s="11" t="s">
         <v>574</v>
-      </c>
-      <c r="E194" s="11" t="s">
-        <v>575</v>
       </c>
       <c r="F194" s="7"/>
       <c r="G194" s="7"/>
@@ -6707,13 +7200,13 @@
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="D195" s="11" t="s">
         <v>576</v>
       </c>
-      <c r="D195" s="11" t="s">
+      <c r="E195" s="4" t="s">
         <v>577</v>
-      </c>
-      <c r="E195" s="4" t="s">
-        <v>578</v>
       </c>
       <c r="F195" s="7"/>
       <c r="G195" s="7"/>
@@ -6728,13 +7221,13 @@
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="D196" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="D196" s="11" t="s">
+      <c r="E196" s="11" t="s">
         <v>580</v>
-      </c>
-      <c r="E196" s="11" t="s">
-        <v>581</v>
       </c>
       <c r="F196" s="7"/>
       <c r="G196" s="7"/>
@@ -6749,13 +7242,13 @@
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="D197" s="11" t="s">
         <v>582</v>
       </c>
-      <c r="D197" s="11" t="s">
+      <c r="E197" s="11" t="s">
         <v>583</v>
-      </c>
-      <c r="E197" s="11" t="s">
-        <v>584</v>
       </c>
       <c r="F197" s="7"/>
       <c r="G197" s="7"/>
@@ -6772,13 +7265,13 @@
         <v>127</v>
       </c>
       <c r="C198" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="D198" s="11" t="s">
         <v>585</v>
       </c>
-      <c r="D198" s="11" t="s">
+      <c r="E198" s="4" t="s">
         <v>586</v>
-      </c>
-      <c r="E198" s="4" t="s">
-        <v>587</v>
       </c>
       <c r="F198" s="7"/>
       <c r="G198" s="7"/>
@@ -6793,13 +7286,13 @@
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="D199" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="D199" s="11" t="s">
+      <c r="E199" s="4" t="s">
         <v>589</v>
-      </c>
-      <c r="E199" s="4" t="s">
-        <v>590</v>
       </c>
       <c r="F199" s="7"/>
       <c r="G199" s="7"/>
@@ -6812,19 +7305,19 @@
     </row>
     <row r="200" ht="14" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>118</v>
       </c>
       <c r="C200" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="D200" s="11" t="s">
         <v>592</v>
       </c>
-      <c r="D200" s="11" t="s">
+      <c r="E200" s="4" t="s">
         <v>593</v>
-      </c>
-      <c r="E200" s="4" t="s">
-        <v>594</v>
       </c>
       <c r="F200" s="7"/>
       <c r="G200" s="7"/>
@@ -6837,19 +7330,19 @@
     </row>
     <row r="201" ht="13" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B201" s="7" t="s">
         <v>118</v>
       </c>
       <c r="C201" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="D201" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="D201" s="4" t="s">
+      <c r="E201" s="4" t="s">
         <v>596</v>
-      </c>
-      <c r="E201" s="4" t="s">
-        <v>597</v>
       </c>
       <c r="F201" s="7"/>
       <c r="G201" s="7"/>
@@ -6862,19 +7355,19 @@
     </row>
     <row r="202" ht="14" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B202" s="7" t="s">
         <v>230</v>
       </c>
       <c r="C202" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="D202" s="11" t="s">
         <v>599</v>
       </c>
-      <c r="D202" s="11" t="s">
+      <c r="E202" s="11" t="s">
         <v>600</v>
-      </c>
-      <c r="E202" s="11" t="s">
-        <v>601</v>
       </c>
       <c r="F202" s="7"/>
       <c r="G202" s="7"/>
@@ -6891,7 +7384,7 @@
         <v>230</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D203" s="11" t="s">
         <v>33</v>
@@ -6912,13 +7405,13 @@
       <c r="A204" s="7"/>
       <c r="B204" s="7"/>
       <c r="C204" s="7" t="s">
+        <v>602</v>
+      </c>
+      <c r="D204" s="11" t="s">
         <v>603</v>
       </c>
-      <c r="D204" s="11" t="s">
+      <c r="E204" t="s">
         <v>604</v>
-      </c>
-      <c r="E204" t="s">
-        <v>605</v>
       </c>
       <c r="F204" s="7"/>
       <c r="G204" s="7"/>
@@ -6933,13 +7426,13 @@
       <c r="A205" s="7"/>
       <c r="B205" s="7"/>
       <c r="C205" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="D205" t="s">
         <v>606</v>
       </c>
-      <c r="D205" t="s">
+      <c r="E205" t="s">
         <v>607</v>
-      </c>
-      <c r="E205" t="s">
-        <v>608</v>
       </c>
       <c r="F205" s="7"/>
       <c r="G205" s="7"/>
@@ -6954,13 +7447,13 @@
       <c r="A206" s="7"/>
       <c r="B206" s="7"/>
       <c r="C206" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="D206" t="s">
         <v>609</v>
       </c>
-      <c r="D206" t="s">
+      <c r="E206" t="s">
         <v>610</v>
-      </c>
-      <c r="E206" t="s">
-        <v>611</v>
       </c>
       <c r="F206" s="7"/>
       <c r="G206" s="7"/>
@@ -6973,186 +7466,186 @@
     </row>
     <row r="207" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C207" t="s">
+        <v>611</v>
+      </c>
+      <c r="D207" t="s">
         <v>612</v>
       </c>
-      <c r="D207" t="s">
+      <c r="E207" t="s">
         <v>613</v>
-      </c>
-      <c r="E207" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="208" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C208" t="s">
+        <v>614</v>
+      </c>
+      <c r="D208" t="s">
         <v>615</v>
       </c>
-      <c r="D208" t="s">
+      <c r="E208" t="s">
         <v>616</v>
-      </c>
-      <c r="E208" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="209" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C209" t="s">
+        <v>617</v>
+      </c>
+      <c r="D209" t="s">
         <v>618</v>
       </c>
-      <c r="D209" t="s">
+      <c r="E209" t="s">
         <v>619</v>
-      </c>
-      <c r="E209" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="210" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C210" t="s">
+        <v>620</v>
+      </c>
+      <c r="D210" t="s">
         <v>621</v>
       </c>
-      <c r="D210" t="s">
+      <c r="E210" t="s">
         <v>622</v>
-      </c>
-      <c r="E210" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="211" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C211" t="s">
+        <v>623</v>
+      </c>
+      <c r="D211" t="s">
         <v>624</v>
       </c>
-      <c r="D211" t="s">
+      <c r="E211" t="s">
         <v>625</v>
-      </c>
-      <c r="E211" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="212" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C212" t="s">
+        <v>626</v>
+      </c>
+      <c r="D212" t="s">
         <v>627</v>
       </c>
-      <c r="D212" t="s">
+      <c r="E212" t="s">
         <v>628</v>
-      </c>
-      <c r="E212" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="213" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C213" t="s">
+        <v>629</v>
+      </c>
+      <c r="D213" t="s">
         <v>630</v>
       </c>
-      <c r="D213" t="s">
+      <c r="E213" t="s">
         <v>631</v>
-      </c>
-      <c r="E213" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="214" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C214" t="s">
+        <v>632</v>
+      </c>
+      <c r="D214" t="s">
         <v>633</v>
       </c>
-      <c r="D214" t="s">
+      <c r="E214" t="s">
         <v>634</v>
-      </c>
-      <c r="E214" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="215" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C215" t="s">
+        <v>635</v>
+      </c>
+      <c r="D215" t="s">
         <v>636</v>
       </c>
-      <c r="D215" t="s">
+      <c r="E215" t="s">
         <v>637</v>
-      </c>
-      <c r="E215" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="216" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C216" t="s">
+        <v>638</v>
+      </c>
+      <c r="D216" t="s">
         <v>639</v>
       </c>
-      <c r="D216" t="s">
+      <c r="E216" t="s">
         <v>640</v>
-      </c>
-      <c r="E216" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="217" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C217" t="s">
+        <v>641</v>
+      </c>
+      <c r="D217" t="s">
         <v>642</v>
       </c>
-      <c r="D217" t="s">
+      <c r="E217" t="s">
         <v>643</v>
-      </c>
-      <c r="E217" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="218" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C218" t="s">
+        <v>644</v>
+      </c>
+      <c r="D218" t="s">
         <v>645</v>
       </c>
-      <c r="D218" t="s">
+      <c r="E218" t="s">
         <v>646</v>
-      </c>
-      <c r="E218" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="219" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C219" t="s">
+        <v>647</v>
+      </c>
+      <c r="D219" t="s">
         <v>648</v>
       </c>
-      <c r="D219" t="s">
+      <c r="E219" t="s">
         <v>649</v>
-      </c>
-      <c r="E219" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="220" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C220" t="s">
+        <v>650</v>
+      </c>
+      <c r="D220" t="s">
         <v>651</v>
       </c>
-      <c r="D220" t="s">
+      <c r="E220" t="s">
         <v>652</v>
-      </c>
-      <c r="E220" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="221" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C221" t="s">
+        <v>653</v>
+      </c>
+      <c r="D221" t="s">
         <v>654</v>
       </c>
-      <c r="D221" t="s">
+      <c r="E221" t="s">
         <v>655</v>
-      </c>
-      <c r="E221" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="222" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C222" t="s">
+        <v>656</v>
+      </c>
+      <c r="D222" t="s">
         <v>657</v>
       </c>
-      <c r="D222" t="s">
+      <c r="E222" t="s">
         <v>658</v>
-      </c>
-      <c r="E222" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="223" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C223" t="s">
+        <v>659</v>
+      </c>
+      <c r="D223" t="s">
         <v>660</v>
-      </c>
-      <c r="D223" t="s">
-        <v>661</v>
       </c>
       <c r="E223" t="s">
         <v>406</v>
@@ -7160,40 +7653,40 @@
     </row>
     <row r="224" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C224" t="s">
+        <v>661</v>
+      </c>
+      <c r="D224" t="s">
         <v>662</v>
       </c>
-      <c r="D224" t="s">
+      <c r="E224" t="s">
         <v>663</v>
-      </c>
-      <c r="E224" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="225" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C225" t="s">
+        <v>664</v>
+      </c>
+      <c r="D225" t="s">
         <v>665</v>
       </c>
-      <c r="D225" t="s">
+      <c r="E225" t="s">
         <v>666</v>
-      </c>
-      <c r="E225" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="226" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C226" t="s">
+        <v>667</v>
+      </c>
+      <c r="D226" t="s">
         <v>668</v>
       </c>
-      <c r="D226" t="s">
+      <c r="E226" t="s">
         <v>669</v>
-      </c>
-      <c r="E226" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="227" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C227" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D227" t="s">
         <v>24</v>
@@ -7204,90 +7697,728 @@
     </row>
     <row r="228" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C228" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D228" t="s">
+        <v>665</v>
+      </c>
+      <c r="E228" t="s">
         <v>666</v>
-      </c>
-      <c r="E228" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="229" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C229" t="s">
+        <v>672</v>
+      </c>
+      <c r="D229" t="s">
         <v>673</v>
       </c>
-      <c r="D229" t="s">
+      <c r="E229" t="s">
         <v>674</v>
-      </c>
-      <c r="E229" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="230" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C230" t="s">
+        <v>675</v>
+      </c>
+      <c r="D230" t="s">
         <v>676</v>
       </c>
-      <c r="D230" t="s">
+      <c r="E230" t="s">
         <v>677</v>
-      </c>
-      <c r="E230" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="231" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C231" t="s">
+        <v>678</v>
+      </c>
+      <c r="D231" t="s">
         <v>679</v>
       </c>
-      <c r="D231" t="s">
+      <c r="E231" t="s">
         <v>680</v>
-      </c>
-      <c r="E231" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="232" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C232" t="s">
+        <v>681</v>
+      </c>
+      <c r="D232" t="s">
         <v>682</v>
       </c>
-      <c r="D232" t="s">
+      <c r="E232" t="s">
         <v>683</v>
-      </c>
-      <c r="E232" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="233" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C233" t="s">
+        <v>684</v>
+      </c>
+      <c r="D233" t="s">
         <v>685</v>
       </c>
-      <c r="D233" t="s">
+      <c r="E233" t="s">
         <v>686</v>
-      </c>
-      <c r="E233" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="234" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C234" t="s">
+        <v>687</v>
+      </c>
+      <c r="D234" t="s">
         <v>688</v>
       </c>
-      <c r="D234" t="s">
+      <c r="E234" t="s">
         <v>689</v>
-      </c>
-      <c r="E234" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="235" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C235" t="s">
+        <v>690</v>
+      </c>
+      <c r="D235" t="s">
         <v>691</v>
       </c>
-      <c r="D235" t="s">
+      <c r="E235" t="s">
         <v>692</v>
       </c>
-      <c r="E235" t="s">
+    </row>
+    <row r="236" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C236" t="s">
         <v>693</v>
+      </c>
+      <c r="D236" t="s">
+        <v>694</v>
+      </c>
+      <c r="E236" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="237" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C237" t="s">
+        <v>696</v>
+      </c>
+      <c r="D237" t="s">
+        <v>697</v>
+      </c>
+      <c r="E237" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="238" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C238" t="s">
+        <v>699</v>
+      </c>
+      <c r="D238" t="s">
+        <v>700</v>
+      </c>
+      <c r="E238" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="239" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C239" t="s">
+        <v>702</v>
+      </c>
+      <c r="D239" t="s">
+        <v>703</v>
+      </c>
+      <c r="E239" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="240" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C240" t="s">
+        <v>705</v>
+      </c>
+      <c r="D240" t="s">
+        <v>706</v>
+      </c>
+      <c r="E240" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="241" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C241" t="s">
+        <v>708</v>
+      </c>
+      <c r="D241" t="s">
+        <v>709</v>
+      </c>
+      <c r="E241" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="242" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C242" t="s">
+        <v>710</v>
+      </c>
+      <c r="D242" t="s">
+        <v>711</v>
+      </c>
+      <c r="E242" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="243" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C243" t="s">
+        <v>713</v>
+      </c>
+      <c r="D243" t="s">
+        <v>714</v>
+      </c>
+      <c r="E243" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="244" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C244" t="s">
+        <v>716</v>
+      </c>
+      <c r="D244" t="s">
+        <v>717</v>
+      </c>
+      <c r="E244" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="245" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C245" t="s">
+        <v>719</v>
+      </c>
+      <c r="D245" t="s">
+        <v>720</v>
+      </c>
+      <c r="E245" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="246" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C246" t="s">
+        <v>722</v>
+      </c>
+      <c r="D246" t="s">
+        <v>723</v>
+      </c>
+      <c r="E246" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="247" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C247" t="s">
+        <v>725</v>
+      </c>
+      <c r="D247" t="s">
+        <v>726</v>
+      </c>
+      <c r="E247" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="248" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C248" t="s">
+        <v>728</v>
+      </c>
+      <c r="D248" t="s">
+        <v>729</v>
+      </c>
+      <c r="E248" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="249" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C249" t="s">
+        <v>731</v>
+      </c>
+      <c r="D249" t="s">
+        <v>732</v>
+      </c>
+      <c r="E249" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="250" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C250" t="s">
+        <v>734</v>
+      </c>
+      <c r="D250" t="s">
+        <v>735</v>
+      </c>
+      <c r="E250" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="251" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C251" t="s">
+        <v>737</v>
+      </c>
+      <c r="D251" t="s">
+        <v>738</v>
+      </c>
+      <c r="E251" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="252" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C252" t="s">
+        <v>740</v>
+      </c>
+      <c r="D252" t="s">
+        <v>741</v>
+      </c>
+      <c r="E252" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="253" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C253" t="s">
+        <v>743</v>
+      </c>
+      <c r="D253" t="s">
+        <v>744</v>
+      </c>
+      <c r="E253" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="254" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C254" t="s">
+        <v>746</v>
+      </c>
+      <c r="D254" t="s">
+        <v>747</v>
+      </c>
+      <c r="E254" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="255" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C255" t="s">
+        <v>749</v>
+      </c>
+      <c r="D255" t="s">
+        <v>750</v>
+      </c>
+      <c r="E255" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="256" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C256" t="s">
+        <v>751</v>
+      </c>
+      <c r="D256" t="s">
+        <v>752</v>
+      </c>
+      <c r="E256" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="257" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C257" t="s">
+        <v>753</v>
+      </c>
+      <c r="D257" t="s">
+        <v>754</v>
+      </c>
+      <c r="E257" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="258" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C258" t="s">
+        <v>756</v>
+      </c>
+      <c r="D258" t="s">
+        <v>757</v>
+      </c>
+      <c r="E258" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="259" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C259" t="s">
+        <v>759</v>
+      </c>
+      <c r="D259" t="s">
+        <v>760</v>
+      </c>
+      <c r="E259" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="260" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C260" t="s">
+        <v>762</v>
+      </c>
+      <c r="D260" t="s">
+        <v>763</v>
+      </c>
+      <c r="E260" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="261" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C261" t="s">
+        <v>765</v>
+      </c>
+      <c r="D261" t="s">
+        <v>766</v>
+      </c>
+      <c r="E261" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="262" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C262" t="s">
+        <v>768</v>
+      </c>
+      <c r="D262" t="s">
+        <v>769</v>
+      </c>
+      <c r="E262" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="263" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C263" t="s">
+        <v>771</v>
+      </c>
+      <c r="D263" t="s">
+        <v>772</v>
+      </c>
+      <c r="E263" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="264" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C264" t="s">
+        <v>774</v>
+      </c>
+      <c r="D264" t="s">
+        <v>775</v>
+      </c>
+      <c r="E264" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="265" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C265" t="s">
+        <v>777</v>
+      </c>
+      <c r="D265" t="s">
+        <v>778</v>
+      </c>
+      <c r="E265" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="266" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C266" t="s">
+        <v>780</v>
+      </c>
+      <c r="D266" t="s">
+        <v>781</v>
+      </c>
+      <c r="E266" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="267" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C267" t="s">
+        <v>783</v>
+      </c>
+      <c r="D267" t="s">
+        <v>784</v>
+      </c>
+      <c r="E267" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="268" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C268" t="s">
+        <v>786</v>
+      </c>
+      <c r="D268" t="s">
+        <v>787</v>
+      </c>
+      <c r="E268" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="269" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C269" t="s">
+        <v>788</v>
+      </c>
+      <c r="D269" t="s">
+        <v>789</v>
+      </c>
+      <c r="E269" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="270" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C270" t="s">
+        <v>791</v>
+      </c>
+      <c r="D270" t="s">
+        <v>514</v>
+      </c>
+      <c r="E270" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="271" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C271" t="s">
+        <v>793</v>
+      </c>
+      <c r="D271" t="s">
+        <v>794</v>
+      </c>
+      <c r="E271" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="272" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C272" t="s">
+        <v>796</v>
+      </c>
+      <c r="D272" t="s">
+        <v>797</v>
+      </c>
+      <c r="E272" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="273" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C273" t="s">
+        <v>799</v>
+      </c>
+      <c r="D273" t="s">
+        <v>800</v>
+      </c>
+      <c r="E273" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="274" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C274" t="s">
+        <v>802</v>
+      </c>
+      <c r="D274" t="s">
+        <v>803</v>
+      </c>
+      <c r="E274" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="275" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C275" t="s">
+        <v>805</v>
+      </c>
+      <c r="D275" t="s">
+        <v>806</v>
+      </c>
+      <c r="E275" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="276" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C276" t="s">
+        <v>807</v>
+      </c>
+      <c r="D276" t="s">
+        <v>57</v>
+      </c>
+      <c r="E276" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="277" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C277" t="s">
+        <v>809</v>
+      </c>
+      <c r="D277" t="s">
+        <v>810</v>
+      </c>
+      <c r="E277" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="278" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C278" t="s">
+        <v>812</v>
+      </c>
+      <c r="D278" t="s">
+        <v>813</v>
+      </c>
+      <c r="E278" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="279" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C279" t="s">
+        <v>815</v>
+      </c>
+      <c r="D279" t="s">
+        <v>816</v>
+      </c>
+      <c r="E279" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="280" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C280" t="s">
+        <v>818</v>
+      </c>
+      <c r="D280" t="s">
+        <v>819</v>
+      </c>
+      <c r="E280" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="281" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C281" t="s">
+        <v>821</v>
+      </c>
+      <c r="D281" t="s">
+        <v>822</v>
+      </c>
+      <c r="E281" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="282" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C282" t="s">
+        <v>824</v>
+      </c>
+      <c r="D282" t="s">
+        <v>825</v>
+      </c>
+      <c r="E282" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="283" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C283" t="s">
+        <v>827</v>
+      </c>
+      <c r="D283" t="s">
+        <v>828</v>
+      </c>
+      <c r="E283" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="284" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C284" t="s">
+        <v>830</v>
+      </c>
+      <c r="D284" t="s">
+        <v>831</v>
+      </c>
+      <c r="E284" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="285" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C285" t="s">
+        <v>833</v>
+      </c>
+      <c r="D285" t="s">
+        <v>834</v>
+      </c>
+      <c r="E285" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="286" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C286" t="s">
+        <v>836</v>
+      </c>
+      <c r="D286" t="s">
+        <v>837</v>
+      </c>
+      <c r="E286" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="287" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C287" t="s">
+        <v>839</v>
+      </c>
+      <c r="D287" t="s">
+        <v>840</v>
+      </c>
+      <c r="E287" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="288" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C288" t="s">
+        <v>842</v>
+      </c>
+      <c r="D288" t="s">
+        <v>843</v>
+      </c>
+      <c r="E288" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="289" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C289" t="s">
+        <v>845</v>
+      </c>
+      <c r="D289" t="s">
+        <v>846</v>
+      </c>
+      <c r="E289" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="290" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C290" t="s">
+        <v>847</v>
+      </c>
+      <c r="D290" t="s">
+        <v>848</v>
+      </c>
+      <c r="E290" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="291" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C291" t="s">
+        <v>850</v>
+      </c>
+      <c r="D291" t="s">
+        <v>851</v>
+      </c>
+      <c r="E291" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="292" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C292" t="s">
+        <v>853</v>
+      </c>
+      <c r="D292" t="s">
+        <v>440</v>
+      </c>
+      <c r="E292" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="293" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C293" t="s">
+        <v>854</v>
+      </c>
+      <c r="D293" t="s">
+        <v>855</v>
+      </c>
+      <c r="E293" t="s">
+        <v>856</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/i18n.xlsx
+++ b/scripts/i18n.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="908">
   <si>
     <t xml:space="preserve">페이지는 [피그마] PFPlay GUI 설계서 합본의 페이지 이름입니다. </t>
   </si>
@@ -2616,6 +2616,159 @@
   </si>
   <si>
     <t>You're #{{position}} of {{total}}</t>
+  </si>
+  <si>
+    <t>pwa.menu_label</t>
+  </si>
+  <si>
+    <t>앱 설치하기</t>
+  </si>
+  <si>
+    <t>Install app</t>
+  </si>
+  <si>
+    <t>pwa.title</t>
+  </si>
+  <si>
+    <t>PFPlay 앱으로 설치하기</t>
+  </si>
+  <si>
+    <t>Install PFPlay</t>
+  </si>
+  <si>
+    <t>pwa.description</t>
+  </si>
+  <si>
+    <t>홈 화면에 추가하면 앱처럼 바로 열고, 알림도 받을 수 있어요.</t>
+  </si>
+  <si>
+    <t>Add it to your home screen to open it like an app and get notifications.</t>
+  </si>
+  <si>
+    <t>pwa.install_now</t>
+  </si>
+  <si>
+    <t>설치하기</t>
+  </si>
+  <si>
+    <t>Install</t>
+  </si>
+  <si>
+    <t>pwa.ios_guide_title</t>
+  </si>
+  <si>
+    <t>Safari에서 홈 화면에 추가해 주세요</t>
+  </si>
+  <si>
+    <t>Add to home screen in Safari</t>
+  </si>
+  <si>
+    <t>pwa.ios_step_1</t>
+  </si>
+  <si>
+    <t>주소창 아래 &lt;b&gt;공유&lt;/b&gt; 버튼을 누르세요.</t>
+  </si>
+  <si>
+    <t>Tap the &lt;b&gt;Share&lt;/b&gt; button below the address bar.</t>
+  </si>
+  <si>
+    <t>pwa.ios_step_2</t>
+  </si>
+  <si>
+    <t>목록에서 &lt;b&gt;홈 화면에 추가&lt;/b&gt;를 고르세요.</t>
+  </si>
+  <si>
+    <t>Choose &lt;b&gt;Add to Home Screen&lt;/b&gt; from the list.</t>
+  </si>
+  <si>
+    <t>pwa.ios_step_3</t>
+  </si>
+  <si>
+    <t>오른쪽 위 &lt;b&gt;추가&lt;/b&gt;를 누르면 끝이에요.</t>
+  </si>
+  <si>
+    <t>Tap &lt;b&gt;Add&lt;/b&gt; in the top right. That's it.</t>
+  </si>
+  <si>
+    <t>pwa.in_app_title</t>
+  </si>
+  <si>
+    <t>여기서는 설치할 수 없어요</t>
+  </si>
+  <si>
+    <t>You can't install from here</t>
+  </si>
+  <si>
+    <t>pwa.in_app_description</t>
+  </si>
+  <si>
+    <t>지금 앱 안에 있는 브라우저라 홈 화면에 추가할 수 없어요. 주소를 복사해 Safari나 Chrome에서 열어 주세요.</t>
+  </si>
+  <si>
+    <t>You're in an in-app browser, which can't add to the home screen. Copy the link and open it in Safari or Chrome.</t>
+  </si>
+  <si>
+    <t>pwa.copy_link</t>
+  </si>
+  <si>
+    <t>주소 복사하기</t>
+  </si>
+  <si>
+    <t>Copy link</t>
+  </si>
+  <si>
+    <t>pwa.copied</t>
+  </si>
+  <si>
+    <t>복사했어요</t>
+  </si>
+  <si>
+    <t>Copied</t>
+  </si>
+  <si>
+    <t>pwa.manual_title</t>
+  </si>
+  <si>
+    <t>홈 화면에 앱을 추가해 주세요</t>
+  </si>
+  <si>
+    <t>Add the app to your home screen</t>
+  </si>
+  <si>
+    <t>pwa.manual_chrome</t>
+  </si>
+  <si>
+    <t>오른쪽 위 &lt;b&gt;⋮&lt;/b&gt; → &lt;b&gt;앱 설치&lt;/b&gt;(또는 홈 화면에 추가)를 누르세요.</t>
+  </si>
+  <si>
+    <t>Tap &lt;b&gt;⋮&lt;/b&gt; in the top right → &lt;b&gt;Install app&lt;/b&gt; (or Add to Home screen).</t>
+  </si>
+  <si>
+    <t>pwa.manual_samsung</t>
+  </si>
+  <si>
+    <t>아래쪽 &lt;b&gt;≡&lt;/b&gt; → &lt;b&gt;현재 페이지 추가&lt;/b&gt; → &lt;b&gt;홈 화면&lt;/b&gt;을 누르세요.</t>
+  </si>
+  <si>
+    <t>Tap &lt;b&gt;≡&lt;/b&gt; at the bottom → &lt;b&gt;Add page to&lt;/b&gt; → &lt;b&gt;Home screen&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>pwa.manual_firefox</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;⋮&lt;/b&gt; → &lt;b&gt;홈 화면에 추가&lt;/b&gt;를 누르세요.</t>
+  </si>
+  <si>
+    <t>Tap &lt;b&gt;⋮&lt;/b&gt; → &lt;b&gt;Add to Home screen&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>pwa.manual_other</t>
+  </si>
+  <si>
+    <t>브라우저 메뉴에서 &lt;b&gt;홈 화면에 추가&lt;/b&gt;(또는 앱 설치)를 선택하세요.</t>
+  </si>
+  <si>
+    <t>Open your browser menu and choose &lt;b&gt;Add to Home screen&lt;/b&gt; (or Install app).</t>
   </si>
 </sst>
 </file>
@@ -2983,7 +3136,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M293"/>
+  <dimension ref="A1:M310"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="12.6640625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.1640625" customWidth="1"/>
@@ -8419,6 +8572,193 @@
       </c>
       <c r="E293" t="s">
         <v>856</v>
+      </c>
+    </row>
+    <row r="294" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C294" t="s">
+        <v>857</v>
+      </c>
+      <c r="D294" t="s">
+        <v>858</v>
+      </c>
+      <c r="E294" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="295" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C295" t="s">
+        <v>860</v>
+      </c>
+      <c r="D295" t="s">
+        <v>861</v>
+      </c>
+      <c r="E295" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="296" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C296" t="s">
+        <v>863</v>
+      </c>
+      <c r="D296" t="s">
+        <v>864</v>
+      </c>
+      <c r="E296" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="297" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C297" t="s">
+        <v>866</v>
+      </c>
+      <c r="D297" t="s">
+        <v>867</v>
+      </c>
+      <c r="E297" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="298" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C298" t="s">
+        <v>869</v>
+      </c>
+      <c r="D298" t="s">
+        <v>870</v>
+      </c>
+      <c r="E298" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="299" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C299" t="s">
+        <v>872</v>
+      </c>
+      <c r="D299" t="s">
+        <v>873</v>
+      </c>
+      <c r="E299" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="300" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C300" t="s">
+        <v>875</v>
+      </c>
+      <c r="D300" t="s">
+        <v>876</v>
+      </c>
+      <c r="E300" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="301" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C301" t="s">
+        <v>878</v>
+      </c>
+      <c r="D301" t="s">
+        <v>879</v>
+      </c>
+      <c r="E301" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="302" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C302" t="s">
+        <v>881</v>
+      </c>
+      <c r="D302" t="s">
+        <v>882</v>
+      </c>
+      <c r="E302" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="303" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C303" t="s">
+        <v>884</v>
+      </c>
+      <c r="D303" t="s">
+        <v>885</v>
+      </c>
+      <c r="E303" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="304" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C304" t="s">
+        <v>887</v>
+      </c>
+      <c r="D304" t="s">
+        <v>888</v>
+      </c>
+      <c r="E304" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="305" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C305" t="s">
+        <v>890</v>
+      </c>
+      <c r="D305" t="s">
+        <v>891</v>
+      </c>
+      <c r="E305" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="306" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C306" t="s">
+        <v>893</v>
+      </c>
+      <c r="D306" t="s">
+        <v>894</v>
+      </c>
+      <c r="E306" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="307" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C307" t="s">
+        <v>896</v>
+      </c>
+      <c r="D307" t="s">
+        <v>897</v>
+      </c>
+      <c r="E307" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="308" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C308" t="s">
+        <v>899</v>
+      </c>
+      <c r="D308" t="s">
+        <v>900</v>
+      </c>
+      <c r="E308" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="309" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C309" t="s">
+        <v>902</v>
+      </c>
+      <c r="D309" t="s">
+        <v>903</v>
+      </c>
+      <c r="E309" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="310" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C310" t="s">
+        <v>905</v>
+      </c>
+      <c r="D310" t="s">
+        <v>906</v>
+      </c>
+      <c r="E310" t="s">
+        <v>907</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/i18n.xlsx
+++ b/scripts/i18n.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="908">
   <si>
     <t xml:space="preserve">페이지는 [피그마] PFPlay GUI 설계서 합본의 페이지 이름입니다. </t>
   </si>
@@ -817,10 +817,10 @@
     <t>onboard.para.domain_format</t>
   </si>
   <si>
-    <t>웹 페이지 주소는 pfplay.xyz/도메인으로 시작</t>
-  </si>
-  <si>
-    <t>Web address starts with pfplay.xyz/domain</t>
+    <t>예: pfplay.xyz/link/my-room</t>
+  </si>
+  <si>
+    <t>e.g. pfplay.xyz/link/my-room</t>
   </si>
   <si>
     <t>onboard.para.guest_limit</t>
@@ -1277,9 +1277,6 @@
     <t>dj.title.current_dj</t>
   </si>
   <si>
-    <t>현재 디제잉</t>
-  </si>
-  <si>
     <t>Now DJing</t>
   </si>
   <si>
@@ -1394,12 +1391,12 @@
     <t>dj.para.no_dj_crew</t>
   </si>
   <si>
-    <t xml:space="preserve">현재 디제잉 인원이 없어요
-파티의 흥을 책임질 DJ가 되어보세요!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No one is DJing now.
-Why not become the DJ and make some noise!</t>
+    <t xml:space="preserve">현재 디제잉하는 사람이 없어요.
+첫 곡을 틀어보세요!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No one is DJing right now.
+Play the first song!</t>
   </si>
   <si>
     <t>dj.para.create_playlist_song</t>
@@ -2123,6 +2120,655 @@
   </si>
   <si>
     <t>Up to 2000 characters allowed</t>
+  </si>
+  <si>
+    <t>common.menu.title</t>
+  </si>
+  <si>
+    <t>메뉴</t>
+  </si>
+  <si>
+    <t>Menu</t>
+  </si>
+  <si>
+    <t>common.menu.notification_settings</t>
+  </si>
+  <si>
+    <t>알림 설정</t>
+  </si>
+  <si>
+    <t>Notification settings</t>
+  </si>
+  <si>
+    <t>common.ec.char_limit_12_short</t>
+  </si>
+  <si>
+    <t>최대 12자, 공백·특수문자 불가</t>
+  </si>
+  <si>
+    <t>Max 12 chars, no spaces</t>
+  </si>
+  <si>
+    <t>common.ec.char_limit_50_short</t>
+  </si>
+  <si>
+    <t>최대 50자</t>
+  </si>
+  <si>
+    <t>Max 50 characters</t>
+  </si>
+  <si>
+    <t>chat.para.playback_summary_skipped</t>
+  </si>
+  <si>
+    <t>스킵</t>
+  </si>
+  <si>
+    <t>skipped</t>
+  </si>
+  <si>
+    <t>chat.para.playback_summary_dj_fallback</t>
+  </si>
+  <si>
+    <t>DJ</t>
+  </si>
+  <si>
+    <t>chat.btn.choose_emoji</t>
+  </si>
+  <si>
+    <t>이모지 선택</t>
+  </si>
+  <si>
+    <t>Choose emoji</t>
+  </si>
+  <si>
+    <t>chat.title.recently_used</t>
+  </si>
+  <si>
+    <t>최근 사용</t>
+  </si>
+  <si>
+    <t>Recently used</t>
+  </si>
+  <si>
+    <t>settings.notifications.title</t>
+  </si>
+  <si>
+    <t>알림</t>
+  </si>
+  <si>
+    <t>Notifications</t>
+  </si>
+  <si>
+    <t>settings.notifications.toggle_label</t>
+  </si>
+  <si>
+    <t>공지 푸시 알림 받기</t>
+  </si>
+  <si>
+    <t>Receive announcement push notifications</t>
+  </si>
+  <si>
+    <t>settings.notifications.description</t>
+  </si>
+  <si>
+    <t>운영 공지와 이벤트 소식을 푸시 알림으로 받아볼 수 있어요.</t>
+  </si>
+  <si>
+    <t>Get operational announcements and event news as push notifications.</t>
+  </si>
+  <si>
+    <t>settings.notifications.needs_install_hint</t>
+  </si>
+  <si>
+    <t>홈 화면에 앱을 추가한 뒤 알림을 켤 수 있어요.</t>
+  </si>
+  <si>
+    <t>Add the app to your home screen first, then you can turn on notifications.</t>
+  </si>
+  <si>
+    <t>settings.notifications.denied_hint</t>
+  </si>
+  <si>
+    <t>브라우저 설정에서 알림 차단을 해제해 주세요.</t>
+  </si>
+  <si>
+    <t>Please unblock notifications in your browser settings.</t>
+  </si>
+  <si>
+    <t>dj.btn.search_and_register_dj</t>
+  </si>
+  <si>
+    <t>곡 검색하고 DJ 등록</t>
+  </si>
+  <si>
+    <t>Search a song and be a DJ</t>
+  </si>
+  <si>
+    <t>dj.btn.pick_from_my_playlist</t>
+  </si>
+  <si>
+    <t>내 플레이리스트에서 고르기</t>
+  </si>
+  <si>
+    <t>Choose from my playlist</t>
+  </si>
+  <si>
+    <t>dj.btn.register_with_this_song</t>
+  </si>
+  <si>
+    <t>이 곡으로 DJ 등록</t>
+  </si>
+  <si>
+    <t>Be a DJ</t>
+  </si>
+  <si>
+    <t>dj.para.search_song_to_dj</t>
+  </si>
+  <si>
+    <t>디제잉할 곡을 검색하세요.</t>
+  </si>
+  <si>
+    <t>Search for a song to DJ</t>
+  </si>
+  <si>
+    <t>dj.para.select_song_to_dj</t>
+  </si>
+  <si>
+    <t>디제잉할 곡을 선택해 주세요</t>
+  </si>
+  <si>
+    <t>Choose a song to DJ</t>
+  </si>
+  <si>
+    <t>dj.para.start_djing_with_this_song</t>
+  </si>
+  <si>
+    <t>이 곡으로 디제잉을 시작해요</t>
+  </si>
+  <si>
+    <t>Let's start DJing with this song</t>
+  </si>
+  <si>
+    <t>playlist.para.now_playing</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>playlist.para.next_up</t>
+  </si>
+  <si>
+    <t>NEXT</t>
+  </si>
+  <si>
+    <t>playlist.ec.exceeded_list_am</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이런! 준회원은 플레이리스트를 1개까지만 만들 수 있어요
+지갑을 연동하면 최대 10개까지 생성할 수 있어요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oh no! Associate members can create only 1 playlist.
+Connect your wallet to create up to 10.</t>
+  </si>
+  <si>
+    <t>partyroom.ec.concurrent_entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다른 기기나 탭에서 입장을 처리하고 있어요.
+잠시 후 다시 시도해 주세요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Another device or tab is entering a party room.
+Please try again in a moment.</t>
+  </si>
+  <si>
+    <t>partyroom.queue.guest_cta_title</t>
+  </si>
+  <si>
+    <t>🎧 음악을 직접 틀어보세요</t>
+  </si>
+  <si>
+    <t>🎧 Play music yourself</t>
+  </si>
+  <si>
+    <t>partyroom.queue.guest_cta_subtitle</t>
+  </si>
+  <si>
+    <t>3초만에 가입 →</t>
+  </si>
+  <si>
+    <t>Sign up in 3 seconds →</t>
+  </si>
+  <si>
+    <t>partyroom.queue.member_action_register</t>
+  </si>
+  <si>
+    <t>+ DJ 등록</t>
+  </si>
+  <si>
+    <t>+ Register as DJ</t>
+  </si>
+  <si>
+    <t>partyroom.queue.member_action_unregister</t>
+  </si>
+  <si>
+    <t>큐에서 나가기</t>
+  </si>
+  <si>
+    <t>Leave queue</t>
+  </si>
+  <si>
+    <t>partyroom.queue.member_action_change_playlist</t>
+  </si>
+  <si>
+    <t>변경</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>partyroom.queue.member_action_manage_playlists</t>
+  </si>
+  <si>
+    <t>내 플레이리스트 관리</t>
+  </si>
+  <si>
+    <t>Manage my playlists</t>
+  </si>
+  <si>
+    <t>partyroom.queue.current_dj_title</t>
+  </si>
+  <si>
+    <t>현재 DJ</t>
+  </si>
+  <si>
+    <t>Current DJ</t>
+  </si>
+  <si>
+    <t>partyroom.queue.empty</t>
+  </si>
+  <si>
+    <t>큐 비어있음</t>
+  </si>
+  <si>
+    <t>Queue empty</t>
+  </si>
+  <si>
+    <t>partyroom.queue.unregister_confirm</t>
+  </si>
+  <si>
+    <t>정말 큐에서 나가시겠어요?</t>
+  </si>
+  <si>
+    <t>Leave the queue?</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_select_playlist_title</t>
+  </si>
+  <si>
+    <t>플레이리스트 선택</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_add_tracks_title</t>
+  </si>
+  <si>
+    <t>곡 추가</t>
+  </si>
+  <si>
+    <t>Add tracks</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_playlists_management_title</t>
+  </si>
+  <si>
+    <t>My playlists</t>
+  </si>
+  <si>
+    <t>partyroom.queue.playlists_empty</t>
+  </si>
+  <si>
+    <t>아직 플레이리스트가 없어요</t>
+  </si>
+  <si>
+    <t>No playlists yet</t>
+  </si>
+  <si>
+    <t>partyroom.queue.playlist_tracks_empty</t>
+  </si>
+  <si>
+    <t>아직 곡이 없어요</t>
+  </si>
+  <si>
+    <t>No songs yet</t>
+  </si>
+  <si>
+    <t>partyroom.queue.create_playlist_cta</t>
+  </si>
+  <si>
+    <t>+ 새 플레이리스트</t>
+  </si>
+  <si>
+    <t>+ New playlist</t>
+  </si>
+  <si>
+    <t>partyroom.queue.create_playlist_placeholder</t>
+  </si>
+  <si>
+    <t>플레이리스트 이름</t>
+  </si>
+  <si>
+    <t>Playlist name</t>
+  </si>
+  <si>
+    <t>partyroom.queue.create_playlist_submit</t>
+  </si>
+  <si>
+    <t>추가</t>
+  </si>
+  <si>
+    <t>partyroom.queue.remove_track_label</t>
+  </si>
+  <si>
+    <t>Remove</t>
+  </si>
+  <si>
+    <t>partyroom.queue.add_tracks_cta</t>
+  </si>
+  <si>
+    <t>+ 곡 추가</t>
+  </si>
+  <si>
+    <t>+ Add songs</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_search_placeholder</t>
+  </si>
+  <si>
+    <t>곡명 또는 아티스트로 검색</t>
+  </si>
+  <si>
+    <t>Search by song or artist</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_empty_search</t>
+  </si>
+  <si>
+    <t>다른 키워드로 시도해보세요</t>
+  </si>
+  <si>
+    <t>Try another keyword</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_search_failed</t>
+  </si>
+  <si>
+    <t>검색에 실패했어요</t>
+  </si>
+  <si>
+    <t>Search failed</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_preview_unavailable</t>
+  </si>
+  <si>
+    <t>재생할 수 없어요</t>
+  </si>
+  <si>
+    <t>Cannot play</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_add_button</t>
+  </si>
+  <si>
+    <t>+ 추가</t>
+  </si>
+  <si>
+    <t>+ Add</t>
+  </si>
+  <si>
+    <t>partyroom.queue.add_success</t>
+  </si>
+  <si>
+    <t>플레이리스트에 추가했어요</t>
+  </si>
+  <si>
+    <t>Added to playlist</t>
+  </si>
+  <si>
+    <t>partyroom.queue.add_already_exists</t>
+  </si>
+  <si>
+    <t>이미 플레이리스트에 있어요</t>
+  </si>
+  <si>
+    <t>Already in playlist</t>
+  </si>
+  <si>
+    <t>partyroom.queue.add_limit_exceeded</t>
+  </si>
+  <si>
+    <t>플레이리스트가 가득 찼어요</t>
+  </si>
+  <si>
+    <t>Playlist is full</t>
+  </si>
+  <si>
+    <t>partyroom.queue.guest_action_blocked</t>
+  </si>
+  <si>
+    <t>로그인이 필요해요</t>
+  </si>
+  <si>
+    <t>Sign-in required</t>
+  </si>
+  <si>
+    <t>partyroom.queue.guide_start</t>
+  </si>
+  <si>
+    <t>시작</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>partyroom.queue.guide_title</t>
+  </si>
+  <si>
+    <t>DJ 규칙</t>
+  </si>
+  <si>
+    <t>DJ rules</t>
+  </si>
+  <si>
+    <t>partyroom.queue.song_count</t>
+  </si>
+  <si>
+    <t>{{count}}곡</t>
+  </si>
+  <si>
+    <t>partyroom.queue.sheet_select_confirm</t>
+  </si>
+  <si>
+    <t>선택 완료</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>partyroom.queue.no_track</t>
+  </si>
+  <si>
+    <t>지금 재생 중인 곡이 없어요</t>
+  </si>
+  <si>
+    <t>No song playing right now</t>
+  </si>
+  <si>
+    <t>partyroom.queue.tab_chat</t>
+  </si>
+  <si>
+    <t>partyroom.queue.my_position</t>
+  </si>
+  <si>
+    <t>내 순서 {{position}}번째 · 총 {{total}}명</t>
+  </si>
+  <si>
+    <t>You're #{{position}} of {{total}}</t>
+  </si>
+  <si>
+    <t>pwa.menu_label</t>
+  </si>
+  <si>
+    <t>앱 설치하기</t>
+  </si>
+  <si>
+    <t>Install app</t>
+  </si>
+  <si>
+    <t>pwa.title</t>
+  </si>
+  <si>
+    <t>PFPlay 앱으로 설치하기</t>
+  </si>
+  <si>
+    <t>Install PFPlay</t>
+  </si>
+  <si>
+    <t>pwa.description</t>
+  </si>
+  <si>
+    <t>홈 화면에 추가하면 앱처럼 바로 열고, 알림도 받을 수 있어요.</t>
+  </si>
+  <si>
+    <t>Add it to your home screen to open it like an app and get notifications.</t>
+  </si>
+  <si>
+    <t>pwa.install_now</t>
+  </si>
+  <si>
+    <t>설치하기</t>
+  </si>
+  <si>
+    <t>Install</t>
+  </si>
+  <si>
+    <t>pwa.ios_guide_title</t>
+  </si>
+  <si>
+    <t>Safari에서 홈 화면에 추가해 주세요</t>
+  </si>
+  <si>
+    <t>Add to home screen in Safari</t>
+  </si>
+  <si>
+    <t>pwa.ios_step_1</t>
+  </si>
+  <si>
+    <t>주소창 아래 &lt;b&gt;공유&lt;/b&gt; 버튼을 누르세요.</t>
+  </si>
+  <si>
+    <t>Tap the &lt;b&gt;Share&lt;/b&gt; button below the address bar.</t>
+  </si>
+  <si>
+    <t>pwa.ios_step_2</t>
+  </si>
+  <si>
+    <t>목록에서 &lt;b&gt;홈 화면에 추가&lt;/b&gt;를 고르세요.</t>
+  </si>
+  <si>
+    <t>Choose &lt;b&gt;Add to Home Screen&lt;/b&gt; from the list.</t>
+  </si>
+  <si>
+    <t>pwa.ios_step_3</t>
+  </si>
+  <si>
+    <t>오른쪽 위 &lt;b&gt;추가&lt;/b&gt;를 누르면 끝이에요.</t>
+  </si>
+  <si>
+    <t>Tap &lt;b&gt;Add&lt;/b&gt; in the top right. That's it.</t>
+  </si>
+  <si>
+    <t>pwa.in_app_title</t>
+  </si>
+  <si>
+    <t>여기서는 설치할 수 없어요</t>
+  </si>
+  <si>
+    <t>You can't install from here</t>
+  </si>
+  <si>
+    <t>pwa.in_app_description</t>
+  </si>
+  <si>
+    <t>지금 앱 안에 있는 브라우저라 홈 화면에 추가할 수 없어요. 주소를 복사해 Safari나 Chrome에서 열어 주세요.</t>
+  </si>
+  <si>
+    <t>You're in an in-app browser, which can't add to the home screen. Copy the link and open it in Safari or Chrome.</t>
+  </si>
+  <si>
+    <t>pwa.copy_link</t>
+  </si>
+  <si>
+    <t>주소 복사하기</t>
+  </si>
+  <si>
+    <t>Copy link</t>
+  </si>
+  <si>
+    <t>pwa.copied</t>
+  </si>
+  <si>
+    <t>복사했어요</t>
+  </si>
+  <si>
+    <t>Copied</t>
+  </si>
+  <si>
+    <t>pwa.manual_title</t>
+  </si>
+  <si>
+    <t>홈 화면에 앱을 추가해 주세요</t>
+  </si>
+  <si>
+    <t>Add the app to your home screen</t>
+  </si>
+  <si>
+    <t>pwa.manual_chrome</t>
+  </si>
+  <si>
+    <t>오른쪽 위 &lt;b&gt;⋮&lt;/b&gt; → &lt;b&gt;앱 설치&lt;/b&gt;(또는 홈 화면에 추가)를 누르세요.</t>
+  </si>
+  <si>
+    <t>Tap &lt;b&gt;⋮&lt;/b&gt; in the top right → &lt;b&gt;Install app&lt;/b&gt; (or Add to Home screen).</t>
+  </si>
+  <si>
+    <t>pwa.manual_samsung</t>
+  </si>
+  <si>
+    <t>아래쪽 &lt;b&gt;≡&lt;/b&gt; → &lt;b&gt;현재 페이지 추가&lt;/b&gt; → &lt;b&gt;홈 화면&lt;/b&gt;을 누르세요.</t>
+  </si>
+  <si>
+    <t>Tap &lt;b&gt;≡&lt;/b&gt; at the bottom → &lt;b&gt;Add page to&lt;/b&gt; → &lt;b&gt;Home screen&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>pwa.manual_firefox</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;⋮&lt;/b&gt; → &lt;b&gt;홈 화면에 추가&lt;/b&gt;를 누르세요.</t>
+  </si>
+  <si>
+    <t>Tap &lt;b&gt;⋮&lt;/b&gt; → &lt;b&gt;Add to Home screen&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>pwa.manual_other</t>
+  </si>
+  <si>
+    <t>브라우저 메뉴에서 &lt;b&gt;홈 화면에 추가&lt;/b&gt;(또는 앱 설치)를 선택하세요.</t>
+  </si>
+  <si>
+    <t>Open your browser menu and choose &lt;b&gt;Add to Home screen&lt;/b&gt; (or Install app).</t>
   </si>
 </sst>
 </file>
@@ -2490,7 +3136,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M235"/>
+  <dimension ref="A1:M310"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="12.6640625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.1640625" customWidth="1"/>
@@ -5597,7 +6243,7 @@
         <v>417</v>
       </c>
       <c r="E143" s="11" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F143" s="7"/>
       <c r="G143" s="15"/>
@@ -5612,13 +6258,13 @@
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="D144" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="D144" s="11" t="s">
+      <c r="E144" s="11" t="s">
         <v>420</v>
-      </c>
-      <c r="E144" s="11" t="s">
-        <v>421</v>
       </c>
       <c r="F144" s="7"/>
       <c r="G144" s="15"/>
@@ -5633,13 +6279,13 @@
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D145" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="D145" s="4" t="s">
+      <c r="E145" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="E145" s="4" t="s">
-        <v>424</v>
       </c>
       <c r="F145" s="7"/>
       <c r="G145" s="17"/>
@@ -5654,13 +6300,13 @@
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D146" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="D146" s="4" t="s">
+      <c r="E146" s="4" t="s">
         <v>426</v>
-      </c>
-      <c r="E146" s="4" t="s">
-        <v>427</v>
       </c>
       <c r="F146" s="7"/>
       <c r="G146" s="7"/>
@@ -5675,13 +6321,13 @@
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="D147" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="D147" s="4" t="s">
+      <c r="E147" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="E147" s="4" t="s">
-        <v>430</v>
       </c>
       <c r="F147" s="7"/>
       <c r="G147" s="7"/>
@@ -5696,13 +6342,13 @@
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D148" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="D148" s="4" t="s">
+      <c r="E148" s="4" t="s">
         <v>432</v>
-      </c>
-      <c r="E148" s="4" t="s">
-        <v>433</v>
       </c>
       <c r="F148" s="7"/>
       <c r="G148" s="7"/>
@@ -5717,13 +6363,13 @@
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D149" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="D149" s="4" t="s">
+      <c r="E149" s="4" t="s">
         <v>435</v>
-      </c>
-      <c r="E149" s="4" t="s">
-        <v>436</v>
       </c>
       <c r="F149" s="7"/>
       <c r="G149" s="7"/>
@@ -5738,13 +6384,13 @@
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D150" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="D150" s="4" t="s">
+      <c r="E150" s="4" t="s">
         <v>438</v>
-      </c>
-      <c r="E150" s="4" t="s">
-        <v>439</v>
       </c>
       <c r="F150" s="7"/>
       <c r="G150" s="7"/>
@@ -5759,13 +6405,13 @@
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="D151" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="D151" s="4" t="s">
+      <c r="E151" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="E151" s="4" t="s">
-        <v>442</v>
       </c>
       <c r="F151" s="7"/>
       <c r="G151" s="7"/>
@@ -5782,13 +6428,13 @@
         <v>11</v>
       </c>
       <c r="C152" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D152" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="D152" s="4" t="s">
+      <c r="E152" s="4" t="s">
         <v>444</v>
-      </c>
-      <c r="E152" s="4" t="s">
-        <v>445</v>
       </c>
       <c r="F152" s="7"/>
       <c r="G152" s="7"/>
@@ -5803,13 +6449,13 @@
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D153" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="D153" s="4" t="s">
+      <c r="E153" s="4" t="s">
         <v>447</v>
-      </c>
-      <c r="E153" s="4" t="s">
-        <v>448</v>
       </c>
       <c r="F153" s="7"/>
       <c r="G153" s="7"/>
@@ -5824,13 +6470,13 @@
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="18" t="s">
+        <v>448</v>
+      </c>
+      <c r="D154" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="D154" s="4" t="s">
+      <c r="E154" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="E154" s="4" t="s">
-        <v>451</v>
       </c>
       <c r="F154" s="7"/>
       <c r="G154" s="7"/>
@@ -5845,13 +6491,13 @@
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="D155" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="D155" s="4" t="s">
+      <c r="E155" s="4" t="s">
         <v>453</v>
-      </c>
-      <c r="E155" s="4" t="s">
-        <v>454</v>
       </c>
       <c r="F155" s="7"/>
       <c r="G155" s="7"/>
@@ -5868,13 +6514,13 @@
         <v>118</v>
       </c>
       <c r="C156" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="D156" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="D156" s="4" t="s">
+      <c r="E156" s="9" t="s">
         <v>456</v>
-      </c>
-      <c r="E156" s="9" t="s">
-        <v>457</v>
       </c>
       <c r="F156" s="7"/>
       <c r="G156" s="7"/>
@@ -5889,13 +6535,13 @@
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="D157" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="D157" s="4" t="s">
+      <c r="E157" s="11" t="s">
         <v>459</v>
-      </c>
-      <c r="E157" s="11" t="s">
-        <v>460</v>
       </c>
       <c r="F157" s="7"/>
       <c r="G157" s="7"/>
@@ -5910,13 +6556,13 @@
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="D158" s="10" t="s">
         <v>461</v>
       </c>
-      <c r="D158" s="10" t="s">
+      <c r="E158" s="11" t="s">
         <v>462</v>
-      </c>
-      <c r="E158" s="11" t="s">
-        <v>463</v>
       </c>
       <c r="F158" s="7"/>
       <c r="G158" s="7"/>
@@ -5931,13 +6577,13 @@
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D159" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="D159" s="4" t="s">
+      <c r="E159" s="11" t="s">
         <v>465</v>
-      </c>
-      <c r="E159" s="11" t="s">
-        <v>466</v>
       </c>
       <c r="F159" s="7"/>
       <c r="G159" s="7"/>
@@ -5952,13 +6598,13 @@
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="D160" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="D160" s="4" t="s">
+      <c r="E160" s="4" t="s">
         <v>468</v>
-      </c>
-      <c r="E160" s="4" t="s">
-        <v>469</v>
       </c>
       <c r="F160" s="7"/>
       <c r="G160" s="7"/>
@@ -5973,13 +6619,13 @@
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D161" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="D161" s="4" t="s">
+      <c r="E161" s="4" t="s">
         <v>471</v>
-      </c>
-      <c r="E161" s="4" t="s">
-        <v>472</v>
       </c>
       <c r="F161" s="7"/>
       <c r="G161" s="7"/>
@@ -5994,13 +6640,13 @@
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="D162" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="D162" s="4" t="s">
+      <c r="E162" s="4" t="s">
         <v>474</v>
-      </c>
-      <c r="E162" s="4" t="s">
-        <v>475</v>
       </c>
       <c r="F162" s="7"/>
       <c r="G162" s="7"/>
@@ -6015,13 +6661,13 @@
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="D163" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="D163" s="4" t="s">
+      <c r="E163" s="4" t="s">
         <v>477</v>
-      </c>
-      <c r="E163" s="4" t="s">
-        <v>478</v>
       </c>
       <c r="F163" s="7"/>
       <c r="G163" s="7"/>
@@ -6036,13 +6682,13 @@
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D164" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="D164" s="4" t="s">
+      <c r="E164" s="11" t="s">
         <v>480</v>
-      </c>
-      <c r="E164" s="11" t="s">
-        <v>481</v>
       </c>
       <c r="F164" s="7"/>
       <c r="G164" s="7"/>
@@ -6057,13 +6703,13 @@
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="D165" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="D165" s="4" t="s">
+      <c r="E165" s="4" t="s">
         <v>483</v>
-      </c>
-      <c r="E165" s="4" t="s">
-        <v>484</v>
       </c>
       <c r="F165" s="7"/>
       <c r="G165" s="7"/>
@@ -6078,13 +6724,13 @@
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="D166" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="D166" s="4" t="s">
+      <c r="E166" s="4" t="s">
         <v>486</v>
-      </c>
-      <c r="E166" s="4" t="s">
-        <v>487</v>
       </c>
       <c r="F166" s="7"/>
       <c r="G166" s="7"/>
@@ -6099,13 +6745,13 @@
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D167" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="D167" s="4" t="s">
+      <c r="E167" s="4" t="s">
         <v>489</v>
-      </c>
-      <c r="E167" s="4" t="s">
-        <v>490</v>
       </c>
       <c r="F167" s="7"/>
       <c r="G167" s="7"/>
@@ -6120,13 +6766,13 @@
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="D168" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="D168" s="4" t="s">
+      <c r="E168" s="4" t="s">
         <v>492</v>
-      </c>
-      <c r="E168" s="4" t="s">
-        <v>493</v>
       </c>
       <c r="F168" s="7"/>
       <c r="G168" s="7"/>
@@ -6141,13 +6787,13 @@
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="D169" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="D169" s="4" t="s">
+      <c r="E169" s="4" t="s">
         <v>495</v>
-      </c>
-      <c r="E169" s="4" t="s">
-        <v>496</v>
       </c>
       <c r="F169" s="7"/>
       <c r="G169" s="7"/>
@@ -6162,13 +6808,13 @@
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="D170" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="D170" s="4" t="s">
+      <c r="E170" s="4" t="s">
         <v>498</v>
-      </c>
-      <c r="E170" s="4" t="s">
-        <v>499</v>
       </c>
       <c r="F170" s="7"/>
       <c r="G170" s="7"/>
@@ -6181,19 +6827,19 @@
     </row>
     <row r="171" ht="13" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B171" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C171" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="D171" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="D171" s="4" t="s">
+      <c r="E171" s="4" t="s">
         <v>502</v>
-      </c>
-      <c r="E171" s="4" t="s">
-        <v>503</v>
       </c>
       <c r="F171" s="7"/>
       <c r="G171" s="7"/>
@@ -6210,13 +6856,13 @@
         <v>118</v>
       </c>
       <c r="C172" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="D172" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="D172" s="4" t="s">
+      <c r="E172" s="11" t="s">
         <v>505</v>
-      </c>
-      <c r="E172" s="11" t="s">
-        <v>506</v>
       </c>
       <c r="F172" s="7"/>
       <c r="G172" s="7"/>
@@ -6231,13 +6877,13 @@
       <c r="A173" s="2"/>
       <c r="B173" s="7"/>
       <c r="C173" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="D173" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="D173" s="4" t="s">
+      <c r="E173" s="11" t="s">
         <v>508</v>
-      </c>
-      <c r="E173" s="11" t="s">
-        <v>509</v>
       </c>
       <c r="F173" s="7"/>
       <c r="G173" s="7"/>
@@ -6252,13 +6898,13 @@
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="D174" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="D174" s="4" t="s">
+      <c r="E174" s="4" t="s">
         <v>511</v>
-      </c>
-      <c r="E174" s="4" t="s">
-        <v>512</v>
       </c>
       <c r="F174" s="7"/>
       <c r="G174" s="7"/>
@@ -6271,19 +6917,19 @@
     </row>
     <row r="175" ht="13" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B175" s="7" t="s">
         <v>230</v>
       </c>
       <c r="C175" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="D175" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="D175" s="4" t="s">
+      <c r="E175" s="4" t="s">
         <v>515</v>
-      </c>
-      <c r="E175" s="4" t="s">
-        <v>516</v>
       </c>
       <c r="F175" s="7"/>
       <c r="G175" s="7"/>
@@ -6298,13 +6944,13 @@
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="D176" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="D176" s="4" t="s">
+      <c r="E176" s="4" t="s">
         <v>518</v>
-      </c>
-      <c r="E176" s="4" t="s">
-        <v>519</v>
       </c>
       <c r="F176" s="7"/>
       <c r="G176" s="7"/>
@@ -6319,13 +6965,13 @@
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="D177" s="11" t="s">
         <v>520</v>
       </c>
-      <c r="D177" s="11" t="s">
+      <c r="E177" s="11" t="s">
         <v>521</v>
-      </c>
-      <c r="E177" s="11" t="s">
-        <v>522</v>
       </c>
       <c r="F177" s="7"/>
       <c r="G177" s="7"/>
@@ -6340,13 +6986,13 @@
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="D178" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="D178" s="11" t="s">
+      <c r="E178" s="11" t="s">
         <v>524</v>
-      </c>
-      <c r="E178" s="11" t="s">
-        <v>525</v>
       </c>
       <c r="F178" s="7"/>
       <c r="G178" s="7"/>
@@ -6363,13 +7009,13 @@
         <v>11</v>
       </c>
       <c r="C179" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="D179" s="11" t="s">
         <v>526</v>
       </c>
-      <c r="D179" s="11" t="s">
+      <c r="E179" s="11" t="s">
         <v>527</v>
-      </c>
-      <c r="E179" s="11" t="s">
-        <v>528</v>
       </c>
       <c r="F179" s="7"/>
       <c r="G179" s="7"/>
@@ -6384,13 +7030,13 @@
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="D180" s="11" t="s">
         <v>529</v>
       </c>
-      <c r="D180" s="11" t="s">
+      <c r="E180" s="11" t="s">
         <v>530</v>
-      </c>
-      <c r="E180" s="11" t="s">
-        <v>531</v>
       </c>
       <c r="F180" s="7"/>
       <c r="G180" s="7"/>
@@ -6405,13 +7051,13 @@
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="10" t="s">
+        <v>531</v>
+      </c>
+      <c r="D181" s="11" t="s">
         <v>532</v>
       </c>
-      <c r="D181" s="11" t="s">
+      <c r="E181" s="11" t="s">
         <v>533</v>
-      </c>
-      <c r="E181" s="11" t="s">
-        <v>534</v>
       </c>
       <c r="F181" s="7"/>
       <c r="G181" s="7"/>
@@ -6426,13 +7072,13 @@
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="10" t="s">
+        <v>534</v>
+      </c>
+      <c r="D182" s="11" t="s">
         <v>535</v>
       </c>
-      <c r="D182" s="11" t="s">
+      <c r="E182" s="11" t="s">
         <v>536</v>
-      </c>
-      <c r="E182" s="11" t="s">
-        <v>537</v>
       </c>
       <c r="F182" s="7"/>
       <c r="G182" s="7"/>
@@ -6447,13 +7093,13 @@
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="D183" s="11" t="s">
         <v>538</v>
       </c>
-      <c r="D183" s="11" t="s">
+      <c r="E183" s="11" t="s">
         <v>539</v>
-      </c>
-      <c r="E183" s="11" t="s">
-        <v>540</v>
       </c>
       <c r="F183" s="7"/>
       <c r="G183" s="7"/>
@@ -6468,13 +7114,13 @@
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="D184" s="11" t="s">
         <v>541</v>
       </c>
-      <c r="D184" s="11" t="s">
+      <c r="E184" s="11" t="s">
         <v>542</v>
-      </c>
-      <c r="E184" s="11" t="s">
-        <v>543</v>
       </c>
       <c r="F184" s="7"/>
       <c r="G184" s="7"/>
@@ -6491,13 +7137,13 @@
         <v>118</v>
       </c>
       <c r="C185" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="D185" s="11" t="s">
         <v>544</v>
       </c>
-      <c r="D185" s="11" t="s">
+      <c r="E185" s="10" t="s">
         <v>545</v>
-      </c>
-      <c r="E185" s="10" t="s">
-        <v>546</v>
       </c>
       <c r="F185" s="7"/>
       <c r="G185" s="7"/>
@@ -6512,13 +7158,13 @@
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="D186" s="11" t="s">
         <v>547</v>
       </c>
-      <c r="D186" s="11" t="s">
+      <c r="E186" s="11" t="s">
         <v>548</v>
-      </c>
-      <c r="E186" s="11" t="s">
-        <v>549</v>
       </c>
       <c r="F186" s="7"/>
       <c r="G186" s="7"/>
@@ -6533,13 +7179,13 @@
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="D187" s="11" t="s">
         <v>550</v>
       </c>
-      <c r="D187" s="11" t="s">
+      <c r="E187" s="11" t="s">
         <v>551</v>
-      </c>
-      <c r="E187" s="11" t="s">
-        <v>552</v>
       </c>
       <c r="F187" s="7"/>
       <c r="G187" s="7"/>
@@ -6554,13 +7200,13 @@
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="D188" s="11" t="s">
         <v>553</v>
       </c>
-      <c r="D188" s="11" t="s">
+      <c r="E188" s="11" t="s">
         <v>554</v>
-      </c>
-      <c r="E188" s="11" t="s">
-        <v>555</v>
       </c>
       <c r="F188" s="7"/>
       <c r="G188" s="7"/>
@@ -6575,13 +7221,13 @@
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="D189" s="11" t="s">
         <v>556</v>
       </c>
-      <c r="D189" s="11" t="s">
+      <c r="E189" s="11" t="s">
         <v>557</v>
-      </c>
-      <c r="E189" s="11" t="s">
-        <v>558</v>
       </c>
       <c r="F189" s="7"/>
       <c r="G189" s="7"/>
@@ -6596,13 +7242,13 @@
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="D190" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="D190" s="11" t="s">
+      <c r="E190" s="11" t="s">
         <v>560</v>
-      </c>
-      <c r="E190" s="11" t="s">
-        <v>561</v>
       </c>
       <c r="F190" s="7"/>
       <c r="G190" s="7"/>
@@ -6619,13 +7265,13 @@
         <v>127</v>
       </c>
       <c r="C191" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="D191" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="D191" s="11" t="s">
+      <c r="E191" s="11" t="s">
         <v>563</v>
-      </c>
-      <c r="E191" s="11" t="s">
-        <v>564</v>
       </c>
       <c r="F191" s="7"/>
       <c r="G191" s="7"/>
@@ -6640,13 +7286,13 @@
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="D192" s="11" t="s">
         <v>565</v>
       </c>
-      <c r="D192" s="11" t="s">
+      <c r="E192" s="11" t="s">
         <v>566</v>
-      </c>
-      <c r="E192" s="11" t="s">
-        <v>567</v>
       </c>
       <c r="F192" s="7"/>
       <c r="G192" s="7"/>
@@ -6661,13 +7307,13 @@
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="D193" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="D193" s="11" t="s">
+      <c r="E193" s="10" t="s">
         <v>569</v>
-      </c>
-      <c r="E193" s="10" t="s">
-        <v>570</v>
       </c>
       <c r="F193" s="7"/>
       <c r="G193" s="7"/>
@@ -6680,19 +7326,19 @@
     </row>
     <row r="194" ht="14" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="B194" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="B194" s="7" t="s">
+      <c r="C194" s="7" t="s">
         <v>572</v>
       </c>
-      <c r="C194" s="7" t="s">
+      <c r="D194" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="D194" s="11" t="s">
+      <c r="E194" s="11" t="s">
         <v>574</v>
-      </c>
-      <c r="E194" s="11" t="s">
-        <v>575</v>
       </c>
       <c r="F194" s="7"/>
       <c r="G194" s="7"/>
@@ -6707,13 +7353,13 @@
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="D195" s="11" t="s">
         <v>576</v>
       </c>
-      <c r="D195" s="11" t="s">
+      <c r="E195" s="4" t="s">
         <v>577</v>
-      </c>
-      <c r="E195" s="4" t="s">
-        <v>578</v>
       </c>
       <c r="F195" s="7"/>
       <c r="G195" s="7"/>
@@ -6728,13 +7374,13 @@
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="D196" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="D196" s="11" t="s">
+      <c r="E196" s="11" t="s">
         <v>580</v>
-      </c>
-      <c r="E196" s="11" t="s">
-        <v>581</v>
       </c>
       <c r="F196" s="7"/>
       <c r="G196" s="7"/>
@@ -6749,13 +7395,13 @@
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="D197" s="11" t="s">
         <v>582</v>
       </c>
-      <c r="D197" s="11" t="s">
+      <c r="E197" s="11" t="s">
         <v>583</v>
-      </c>
-      <c r="E197" s="11" t="s">
-        <v>584</v>
       </c>
       <c r="F197" s="7"/>
       <c r="G197" s="7"/>
@@ -6772,13 +7418,13 @@
         <v>127</v>
       </c>
       <c r="C198" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="D198" s="11" t="s">
         <v>585</v>
       </c>
-      <c r="D198" s="11" t="s">
+      <c r="E198" s="4" t="s">
         <v>586</v>
-      </c>
-      <c r="E198" s="4" t="s">
-        <v>587</v>
       </c>
       <c r="F198" s="7"/>
       <c r="G198" s="7"/>
@@ -6793,13 +7439,13 @@
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="D199" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="D199" s="11" t="s">
+      <c r="E199" s="4" t="s">
         <v>589</v>
-      </c>
-      <c r="E199" s="4" t="s">
-        <v>590</v>
       </c>
       <c r="F199" s="7"/>
       <c r="G199" s="7"/>
@@ -6812,19 +7458,19 @@
     </row>
     <row r="200" ht="14" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>118</v>
       </c>
       <c r="C200" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="D200" s="11" t="s">
         <v>592</v>
       </c>
-      <c r="D200" s="11" t="s">
+      <c r="E200" s="4" t="s">
         <v>593</v>
-      </c>
-      <c r="E200" s="4" t="s">
-        <v>594</v>
       </c>
       <c r="F200" s="7"/>
       <c r="G200" s="7"/>
@@ -6837,19 +7483,19 @@
     </row>
     <row r="201" ht="13" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B201" s="7" t="s">
         <v>118</v>
       </c>
       <c r="C201" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="D201" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="D201" s="4" t="s">
+      <c r="E201" s="4" t="s">
         <v>596</v>
-      </c>
-      <c r="E201" s="4" t="s">
-        <v>597</v>
       </c>
       <c r="F201" s="7"/>
       <c r="G201" s="7"/>
@@ -6862,19 +7508,19 @@
     </row>
     <row r="202" ht="14" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B202" s="7" t="s">
         <v>230</v>
       </c>
       <c r="C202" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="D202" s="11" t="s">
         <v>599</v>
       </c>
-      <c r="D202" s="11" t="s">
+      <c r="E202" s="11" t="s">
         <v>600</v>
-      </c>
-      <c r="E202" s="11" t="s">
-        <v>601</v>
       </c>
       <c r="F202" s="7"/>
       <c r="G202" s="7"/>
@@ -6891,7 +7537,7 @@
         <v>230</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D203" s="11" t="s">
         <v>33</v>
@@ -6912,13 +7558,13 @@
       <c r="A204" s="7"/>
       <c r="B204" s="7"/>
       <c r="C204" s="7" t="s">
+        <v>602</v>
+      </c>
+      <c r="D204" s="11" t="s">
         <v>603</v>
       </c>
-      <c r="D204" s="11" t="s">
+      <c r="E204" t="s">
         <v>604</v>
-      </c>
-      <c r="E204" t="s">
-        <v>605</v>
       </c>
       <c r="F204" s="7"/>
       <c r="G204" s="7"/>
@@ -6933,13 +7579,13 @@
       <c r="A205" s="7"/>
       <c r="B205" s="7"/>
       <c r="C205" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="D205" t="s">
         <v>606</v>
       </c>
-      <c r="D205" t="s">
+      <c r="E205" t="s">
         <v>607</v>
-      </c>
-      <c r="E205" t="s">
-        <v>608</v>
       </c>
       <c r="F205" s="7"/>
       <c r="G205" s="7"/>
@@ -6954,13 +7600,13 @@
       <c r="A206" s="7"/>
       <c r="B206" s="7"/>
       <c r="C206" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="D206" t="s">
         <v>609</v>
       </c>
-      <c r="D206" t="s">
+      <c r="E206" t="s">
         <v>610</v>
-      </c>
-      <c r="E206" t="s">
-        <v>611</v>
       </c>
       <c r="F206" s="7"/>
       <c r="G206" s="7"/>
@@ -6973,186 +7619,186 @@
     </row>
     <row r="207" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C207" t="s">
+        <v>611</v>
+      </c>
+      <c r="D207" t="s">
         <v>612</v>
       </c>
-      <c r="D207" t="s">
+      <c r="E207" t="s">
         <v>613</v>
-      </c>
-      <c r="E207" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="208" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C208" t="s">
+        <v>614</v>
+      </c>
+      <c r="D208" t="s">
         <v>615</v>
       </c>
-      <c r="D208" t="s">
+      <c r="E208" t="s">
         <v>616</v>
-      </c>
-      <c r="E208" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="209" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C209" t="s">
+        <v>617</v>
+      </c>
+      <c r="D209" t="s">
         <v>618</v>
       </c>
-      <c r="D209" t="s">
+      <c r="E209" t="s">
         <v>619</v>
-      </c>
-      <c r="E209" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="210" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C210" t="s">
+        <v>620</v>
+      </c>
+      <c r="D210" t="s">
         <v>621</v>
       </c>
-      <c r="D210" t="s">
+      <c r="E210" t="s">
         <v>622</v>
-      </c>
-      <c r="E210" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="211" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C211" t="s">
+        <v>623</v>
+      </c>
+      <c r="D211" t="s">
         <v>624</v>
       </c>
-      <c r="D211" t="s">
+      <c r="E211" t="s">
         <v>625</v>
-      </c>
-      <c r="E211" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="212" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C212" t="s">
+        <v>626</v>
+      </c>
+      <c r="D212" t="s">
         <v>627</v>
       </c>
-      <c r="D212" t="s">
+      <c r="E212" t="s">
         <v>628</v>
-      </c>
-      <c r="E212" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="213" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C213" t="s">
+        <v>629</v>
+      </c>
+      <c r="D213" t="s">
         <v>630</v>
       </c>
-      <c r="D213" t="s">
+      <c r="E213" t="s">
         <v>631</v>
-      </c>
-      <c r="E213" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="214" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C214" t="s">
+        <v>632</v>
+      </c>
+      <c r="D214" t="s">
         <v>633</v>
       </c>
-      <c r="D214" t="s">
+      <c r="E214" t="s">
         <v>634</v>
-      </c>
-      <c r="E214" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="215" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C215" t="s">
+        <v>635</v>
+      </c>
+      <c r="D215" t="s">
         <v>636</v>
       </c>
-      <c r="D215" t="s">
+      <c r="E215" t="s">
         <v>637</v>
-      </c>
-      <c r="E215" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="216" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C216" t="s">
+        <v>638</v>
+      </c>
+      <c r="D216" t="s">
         <v>639</v>
       </c>
-      <c r="D216" t="s">
+      <c r="E216" t="s">
         <v>640</v>
-      </c>
-      <c r="E216" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="217" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C217" t="s">
+        <v>641</v>
+      </c>
+      <c r="D217" t="s">
         <v>642</v>
       </c>
-      <c r="D217" t="s">
+      <c r="E217" t="s">
         <v>643</v>
-      </c>
-      <c r="E217" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="218" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C218" t="s">
+        <v>644</v>
+      </c>
+      <c r="D218" t="s">
         <v>645</v>
       </c>
-      <c r="D218" t="s">
+      <c r="E218" t="s">
         <v>646</v>
-      </c>
-      <c r="E218" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="219" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C219" t="s">
+        <v>647</v>
+      </c>
+      <c r="D219" t="s">
         <v>648</v>
       </c>
-      <c r="D219" t="s">
+      <c r="E219" t="s">
         <v>649</v>
-      </c>
-      <c r="E219" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="220" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C220" t="s">
+        <v>650</v>
+      </c>
+      <c r="D220" t="s">
         <v>651</v>
       </c>
-      <c r="D220" t="s">
+      <c r="E220" t="s">
         <v>652</v>
-      </c>
-      <c r="E220" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="221" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C221" t="s">
+        <v>653</v>
+      </c>
+      <c r="D221" t="s">
         <v>654</v>
       </c>
-      <c r="D221" t="s">
+      <c r="E221" t="s">
         <v>655</v>
-      </c>
-      <c r="E221" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="222" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C222" t="s">
+        <v>656</v>
+      </c>
+      <c r="D222" t="s">
         <v>657</v>
       </c>
-      <c r="D222" t="s">
+      <c r="E222" t="s">
         <v>658</v>
-      </c>
-      <c r="E222" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="223" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C223" t="s">
+        <v>659</v>
+      </c>
+      <c r="D223" t="s">
         <v>660</v>
-      </c>
-      <c r="D223" t="s">
-        <v>661</v>
       </c>
       <c r="E223" t="s">
         <v>406</v>
@@ -7160,40 +7806,40 @@
     </row>
     <row r="224" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C224" t="s">
+        <v>661</v>
+      </c>
+      <c r="D224" t="s">
         <v>662</v>
       </c>
-      <c r="D224" t="s">
+      <c r="E224" t="s">
         <v>663</v>
-      </c>
-      <c r="E224" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="225" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C225" t="s">
+        <v>664</v>
+      </c>
+      <c r="D225" t="s">
         <v>665</v>
       </c>
-      <c r="D225" t="s">
+      <c r="E225" t="s">
         <v>666</v>
-      </c>
-      <c r="E225" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="226" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C226" t="s">
+        <v>667</v>
+      </c>
+      <c r="D226" t="s">
         <v>668</v>
       </c>
-      <c r="D226" t="s">
+      <c r="E226" t="s">
         <v>669</v>
-      </c>
-      <c r="E226" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="227" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C227" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D227" t="s">
         <v>24</v>
@@ -7204,90 +7850,915 @@
     </row>
     <row r="228" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C228" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D228" t="s">
+        <v>665</v>
+      </c>
+      <c r="E228" t="s">
         <v>666</v>
-      </c>
-      <c r="E228" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="229" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C229" t="s">
+        <v>672</v>
+      </c>
+      <c r="D229" t="s">
         <v>673</v>
       </c>
-      <c r="D229" t="s">
+      <c r="E229" t="s">
         <v>674</v>
-      </c>
-      <c r="E229" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="230" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C230" t="s">
+        <v>675</v>
+      </c>
+      <c r="D230" t="s">
         <v>676</v>
       </c>
-      <c r="D230" t="s">
+      <c r="E230" t="s">
         <v>677</v>
-      </c>
-      <c r="E230" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="231" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C231" t="s">
+        <v>678</v>
+      </c>
+      <c r="D231" t="s">
         <v>679</v>
       </c>
-      <c r="D231" t="s">
+      <c r="E231" t="s">
         <v>680</v>
-      </c>
-      <c r="E231" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="232" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C232" t="s">
+        <v>681</v>
+      </c>
+      <c r="D232" t="s">
         <v>682</v>
       </c>
-      <c r="D232" t="s">
+      <c r="E232" t="s">
         <v>683</v>
-      </c>
-      <c r="E232" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="233" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C233" t="s">
+        <v>684</v>
+      </c>
+      <c r="D233" t="s">
         <v>685</v>
       </c>
-      <c r="D233" t="s">
+      <c r="E233" t="s">
         <v>686</v>
-      </c>
-      <c r="E233" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="234" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C234" t="s">
+        <v>687</v>
+      </c>
+      <c r="D234" t="s">
         <v>688</v>
       </c>
-      <c r="D234" t="s">
+      <c r="E234" t="s">
         <v>689</v>
-      </c>
-      <c r="E234" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="235" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C235" t="s">
+        <v>690</v>
+      </c>
+      <c r="D235" t="s">
         <v>691</v>
       </c>
-      <c r="D235" t="s">
+      <c r="E235" t="s">
         <v>692</v>
       </c>
-      <c r="E235" t="s">
+    </row>
+    <row r="236" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C236" t="s">
         <v>693</v>
+      </c>
+      <c r="D236" t="s">
+        <v>694</v>
+      </c>
+      <c r="E236" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="237" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C237" t="s">
+        <v>696</v>
+      </c>
+      <c r="D237" t="s">
+        <v>697</v>
+      </c>
+      <c r="E237" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="238" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C238" t="s">
+        <v>699</v>
+      </c>
+      <c r="D238" t="s">
+        <v>700</v>
+      </c>
+      <c r="E238" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="239" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C239" t="s">
+        <v>702</v>
+      </c>
+      <c r="D239" t="s">
+        <v>703</v>
+      </c>
+      <c r="E239" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="240" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C240" t="s">
+        <v>705</v>
+      </c>
+      <c r="D240" t="s">
+        <v>706</v>
+      </c>
+      <c r="E240" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="241" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C241" t="s">
+        <v>708</v>
+      </c>
+      <c r="D241" t="s">
+        <v>709</v>
+      </c>
+      <c r="E241" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="242" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C242" t="s">
+        <v>710</v>
+      </c>
+      <c r="D242" t="s">
+        <v>711</v>
+      </c>
+      <c r="E242" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="243" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C243" t="s">
+        <v>713</v>
+      </c>
+      <c r="D243" t="s">
+        <v>714</v>
+      </c>
+      <c r="E243" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="244" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C244" t="s">
+        <v>716</v>
+      </c>
+      <c r="D244" t="s">
+        <v>717</v>
+      </c>
+      <c r="E244" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="245" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C245" t="s">
+        <v>719</v>
+      </c>
+      <c r="D245" t="s">
+        <v>720</v>
+      </c>
+      <c r="E245" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="246" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C246" t="s">
+        <v>722</v>
+      </c>
+      <c r="D246" t="s">
+        <v>723</v>
+      </c>
+      <c r="E246" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="247" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C247" t="s">
+        <v>725</v>
+      </c>
+      <c r="D247" t="s">
+        <v>726</v>
+      </c>
+      <c r="E247" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="248" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C248" t="s">
+        <v>728</v>
+      </c>
+      <c r="D248" t="s">
+        <v>729</v>
+      </c>
+      <c r="E248" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="249" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C249" t="s">
+        <v>731</v>
+      </c>
+      <c r="D249" t="s">
+        <v>732</v>
+      </c>
+      <c r="E249" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="250" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C250" t="s">
+        <v>734</v>
+      </c>
+      <c r="D250" t="s">
+        <v>735</v>
+      </c>
+      <c r="E250" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="251" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C251" t="s">
+        <v>737</v>
+      </c>
+      <c r="D251" t="s">
+        <v>738</v>
+      </c>
+      <c r="E251" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="252" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C252" t="s">
+        <v>740</v>
+      </c>
+      <c r="D252" t="s">
+        <v>741</v>
+      </c>
+      <c r="E252" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="253" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C253" t="s">
+        <v>743</v>
+      </c>
+      <c r="D253" t="s">
+        <v>744</v>
+      </c>
+      <c r="E253" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="254" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C254" t="s">
+        <v>746</v>
+      </c>
+      <c r="D254" t="s">
+        <v>747</v>
+      </c>
+      <c r="E254" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="255" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C255" t="s">
+        <v>749</v>
+      </c>
+      <c r="D255" t="s">
+        <v>750</v>
+      </c>
+      <c r="E255" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="256" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C256" t="s">
+        <v>751</v>
+      </c>
+      <c r="D256" t="s">
+        <v>752</v>
+      </c>
+      <c r="E256" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="257" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C257" t="s">
+        <v>753</v>
+      </c>
+      <c r="D257" t="s">
+        <v>754</v>
+      </c>
+      <c r="E257" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="258" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C258" t="s">
+        <v>756</v>
+      </c>
+      <c r="D258" t="s">
+        <v>757</v>
+      </c>
+      <c r="E258" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="259" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C259" t="s">
+        <v>759</v>
+      </c>
+      <c r="D259" t="s">
+        <v>760</v>
+      </c>
+      <c r="E259" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="260" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C260" t="s">
+        <v>762</v>
+      </c>
+      <c r="D260" t="s">
+        <v>763</v>
+      </c>
+      <c r="E260" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="261" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C261" t="s">
+        <v>765</v>
+      </c>
+      <c r="D261" t="s">
+        <v>766</v>
+      </c>
+      <c r="E261" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="262" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C262" t="s">
+        <v>768</v>
+      </c>
+      <c r="D262" t="s">
+        <v>769</v>
+      </c>
+      <c r="E262" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="263" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C263" t="s">
+        <v>771</v>
+      </c>
+      <c r="D263" t="s">
+        <v>772</v>
+      </c>
+      <c r="E263" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="264" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C264" t="s">
+        <v>774</v>
+      </c>
+      <c r="D264" t="s">
+        <v>775</v>
+      </c>
+      <c r="E264" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="265" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C265" t="s">
+        <v>777</v>
+      </c>
+      <c r="D265" t="s">
+        <v>778</v>
+      </c>
+      <c r="E265" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="266" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C266" t="s">
+        <v>780</v>
+      </c>
+      <c r="D266" t="s">
+        <v>781</v>
+      </c>
+      <c r="E266" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="267" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C267" t="s">
+        <v>783</v>
+      </c>
+      <c r="D267" t="s">
+        <v>784</v>
+      </c>
+      <c r="E267" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="268" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C268" t="s">
+        <v>786</v>
+      </c>
+      <c r="D268" t="s">
+        <v>787</v>
+      </c>
+      <c r="E268" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="269" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C269" t="s">
+        <v>788</v>
+      </c>
+      <c r="D269" t="s">
+        <v>789</v>
+      </c>
+      <c r="E269" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="270" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C270" t="s">
+        <v>791</v>
+      </c>
+      <c r="D270" t="s">
+        <v>514</v>
+      </c>
+      <c r="E270" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="271" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C271" t="s">
+        <v>793</v>
+      </c>
+      <c r="D271" t="s">
+        <v>794</v>
+      </c>
+      <c r="E271" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="272" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C272" t="s">
+        <v>796</v>
+      </c>
+      <c r="D272" t="s">
+        <v>797</v>
+      </c>
+      <c r="E272" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="273" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C273" t="s">
+        <v>799</v>
+      </c>
+      <c r="D273" t="s">
+        <v>800</v>
+      </c>
+      <c r="E273" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="274" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C274" t="s">
+        <v>802</v>
+      </c>
+      <c r="D274" t="s">
+        <v>803</v>
+      </c>
+      <c r="E274" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="275" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C275" t="s">
+        <v>805</v>
+      </c>
+      <c r="D275" t="s">
+        <v>806</v>
+      </c>
+      <c r="E275" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="276" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C276" t="s">
+        <v>807</v>
+      </c>
+      <c r="D276" t="s">
+        <v>57</v>
+      </c>
+      <c r="E276" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="277" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C277" t="s">
+        <v>809</v>
+      </c>
+      <c r="D277" t="s">
+        <v>810</v>
+      </c>
+      <c r="E277" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="278" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C278" t="s">
+        <v>812</v>
+      </c>
+      <c r="D278" t="s">
+        <v>813</v>
+      </c>
+      <c r="E278" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="279" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C279" t="s">
+        <v>815</v>
+      </c>
+      <c r="D279" t="s">
+        <v>816</v>
+      </c>
+      <c r="E279" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="280" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C280" t="s">
+        <v>818</v>
+      </c>
+      <c r="D280" t="s">
+        <v>819</v>
+      </c>
+      <c r="E280" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="281" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C281" t="s">
+        <v>821</v>
+      </c>
+      <c r="D281" t="s">
+        <v>822</v>
+      </c>
+      <c r="E281" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="282" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C282" t="s">
+        <v>824</v>
+      </c>
+      <c r="D282" t="s">
+        <v>825</v>
+      </c>
+      <c r="E282" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="283" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C283" t="s">
+        <v>827</v>
+      </c>
+      <c r="D283" t="s">
+        <v>828</v>
+      </c>
+      <c r="E283" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="284" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C284" t="s">
+        <v>830</v>
+      </c>
+      <c r="D284" t="s">
+        <v>831</v>
+      </c>
+      <c r="E284" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="285" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C285" t="s">
+        <v>833</v>
+      </c>
+      <c r="D285" t="s">
+        <v>834</v>
+      </c>
+      <c r="E285" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="286" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C286" t="s">
+        <v>836</v>
+      </c>
+      <c r="D286" t="s">
+        <v>837</v>
+      </c>
+      <c r="E286" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="287" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C287" t="s">
+        <v>839</v>
+      </c>
+      <c r="D287" t="s">
+        <v>840</v>
+      </c>
+      <c r="E287" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="288" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C288" t="s">
+        <v>842</v>
+      </c>
+      <c r="D288" t="s">
+        <v>843</v>
+      </c>
+      <c r="E288" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="289" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C289" t="s">
+        <v>845</v>
+      </c>
+      <c r="D289" t="s">
+        <v>846</v>
+      </c>
+      <c r="E289" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="290" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C290" t="s">
+        <v>847</v>
+      </c>
+      <c r="D290" t="s">
+        <v>848</v>
+      </c>
+      <c r="E290" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="291" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C291" t="s">
+        <v>850</v>
+      </c>
+      <c r="D291" t="s">
+        <v>851</v>
+      </c>
+      <c r="E291" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="292" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C292" t="s">
+        <v>853</v>
+      </c>
+      <c r="D292" t="s">
+        <v>440</v>
+      </c>
+      <c r="E292" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="293" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C293" t="s">
+        <v>854</v>
+      </c>
+      <c r="D293" t="s">
+        <v>855</v>
+      </c>
+      <c r="E293" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="294" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C294" t="s">
+        <v>857</v>
+      </c>
+      <c r="D294" t="s">
+        <v>858</v>
+      </c>
+      <c r="E294" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="295" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C295" t="s">
+        <v>860</v>
+      </c>
+      <c r="D295" t="s">
+        <v>861</v>
+      </c>
+      <c r="E295" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="296" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C296" t="s">
+        <v>863</v>
+      </c>
+      <c r="D296" t="s">
+        <v>864</v>
+      </c>
+      <c r="E296" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="297" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C297" t="s">
+        <v>866</v>
+      </c>
+      <c r="D297" t="s">
+        <v>867</v>
+      </c>
+      <c r="E297" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="298" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C298" t="s">
+        <v>869</v>
+      </c>
+      <c r="D298" t="s">
+        <v>870</v>
+      </c>
+      <c r="E298" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="299" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C299" t="s">
+        <v>872</v>
+      </c>
+      <c r="D299" t="s">
+        <v>873</v>
+      </c>
+      <c r="E299" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="300" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C300" t="s">
+        <v>875</v>
+      </c>
+      <c r="D300" t="s">
+        <v>876</v>
+      </c>
+      <c r="E300" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="301" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C301" t="s">
+        <v>878</v>
+      </c>
+      <c r="D301" t="s">
+        <v>879</v>
+      </c>
+      <c r="E301" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="302" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C302" t="s">
+        <v>881</v>
+      </c>
+      <c r="D302" t="s">
+        <v>882</v>
+      </c>
+      <c r="E302" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="303" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C303" t="s">
+        <v>884</v>
+      </c>
+      <c r="D303" t="s">
+        <v>885</v>
+      </c>
+      <c r="E303" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="304" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C304" t="s">
+        <v>887</v>
+      </c>
+      <c r="D304" t="s">
+        <v>888</v>
+      </c>
+      <c r="E304" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="305" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C305" t="s">
+        <v>890</v>
+      </c>
+      <c r="D305" t="s">
+        <v>891</v>
+      </c>
+      <c r="E305" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="306" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C306" t="s">
+        <v>893</v>
+      </c>
+      <c r="D306" t="s">
+        <v>894</v>
+      </c>
+      <c r="E306" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="307" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C307" t="s">
+        <v>896</v>
+      </c>
+      <c r="D307" t="s">
+        <v>897</v>
+      </c>
+      <c r="E307" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="308" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C308" t="s">
+        <v>899</v>
+      </c>
+      <c r="D308" t="s">
+        <v>900</v>
+      </c>
+      <c r="E308" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="309" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C309" t="s">
+        <v>902</v>
+      </c>
+      <c r="D309" t="s">
+        <v>903</v>
+      </c>
+      <c r="E309" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="310" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C310" t="s">
+        <v>905</v>
+      </c>
+      <c r="D310" t="s">
+        <v>906</v>
+      </c>
+      <c r="E310" t="s">
+        <v>907</v>
       </c>
     </row>
   </sheetData>
